--- a/public/reports/monthly_review/2026-10.xlsx
+++ b/public/reports/monthly_review/2026-10.xlsx
@@ -326,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -421,6 +421,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1031,7 +1034,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/01, %</t>
+          <t>미국 종가 기준 09/30 → 10/02, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1101,19 +1104,19 @@
         <v>7156</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>0.19</v>
+        <v>0.93</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>0.04</v>
+        <v>0.53</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>0.31</v>
+        <v>1.23</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>-6.3</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>1.59</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="9">
@@ -1168,11 +1171,11 @@
       </c>
       <c r="C12" s="31" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>반도체</t>
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>1.95</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="13">
@@ -1188,11 +1191,11 @@
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
-          <t>반도체</t>
+          <t>에너지</t>
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="14">
@@ -1212,7 +1215,7 @@
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>1.05</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="15">
@@ -1232,7 +1235,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-2.01</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="16">
@@ -1252,7 +1255,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>-1.32</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="17">
@@ -1268,11 +1271,13 @@
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>소재</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="n">
-        <v>-0.33</v>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1980,7 +1985,7 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="D46" s="34" t="inlineStr">
+      <c r="D46" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2021,7 +2026,7 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="D47" s="34" t="inlineStr">
+      <c r="D47" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2062,7 +2067,7 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="D48" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -2103,7 +2108,7 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="D49" s="34" t="inlineStr">
+      <c r="D49" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2144,7 +2149,7 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="D50" s="34" t="inlineStr">
+      <c r="D50" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2185,7 +2190,7 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="D51" s="34" t="inlineStr">
+      <c r="D51" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
@@ -2226,7 +2231,7 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="D52" s="34" t="inlineStr">
+      <c r="D52" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2267,7 +2272,7 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="D53" s="34" t="inlineStr">
+      <c r="D53" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2308,7 +2313,7 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="D54" s="34" t="inlineStr">
+      <c r="D54" s="35" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -2349,7 +2354,7 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="D55" s="34" t="inlineStr">
+      <c r="D55" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -2386,7 +2391,7 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
+      <c r="D56" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2427,7 +2432,7 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="D57" s="34" t="inlineStr">
+      <c r="D57" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2468,7 +2473,7 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="D58" s="34" t="inlineStr">
+      <c r="D58" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -2509,7 +2514,7 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="D59" s="34" t="inlineStr">
+      <c r="D59" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2550,7 +2555,7 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="D60" s="34" t="inlineStr">
+      <c r="D60" s="35" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -2591,7 +2596,7 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="D61" s="34" t="inlineStr">
+      <c r="D61" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2632,7 +2637,7 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="D62" s="34" t="inlineStr">
+      <c r="D62" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2667,7 +2672,7 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="D63" s="34" t="inlineStr">
+      <c r="D63" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
@@ -2708,7 +2713,7 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="D64" s="34" t="inlineStr">
+      <c r="D64" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -2745,7 +2750,7 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="D65" s="34" t="inlineStr">
+      <c r="D65" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2799,7 +2804,7 @@
       <c r="K67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="35" t="inlineStr">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>● 동반강세 — 추세 지속형 상방 관찰</t>
         </is>
@@ -2816,12 +2821,12 @@
           <t>한화</t>
         </is>
       </c>
-      <c r="B69" s="34" t="inlineStr">
+      <c r="B69" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C69" s="36" t="n">
+      <c r="C69" s="37" t="n">
         <v>3</v>
       </c>
       <c r="D69" s="31" t="inlineStr"/>
@@ -2831,12 +2836,12 @@
           <t>일신방직</t>
         </is>
       </c>
-      <c r="H69" s="34" t="inlineStr">
+      <c r="H69" s="35" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="I69" s="37" t="n">
+      <c r="I69" s="38" t="n">
         <v>3</v>
       </c>
       <c r="J69" s="31" t="inlineStr"/>
@@ -2860,12 +2865,12 @@
           <t>흥아해운</t>
         </is>
       </c>
-      <c r="B71" s="34" t="inlineStr">
+      <c r="B71" s="35" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="C71" s="36" t="n">
+      <c r="C71" s="37" t="n">
         <v>2</v>
       </c>
       <c r="D71" s="31" t="inlineStr"/>
@@ -2875,12 +2880,12 @@
           <t>F&amp;F</t>
         </is>
       </c>
-      <c r="H71" s="34" t="inlineStr">
+      <c r="H71" s="35" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="I71" s="37" t="n">
+      <c r="I71" s="38" t="n">
         <v>1</v>
       </c>
       <c r="J71" s="31" t="inlineStr"/>
@@ -2904,12 +2909,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="B73" s="34" t="inlineStr">
+      <c r="B73" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="C73" s="36" t="n">
+      <c r="C73" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D73" s="31" t="inlineStr"/>
@@ -2928,12 +2933,12 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="B75" s="34" t="inlineStr">
+      <c r="B75" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C75" s="36" t="n">
+      <c r="C75" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="31" t="inlineStr"/>
@@ -2952,12 +2957,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="B77" s="34" t="inlineStr">
+      <c r="B77" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C77" s="36" t="n">
+      <c r="C77" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D77" s="31" t="inlineStr"/>
@@ -2972,12 +2977,12 @@
     </row>
     <row r="79"/>
     <row r="80">
-      <c r="A80" s="38" t="inlineStr">
+      <c r="A80" s="39" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G80" s="39" t="inlineStr">
+      <c r="G80" s="40" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
@@ -2989,12 +2994,12 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="B81" s="34" t="inlineStr">
+      <c r="B81" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="C81" s="40" t="n">
+      <c r="C81" s="41" t="n">
         <v>-3</v>
       </c>
       <c r="D81" s="31" t="inlineStr"/>
@@ -3004,12 +3009,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="H81" s="41" t="inlineStr">
+      <c r="H81" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I81" s="42" t="n">
+      <c r="I81" s="43" t="n">
         <v>-4</v>
       </c>
       <c r="J81" s="31" t="inlineStr"/>
@@ -3033,12 +3038,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="B83" s="34" t="inlineStr">
+      <c r="B83" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="C83" s="40" t="n">
+      <c r="C83" s="41" t="n">
         <v>-1</v>
       </c>
       <c r="D83" s="31" t="inlineStr"/>
@@ -3048,12 +3053,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="H83" s="34" t="inlineStr">
+      <c r="H83" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="I83" s="42" t="n">
+      <c r="I83" s="43" t="n">
         <v>-3</v>
       </c>
       <c r="J83" s="31" t="inlineStr"/>
@@ -3072,32 +3077,32 @@
       </c>
     </row>
     <row r="85" ht="31" customHeight="1" s="15">
-      <c r="A85" s="43" t="inlineStr">
+      <c r="A85" s="44" t="inlineStr">
         <is>
           <t>HD현대마린솔루션</t>
         </is>
       </c>
-      <c r="B85" s="34" t="inlineStr">
+      <c r="B85" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="C85" s="40" t="n">
+      <c r="C85" s="41" t="n">
         <v>-1</v>
       </c>
       <c r="D85" s="31" t="inlineStr"/>
       <c r="E85" s="31" t="inlineStr"/>
-      <c r="G85" s="43" t="inlineStr">
+      <c r="G85" s="44" t="inlineStr">
         <is>
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="H85" s="34" t="inlineStr">
+      <c r="H85" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="I85" s="42" t="n">
+      <c r="I85" s="43" t="n">
         <v>-3</v>
       </c>
       <c r="J85" s="31" t="inlineStr"/>
@@ -3121,12 +3126,12 @@
           <t>SK바이오팜</t>
         </is>
       </c>
-      <c r="B87" s="34" t="inlineStr">
+      <c r="B87" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="C87" s="40" t="n">
+      <c r="C87" s="41" t="n">
         <v>-1</v>
       </c>
       <c r="D87" s="31" t="inlineStr"/>
@@ -3136,12 +3141,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="H87" s="41" t="inlineStr">
+      <c r="H87" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I87" s="42" t="n">
+      <c r="I87" s="43" t="n">
         <v>-3</v>
       </c>
       <c r="J87" s="31" t="inlineStr"/>
@@ -3165,12 +3170,12 @@
           <t>리가켐바이오</t>
         </is>
       </c>
-      <c r="B89" s="34" t="inlineStr">
+      <c r="B89" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="C89" s="40" t="n">
+      <c r="C89" s="41" t="n">
         <v>-1</v>
       </c>
       <c r="D89" s="31" t="inlineStr"/>
@@ -3180,12 +3185,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="H89" s="41" t="inlineStr">
+      <c r="H89" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I89" s="42" t="n">
+      <c r="I89" s="43" t="n">
         <v>-3</v>
       </c>
       <c r="J89" s="31" t="inlineStr"/>
@@ -3205,7 +3210,7 @@
     </row>
     <row r="91"/>
     <row r="92" ht="31" customHeight="1" s="15">
-      <c r="A92" s="44" t="inlineStr">
+      <c r="A92" s="45" t="inlineStr">
         <is>
           <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
@@ -3395,7 +3400,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D108" s="34" t="inlineStr">
+      <c r="D108" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -3430,7 +3435,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D109" s="34" t="inlineStr">
+      <c r="D109" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3465,7 +3470,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D110" s="34" t="inlineStr">
+      <c r="D110" s="35" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -3500,7 +3505,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D111" s="34" t="inlineStr">
+      <c r="D111" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -3728,62 +3733,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="46" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="46" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="46" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="46" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="I5" s="45" t="inlineStr">
+      <c r="I5" s="46" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="46" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="46" t="inlineStr">
         <is>
           <t>월간등락(%)</t>
         </is>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="46" t="inlineStr">
         <is>
           <t>신고가대비(%)</t>
         </is>
@@ -3800,36 +3805,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D6" s="46" t="n">
+      <c r="D6" s="47" t="n">
         <v>54</v>
       </c>
-      <c r="E6" s="46" t="n">
+      <c r="E6" s="47" t="n">
         <v>577</v>
       </c>
-      <c r="F6" s="47" t="n">
+      <c r="F6" s="48" t="n">
         <v>-523</v>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="48" t="n">
         <v>-84</v>
       </c>
-      <c r="H6" s="48" t="n">
+      <c r="H6" s="49" t="n">
         <v>187.5</v>
       </c>
-      <c r="I6" s="48" t="n">
+      <c r="I6" s="49" t="n">
         <v>4179.2</v>
       </c>
-      <c r="J6" s="49" t="n">
+      <c r="J6" s="50" t="n">
         <v>405.2</v>
       </c>
-      <c r="K6" s="50" t="n">
+      <c r="K6" s="51" t="n">
         <v>2.28</v>
       </c>
-      <c r="L6" s="51" t="n">
+      <c r="L6" s="52" t="n">
         <v>-7.86</v>
       </c>
     </row>
@@ -3844,36 +3849,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D7" s="46" t="n">
+      <c r="D7" s="47" t="n">
         <v>382</v>
       </c>
-      <c r="E7" s="46" t="n">
+      <c r="E7" s="47" t="n">
         <v>408</v>
       </c>
-      <c r="F7" s="47" t="n">
+      <c r="F7" s="48" t="n">
         <v>-26</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="48" t="n">
         <v>-411</v>
       </c>
-      <c r="H7" s="48" t="n">
+      <c r="H7" s="49" t="n">
         <v>194</v>
       </c>
-      <c r="I7" s="48" t="n">
+      <c r="I7" s="49" t="n">
         <v>10105.3</v>
       </c>
-      <c r="J7" s="49" t="n">
+      <c r="J7" s="50" t="n">
         <v>545.2</v>
       </c>
-      <c r="K7" s="50" t="n">
+      <c r="K7" s="51" t="n">
         <v>11.57</v>
       </c>
-      <c r="L7" s="52" t="n">
+      <c r="L7" s="53" t="n">
         <v>-2.03</v>
       </c>
     </row>
@@ -3888,36 +3893,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D8" s="46" t="n">
+      <c r="D8" s="47" t="n">
         <v>194</v>
       </c>
-      <c r="E8" s="46" t="n">
+      <c r="E8" s="47" t="n">
         <v>200</v>
       </c>
-      <c r="F8" s="47" t="n">
+      <c r="F8" s="48" t="n">
         <v>-6</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="48" t="n">
         <v>-191</v>
       </c>
-      <c r="H8" s="48" t="n">
+      <c r="H8" s="49" t="n">
         <v>128.2</v>
       </c>
-      <c r="I8" s="48" t="n">
+      <c r="I8" s="49" t="n">
         <v>3509</v>
       </c>
-      <c r="J8" s="53" t="n">
+      <c r="J8" s="54" t="n">
         <v>-352.6</v>
       </c>
-      <c r="K8" s="50" t="n">
+      <c r="K8" s="51" t="n">
         <v>1.98</v>
       </c>
-      <c r="L8" s="51" t="n">
+      <c r="L8" s="52" t="n">
         <v>-7.07</v>
       </c>
     </row>
@@ -3932,36 +3937,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D9" s="46" t="n">
+      <c r="D9" s="47" t="n">
         <v>174</v>
       </c>
-      <c r="E9" s="46" t="n">
+      <c r="E9" s="47" t="n">
         <v>223</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="F9" s="48" t="n">
         <v>-49</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="48" t="n">
         <v>-162</v>
       </c>
-      <c r="H9" s="48" t="n">
+      <c r="H9" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="I9" s="48" t="n">
+      <c r="I9" s="49" t="n">
         <v>556.4</v>
       </c>
-      <c r="J9" s="49" t="n">
+      <c r="J9" s="50" t="n">
         <v>68.8</v>
       </c>
-      <c r="K9" s="50" t="n">
+      <c r="K9" s="51" t="n">
         <v>14.52</v>
       </c>
-      <c r="L9" s="52" t="n">
+      <c r="L9" s="53" t="n">
         <v>-2.69</v>
       </c>
     </row>
@@ -3976,36 +3981,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="48" t="n">
         <v>-129</v>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="48" t="n">
         <v>-131</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="46" t="n">
+      <c r="G10" s="47" t="n">
         <v>120</v>
       </c>
-      <c r="H10" s="48" t="n">
+      <c r="H10" s="49" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="I10" s="48" t="n">
+      <c r="I10" s="49" t="n">
         <v>1958.5</v>
       </c>
-      <c r="J10" s="53" t="n">
+      <c r="J10" s="54" t="n">
         <v>-47.9</v>
       </c>
-      <c r="K10" s="54" t="n">
+      <c r="K10" s="55" t="n">
         <v>-4.84</v>
       </c>
-      <c r="L10" s="51" t="n">
+      <c r="L10" s="52" t="n">
         <v>-6.56</v>
       </c>
     </row>
@@ -4020,36 +4025,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="46" t="n">
+      <c r="D11" s="47" t="n">
         <v>111</v>
       </c>
-      <c r="E11" s="46" t="n">
+      <c r="E11" s="47" t="n">
         <v>107</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="48" t="n">
         <v>-96</v>
       </c>
-      <c r="H11" s="48" t="n">
+      <c r="H11" s="49" t="n">
         <v>5.5</v>
       </c>
-      <c r="I11" s="48" t="n">
+      <c r="I11" s="49" t="n">
         <v>275.5</v>
       </c>
-      <c r="J11" s="49" t="n">
+      <c r="J11" s="50" t="n">
         <v>14.9</v>
       </c>
-      <c r="K11" s="50" t="n">
+      <c r="K11" s="51" t="n">
         <v>19.39</v>
       </c>
-      <c r="L11" s="55" t="n">
+      <c r="L11" s="56" t="n">
         <v>-0.85</v>
       </c>
     </row>
@@ -4064,36 +4069,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="47" t="n">
         <v>126</v>
       </c>
-      <c r="E12" s="46" t="n">
+      <c r="E12" s="47" t="n">
         <v>65</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="47" t="n">
         <v>61</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="48" t="n">
         <v>-120</v>
       </c>
-      <c r="H12" s="48" t="n">
+      <c r="H12" s="49" t="n">
         <v>29.3</v>
       </c>
-      <c r="I12" s="48" t="n">
+      <c r="I12" s="49" t="n">
         <v>1905.1</v>
       </c>
-      <c r="J12" s="49" t="n">
+      <c r="J12" s="50" t="n">
         <v>112.8</v>
       </c>
-      <c r="K12" s="50" t="n">
+      <c r="K12" s="51" t="n">
         <v>0.87</v>
       </c>
-      <c r="L12" s="51" t="n">
+      <c r="L12" s="52" t="n">
         <v>-9.640000000000001</v>
       </c>
     </row>
@@ -4108,36 +4113,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="47" t="n">
         <v>161</v>
       </c>
-      <c r="E13" s="46" t="n">
+      <c r="E13" s="47" t="n">
         <v>54</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="47" t="n">
         <v>108</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="48" t="n">
         <v>-157</v>
       </c>
-      <c r="H13" s="48" t="n">
+      <c r="H13" s="49" t="n">
         <v>8.6</v>
       </c>
-      <c r="I13" s="48" t="n">
+      <c r="I13" s="49" t="n">
         <v>1252.2</v>
       </c>
-      <c r="J13" s="49" t="n">
+      <c r="J13" s="50" t="n">
         <v>25.7</v>
       </c>
-      <c r="K13" s="50" t="n">
+      <c r="K13" s="51" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L13" s="51" t="n">
+      <c r="L13" s="52" t="n">
         <v>-5.77</v>
       </c>
     </row>
@@ -4152,36 +4157,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="D14" s="46" t="n">
+      <c r="D14" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="E14" s="47" t="n">
+      <c r="E14" s="48" t="n">
         <v>-2</v>
       </c>
-      <c r="F14" s="46" t="n">
+      <c r="F14" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="G14" s="47" t="n">
+      <c r="G14" s="48" t="n">
         <v>-8</v>
       </c>
-      <c r="H14" s="48" t="n">
+      <c r="H14" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="48" t="n">
+      <c r="I14" s="49" t="n">
         <v>23.3</v>
       </c>
-      <c r="J14" s="53" t="n">
+      <c r="J14" s="54" t="n">
         <v>-5.7</v>
       </c>
-      <c r="K14" s="50" t="n">
+      <c r="K14" s="51" t="n">
         <v>20.97</v>
       </c>
-      <c r="L14" s="51" t="n">
+      <c r="L14" s="52" t="n">
         <v>-6.38</v>
       </c>
     </row>
@@ -4196,36 +4201,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="48" t="n">
         <v>-168</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="48" t="n">
         <v>-202</v>
       </c>
-      <c r="F15" s="46" t="n">
+      <c r="F15" s="47" t="n">
         <v>34</v>
       </c>
-      <c r="G15" s="46" t="n">
+      <c r="G15" s="47" t="n">
         <v>27</v>
       </c>
-      <c r="H15" s="48" t="n">
+      <c r="H15" s="49" t="n">
         <v>29</v>
       </c>
-      <c r="I15" s="48" t="n">
+      <c r="I15" s="49" t="n">
         <v>2561</v>
       </c>
-      <c r="J15" s="53" t="n">
+      <c r="J15" s="54" t="n">
         <v>-156.7</v>
       </c>
-      <c r="K15" s="54" t="n">
+      <c r="K15" s="55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="L15" s="51" t="n">
+      <c r="L15" s="52" t="n">
         <v>-9.380000000000001</v>
       </c>
     </row>
@@ -4240,36 +4245,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="48" t="n">
         <v>-1</v>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="48" t="n">
         <v>-1</v>
       </c>
-      <c r="F16" s="56" t="n">
+      <c r="F16" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="46" t="n">
+      <c r="G16" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="48" t="n">
+      <c r="H16" s="49" t="n">
         <v>0.6</v>
       </c>
-      <c r="I16" s="48" t="n">
+      <c r="I16" s="49" t="n">
         <v>21.2</v>
       </c>
-      <c r="J16" s="49" t="n">
+      <c r="J16" s="50" t="n">
         <v>3.3</v>
       </c>
-      <c r="K16" s="50" t="n">
+      <c r="K16" s="51" t="n">
         <v>40.46</v>
       </c>
-      <c r="L16" s="51" t="n">
+      <c r="L16" s="52" t="n">
         <v>-9.27</v>
       </c>
     </row>
@@ -4284,36 +4289,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D17" s="46" t="n">
+      <c r="D17" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="E17" s="46" t="n">
+      <c r="E17" s="47" t="n">
         <v>72</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="48" t="n">
         <v>-60</v>
       </c>
-      <c r="G17" s="47" t="n">
+      <c r="G17" s="48" t="n">
         <v>-10</v>
       </c>
-      <c r="H17" s="48" t="n">
+      <c r="H17" s="49" t="n">
         <v>2.5</v>
       </c>
-      <c r="I17" s="48" t="n">
+      <c r="I17" s="49" t="n">
         <v>323.4</v>
       </c>
-      <c r="J17" s="49" t="n">
+      <c r="J17" s="50" t="n">
         <v>10.5</v>
       </c>
-      <c r="K17" s="54" t="n">
+      <c r="K17" s="55" t="n">
         <v>-1.4</v>
       </c>
-      <c r="L17" s="51" t="n">
+      <c r="L17" s="52" t="n">
         <v>-5.01</v>
       </c>
     </row>
@@ -4328,36 +4333,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="47" t="n">
         <v>89</v>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="E18" s="47" t="n">
         <v>14</v>
       </c>
-      <c r="F18" s="46" t="n">
+      <c r="F18" s="47" t="n">
         <v>75</v>
       </c>
-      <c r="G18" s="47" t="n">
+      <c r="G18" s="48" t="n">
         <v>-90</v>
       </c>
-      <c r="H18" s="48" t="n">
+      <c r="H18" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="48" t="n">
+      <c r="I18" s="49" t="n">
         <v>194.2</v>
       </c>
-      <c r="J18" s="49" t="n">
+      <c r="J18" s="50" t="n">
         <v>23.7</v>
       </c>
-      <c r="K18" s="50" t="n">
+      <c r="K18" s="51" t="n">
         <v>18.41</v>
       </c>
-      <c r="L18" s="55" t="n">
+      <c r="L18" s="56" t="n">
         <v>-0.85</v>
       </c>
     </row>
@@ -4372,36 +4377,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D19" s="46" t="n">
+      <c r="D19" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="E19" s="46" t="n">
+      <c r="E19" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="F19" s="48" t="n">
         <v>-6</v>
       </c>
-      <c r="G19" s="47" t="n">
+      <c r="G19" s="48" t="n">
         <v>-10</v>
       </c>
-      <c r="H19" s="48" t="n">
+      <c r="H19" s="49" t="n">
         <v>6.8</v>
       </c>
-      <c r="I19" s="48" t="n">
+      <c r="I19" s="49" t="n">
         <v>157.5</v>
       </c>
-      <c r="J19" s="53" t="n">
+      <c r="J19" s="54" t="n">
         <v>-0.6</v>
       </c>
-      <c r="K19" s="50" t="n">
+      <c r="K19" s="51" t="n">
         <v>1.32</v>
       </c>
-      <c r="L19" s="55" t="n">
+      <c r="L19" s="56" t="n">
         <v>-1.52</v>
       </c>
     </row>
@@ -4416,36 +4421,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D20" s="48" t="n">
         <v>-8</v>
       </c>
-      <c r="E20" s="47" t="n">
+      <c r="E20" s="48" t="n">
         <v>-8</v>
       </c>
-      <c r="F20" s="56" t="n">
+      <c r="F20" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="46" t="n">
+      <c r="G20" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="H20" s="48" t="n">
+      <c r="H20" s="49" t="n">
         <v>3.6</v>
       </c>
-      <c r="I20" s="48" t="n">
+      <c r="I20" s="49" t="n">
         <v>42</v>
       </c>
-      <c r="J20" s="49" t="n">
+      <c r="J20" s="50" t="n">
         <v>1.7</v>
       </c>
-      <c r="K20" s="50" t="n">
+      <c r="K20" s="51" t="n">
         <v>15.07</v>
       </c>
-      <c r="L20" s="51" t="n">
+      <c r="L20" s="52" t="n">
         <v>-5.89</v>
       </c>
     </row>
@@ -4460,36 +4465,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D21" s="46" t="n">
+      <c r="D21" s="47" t="n">
         <v>36</v>
       </c>
-      <c r="E21" s="46" t="n">
+      <c r="E21" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="F21" s="46" t="n">
+      <c r="F21" s="47" t="n">
         <v>29</v>
       </c>
-      <c r="G21" s="47" t="n">
+      <c r="G21" s="48" t="n">
         <v>-38</v>
       </c>
-      <c r="H21" s="48" t="n">
+      <c r="H21" s="49" t="n">
         <v>2.7</v>
       </c>
-      <c r="I21" s="48" t="n">
+      <c r="I21" s="49" t="n">
         <v>192.2</v>
       </c>
-      <c r="J21" s="49" t="n">
+      <c r="J21" s="50" t="n">
         <v>3.2</v>
       </c>
-      <c r="K21" s="50" t="n">
+      <c r="K21" s="51" t="n">
         <v>7.53</v>
       </c>
-      <c r="L21" s="52" t="n">
+      <c r="L21" s="53" t="n">
         <v>-3.51</v>
       </c>
     </row>
@@ -4504,36 +4509,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D22" s="46" t="n">
+      <c r="D22" s="47" t="n">
         <v>116</v>
       </c>
-      <c r="E22" s="46" t="n">
+      <c r="E22" s="47" t="n">
         <v>65</v>
       </c>
-      <c r="F22" s="46" t="n">
+      <c r="F22" s="47" t="n">
         <v>51</v>
       </c>
-      <c r="G22" s="47" t="n">
+      <c r="G22" s="48" t="n">
         <v>-109</v>
       </c>
-      <c r="H22" s="48" t="n">
+      <c r="H22" s="49" t="n">
         <v>5.2</v>
       </c>
-      <c r="I22" s="48" t="n">
+      <c r="I22" s="49" t="n">
         <v>194.2</v>
       </c>
-      <c r="J22" s="49" t="n">
+      <c r="J22" s="50" t="n">
         <v>16.9</v>
       </c>
-      <c r="K22" s="50" t="n">
+      <c r="K22" s="51" t="n">
         <v>14.08</v>
       </c>
-      <c r="L22" s="51" t="n">
+      <c r="L22" s="52" t="n">
         <v>-7.47</v>
       </c>
     </row>
@@ -4548,36 +4553,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D23" s="46" t="n">
+      <c r="D23" s="47" t="n">
         <v>74</v>
       </c>
-      <c r="E23" s="46" t="n">
+      <c r="E23" s="47" t="n">
         <v>47</v>
       </c>
-      <c r="F23" s="46" t="n">
+      <c r="F23" s="47" t="n">
         <v>26</v>
       </c>
-      <c r="G23" s="47" t="n">
+      <c r="G23" s="48" t="n">
         <v>-74</v>
       </c>
-      <c r="H23" s="48" t="n">
+      <c r="H23" s="49" t="n">
         <v>21.7</v>
       </c>
-      <c r="I23" s="48" t="n">
+      <c r="I23" s="49" t="n">
         <v>827.4</v>
       </c>
-      <c r="J23" s="49" t="n">
+      <c r="J23" s="50" t="n">
         <v>41.6</v>
       </c>
-      <c r="K23" s="50" t="n">
+      <c r="K23" s="51" t="n">
         <v>3.8</v>
       </c>
-      <c r="L23" s="52" t="n">
+      <c r="L23" s="53" t="n">
         <v>-2.17</v>
       </c>
     </row>
@@ -4592,36 +4597,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="D24" s="48" t="n">
         <v>-3</v>
       </c>
-      <c r="E24" s="46" t="n">
+      <c r="E24" s="47" t="n">
         <v>12</v>
       </c>
-      <c r="F24" s="47" t="n">
+      <c r="F24" s="48" t="n">
         <v>-15</v>
       </c>
-      <c r="G24" s="46" t="n">
+      <c r="G24" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="48" t="n">
+      <c r="H24" s="49" t="n">
         <v>9.6</v>
       </c>
-      <c r="I24" s="48" t="n">
+      <c r="I24" s="49" t="n">
         <v>632.8</v>
       </c>
-      <c r="J24" s="49" t="n">
+      <c r="J24" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="K24" s="50" t="n">
+      <c r="K24" s="51" t="n">
         <v>2.59</v>
       </c>
-      <c r="L24" s="52" t="n">
+      <c r="L24" s="53" t="n">
         <v>-3.11</v>
       </c>
     </row>
@@ -4636,36 +4641,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="48" t="n">
         <v>-7</v>
       </c>
-      <c r="E25" s="46" t="n">
+      <c r="E25" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="47" t="n">
+      <c r="F25" s="48" t="n">
         <v>-8</v>
       </c>
-      <c r="G25" s="46" t="n">
+      <c r="G25" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="H25" s="48" t="n">
+      <c r="H25" s="49" t="n">
         <v>2.2</v>
       </c>
-      <c r="I25" s="48" t="n">
+      <c r="I25" s="49" t="n">
         <v>54.5</v>
       </c>
-      <c r="J25" s="49" t="n">
+      <c r="J25" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="K25" s="54" t="n">
+      <c r="K25" s="55" t="n">
         <v>-2.85</v>
       </c>
-      <c r="L25" s="51" t="n">
+      <c r="L25" s="52" t="n">
         <v>-7.14</v>
       </c>
     </row>
@@ -4680,36 +4685,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr">
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D26" s="46" t="n">
+      <c r="D26" s="47" t="n">
         <v>19</v>
       </c>
-      <c r="E26" s="47" t="n">
+      <c r="E26" s="48" t="n">
         <v>-9</v>
       </c>
-      <c r="F26" s="46" t="n">
+      <c r="F26" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G26" s="47" t="n">
+      <c r="G26" s="48" t="n">
         <v>-19</v>
       </c>
-      <c r="H26" s="48" t="n">
+      <c r="H26" s="49" t="n">
         <v>3.4</v>
       </c>
-      <c r="I26" s="48" t="n">
+      <c r="I26" s="49" t="n">
         <v>31.8</v>
       </c>
-      <c r="J26" s="53" t="n">
+      <c r="J26" s="54" t="n">
         <v>-2.1</v>
       </c>
-      <c r="K26" s="50" t="n">
+      <c r="K26" s="51" t="n">
         <v>2.3</v>
       </c>
-      <c r="L26" s="51" t="n">
+      <c r="L26" s="52" t="n">
         <v>-6.37</v>
       </c>
     </row>
@@ -4724,36 +4729,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D27" s="46" t="n">
+      <c r="D27" s="47" t="n">
         <v>42</v>
       </c>
-      <c r="E27" s="46" t="n">
+      <c r="E27" s="47" t="n">
         <v>36</v>
       </c>
-      <c r="F27" s="46" t="n">
+      <c r="F27" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="G27" s="47" t="n">
+      <c r="G27" s="48" t="n">
         <v>-42</v>
       </c>
-      <c r="H27" s="48" t="n">
+      <c r="H27" s="49" t="n">
         <v>4.5</v>
       </c>
-      <c r="I27" s="48" t="n">
+      <c r="I27" s="49" t="n">
         <v>402</v>
       </c>
-      <c r="J27" s="49" t="n">
+      <c r="J27" s="50" t="n">
         <v>14.3</v>
       </c>
-      <c r="K27" s="50" t="n">
+      <c r="K27" s="51" t="n">
         <v>2.81</v>
       </c>
-      <c r="L27" s="52" t="n">
+      <c r="L27" s="53" t="n">
         <v>-2.34</v>
       </c>
     </row>
@@ -4768,36 +4773,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C28" s="34" t="inlineStr">
+      <c r="C28" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D28" s="46" t="n">
+      <c r="D28" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="E28" s="47" t="n">
+      <c r="E28" s="48" t="n">
         <v>-6</v>
       </c>
-      <c r="F28" s="46" t="n">
+      <c r="F28" s="47" t="n">
         <v>15</v>
       </c>
-      <c r="G28" s="47" t="n">
+      <c r="G28" s="48" t="n">
         <v>-9</v>
       </c>
-      <c r="H28" s="48" t="n">
+      <c r="H28" s="49" t="n">
         <v>10.9</v>
       </c>
-      <c r="I28" s="48" t="n">
+      <c r="I28" s="49" t="n">
         <v>328.8</v>
       </c>
-      <c r="J28" s="49" t="n">
+      <c r="J28" s="50" t="n">
         <v>8.4</v>
       </c>
-      <c r="K28" s="50" t="n">
+      <c r="K28" s="51" t="n">
         <v>2.6</v>
       </c>
-      <c r="L28" s="51" t="n">
+      <c r="L28" s="52" t="n">
         <v>-9.33</v>
       </c>
     </row>
@@ -4812,36 +4817,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D29" s="46" t="n">
+      <c r="D29" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="E29" s="46" t="n">
+      <c r="E29" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="F29" s="56" t="n">
+      <c r="F29" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="47" t="n">
+      <c r="G29" s="48" t="n">
         <v>-7</v>
       </c>
-      <c r="H29" s="48" t="n">
+      <c r="H29" s="49" t="n">
         <v>3.6</v>
       </c>
-      <c r="I29" s="48" t="n">
+      <c r="I29" s="49" t="n">
         <v>322.4</v>
       </c>
-      <c r="J29" s="49" t="n">
+      <c r="J29" s="50" t="n">
         <v>3.1</v>
       </c>
-      <c r="K29" s="50" t="n">
+      <c r="K29" s="51" t="n">
         <v>3.68</v>
       </c>
-      <c r="L29" s="52" t="n">
+      <c r="L29" s="53" t="n">
         <v>-4.92</v>
       </c>
     </row>
@@ -4856,36 +4861,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C30" s="34" t="inlineStr">
+      <c r="C30" s="35" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="D30" s="46" t="n">
+      <c r="D30" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="E30" s="47" t="n">
+      <c r="E30" s="48" t="n">
         <v>-3</v>
       </c>
-      <c r="F30" s="46" t="n">
+      <c r="F30" s="47" t="n">
         <v>14</v>
       </c>
-      <c r="G30" s="47" t="n">
+      <c r="G30" s="48" t="n">
         <v>-10</v>
       </c>
-      <c r="H30" s="48" t="n">
+      <c r="H30" s="49" t="n">
         <v>2.3</v>
       </c>
-      <c r="I30" s="48" t="n">
+      <c r="I30" s="49" t="n">
         <v>66.5</v>
       </c>
-      <c r="J30" s="49" t="n">
+      <c r="J30" s="50" t="n">
         <v>0.3</v>
       </c>
-      <c r="K30" s="50" t="n">
+      <c r="K30" s="51" t="n">
         <v>3.07</v>
       </c>
-      <c r="L30" s="52" t="n">
+      <c r="L30" s="53" t="n">
         <v>-4.33</v>
       </c>
     </row>
@@ -4900,36 +4905,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C31" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D31" s="46" t="n">
+      <c r="D31" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="E31" s="46" t="n">
+      <c r="E31" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="F31" s="47" t="n">
+      <c r="F31" s="48" t="n">
         <v>-4</v>
       </c>
-      <c r="G31" s="47" t="n">
+      <c r="G31" s="48" t="n">
         <v>-6</v>
       </c>
-      <c r="H31" s="48" t="n">
+      <c r="H31" s="49" t="n">
         <v>0.4</v>
       </c>
-      <c r="I31" s="48" t="n">
+      <c r="I31" s="49" t="n">
         <v>177.8</v>
       </c>
-      <c r="J31" s="53" t="n">
+      <c r="J31" s="54" t="n">
         <v>-14.6</v>
       </c>
-      <c r="K31" s="50" t="n">
+      <c r="K31" s="51" t="n">
         <v>0.57</v>
       </c>
-      <c r="L31" s="55" t="n">
+      <c r="L31" s="56" t="n">
         <v>-1.24</v>
       </c>
     </row>
@@ -4944,36 +4949,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C32" s="34" t="inlineStr">
+      <c r="C32" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D32" s="46" t="n">
+      <c r="D32" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="E32" s="46" t="n">
+      <c r="E32" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="F32" s="56" t="n">
+      <c r="F32" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="47" t="n">
+      <c r="G32" s="48" t="n">
         <v>-4</v>
       </c>
-      <c r="H32" s="48" t="n">
+      <c r="H32" s="49" t="n">
         <v>2.1</v>
       </c>
-      <c r="I32" s="48" t="n">
+      <c r="I32" s="49" t="n">
         <v>38.5</v>
       </c>
-      <c r="J32" s="53" t="n">
+      <c r="J32" s="54" t="n">
         <v>-1.3</v>
       </c>
-      <c r="K32" s="50" t="n">
+      <c r="K32" s="51" t="n">
         <v>7.25</v>
       </c>
-      <c r="L32" s="52" t="n">
+      <c r="L32" s="53" t="n">
         <v>-4.04</v>
       </c>
     </row>
@@ -4988,34 +4993,34 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C33" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D33" s="46" t="n">
+      <c r="D33" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="46" t="n">
+      <c r="E33" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="56" t="n">
+      <c r="F33" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="47" t="n">
+      <c r="G33" s="48" t="n">
         <v>-3</v>
       </c>
-      <c r="H33" s="48" t="inlineStr"/>
-      <c r="I33" s="48" t="n">
+      <c r="H33" s="49" t="inlineStr"/>
+      <c r="I33" s="49" t="n">
         <v>33.9</v>
       </c>
-      <c r="J33" s="57" t="n">
+      <c r="J33" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="54" t="n">
+      <c r="K33" s="55" t="n">
         <v>-0.48</v>
       </c>
-      <c r="L33" s="52" t="n">
+      <c r="L33" s="53" t="n">
         <v>-3.57</v>
       </c>
     </row>
@@ -5030,36 +5035,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C34" s="34" t="inlineStr">
+      <c r="C34" s="35" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="48" t="n">
         <v>-17</v>
       </c>
-      <c r="E34" s="47" t="n">
+      <c r="E34" s="48" t="n">
         <v>-16</v>
       </c>
-      <c r="F34" s="47" t="n">
+      <c r="F34" s="48" t="n">
         <v>-1</v>
       </c>
-      <c r="G34" s="46" t="n">
+      <c r="G34" s="47" t="n">
         <v>13</v>
       </c>
-      <c r="H34" s="48" t="n">
+      <c r="H34" s="49" t="n">
         <v>1.7</v>
       </c>
-      <c r="I34" s="48" t="n">
+      <c r="I34" s="49" t="n">
         <v>793</v>
       </c>
-      <c r="J34" s="53" t="n">
+      <c r="J34" s="54" t="n">
         <v>-15.8</v>
       </c>
-      <c r="K34" s="54" t="n">
+      <c r="K34" s="55" t="n">
         <v>-1.57</v>
       </c>
-      <c r="L34" s="51" t="n">
+      <c r="L34" s="52" t="n">
         <v>-8.83</v>
       </c>
     </row>
@@ -5074,36 +5079,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D35" s="46" t="n">
+      <c r="D35" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="E35" s="46" t="n">
+      <c r="E35" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="46" t="n">
+      <c r="F35" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="G35" s="47" t="n">
+      <c r="G35" s="48" t="n">
         <v>-9</v>
       </c>
-      <c r="H35" s="48" t="n">
+      <c r="H35" s="49" t="n">
         <v>1.2</v>
       </c>
-      <c r="I35" s="48" t="n">
+      <c r="I35" s="49" t="n">
         <v>235.9</v>
       </c>
-      <c r="J35" s="49" t="n">
+      <c r="J35" s="50" t="n">
         <v>11.3</v>
       </c>
-      <c r="K35" s="50" t="n">
+      <c r="K35" s="51" t="n">
         <v>3.77</v>
       </c>
-      <c r="L35" s="51" t="n">
+      <c r="L35" s="52" t="n">
         <v>-7.27</v>
       </c>
     </row>
@@ -5181,7 +5186,7 @@
           <t>F1 외국인</t>
         </is>
       </c>
-      <c r="E3" s="58" t="inlineStr">
+      <c r="E3" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -5191,111 +5196,111 @@
           <t>F2 기관계</t>
         </is>
       </c>
-      <c r="N3" s="58" t="inlineStr">
+      <c r="N3" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J4" s="59" t="inlineStr">
+      <c r="J4" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N4" s="60" t="inlineStr">
+      <c r="N4" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M5" s="45" t="inlineStr">
+      <c r="M5" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N5" s="45" t="inlineStr">
+      <c r="N5" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O5" s="45" t="inlineStr">
+      <c r="O5" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P5" s="45" t="inlineStr">
+      <c r="P5" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q5" s="45" t="inlineStr">
+      <c r="Q5" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -5310,12 +5315,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="48" t="n">
         <v>3188</v>
       </c>
       <c r="E6" s="30" t="n">
@@ -5326,12 +5331,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G6" s="34" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H6" s="61" t="n">
+      <c r="H6" s="62" t="n">
         <v>-4440</v>
       </c>
       <c r="J6" s="30" t="n">
@@ -5342,12 +5347,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L6" s="34" t="inlineStr">
+      <c r="L6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M6" s="47" t="n">
+      <c r="M6" s="48" t="n">
         <v>1838</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -5358,12 +5363,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P6" s="34" t="inlineStr">
+      <c r="P6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q6" s="61" t="n">
+      <c r="Q6" s="62" t="n">
         <v>-852</v>
       </c>
     </row>
@@ -5376,12 +5381,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="48" t="n">
         <v>1283</v>
       </c>
       <c r="E7" s="30" t="n">
@@ -5392,12 +5397,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G7" s="34" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H7" s="61" t="n">
+      <c r="H7" s="62" t="n">
         <v>-3146</v>
       </c>
       <c r="J7" s="30" t="n">
@@ -5408,12 +5413,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L7" s="34" t="inlineStr">
+      <c r="L7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M7" s="47" t="n">
+      <c r="M7" s="48" t="n">
         <v>1777</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -5424,12 +5429,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="P7" s="34" t="inlineStr">
+      <c r="P7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q7" s="61" t="n">
+      <c r="Q7" s="62" t="n">
         <v>-632</v>
       </c>
     </row>
@@ -5442,12 +5447,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="48" t="n">
         <v>716</v>
       </c>
       <c r="E8" s="30" t="n">
@@ -5458,12 +5463,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="G8" s="34" t="inlineStr">
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H8" s="61" t="n">
+      <c r="H8" s="62" t="n">
         <v>-769</v>
       </c>
       <c r="J8" s="30" t="n">
@@ -5474,12 +5479,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L8" s="34" t="inlineStr">
+      <c r="L8" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M8" s="47" t="n">
+      <c r="M8" s="48" t="n">
         <v>1297</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -5490,12 +5495,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="P8" s="34" t="inlineStr">
+      <c r="P8" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q8" s="61" t="n">
+      <c r="Q8" s="62" t="n">
         <v>-562</v>
       </c>
     </row>
@@ -5508,12 +5513,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="48" t="n">
         <v>449</v>
       </c>
       <c r="E9" s="30" t="n">
@@ -5524,12 +5529,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G9" s="34" t="inlineStr">
+      <c r="G9" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H9" s="61" t="n">
+      <c r="H9" s="62" t="n">
         <v>-675</v>
       </c>
       <c r="J9" s="30" t="n">
@@ -5540,12 +5545,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L9" s="34" t="inlineStr">
+      <c r="L9" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M9" s="47" t="n">
+      <c r="M9" s="48" t="n">
         <v>942</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -5556,12 +5561,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P9" s="34" t="inlineStr">
+      <c r="P9" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q9" s="61" t="n">
+      <c r="Q9" s="62" t="n">
         <v>-506</v>
       </c>
     </row>
@@ -5574,12 +5579,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="48" t="n">
         <v>349</v>
       </c>
       <c r="E10" s="30" t="n">
@@ -5590,12 +5595,12 @@
           <t>우리금융지주</t>
         </is>
       </c>
-      <c r="G10" s="34" t="inlineStr">
+      <c r="G10" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H10" s="61" t="n">
+      <c r="H10" s="62" t="n">
         <v>-648</v>
       </c>
       <c r="J10" s="30" t="n">
@@ -5606,12 +5611,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L10" s="34" t="inlineStr">
+      <c r="L10" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M10" s="47" t="n">
+      <c r="M10" s="48" t="n">
         <v>582</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -5622,12 +5627,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P10" s="34" t="inlineStr">
+      <c r="P10" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q10" s="61" t="n">
+      <c r="Q10" s="62" t="n">
         <v>-504</v>
       </c>
     </row>
@@ -5640,12 +5645,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="48" t="n">
         <v>341</v>
       </c>
       <c r="E11" s="30" t="n">
@@ -5656,12 +5661,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G11" s="34" t="inlineStr">
+      <c r="G11" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H11" s="61" t="n">
+      <c r="H11" s="62" t="n">
         <v>-625</v>
       </c>
       <c r="J11" s="30" t="n">
@@ -5672,12 +5677,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="L11" s="34" t="inlineStr">
+      <c r="L11" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M11" s="47" t="n">
+      <c r="M11" s="48" t="n">
         <v>533</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -5688,12 +5693,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P11" s="34" t="inlineStr">
+      <c r="P11" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q11" s="61" t="n">
+      <c r="Q11" s="62" t="n">
         <v>-466</v>
       </c>
     </row>
@@ -5706,12 +5711,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="48" t="n">
         <v>270</v>
       </c>
       <c r="E12" s="30" t="n">
@@ -5722,12 +5727,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="G12" s="34" t="inlineStr">
+      <c r="G12" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H12" s="61" t="n">
+      <c r="H12" s="62" t="n">
         <v>-442</v>
       </c>
       <c r="J12" s="30" t="n">
@@ -5738,12 +5743,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="L12" s="34" t="inlineStr">
+      <c r="L12" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M12" s="47" t="n">
+      <c r="M12" s="48" t="n">
         <v>513</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -5754,12 +5759,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="P12" s="34" t="inlineStr">
+      <c r="P12" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="Q12" s="61" t="n">
+      <c r="Q12" s="62" t="n">
         <v>-367</v>
       </c>
     </row>
@@ -5772,12 +5777,12 @@
           <t>삼화콘덴서</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="48" t="n">
         <v>262</v>
       </c>
       <c r="E13" s="30" t="n">
@@ -5788,12 +5793,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G13" s="34" t="inlineStr">
+      <c r="G13" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H13" s="61" t="n">
+      <c r="H13" s="62" t="n">
         <v>-424</v>
       </c>
       <c r="J13" s="30" t="n">
@@ -5804,12 +5809,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L13" s="34" t="inlineStr">
+      <c r="L13" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M13" s="47" t="n">
+      <c r="M13" s="48" t="n">
         <v>451</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -5820,12 +5825,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P13" s="41" t="inlineStr">
+      <c r="P13" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q13" s="61" t="n">
+      <c r="Q13" s="62" t="n">
         <v>-343</v>
       </c>
     </row>
@@ -5838,12 +5843,12 @@
           <t>고영</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="48" t="n">
         <v>256</v>
       </c>
       <c r="E14" s="30" t="n">
@@ -5854,12 +5859,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="G14" s="34" t="inlineStr">
+      <c r="G14" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H14" s="61" t="n">
+      <c r="H14" s="62" t="n">
         <v>-408</v>
       </c>
       <c r="J14" s="30" t="n">
@@ -5870,12 +5875,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="L14" s="34" t="inlineStr">
+      <c r="L14" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M14" s="47" t="n">
+      <c r="M14" s="48" t="n">
         <v>447</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -5886,12 +5891,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P14" s="41" t="inlineStr">
+      <c r="P14" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q14" s="61" t="n">
+      <c r="Q14" s="62" t="n">
         <v>-307</v>
       </c>
     </row>
@@ -5904,12 +5909,12 @@
           <t>SFA반도체</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="48" t="n">
         <v>238</v>
       </c>
       <c r="E15" s="30" t="n">
@@ -5920,12 +5925,12 @@
           <t>신한지주</t>
         </is>
       </c>
-      <c r="G15" s="34" t="inlineStr">
+      <c r="G15" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H15" s="61" t="n">
+      <c r="H15" s="62" t="n">
         <v>-393</v>
       </c>
       <c r="J15" s="30" t="n">
@@ -5936,12 +5941,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="L15" s="41" t="inlineStr">
+      <c r="L15" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M15" s="47" t="n">
+      <c r="M15" s="48" t="n">
         <v>424</v>
       </c>
       <c r="N15" s="30" t="n">
@@ -5952,12 +5957,12 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="P15" s="34" t="inlineStr">
+      <c r="P15" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q15" s="61" t="n">
+      <c r="Q15" s="62" t="n">
         <v>-217</v>
       </c>
     </row>
@@ -5968,7 +5973,7 @@
           <t>F3 외인+기관</t>
         </is>
       </c>
-      <c r="E17" s="58" t="inlineStr">
+      <c r="E17" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -5978,111 +5983,111 @@
           <t>F4 개인</t>
         </is>
       </c>
-      <c r="N17" s="58" t="inlineStr">
+      <c r="N17" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="59" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E18" s="60" t="inlineStr">
+      <c r="E18" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J18" s="59" t="inlineStr">
+      <c r="J18" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N18" s="60" t="inlineStr">
+      <c r="N18" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C19" s="45" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D19" s="45" t="inlineStr">
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E19" s="45" t="inlineStr">
+      <c r="E19" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F19" s="45" t="inlineStr">
+      <c r="F19" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G19" s="45" t="inlineStr">
+      <c r="G19" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H19" s="45" t="inlineStr">
+      <c r="H19" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J19" s="45" t="inlineStr">
+      <c r="J19" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K19" s="45" t="inlineStr">
+      <c r="K19" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L19" s="45" t="inlineStr">
+      <c r="L19" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M19" s="45" t="inlineStr">
+      <c r="M19" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N19" s="45" t="inlineStr">
+      <c r="N19" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O19" s="45" t="inlineStr">
+      <c r="O19" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P19" s="45" t="inlineStr">
+      <c r="P19" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q19" s="45" t="inlineStr">
+      <c r="Q19" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -6097,12 +6102,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D20" s="48" t="n">
         <v>4485</v>
       </c>
       <c r="E20" s="30" t="n">
@@ -6113,12 +6118,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G20" s="34" t="inlineStr">
+      <c r="G20" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H20" s="61" t="n">
+      <c r="H20" s="62" t="n">
         <v>-2602</v>
       </c>
       <c r="J20" s="30" t="n">
@@ -6129,12 +6134,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="L20" s="34" t="inlineStr">
+      <c r="L20" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M20" s="47" t="n">
+      <c r="M20" s="48" t="n">
         <v>924</v>
       </c>
       <c r="N20" s="30" t="n">
@@ -6145,12 +6150,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P20" s="34" t="inlineStr">
+      <c r="P20" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q20" s="61" t="n">
+      <c r="Q20" s="62" t="n">
         <v>-17231</v>
       </c>
     </row>
@@ -6163,12 +6168,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="D21" s="48" t="n">
         <v>796</v>
       </c>
       <c r="E21" s="30" t="n">
@@ -6179,12 +6184,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G21" s="34" t="inlineStr">
+      <c r="G21" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H21" s="61" t="n">
+      <c r="H21" s="62" t="n">
         <v>-1369</v>
       </c>
       <c r="J21" s="30" t="n">
@@ -6195,12 +6200,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="L21" s="34" t="inlineStr">
+      <c r="L21" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M21" s="47" t="n">
+      <c r="M21" s="48" t="n">
         <v>782</v>
       </c>
       <c r="N21" s="30" t="n">
@@ -6211,12 +6216,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P21" s="34" t="inlineStr">
+      <c r="P21" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q21" s="61" t="n">
+      <c r="Q21" s="62" t="n">
         <v>-9470</v>
       </c>
     </row>
@@ -6229,12 +6234,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="D22" s="48" t="n">
         <v>594</v>
       </c>
       <c r="E22" s="30" t="n">
@@ -6245,12 +6250,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G22" s="34" t="inlineStr">
+      <c r="G22" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H22" s="61" t="n">
+      <c r="H22" s="62" t="n">
         <v>-928</v>
       </c>
       <c r="J22" s="30" t="n">
@@ -6261,12 +6266,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="L22" s="34" t="inlineStr">
+      <c r="L22" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M22" s="47" t="n">
+      <c r="M22" s="48" t="n">
         <v>773</v>
       </c>
       <c r="N22" s="30" t="n">
@@ -6277,12 +6282,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="P22" s="34" t="inlineStr">
+      <c r="P22" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q22" s="61" t="n">
+      <c r="Q22" s="62" t="n">
         <v>-4521</v>
       </c>
     </row>
@@ -6295,12 +6300,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="48" t="n">
         <v>503</v>
       </c>
       <c r="E23" s="30" t="n">
@@ -6311,12 +6316,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G23" s="34" t="inlineStr">
+      <c r="G23" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H23" s="61" t="n">
+      <c r="H23" s="62" t="n">
         <v>-789</v>
       </c>
       <c r="J23" s="30" t="n">
@@ -6327,12 +6332,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="L23" s="41" t="inlineStr">
+      <c r="L23" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M23" s="47" t="n">
+      <c r="M23" s="48" t="n">
         <v>729</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -6343,12 +6348,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="P23" s="34" t="inlineStr">
+      <c r="P23" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q23" s="61" t="n">
+      <c r="Q23" s="62" t="n">
         <v>-789</v>
       </c>
     </row>
@@ -6361,12 +6366,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="D24" s="48" t="n">
         <v>497</v>
       </c>
       <c r="E24" s="30" t="n">
@@ -6377,12 +6382,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G24" s="41" t="inlineStr">
+      <c r="G24" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H24" s="61" t="n">
+      <c r="H24" s="62" t="n">
         <v>-723</v>
       </c>
       <c r="J24" s="30" t="n">
@@ -6393,12 +6398,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="L24" s="34" t="inlineStr">
+      <c r="L24" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M24" s="47" t="n">
+      <c r="M24" s="48" t="n">
         <v>716</v>
       </c>
       <c r="N24" s="30" t="n">
@@ -6409,12 +6414,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="P24" s="34" t="inlineStr">
+      <c r="P24" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="Q24" s="61" t="n">
+      <c r="Q24" s="62" t="n">
         <v>-591</v>
       </c>
     </row>
@@ -6427,12 +6432,12 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="48" t="n">
         <v>467</v>
       </c>
       <c r="E25" s="30" t="n">
@@ -6443,12 +6448,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="G25" s="34" t="inlineStr">
+      <c r="G25" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H25" s="61" t="n">
+      <c r="H25" s="62" t="n">
         <v>-684</v>
       </c>
       <c r="J25" s="30" t="n">
@@ -6459,12 +6464,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="L25" s="34" t="inlineStr">
+      <c r="L25" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="M25" s="47" t="n">
+      <c r="M25" s="48" t="n">
         <v>426</v>
       </c>
       <c r="N25" s="30" t="n">
@@ -6475,12 +6480,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="P25" s="34" t="inlineStr">
+      <c r="P25" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q25" s="61" t="n">
+      <c r="Q25" s="62" t="n">
         <v>-499</v>
       </c>
     </row>
@@ -6493,12 +6498,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr">
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D26" s="47" t="n">
+      <c r="D26" s="48" t="n">
         <v>432</v>
       </c>
       <c r="E26" s="30" t="n">
@@ -6509,12 +6514,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="G26" s="34" t="inlineStr">
+      <c r="G26" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H26" s="61" t="n">
+      <c r="H26" s="62" t="n">
         <v>-560</v>
       </c>
       <c r="J26" s="30" t="n">
@@ -6525,12 +6530,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="L26" s="34" t="inlineStr">
+      <c r="L26" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M26" s="47" t="n">
+      <c r="M26" s="48" t="n">
         <v>413</v>
       </c>
       <c r="N26" s="30" t="n">
@@ -6541,12 +6546,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="P26" s="34" t="inlineStr">
+      <c r="P26" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q26" s="61" t="n">
+      <c r="Q26" s="62" t="n">
         <v>-486</v>
       </c>
     </row>
@@ -6559,12 +6564,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="48" t="n">
         <v>416</v>
       </c>
       <c r="E27" s="30" t="n">
@@ -6575,12 +6580,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="G27" s="34" t="inlineStr">
+      <c r="G27" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="H27" s="61" t="n">
+      <c r="H27" s="62" t="n">
         <v>-440</v>
       </c>
       <c r="J27" s="30" t="n">
@@ -6591,12 +6596,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="L27" s="34" t="inlineStr">
+      <c r="L27" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M27" s="47" t="n">
+      <c r="M27" s="48" t="n">
         <v>413</v>
       </c>
       <c r="N27" s="30" t="n">
@@ -6607,12 +6612,12 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="P27" s="34" t="inlineStr">
+      <c r="P27" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="Q27" s="61" t="n">
+      <c r="Q27" s="62" t="n">
         <v>-468</v>
       </c>
     </row>
@@ -6625,12 +6630,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="C28" s="41" t="inlineStr">
+      <c r="C28" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D28" s="47" t="n">
+      <c r="D28" s="48" t="n">
         <v>385</v>
       </c>
       <c r="E28" s="30" t="n">
@@ -6641,12 +6646,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="G28" s="34" t="inlineStr">
+      <c r="G28" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H28" s="61" t="n">
+      <c r="H28" s="62" t="n">
         <v>-423</v>
       </c>
       <c r="J28" s="30" t="n">
@@ -6657,12 +6662,12 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="L28" s="34" t="inlineStr">
+      <c r="L28" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M28" s="47" t="n">
+      <c r="M28" s="48" t="n">
         <v>307</v>
       </c>
       <c r="N28" s="30" t="n">
@@ -6673,12 +6678,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P28" s="34" t="inlineStr">
+      <c r="P28" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q28" s="61" t="n">
+      <c r="Q28" s="62" t="n">
         <v>-462</v>
       </c>
     </row>
@@ -6691,12 +6696,12 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D29" s="47" t="n">
+      <c r="D29" s="48" t="n">
         <v>365</v>
       </c>
       <c r="E29" s="30" t="n">
@@ -6707,12 +6712,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="G29" s="34" t="inlineStr">
+      <c r="G29" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H29" s="61" t="n">
+      <c r="H29" s="62" t="n">
         <v>-423</v>
       </c>
       <c r="J29" s="30" t="n">
@@ -6723,12 +6728,12 @@
           <t>우리금융지주</t>
         </is>
       </c>
-      <c r="L29" s="34" t="inlineStr">
+      <c r="L29" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M29" s="47" t="n">
+      <c r="M29" s="48" t="n">
         <v>299</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -6739,12 +6744,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="P29" s="34" t="inlineStr">
+      <c r="P29" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q29" s="61" t="n">
+      <c r="Q29" s="62" t="n">
         <v>-407</v>
       </c>
     </row>
@@ -6755,7 +6760,7 @@
           <t>F5 금융투자</t>
         </is>
       </c>
-      <c r="E31" s="58" t="inlineStr">
+      <c r="E31" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -6765,111 +6770,111 @@
           <t>F6 투신(사모)</t>
         </is>
       </c>
-      <c r="N31" s="58" t="inlineStr">
+      <c r="N31" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="59" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E32" s="60" t="inlineStr">
+      <c r="E32" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J32" s="59" t="inlineStr">
+      <c r="J32" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N32" s="60" t="inlineStr">
+      <c r="N32" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="45" t="inlineStr">
+      <c r="A33" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B33" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C33" s="45" t="inlineStr">
+      <c r="C33" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D33" s="45" t="inlineStr">
+      <c r="D33" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E33" s="45" t="inlineStr">
+      <c r="E33" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F33" s="45" t="inlineStr">
+      <c r="F33" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G33" s="45" t="inlineStr">
+      <c r="G33" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H33" s="45" t="inlineStr">
+      <c r="H33" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J33" s="45" t="inlineStr">
+      <c r="J33" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K33" s="45" t="inlineStr">
+      <c r="K33" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L33" s="45" t="inlineStr">
+      <c r="L33" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M33" s="45" t="inlineStr">
+      <c r="M33" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N33" s="45" t="inlineStr">
+      <c r="N33" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O33" s="45" t="inlineStr">
+      <c r="O33" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P33" s="45" t="inlineStr">
+      <c r="P33" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q33" s="45" t="inlineStr">
+      <c r="Q33" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -6884,12 +6889,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C34" s="34" t="inlineStr">
+      <c r="C34" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="48" t="n">
         <v>562</v>
       </c>
       <c r="E34" s="30" t="n">
@@ -6900,12 +6905,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="G34" s="41" t="inlineStr">
+      <c r="G34" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H34" s="61" t="n">
+      <c r="H34" s="62" t="n">
         <v>-127</v>
       </c>
       <c r="J34" s="30" t="n">
@@ -6916,12 +6921,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L34" s="34" t="inlineStr">
+      <c r="L34" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M34" s="47" t="n">
+      <c r="M34" s="48" t="n">
         <v>897</v>
       </c>
       <c r="N34" s="30" t="n">
@@ -6932,12 +6937,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P34" s="34" t="inlineStr">
+      <c r="P34" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q34" s="61" t="n">
+      <c r="Q34" s="62" t="n">
         <v>-543</v>
       </c>
     </row>
@@ -6950,12 +6955,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D35" s="47" t="n">
+      <c r="D35" s="48" t="n">
         <v>411</v>
       </c>
       <c r="E35" s="30" t="n">
@@ -6966,12 +6971,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G35" s="41" t="inlineStr">
+      <c r="G35" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H35" s="61" t="n">
+      <c r="H35" s="62" t="n">
         <v>-108</v>
       </c>
       <c r="J35" s="30" t="n">
@@ -6982,12 +6987,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L35" s="34" t="inlineStr">
+      <c r="L35" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M35" s="47" t="n">
+      <c r="M35" s="48" t="n">
         <v>702</v>
       </c>
       <c r="N35" s="30" t="n">
@@ -6998,12 +7003,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="P35" s="34" t="inlineStr">
+      <c r="P35" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q35" s="61" t="n">
+      <c r="Q35" s="62" t="n">
         <v>-420</v>
       </c>
     </row>
@@ -7016,12 +7021,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C36" s="34" t="inlineStr">
+      <c r="C36" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D36" s="47" t="n">
+      <c r="D36" s="48" t="n">
         <v>321</v>
       </c>
       <c r="E36" s="30" t="n">
@@ -7032,12 +7037,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="G36" s="34" t="inlineStr">
+      <c r="G36" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H36" s="61" t="n">
+      <c r="H36" s="62" t="n">
         <v>-98</v>
       </c>
       <c r="J36" s="30" t="n">
@@ -7048,12 +7053,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L36" s="34" t="inlineStr">
+      <c r="L36" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M36" s="47" t="n">
+      <c r="M36" s="48" t="n">
         <v>605</v>
       </c>
       <c r="N36" s="30" t="n">
@@ -7064,12 +7069,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P36" s="34" t="inlineStr">
+      <c r="P36" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q36" s="61" t="n">
+      <c r="Q36" s="62" t="n">
         <v>-314</v>
       </c>
     </row>
@@ -7082,12 +7087,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="C37" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D37" s="47" t="n">
+      <c r="D37" s="48" t="n">
         <v>273</v>
       </c>
       <c r="E37" s="30" t="n">
@@ -7098,12 +7103,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="G37" s="34" t="inlineStr">
+      <c r="G37" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="H37" s="61" t="n">
+      <c r="H37" s="62" t="n">
         <v>-75</v>
       </c>
       <c r="J37" s="30" t="n">
@@ -7114,12 +7119,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L37" s="34" t="inlineStr">
+      <c r="L37" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M37" s="47" t="n">
+      <c r="M37" s="48" t="n">
         <v>370</v>
       </c>
       <c r="N37" s="30" t="n">
@@ -7130,12 +7135,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P37" s="34" t="inlineStr">
+      <c r="P37" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q37" s="61" t="n">
+      <c r="Q37" s="62" t="n">
         <v>-206</v>
       </c>
     </row>
@@ -7148,12 +7153,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="C38" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D38" s="47" t="n">
+      <c r="D38" s="48" t="n">
         <v>271</v>
       </c>
       <c r="E38" s="30" t="n">
@@ -7164,12 +7169,12 @@
           <t>대한항공</t>
         </is>
       </c>
-      <c r="G38" s="34" t="inlineStr">
+      <c r="G38" s="35" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="H38" s="61" t="n">
+      <c r="H38" s="62" t="n">
         <v>-56</v>
       </c>
       <c r="J38" s="30" t="n">
@@ -7180,12 +7185,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="L38" s="34" t="inlineStr">
+      <c r="L38" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M38" s="47" t="n">
+      <c r="M38" s="48" t="n">
         <v>307</v>
       </c>
       <c r="N38" s="30" t="n">
@@ -7196,12 +7201,12 @@
           <t>HD현대일렉트릭</t>
         </is>
       </c>
-      <c r="P38" s="34" t="inlineStr">
+      <c r="P38" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q38" s="61" t="n">
+      <c r="Q38" s="62" t="n">
         <v>-190</v>
       </c>
     </row>
@@ -7214,12 +7219,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="C39" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D39" s="47" t="n">
+      <c r="D39" s="48" t="n">
         <v>261</v>
       </c>
       <c r="E39" s="30" t="n">
@@ -7230,12 +7235,12 @@
           <t>피에스케이</t>
         </is>
       </c>
-      <c r="G39" s="34" t="inlineStr">
+      <c r="G39" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H39" s="61" t="n">
+      <c r="H39" s="62" t="n">
         <v>-53</v>
       </c>
       <c r="J39" s="30" t="n">
@@ -7246,12 +7251,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="L39" s="41" t="inlineStr">
+      <c r="L39" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M39" s="47" t="n">
+      <c r="M39" s="48" t="n">
         <v>239</v>
       </c>
       <c r="N39" s="30" t="n">
@@ -7262,12 +7267,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P39" s="41" t="inlineStr">
+      <c r="P39" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q39" s="61" t="n">
+      <c r="Q39" s="62" t="n">
         <v>-188</v>
       </c>
     </row>
@@ -7280,12 +7285,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C40" s="34" t="inlineStr">
+      <c r="C40" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D40" s="47" t="n">
+      <c r="D40" s="48" t="n">
         <v>232</v>
       </c>
       <c r="E40" s="30" t="n">
@@ -7296,12 +7301,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="G40" s="34" t="inlineStr">
+      <c r="G40" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H40" s="61" t="n">
+      <c r="H40" s="62" t="n">
         <v>-52</v>
       </c>
       <c r="J40" s="30" t="n">
@@ -7312,12 +7317,12 @@
           <t>NC</t>
         </is>
       </c>
-      <c r="L40" s="34" t="inlineStr">
+      <c r="L40" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M40" s="47" t="n">
+      <c r="M40" s="48" t="n">
         <v>238</v>
       </c>
       <c r="N40" s="30" t="n">
@@ -7328,12 +7333,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P40" s="34" t="inlineStr">
+      <c r="P40" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q40" s="61" t="n">
+      <c r="Q40" s="62" t="n">
         <v>-179</v>
       </c>
     </row>
@@ -7346,12 +7351,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="C41" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D41" s="47" t="n">
+      <c r="D41" s="48" t="n">
         <v>208</v>
       </c>
       <c r="E41" s="30" t="n">
@@ -7362,12 +7367,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="G41" s="34" t="inlineStr">
+      <c r="G41" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H41" s="61" t="n">
+      <c r="H41" s="62" t="n">
         <v>-46</v>
       </c>
       <c r="J41" s="30" t="n">
@@ -7378,12 +7383,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="L41" s="34" t="inlineStr">
+      <c r="L41" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M41" s="47" t="n">
+      <c r="M41" s="48" t="n">
         <v>222</v>
       </c>
       <c r="N41" s="30" t="n">
@@ -7394,12 +7399,12 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="P41" s="34" t="inlineStr">
+      <c r="P41" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q41" s="61" t="n">
+      <c r="Q41" s="62" t="n">
         <v>-160</v>
       </c>
     </row>
@@ -7412,12 +7417,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C42" s="34" t="inlineStr">
+      <c r="C42" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D42" s="47" t="n">
+      <c r="D42" s="48" t="n">
         <v>191</v>
       </c>
       <c r="E42" s="30" t="n">
@@ -7428,12 +7433,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G42" s="34" t="inlineStr">
+      <c r="G42" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H42" s="61" t="n">
+      <c r="H42" s="62" t="n">
         <v>-39</v>
       </c>
       <c r="J42" s="30" t="n">
@@ -7444,12 +7449,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L42" s="34" t="inlineStr">
+      <c r="L42" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M42" s="47" t="n">
+      <c r="M42" s="48" t="n">
         <v>204</v>
       </c>
       <c r="N42" s="30" t="n">
@@ -7460,12 +7465,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="P42" s="34" t="inlineStr">
+      <c r="P42" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q42" s="61" t="n">
+      <c r="Q42" s="62" t="n">
         <v>-154</v>
       </c>
     </row>
@@ -7478,12 +7483,12 @@
           <t>신한지주</t>
         </is>
       </c>
-      <c r="C43" s="34" t="inlineStr">
+      <c r="C43" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D43" s="47" t="n">
+      <c r="D43" s="48" t="n">
         <v>184</v>
       </c>
       <c r="E43" s="30" t="n">
@@ -7494,12 +7499,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="G43" s="41" t="inlineStr">
+      <c r="G43" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H43" s="61" t="n">
+      <c r="H43" s="62" t="n">
         <v>-36</v>
       </c>
       <c r="J43" s="30" t="n">
@@ -7510,12 +7515,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="L43" s="34" t="inlineStr">
+      <c r="L43" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M43" s="47" t="n">
+      <c r="M43" s="48" t="n">
         <v>168</v>
       </c>
       <c r="N43" s="30" t="n">
@@ -7526,12 +7531,12 @@
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="P43" s="34" t="inlineStr">
+      <c r="P43" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="Q43" s="61" t="n">
+      <c r="Q43" s="62" t="n">
         <v>-153</v>
       </c>
     </row>
@@ -7542,7 +7547,7 @@
           <t>F7 연기금</t>
         </is>
       </c>
-      <c r="E45" s="58" t="inlineStr">
+      <c r="E45" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -7552,111 +7557,111 @@
           <t>F8 보험</t>
         </is>
       </c>
-      <c r="N45" s="58" t="inlineStr">
+      <c r="N45" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="59" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E46" s="60" t="inlineStr">
+      <c r="E46" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J46" s="59" t="inlineStr">
+      <c r="J46" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N46" s="60" t="inlineStr">
+      <c r="N46" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="45" t="inlineStr">
+      <c r="A47" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B47" s="45" t="inlineStr">
+      <c r="B47" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C47" s="45" t="inlineStr">
+      <c r="C47" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D47" s="45" t="inlineStr">
+      <c r="D47" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E47" s="45" t="inlineStr">
+      <c r="E47" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F47" s="45" t="inlineStr">
+      <c r="F47" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G47" s="45" t="inlineStr">
+      <c r="G47" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H47" s="45" t="inlineStr">
+      <c r="H47" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J47" s="45" t="inlineStr">
+      <c r="J47" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K47" s="45" t="inlineStr">
+      <c r="K47" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L47" s="45" t="inlineStr">
+      <c r="L47" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M47" s="45" t="inlineStr">
+      <c r="M47" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N47" s="45" t="inlineStr">
+      <c r="N47" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O47" s="45" t="inlineStr">
+      <c r="O47" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P47" s="45" t="inlineStr">
+      <c r="P47" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q47" s="45" t="inlineStr">
+      <c r="Q47" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -7671,12 +7676,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C48" s="34" t="inlineStr">
+      <c r="C48" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D48" s="47" t="n">
+      <c r="D48" s="48" t="n">
         <v>604</v>
       </c>
       <c r="E48" s="30" t="n">
@@ -7687,12 +7692,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G48" s="34" t="inlineStr">
+      <c r="G48" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H48" s="61" t="n">
+      <c r="H48" s="62" t="n">
         <v>-384</v>
       </c>
       <c r="J48" s="30" t="n">
@@ -7703,12 +7708,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L48" s="34" t="inlineStr">
+      <c r="L48" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M48" s="47" t="n">
+      <c r="M48" s="48" t="n">
         <v>192</v>
       </c>
       <c r="N48" s="30" t="n">
@@ -7719,12 +7724,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P48" s="34" t="inlineStr">
+      <c r="P48" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q48" s="61" t="n">
+      <c r="Q48" s="62" t="n">
         <v>-67</v>
       </c>
     </row>
@@ -7737,12 +7742,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C49" s="34" t="inlineStr">
+      <c r="C49" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D49" s="47" t="n">
+      <c r="D49" s="48" t="n">
         <v>551</v>
       </c>
       <c r="E49" s="30" t="n">
@@ -7753,12 +7758,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="G49" s="34" t="inlineStr">
+      <c r="G49" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H49" s="61" t="n">
+      <c r="H49" s="62" t="n">
         <v>-382</v>
       </c>
       <c r="J49" s="30" t="n">
@@ -7769,12 +7774,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L49" s="34" t="inlineStr">
+      <c r="L49" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M49" s="47" t="n">
+      <c r="M49" s="48" t="n">
         <v>133</v>
       </c>
       <c r="N49" s="30" t="n">
@@ -7785,12 +7790,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P49" s="34" t="inlineStr">
+      <c r="P49" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q49" s="61" t="n">
+      <c r="Q49" s="62" t="n">
         <v>-48</v>
       </c>
     </row>
@@ -7803,12 +7808,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C50" s="34" t="inlineStr">
+      <c r="C50" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D50" s="47" t="n">
+      <c r="D50" s="48" t="n">
         <v>382</v>
       </c>
       <c r="E50" s="30" t="n">
@@ -7819,12 +7824,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G50" s="41" t="inlineStr">
+      <c r="G50" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H50" s="61" t="n">
+      <c r="H50" s="62" t="n">
         <v>-296</v>
       </c>
       <c r="J50" s="30" t="n">
@@ -7835,12 +7840,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="L50" s="41" t="inlineStr">
+      <c r="L50" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M50" s="47" t="n">
+      <c r="M50" s="48" t="n">
         <v>56</v>
       </c>
       <c r="N50" s="30" t="n">
@@ -7851,12 +7856,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P50" s="34" t="inlineStr">
+      <c r="P50" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q50" s="61" t="n">
+      <c r="Q50" s="62" t="n">
         <v>-45</v>
       </c>
     </row>
@@ -7869,12 +7874,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C51" s="34" t="inlineStr">
+      <c r="C51" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D51" s="47" t="n">
+      <c r="D51" s="48" t="n">
         <v>246</v>
       </c>
       <c r="E51" s="30" t="n">
@@ -7885,12 +7890,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="G51" s="41" t="inlineStr">
+      <c r="G51" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H51" s="61" t="n">
+      <c r="H51" s="62" t="n">
         <v>-183</v>
       </c>
       <c r="J51" s="30" t="n">
@@ -7901,12 +7906,12 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="L51" s="34" t="inlineStr">
+      <c r="L51" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="M51" s="47" t="n">
+      <c r="M51" s="48" t="n">
         <v>45</v>
       </c>
       <c r="N51" s="30" t="n">
@@ -7917,12 +7922,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P51" s="41" t="inlineStr">
+      <c r="P51" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q51" s="61" t="n">
+      <c r="Q51" s="62" t="n">
         <v>-36</v>
       </c>
     </row>
@@ -7935,12 +7940,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C52" s="34" t="inlineStr">
+      <c r="C52" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D52" s="47" t="n">
+      <c r="D52" s="48" t="n">
         <v>233</v>
       </c>
       <c r="E52" s="30" t="n">
@@ -7951,12 +7956,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="G52" s="34" t="inlineStr">
+      <c r="G52" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="H52" s="61" t="n">
+      <c r="H52" s="62" t="n">
         <v>-151</v>
       </c>
       <c r="J52" s="30" t="n">
@@ -7967,12 +7972,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L52" s="34" t="inlineStr">
+      <c r="L52" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M52" s="47" t="n">
+      <c r="M52" s="48" t="n">
         <v>42</v>
       </c>
       <c r="N52" s="30" t="n">
@@ -7983,12 +7988,12 @@
           <t>하나금융지주</t>
         </is>
       </c>
-      <c r="P52" s="34" t="inlineStr">
+      <c r="P52" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q52" s="61" t="n">
+      <c r="Q52" s="62" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -8001,12 +8006,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="C53" s="34" t="inlineStr">
+      <c r="C53" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D53" s="47" t="n">
+      <c r="D53" s="48" t="n">
         <v>210</v>
       </c>
       <c r="E53" s="30" t="n">
@@ -8017,12 +8022,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="G53" s="34" t="inlineStr">
+      <c r="G53" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H53" s="61" t="n">
+      <c r="H53" s="62" t="n">
         <v>-148</v>
       </c>
       <c r="J53" s="30" t="n">
@@ -8033,12 +8038,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L53" s="34" t="inlineStr">
+      <c r="L53" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M53" s="47" t="n">
+      <c r="M53" s="48" t="n">
         <v>36</v>
       </c>
       <c r="N53" s="30" t="n">
@@ -8049,12 +8054,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="P53" s="41" t="inlineStr">
+      <c r="P53" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q53" s="61" t="n">
+      <c r="Q53" s="62" t="n">
         <v>-19</v>
       </c>
     </row>
@@ -8067,12 +8072,12 @@
           <t>우리금융지주</t>
         </is>
       </c>
-      <c r="C54" s="34" t="inlineStr">
+      <c r="C54" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D54" s="47" t="n">
+      <c r="D54" s="48" t="n">
         <v>206</v>
       </c>
       <c r="E54" s="30" t="n">
@@ -8083,12 +8088,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="G54" s="34" t="inlineStr">
+      <c r="G54" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H54" s="61" t="n">
+      <c r="H54" s="62" t="n">
         <v>-114</v>
       </c>
       <c r="J54" s="30" t="n">
@@ -8099,12 +8104,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L54" s="34" t="inlineStr">
+      <c r="L54" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M54" s="47" t="n">
+      <c r="M54" s="48" t="n">
         <v>35</v>
       </c>
       <c r="N54" s="30" t="n">
@@ -8115,12 +8120,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="P54" s="34" t="inlineStr">
+      <c r="P54" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q54" s="61" t="n">
+      <c r="Q54" s="62" t="n">
         <v>-18</v>
       </c>
     </row>
@@ -8133,12 +8138,12 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="C55" s="34" t="inlineStr">
+      <c r="C55" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="D55" s="47" t="n">
+      <c r="D55" s="48" t="n">
         <v>181</v>
       </c>
       <c r="E55" s="30" t="n">
@@ -8149,12 +8154,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="G55" s="34" t="inlineStr">
+      <c r="G55" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H55" s="61" t="n">
+      <c r="H55" s="62" t="n">
         <v>-108</v>
       </c>
       <c r="J55" s="30" t="n">
@@ -8165,12 +8170,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="L55" s="34" t="inlineStr">
+      <c r="L55" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M55" s="47" t="n">
+      <c r="M55" s="48" t="n">
         <v>33</v>
       </c>
       <c r="N55" s="30" t="n">
@@ -8181,12 +8186,12 @@
           <t>GS</t>
         </is>
       </c>
-      <c r="P55" s="34" t="inlineStr">
+      <c r="P55" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q55" s="61" t="n">
+      <c r="Q55" s="62" t="n">
         <v>-17</v>
       </c>
     </row>
@@ -8199,12 +8204,12 @@
           <t>NC</t>
         </is>
       </c>
-      <c r="C56" s="34" t="inlineStr">
+      <c r="C56" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D56" s="47" t="n">
+      <c r="D56" s="48" t="n">
         <v>175</v>
       </c>
       <c r="E56" s="30" t="n">
@@ -8215,12 +8220,12 @@
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="G56" s="34" t="inlineStr">
+      <c r="G56" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H56" s="61" t="n">
+      <c r="H56" s="62" t="n">
         <v>-98</v>
       </c>
       <c r="J56" s="30" t="n">
@@ -8231,12 +8236,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L56" s="34" t="inlineStr">
+      <c r="L56" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M56" s="47" t="n">
+      <c r="M56" s="48" t="n">
         <v>32</v>
       </c>
       <c r="N56" s="30" t="n">
@@ -8247,12 +8252,12 @@
           <t>한국콜마</t>
         </is>
       </c>
-      <c r="P56" s="34" t="inlineStr">
+      <c r="P56" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q56" s="61" t="n">
+      <c r="Q56" s="62" t="n">
         <v>-15</v>
       </c>
     </row>
@@ -8265,12 +8270,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="C57" s="34" t="inlineStr">
+      <c r="C57" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D57" s="47" t="n">
+      <c r="D57" s="48" t="n">
         <v>164</v>
       </c>
       <c r="E57" s="30" t="n">
@@ -8281,12 +8286,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G57" s="41" t="inlineStr">
+      <c r="G57" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H57" s="61" t="n">
+      <c r="H57" s="62" t="n">
         <v>-97</v>
       </c>
       <c r="J57" s="30" t="n">
@@ -8297,12 +8302,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L57" s="34" t="inlineStr">
+      <c r="L57" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M57" s="47" t="n">
+      <c r="M57" s="48" t="n">
         <v>30</v>
       </c>
       <c r="N57" s="30" t="n">
@@ -8313,12 +8318,12 @@
           <t>GS건설</t>
         </is>
       </c>
-      <c r="P57" s="34" t="inlineStr">
+      <c r="P57" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="Q57" s="61" t="n">
+      <c r="Q57" s="62" t="n">
         <v>-13</v>
       </c>
     </row>
@@ -8329,61 +8334,61 @@
           <t>F9 기타법인</t>
         </is>
       </c>
-      <c r="E59" s="58" t="inlineStr">
+      <c r="E59" s="59" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="59" t="inlineStr">
+      <c r="A60" s="60" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E60" s="60" t="inlineStr">
+      <c r="E60" s="61" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="45" t="inlineStr">
+      <c r="A61" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B61" s="45" t="inlineStr">
+      <c r="B61" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C61" s="45" t="inlineStr">
+      <c r="C61" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D61" s="45" t="inlineStr">
+      <c r="D61" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E61" s="45" t="inlineStr">
+      <c r="E61" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F61" s="45" t="inlineStr">
+      <c r="F61" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G61" s="45" t="inlineStr">
+      <c r="G61" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H61" s="45" t="inlineStr">
+      <c r="H61" s="46" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -8398,12 +8403,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C62" s="34" t="inlineStr">
+      <c r="C62" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D62" s="47" t="n">
+      <c r="D62" s="48" t="n">
         <v>19833</v>
       </c>
       <c r="E62" s="30" t="n">
@@ -8414,12 +8419,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="G62" s="34" t="inlineStr">
+      <c r="G62" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H62" s="61" t="n">
+      <c r="H62" s="62" t="n">
         <v>-222</v>
       </c>
     </row>
@@ -8432,12 +8437,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C63" s="34" t="inlineStr">
+      <c r="C63" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D63" s="47" t="n">
+      <c r="D63" s="48" t="n">
         <v>10839</v>
       </c>
       <c r="E63" s="30" t="n">
@@ -8448,12 +8453,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G63" s="34" t="inlineStr">
+      <c r="G63" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H63" s="61" t="n">
+      <c r="H63" s="62" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -8466,12 +8471,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="C64" s="34" t="inlineStr">
+      <c r="C64" s="35" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D64" s="47" t="n">
+      <c r="D64" s="48" t="n">
         <v>185</v>
       </c>
       <c r="E64" s="30" t="n">
@@ -8482,12 +8487,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="G64" s="34" t="inlineStr">
+      <c r="G64" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H64" s="61" t="n">
+      <c r="H64" s="62" t="n">
         <v>-32</v>
       </c>
     </row>
@@ -8500,12 +8505,12 @@
           <t>KT&amp;G</t>
         </is>
       </c>
-      <c r="C65" s="34" t="inlineStr">
+      <c r="C65" s="35" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D65" s="47" t="n">
+      <c r="D65" s="48" t="n">
         <v>70</v>
       </c>
       <c r="E65" s="30" t="n">
@@ -8516,12 +8521,12 @@
           <t>코스모로보틱스</t>
         </is>
       </c>
-      <c r="G65" s="41" t="inlineStr">
+      <c r="G65" s="42" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="H65" s="61" t="n">
+      <c r="H65" s="62" t="n">
         <v>-19</v>
       </c>
     </row>
@@ -8534,12 +8539,12 @@
           <t>서진시스템</t>
         </is>
       </c>
-      <c r="C66" s="34" t="inlineStr">
+      <c r="C66" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D66" s="47" t="n">
+      <c r="D66" s="48" t="n">
         <v>54</v>
       </c>
       <c r="E66" s="30" t="n">
@@ -8550,12 +8555,12 @@
           <t>SK텔레콤</t>
         </is>
       </c>
-      <c r="G66" s="34" t="inlineStr">
+      <c r="G66" s="35" t="inlineStr">
         <is>
           <t>통신</t>
         </is>
       </c>
-      <c r="H66" s="61" t="n">
+      <c r="H66" s="62" t="n">
         <v>-18</v>
       </c>
     </row>
@@ -8568,12 +8573,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="C67" s="41" t="inlineStr">
+      <c r="C67" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D67" s="47" t="n">
+      <c r="D67" s="48" t="n">
         <v>40</v>
       </c>
       <c r="E67" s="30" t="n">
@@ -8584,12 +8589,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="G67" s="34" t="inlineStr">
+      <c r="G67" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H67" s="61" t="n">
+      <c r="H67" s="62" t="n">
         <v>-18</v>
       </c>
     </row>
@@ -8602,12 +8607,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="C68" s="34" t="inlineStr">
+      <c r="C68" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D68" s="47" t="n">
+      <c r="D68" s="48" t="n">
         <v>36</v>
       </c>
       <c r="E68" s="30" t="n">
@@ -8618,12 +8623,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="G68" s="34" t="inlineStr">
+      <c r="G68" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H68" s="61" t="n">
+      <c r="H68" s="62" t="n">
         <v>-16</v>
       </c>
     </row>
@@ -8636,12 +8641,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C69" s="34" t="inlineStr">
+      <c r="C69" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D69" s="47" t="n">
+      <c r="D69" s="48" t="n">
         <v>35</v>
       </c>
       <c r="E69" s="30" t="n">
@@ -8652,12 +8657,12 @@
           <t>오킨스전자</t>
         </is>
       </c>
-      <c r="G69" s="34" t="inlineStr">
+      <c r="G69" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H69" s="61" t="n">
+      <c r="H69" s="62" t="n">
         <v>-14</v>
       </c>
     </row>
@@ -8670,12 +8675,12 @@
           <t>파두</t>
         </is>
       </c>
-      <c r="C70" s="34" t="inlineStr">
+      <c r="C70" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D70" s="47" t="n">
+      <c r="D70" s="48" t="n">
         <v>35</v>
       </c>
       <c r="E70" s="30" t="n">
@@ -8686,12 +8691,12 @@
           <t>디아이</t>
         </is>
       </c>
-      <c r="G70" s="41" t="inlineStr">
+      <c r="G70" s="42" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="H70" s="61" t="n">
+      <c r="H70" s="62" t="n">
         <v>-11</v>
       </c>
     </row>
@@ -8704,12 +8709,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C71" s="34" t="inlineStr">
+      <c r="C71" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D71" s="47" t="n">
+      <c r="D71" s="48" t="n">
         <v>31</v>
       </c>
       <c r="E71" s="30" t="n">
@@ -8720,18 +8725,18 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="G71" s="34" t="inlineStr">
+      <c r="G71" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H71" s="61" t="n">
+      <c r="H71" s="62" t="n">
         <v>-11</v>
       </c>
     </row>
     <row r="72"/>
     <row r="73" ht="31" customHeight="1" s="15">
-      <c r="A73" s="62" t="inlineStr">
+      <c r="A73" s="63" t="inlineStr">
         <is>
           <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드, 기타법인=일반법인(자사주 매입 등) (확정 병합분) · 외인+기관=합산 카드와 동일</t>
         </is>
@@ -8849,87 +8854,87 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="46" t="inlineStr">
         <is>
           <t>금액(억)</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="46" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="46" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="46" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="46" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="N4" s="46" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O4" s="45" t="inlineStr">
+      <c r="O4" s="46" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P4" s="45" t="inlineStr">
+      <c r="P4" s="46" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q4" s="45" t="inlineStr">
+      <c r="Q4" s="46" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="R4" s="45" t="inlineStr">
+      <c r="R4" s="46" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="S4" s="45" t="inlineStr">
+      <c r="S4" s="46" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
@@ -8944,15 +8949,15 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D5" s="63" t="n">
+      <c r="D5" s="64" t="n">
         <v>4082</v>
       </c>
-      <c r="E5" s="64" t="n">
+      <c r="E5" s="65" t="n">
         <v>0.03</v>
       </c>
       <c r="G5" s="30" t="n">
@@ -8963,18 +8968,18 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="I5" s="34" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J5" s="47" t="n">
+      <c r="J5" s="48" t="n">
         <v>10005.6</v>
       </c>
-      <c r="K5" s="65" t="n">
+      <c r="K5" s="66" t="n">
         <v>209723.2</v>
       </c>
-      <c r="L5" s="64" t="n">
+      <c r="L5" s="65" t="n">
         <v>1.3</v>
       </c>
       <c r="N5" s="30" t="n">
@@ -8985,18 +8990,18 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="P5" s="34" t="inlineStr">
+      <c r="P5" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q5" s="61" t="n">
+      <c r="Q5" s="62" t="n">
         <v>-434.6</v>
       </c>
-      <c r="R5" s="65" t="n">
+      <c r="R5" s="66" t="n">
         <v>13173.4</v>
       </c>
-      <c r="S5" s="64" t="n">
+      <c r="S5" s="65" t="n">
         <v>3.16</v>
       </c>
     </row>
@@ -9009,15 +9014,15 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="63" t="n">
+      <c r="D6" s="64" t="n">
         <v>2200</v>
       </c>
-      <c r="E6" s="64" t="n">
+      <c r="E6" s="65" t="n">
         <v>0.01</v>
       </c>
       <c r="G6" s="30" t="n">
@@ -9028,18 +9033,18 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="I6" s="34" t="inlineStr">
+      <c r="I6" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J6" s="47" t="n">
+      <c r="J6" s="48" t="n">
         <v>7293.8</v>
       </c>
-      <c r="K6" s="65" t="n">
+      <c r="K6" s="66" t="n">
         <v>233010.9</v>
       </c>
-      <c r="L6" s="64" t="n">
+      <c r="L6" s="65" t="n">
         <v>1.74</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -9050,18 +9055,18 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="P6" s="34" t="inlineStr">
+      <c r="P6" s="35" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q6" s="61" t="n">
+      <c r="Q6" s="62" t="n">
         <v>-352.6</v>
       </c>
-      <c r="R6" s="65" t="n">
+      <c r="R6" s="66" t="n">
         <v>3509</v>
       </c>
-      <c r="S6" s="64" t="n">
+      <c r="S6" s="65" t="n">
         <v>2.09</v>
       </c>
     </row>
@@ -9074,15 +9079,15 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D7" s="63" t="n">
+      <c r="D7" s="64" t="n">
         <v>952</v>
       </c>
-      <c r="E7" s="64" t="n">
+      <c r="E7" s="65" t="n">
         <v>0.18</v>
       </c>
       <c r="G7" s="30" t="n">
@@ -9093,18 +9098,18 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="I7" s="34" t="inlineStr">
+      <c r="I7" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="48" t="n">
         <v>2471.1</v>
       </c>
-      <c r="K7" s="65" t="n">
+      <c r="K7" s="66" t="n">
         <v>52054.5</v>
       </c>
-      <c r="L7" s="64" t="n">
+      <c r="L7" s="65" t="n">
         <v>20.34</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -9115,18 +9120,18 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="P7" s="34" t="inlineStr">
+      <c r="P7" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q7" s="61" t="n">
+      <c r="Q7" s="62" t="n">
         <v>-212.7</v>
       </c>
-      <c r="R7" s="65" t="n">
+      <c r="R7" s="66" t="n">
         <v>9472.299999999999</v>
       </c>
-      <c r="S7" s="64" t="n">
+      <c r="S7" s="65" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -9139,11 +9144,11 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr"/>
-      <c r="D8" s="63" t="n">
+      <c r="C8" s="35" t="inlineStr"/>
+      <c r="D8" s="64" t="n">
         <v>756</v>
       </c>
-      <c r="E8" s="64" t="n">
+      <c r="E8" s="65" t="n">
         <v>0.11</v>
       </c>
       <c r="G8" s="30" t="n">
@@ -9154,18 +9159,18 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="I8" s="41" t="inlineStr">
+      <c r="I8" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="48" t="n">
         <v>1101.6</v>
       </c>
-      <c r="K8" s="65" t="n">
+      <c r="K8" s="66" t="n">
         <v>6040.8</v>
       </c>
-      <c r="L8" s="64" t="n">
+      <c r="L8" s="65" t="n">
         <v>1.76</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -9176,14 +9181,14 @@
           <t>KT&amp;G</t>
         </is>
       </c>
-      <c r="P8" s="34" t="inlineStr"/>
-      <c r="Q8" s="61" t="n">
+      <c r="P8" s="35" t="inlineStr"/>
+      <c r="Q8" s="62" t="n">
         <v>-156.7</v>
       </c>
-      <c r="R8" s="65" t="n">
+      <c r="R8" s="66" t="n">
         <v>2561</v>
       </c>
-      <c r="S8" s="64" t="n">
+      <c r="S8" s="65" t="n">
         <v>1.41</v>
       </c>
     </row>
@@ -9196,15 +9201,15 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D9" s="63" t="n">
+      <c r="D9" s="64" t="n">
         <v>618</v>
       </c>
-      <c r="E9" s="64" t="n">
+      <c r="E9" s="65" t="n">
         <v>0.04</v>
       </c>
       <c r="G9" s="30" t="n">
@@ -9215,18 +9220,18 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="I9" s="34" t="inlineStr">
+      <c r="I9" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J9" s="47" t="n">
+      <c r="J9" s="48" t="n">
         <v>1066.7</v>
       </c>
-      <c r="K9" s="65" t="n">
+      <c r="K9" s="66" t="n">
         <v>11525</v>
       </c>
-      <c r="L9" s="64" t="n">
+      <c r="L9" s="65" t="n">
         <v>16.36</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -9237,18 +9242,18 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="P9" s="34" t="inlineStr">
+      <c r="P9" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q9" s="61" t="n">
+      <c r="Q9" s="62" t="n">
         <v>-153.2</v>
       </c>
-      <c r="R9" s="65" t="n">
+      <c r="R9" s="66" t="n">
         <v>32814.7</v>
       </c>
-      <c r="S9" s="64" t="n">
+      <c r="S9" s="65" t="n">
         <v>3.89</v>
       </c>
     </row>
@@ -9261,15 +9266,15 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D10" s="63" t="n">
+      <c r="D10" s="64" t="n">
         <v>488</v>
       </c>
-      <c r="E10" s="64" t="n">
+      <c r="E10" s="65" t="n">
         <v>0.19</v>
       </c>
       <c r="G10" s="30" t="n">
@@ -9280,18 +9285,18 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="I10" s="34" t="inlineStr">
+      <c r="I10" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J10" s="47" t="n">
+      <c r="J10" s="48" t="n">
         <v>953</v>
       </c>
-      <c r="K10" s="65" t="n">
+      <c r="K10" s="66" t="n">
         <v>37435.2</v>
       </c>
-      <c r="L10" s="64" t="n">
+      <c r="L10" s="65" t="n">
         <v>3.21</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -9302,18 +9307,18 @@
           <t>GS건설</t>
         </is>
       </c>
-      <c r="P10" s="34" t="inlineStr">
+      <c r="P10" s="35" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="Q10" s="61" t="n">
+      <c r="Q10" s="62" t="n">
         <v>-142.1</v>
       </c>
-      <c r="R10" s="65" t="n">
+      <c r="R10" s="66" t="n">
         <v>2301.4</v>
       </c>
-      <c r="S10" s="64" t="n">
+      <c r="S10" s="65" t="n">
         <v>8.16</v>
       </c>
     </row>
@@ -9326,15 +9331,15 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D11" s="63" t="n">
+      <c r="D11" s="64" t="n">
         <v>446</v>
       </c>
-      <c r="E11" s="64" t="n">
+      <c r="E11" s="65" t="n">
         <v>0.08</v>
       </c>
       <c r="G11" s="30" t="n">
@@ -9345,14 +9350,14 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="I11" s="34" t="inlineStr"/>
-      <c r="J11" s="47" t="n">
+      <c r="I11" s="35" t="inlineStr"/>
+      <c r="J11" s="48" t="n">
         <v>869.9</v>
       </c>
-      <c r="K11" s="65" t="n">
+      <c r="K11" s="66" t="n">
         <v>25404.9</v>
       </c>
-      <c r="L11" s="64" t="n">
+      <c r="L11" s="65" t="n">
         <v>1.55</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -9363,18 +9368,18 @@
           <t>POSCO홀딩스</t>
         </is>
       </c>
-      <c r="P11" s="34" t="inlineStr">
+      <c r="P11" s="35" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="Q11" s="61" t="n">
+      <c r="Q11" s="62" t="n">
         <v>-129.3</v>
       </c>
-      <c r="R11" s="65" t="n">
+      <c r="R11" s="66" t="n">
         <v>6987.6</v>
       </c>
-      <c r="S11" s="64" t="n">
+      <c r="S11" s="65" t="n">
         <v>2.88</v>
       </c>
     </row>
@@ -9387,15 +9392,15 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="63" t="n">
+      <c r="D12" s="64" t="n">
         <v>401</v>
       </c>
-      <c r="E12" s="64" t="n">
+      <c r="E12" s="65" t="n">
         <v>0.03</v>
       </c>
       <c r="G12" s="30" t="n">
@@ -9406,18 +9411,18 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="I12" s="34" t="inlineStr">
+      <c r="I12" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="48" t="n">
         <v>860.9</v>
       </c>
-      <c r="K12" s="65" t="n">
+      <c r="K12" s="66" t="n">
         <v>6783.7</v>
       </c>
-      <c r="L12" s="64" t="n">
+      <c r="L12" s="65" t="n">
         <v>22.33</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -9428,18 +9433,18 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="P12" s="34" t="inlineStr">
+      <c r="P12" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q12" s="61" t="n">
+      <c r="Q12" s="62" t="n">
         <v>-104.3</v>
       </c>
-      <c r="R12" s="65" t="n">
+      <c r="R12" s="66" t="n">
         <v>6800.1</v>
       </c>
-      <c r="S12" s="64" t="n">
+      <c r="S12" s="65" t="n">
         <v>1.15</v>
       </c>
     </row>
@@ -9452,15 +9457,15 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D13" s="63" t="n">
+      <c r="D13" s="64" t="n">
         <v>384</v>
       </c>
-      <c r="E13" s="64" t="n">
+      <c r="E13" s="65" t="n">
         <v>0.54</v>
       </c>
       <c r="G13" s="30" t="n">
@@ -9471,18 +9476,18 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="I13" s="34" t="inlineStr">
+      <c r="I13" s="35" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="48" t="n">
         <v>741.7</v>
       </c>
-      <c r="K13" s="65" t="n">
+      <c r="K13" s="66" t="n">
         <v>18198.2</v>
       </c>
-      <c r="L13" s="64" t="n">
+      <c r="L13" s="65" t="n">
         <v>15.75</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -9493,18 +9498,18 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P13" s="34" t="inlineStr">
+      <c r="P13" s="35" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q13" s="61" t="n">
+      <c r="Q13" s="62" t="n">
         <v>-95.3</v>
       </c>
-      <c r="R13" s="65" t="n">
+      <c r="R13" s="66" t="n">
         <v>11020.5</v>
       </c>
-      <c r="S13" s="64" t="n">
+      <c r="S13" s="65" t="n">
         <v>3.79</v>
       </c>
     </row>
@@ -9517,15 +9522,15 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D14" s="63" t="n">
+      <c r="D14" s="64" t="n">
         <v>336</v>
       </c>
-      <c r="E14" s="64" t="n">
+      <c r="E14" s="65" t="n">
         <v>0.24</v>
       </c>
       <c r="G14" s="30" t="n">
@@ -9536,18 +9541,18 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="I14" s="34" t="inlineStr">
+      <c r="I14" s="35" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J14" s="47" t="n">
+      <c r="J14" s="48" t="n">
         <v>662.7</v>
       </c>
-      <c r="K14" s="65" t="n">
+      <c r="K14" s="66" t="n">
         <v>7947.5</v>
       </c>
-      <c r="L14" s="64" t="n">
+      <c r="L14" s="65" t="n">
         <v>14</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -9558,24 +9563,24 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="P14" s="34" t="inlineStr">
+      <c r="P14" s="35" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q14" s="61" t="n">
+      <c r="Q14" s="62" t="n">
         <v>-91.3</v>
       </c>
-      <c r="R14" s="65" t="n">
+      <c r="R14" s="66" t="n">
         <v>2623.4</v>
       </c>
-      <c r="S14" s="64" t="n">
+      <c r="S14" s="65" t="n">
         <v>2.82</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16" ht="31" customHeight="1" s="15">
-      <c r="A16" s="62" t="inlineStr">
+      <c r="A16" s="63" t="inlineStr">
         <is>
           <t>랭킹 유니버스(순매수 상위 30 등재 종목) 한정 · 대차 증감=전월말 대비 최신 잔고 · 시총대비(%)=공매도 누적 금액÷시가총액, 대차잔고÷시가총액(KIS 마스터 시총(주 1회 갱신))</t>
         </is>
@@ -9668,77 +9673,77 @@
       <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="46" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="46" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="46" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="46" t="inlineStr">
         <is>
           <t>기관(합)</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="46" t="inlineStr">
         <is>
           <t>외인+기관</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="46" t="inlineStr">
         <is>
           <t>금융투자</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="46" t="inlineStr">
         <is>
           <t>투신(사모)</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="46" t="inlineStr">
         <is>
           <t>연기금</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="46" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="M4" s="45" t="inlineStr">
+      <c r="M4" s="46" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="N4" s="46" t="inlineStr">
         <is>
           <t>기타법인</t>
         </is>
       </c>
-      <c r="O4" s="45" t="inlineStr">
+      <c r="O4" s="46" t="inlineStr">
         <is>
           <t>신호</t>
         </is>
@@ -9750,46 +9755,46 @@
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="B5" s="66" t="n">
+      <c r="B5" s="67" t="n">
         <v>35.11</v>
       </c>
-      <c r="C5" s="66" t="n">
+      <c r="C5" s="67" t="n">
         <v>33.36</v>
       </c>
-      <c r="D5" s="66" t="n">
+      <c r="D5" s="67" t="n">
         <v>2.71</v>
       </c>
-      <c r="E5" s="66" t="n">
+      <c r="E5" s="67" t="n">
         <v>6.29</v>
       </c>
-      <c r="F5" s="67" t="n">
+      <c r="F5" s="68" t="n">
         <v>151</v>
       </c>
-      <c r="G5" s="68" t="n">
+      <c r="G5" s="69" t="n">
         <v>-57</v>
       </c>
-      <c r="H5" s="67" t="n">
+      <c r="H5" s="68" t="n">
         <v>95</v>
       </c>
-      <c r="I5" s="67" t="n">
+      <c r="I5" s="68" t="n">
         <v>7</v>
       </c>
-      <c r="J5" s="68" t="n">
+      <c r="J5" s="69" t="n">
         <v>-37</v>
       </c>
-      <c r="K5" s="68" t="n">
+      <c r="K5" s="69" t="n">
         <v>-29</v>
       </c>
-      <c r="L5" s="67" t="n">
+      <c r="L5" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="M5" s="68" t="n">
+      <c r="M5" s="69" t="n">
         <v>-88</v>
       </c>
-      <c r="N5" s="68" t="n">
+      <c r="N5" s="69" t="n">
         <v>-7</v>
       </c>
-      <c r="O5" s="59" t="inlineStr">
+      <c r="O5" s="60" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -9801,43 +9806,43 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="B6" s="66" t="n">
+      <c r="B6" s="67" t="n">
         <v>3.11</v>
       </c>
-      <c r="C6" s="69" t="n">
+      <c r="C6" s="70" t="n">
         <v>-15.24</v>
       </c>
-      <c r="D6" s="66" t="n">
+      <c r="D6" s="67" t="n">
         <v>1.7</v>
       </c>
-      <c r="E6" s="66" t="n">
+      <c r="E6" s="67" t="n">
         <v>3.33</v>
       </c>
-      <c r="F6" s="68" t="n">
+      <c r="F6" s="69" t="n">
         <v>-498</v>
       </c>
-      <c r="G6" s="67" t="n">
+      <c r="G6" s="68" t="n">
         <v>545</v>
       </c>
-      <c r="H6" s="67" t="n">
+      <c r="H6" s="68" t="n">
         <v>46</v>
       </c>
-      <c r="I6" s="67" t="n">
+      <c r="I6" s="68" t="n">
         <v>119</v>
       </c>
-      <c r="J6" s="67" t="n">
+      <c r="J6" s="68" t="n">
         <v>233</v>
       </c>
-      <c r="K6" s="67" t="n">
+      <c r="K6" s="68" t="n">
         <v>118</v>
       </c>
-      <c r="L6" s="67" t="n">
+      <c r="L6" s="68" t="n">
         <v>74</v>
       </c>
-      <c r="M6" s="68" t="n">
+      <c r="M6" s="69" t="n">
         <v>-75</v>
       </c>
-      <c r="N6" s="67" t="n">
+      <c r="N6" s="68" t="n">
         <v>28</v>
       </c>
       <c r="O6" s="30" t="inlineStr"/>
@@ -9848,43 +9853,43 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="B7" s="66" t="n">
+      <c r="B7" s="67" t="n">
         <v>123.01</v>
       </c>
-      <c r="C7" s="66" t="n">
+      <c r="C7" s="67" t="n">
         <v>69.20999999999999</v>
       </c>
-      <c r="D7" s="69" t="n">
+      <c r="D7" s="70" t="n">
         <v>-9</v>
       </c>
-      <c r="E7" s="66" t="n">
+      <c r="E7" s="67" t="n">
         <v>3.25</v>
       </c>
-      <c r="F7" s="68" t="n">
+      <c r="F7" s="69" t="n">
         <v>-2315</v>
       </c>
-      <c r="G7" s="67" t="n">
+      <c r="G7" s="68" t="n">
         <v>5958</v>
       </c>
-      <c r="H7" s="67" t="n">
+      <c r="H7" s="68" t="n">
         <v>3643</v>
       </c>
-      <c r="I7" s="67" t="n">
+      <c r="I7" s="68" t="n">
         <v>2049</v>
       </c>
-      <c r="J7" s="67" t="n">
+      <c r="J7" s="68" t="n">
         <v>1311</v>
       </c>
-      <c r="K7" s="67" t="n">
+      <c r="K7" s="68" t="n">
         <v>2044</v>
       </c>
-      <c r="L7" s="67" t="n">
+      <c r="L7" s="68" t="n">
         <v>524</v>
       </c>
-      <c r="M7" s="68" t="n">
+      <c r="M7" s="69" t="n">
         <v>-34226</v>
       </c>
-      <c r="N7" s="67" t="n">
+      <c r="N7" s="68" t="n">
         <v>30583</v>
       </c>
       <c r="O7" s="30" t="inlineStr"/>
@@ -9895,43 +9900,43 @@
           <t>제조</t>
         </is>
       </c>
-      <c r="B8" s="66" t="n">
+      <c r="B8" s="67" t="n">
         <v>77.8</v>
       </c>
-      <c r="C8" s="66" t="n">
+      <c r="C8" s="67" t="n">
         <v>41.7</v>
       </c>
-      <c r="D8" s="69" t="n">
+      <c r="D8" s="70" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="E8" s="66" t="n">
+      <c r="E8" s="67" t="n">
         <v>2.93</v>
       </c>
-      <c r="F8" s="68" t="n">
+      <c r="F8" s="69" t="n">
         <v>-3615</v>
       </c>
-      <c r="G8" s="67" t="n">
+      <c r="G8" s="68" t="n">
         <v>6335</v>
       </c>
-      <c r="H8" s="67" t="n">
+      <c r="H8" s="68" t="n">
         <v>2720</v>
       </c>
-      <c r="I8" s="67" t="n">
+      <c r="I8" s="68" t="n">
         <v>3011</v>
       </c>
-      <c r="J8" s="67" t="n">
+      <c r="J8" s="68" t="n">
         <v>1186</v>
       </c>
-      <c r="K8" s="67" t="n">
+      <c r="K8" s="68" t="n">
         <v>1596</v>
       </c>
-      <c r="L8" s="67" t="n">
+      <c r="L8" s="68" t="n">
         <v>483</v>
       </c>
-      <c r="M8" s="68" t="n">
+      <c r="M8" s="69" t="n">
         <v>-33800</v>
       </c>
-      <c r="N8" s="67" t="n">
+      <c r="N8" s="68" t="n">
         <v>31080</v>
       </c>
       <c r="O8" s="30" t="inlineStr"/>
@@ -9942,46 +9947,46 @@
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="B9" s="69" t="n">
+      <c r="B9" s="70" t="n">
         <v>-3.33</v>
       </c>
-      <c r="C9" s="69" t="n">
+      <c r="C9" s="70" t="n">
         <v>-1.43</v>
       </c>
-      <c r="D9" s="69" t="n">
+      <c r="D9" s="70" t="n">
         <v>-3.05</v>
       </c>
-      <c r="E9" s="66" t="n">
+      <c r="E9" s="67" t="n">
         <v>2.48</v>
       </c>
-      <c r="F9" s="67" t="n">
+      <c r="F9" s="68" t="n">
         <v>7</v>
       </c>
-      <c r="G9" s="68" t="n">
+      <c r="G9" s="69" t="n">
         <v>-1</v>
       </c>
-      <c r="H9" s="67" t="n">
+      <c r="H9" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I9" s="67" t="n">
+      <c r="I9" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="67" t="n">
+      <c r="J9" s="68" t="n">
         <v>11</v>
       </c>
-      <c r="K9" s="68" t="n">
+      <c r="K9" s="69" t="n">
         <v>-13</v>
       </c>
-      <c r="L9" s="68" t="n">
+      <c r="L9" s="69" t="n">
         <v>-2</v>
       </c>
-      <c r="M9" s="68" t="n">
+      <c r="M9" s="69" t="n">
         <v>-31</v>
       </c>
-      <c r="N9" s="67" t="n">
+      <c r="N9" s="68" t="n">
         <v>25</v>
       </c>
-      <c r="O9" s="70" t="inlineStr">
+      <c r="O9" s="71" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -9993,43 +9998,43 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="B10" s="66" t="n">
+      <c r="B10" s="67" t="n">
         <v>15.09</v>
       </c>
-      <c r="C10" s="69" t="n">
+      <c r="C10" s="70" t="n">
         <v>-31.98</v>
       </c>
-      <c r="D10" s="69" t="n">
+      <c r="D10" s="70" t="n">
         <v>-14.87</v>
       </c>
-      <c r="E10" s="66" t="n">
+      <c r="E10" s="67" t="n">
         <v>2.41</v>
       </c>
-      <c r="F10" s="67" t="n">
+      <c r="F10" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="G10" s="67" t="n">
+      <c r="G10" s="68" t="n">
         <v>191</v>
       </c>
-      <c r="H10" s="67" t="n">
+      <c r="H10" s="68" t="n">
         <v>217</v>
       </c>
-      <c r="I10" s="67" t="n">
+      <c r="I10" s="68" t="n">
         <v>63</v>
       </c>
-      <c r="J10" s="68" t="n">
+      <c r="J10" s="69" t="n">
         <v>-7</v>
       </c>
-      <c r="K10" s="67" t="n">
+      <c r="K10" s="68" t="n">
         <v>95</v>
       </c>
-      <c r="L10" s="67" t="n">
+      <c r="L10" s="68" t="n">
         <v>9</v>
       </c>
-      <c r="M10" s="68" t="n">
+      <c r="M10" s="69" t="n">
         <v>-225</v>
       </c>
-      <c r="N10" s="67" t="n">
+      <c r="N10" s="68" t="n">
         <v>7</v>
       </c>
       <c r="O10" s="30" t="inlineStr"/>
@@ -10040,46 +10045,46 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="B11" s="66" t="n">
+      <c r="B11" s="67" t="n">
         <v>20.47</v>
       </c>
-      <c r="C11" s="66" t="n">
+      <c r="C11" s="67" t="n">
         <v>7.05</v>
       </c>
-      <c r="D11" s="66" t="n">
+      <c r="D11" s="67" t="n">
         <v>11.01</v>
       </c>
-      <c r="E11" s="66" t="n">
+      <c r="E11" s="67" t="n">
         <v>2.16</v>
       </c>
-      <c r="F11" s="67" t="n">
+      <c r="F11" s="68" t="n">
         <v>739</v>
       </c>
-      <c r="G11" s="67" t="n">
+      <c r="G11" s="68" t="n">
         <v>129</v>
       </c>
-      <c r="H11" s="67" t="n">
+      <c r="H11" s="68" t="n">
         <v>868</v>
       </c>
-      <c r="I11" s="67" t="n">
+      <c r="I11" s="68" t="n">
         <v>237</v>
       </c>
-      <c r="J11" s="67" t="n">
+      <c r="J11" s="68" t="n">
         <v>80</v>
       </c>
-      <c r="K11" s="68" t="n">
+      <c r="K11" s="69" t="n">
         <v>-149</v>
       </c>
-      <c r="L11" s="68" t="n">
+      <c r="L11" s="69" t="n">
         <v>-59</v>
       </c>
-      <c r="M11" s="68" t="n">
+      <c r="M11" s="69" t="n">
         <v>-924</v>
       </c>
-      <c r="N11" s="67" t="n">
+      <c r="N11" s="68" t="n">
         <v>56</v>
       </c>
-      <c r="O11" s="59" t="inlineStr">
+      <c r="O11" s="60" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10091,46 +10096,46 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="B12" s="69" t="n">
+      <c r="B12" s="70" t="n">
         <v>-5.42</v>
       </c>
-      <c r="C12" s="69" t="n">
+      <c r="C12" s="70" t="n">
         <v>-22.35</v>
       </c>
-      <c r="D12" s="69" t="n">
+      <c r="D12" s="70" t="n">
         <v>-21.62</v>
       </c>
-      <c r="E12" s="66" t="n">
+      <c r="E12" s="67" t="n">
         <v>1.94</v>
       </c>
-      <c r="F12" s="68" t="n">
+      <c r="F12" s="69" t="n">
         <v>-780</v>
       </c>
-      <c r="G12" s="68" t="n">
+      <c r="G12" s="69" t="n">
         <v>-327</v>
       </c>
-      <c r="H12" s="68" t="n">
+      <c r="H12" s="69" t="n">
         <v>-1106</v>
       </c>
-      <c r="I12" s="67" t="n">
+      <c r="I12" s="68" t="n">
         <v>158</v>
       </c>
-      <c r="J12" s="67" t="n">
+      <c r="J12" s="68" t="n">
         <v>52</v>
       </c>
-      <c r="K12" s="68" t="n">
+      <c r="K12" s="69" t="n">
         <v>-533</v>
       </c>
-      <c r="L12" s="68" t="n">
+      <c r="L12" s="69" t="n">
         <v>-11</v>
       </c>
-      <c r="M12" s="67" t="n">
+      <c r="M12" s="68" t="n">
         <v>1069</v>
       </c>
-      <c r="N12" s="67" t="n">
+      <c r="N12" s="68" t="n">
         <v>38</v>
       </c>
-      <c r="O12" s="60" t="inlineStr">
+      <c r="O12" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10142,46 +10147,46 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="B13" s="69" t="n">
+      <c r="B13" s="70" t="n">
         <v>-13.29</v>
       </c>
-      <c r="C13" s="69" t="n">
+      <c r="C13" s="70" t="n">
         <v>-0.96</v>
       </c>
-      <c r="D13" s="69" t="n">
+      <c r="D13" s="70" t="n">
         <v>-5.56</v>
       </c>
-      <c r="E13" s="66" t="n">
+      <c r="E13" s="67" t="n">
         <v>1.5</v>
       </c>
-      <c r="F13" s="68" t="n">
+      <c r="F13" s="69" t="n">
         <v>-481</v>
       </c>
-      <c r="G13" s="68" t="n">
+      <c r="G13" s="69" t="n">
         <v>-220</v>
       </c>
-      <c r="H13" s="68" t="n">
+      <c r="H13" s="69" t="n">
         <v>-702</v>
       </c>
-      <c r="I13" s="67" t="n">
+      <c r="I13" s="68" t="n">
         <v>99</v>
       </c>
-      <c r="J13" s="67" t="n">
+      <c r="J13" s="68" t="n">
         <v>131</v>
       </c>
-      <c r="K13" s="68" t="n">
+      <c r="K13" s="69" t="n">
         <v>-413</v>
       </c>
-      <c r="L13" s="68" t="n">
+      <c r="L13" s="69" t="n">
         <v>-36</v>
       </c>
-      <c r="M13" s="67" t="n">
+      <c r="M13" s="68" t="n">
         <v>710</v>
       </c>
-      <c r="N13" s="68" t="n">
+      <c r="N13" s="69" t="n">
         <v>-8</v>
       </c>
-      <c r="O13" s="60" t="inlineStr">
+      <c r="O13" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10193,43 +10198,43 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="B14" s="66" t="n">
+      <c r="B14" s="67" t="n">
         <v>14.8</v>
       </c>
-      <c r="C14" s="69" t="n">
+      <c r="C14" s="70" t="n">
         <v>-9.01</v>
       </c>
-      <c r="D14" s="69" t="n">
+      <c r="D14" s="70" t="n">
         <v>-0.63</v>
       </c>
-      <c r="E14" s="66" t="n">
+      <c r="E14" s="67" t="n">
         <v>1.48</v>
       </c>
-      <c r="F14" s="68" t="n">
+      <c r="F14" s="69" t="n">
         <v>-296</v>
       </c>
-      <c r="G14" s="68" t="n">
+      <c r="G14" s="69" t="n">
         <v>-99</v>
       </c>
-      <c r="H14" s="68" t="n">
+      <c r="H14" s="69" t="n">
         <v>-394</v>
       </c>
-      <c r="I14" s="67" t="n">
+      <c r="I14" s="68" t="n">
         <v>236</v>
       </c>
-      <c r="J14" s="68" t="n">
+      <c r="J14" s="69" t="n">
         <v>-411</v>
       </c>
-      <c r="K14" s="67" t="n">
+      <c r="K14" s="68" t="n">
         <v>119</v>
       </c>
-      <c r="L14" s="68" t="n">
+      <c r="L14" s="69" t="n">
         <v>-42</v>
       </c>
-      <c r="M14" s="67" t="n">
+      <c r="M14" s="68" t="n">
         <v>390</v>
       </c>
-      <c r="N14" s="67" t="n">
+      <c r="N14" s="68" t="n">
         <v>5</v>
       </c>
       <c r="O14" s="30" t="inlineStr"/>
@@ -10240,43 +10245,43 @@
           <t>통신</t>
         </is>
       </c>
-      <c r="B15" s="66" t="n">
+      <c r="B15" s="67" t="n">
         <v>24.89</v>
       </c>
-      <c r="C15" s="69" t="n">
+      <c r="C15" s="70" t="n">
         <v>-0.14</v>
       </c>
-      <c r="D15" s="69" t="n">
+      <c r="D15" s="70" t="n">
         <v>-0.73</v>
       </c>
-      <c r="E15" s="66" t="n">
+      <c r="E15" s="67" t="n">
         <v>1.34</v>
       </c>
-      <c r="F15" s="67" t="n">
+      <c r="F15" s="68" t="n">
         <v>138</v>
       </c>
-      <c r="G15" s="68" t="n">
+      <c r="G15" s="69" t="n">
         <v>-82</v>
       </c>
-      <c r="H15" s="67" t="n">
+      <c r="H15" s="68" t="n">
         <v>55</v>
       </c>
-      <c r="I15" s="68" t="n">
+      <c r="I15" s="69" t="n">
         <v>-8</v>
       </c>
-      <c r="J15" s="68" t="n">
+      <c r="J15" s="69" t="n">
         <v>-5</v>
       </c>
-      <c r="K15" s="68" t="n">
+      <c r="K15" s="69" t="n">
         <v>-61</v>
       </c>
-      <c r="L15" s="68" t="n">
+      <c r="L15" s="69" t="n">
         <v>-7</v>
       </c>
-      <c r="M15" s="68" t="n">
+      <c r="M15" s="69" t="n">
         <v>-40</v>
       </c>
-      <c r="N15" s="68" t="n">
+      <c r="N15" s="69" t="n">
         <v>-15</v>
       </c>
       <c r="O15" s="30" t="inlineStr"/>
@@ -10287,46 +10292,46 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="B16" s="66" t="n">
+      <c r="B16" s="67" t="n">
         <v>11.39</v>
       </c>
-      <c r="C16" s="66" t="n">
+      <c r="C16" s="67" t="n">
         <v>4.26</v>
       </c>
-      <c r="D16" s="66" t="n">
+      <c r="D16" s="67" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="E16" s="66" t="n">
+      <c r="E16" s="67" t="n">
         <v>1.21</v>
       </c>
-      <c r="F16" s="67" t="n">
+      <c r="F16" s="68" t="n">
         <v>73</v>
       </c>
-      <c r="G16" s="67" t="n">
+      <c r="G16" s="68" t="n">
         <v>115</v>
       </c>
-      <c r="H16" s="67" t="n">
+      <c r="H16" s="68" t="n">
         <v>188</v>
       </c>
-      <c r="I16" s="68" t="n">
+      <c r="I16" s="69" t="n">
         <v>-4</v>
       </c>
-      <c r="J16" s="67" t="n">
+      <c r="J16" s="68" t="n">
         <v>117</v>
       </c>
-      <c r="K16" s="67" t="n">
+      <c r="K16" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="L16" s="68" t="n">
+      <c r="L16" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="M16" s="68" t="n">
+      <c r="M16" s="69" t="n">
         <v>-212</v>
       </c>
-      <c r="N16" s="67" t="n">
+      <c r="N16" s="68" t="n">
         <v>24</v>
       </c>
-      <c r="O16" s="59" t="inlineStr">
+      <c r="O16" s="60" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10338,43 +10343,43 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="B17" s="66" t="n">
+      <c r="B17" s="67" t="n">
         <v>53.83</v>
       </c>
-      <c r="C17" s="66" t="n">
+      <c r="C17" s="67" t="n">
         <v>29.06</v>
       </c>
-      <c r="D17" s="69" t="n">
+      <c r="D17" s="70" t="n">
         <v>-8.49</v>
       </c>
-      <c r="E17" s="66" t="n">
+      <c r="E17" s="67" t="n">
         <v>0.88</v>
       </c>
-      <c r="F17" s="67" t="n">
+      <c r="F17" s="68" t="n">
         <v>61</v>
       </c>
-      <c r="G17" s="68" t="n">
+      <c r="G17" s="69" t="n">
         <v>-60</v>
       </c>
-      <c r="H17" s="71" t="n">
+      <c r="H17" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="67" t="n">
+      <c r="I17" s="68" t="n">
         <v>138</v>
       </c>
-      <c r="J17" s="68" t="n">
+      <c r="J17" s="69" t="n">
         <v>-21</v>
       </c>
-      <c r="K17" s="68" t="n">
+      <c r="K17" s="69" t="n">
         <v>-170</v>
       </c>
-      <c r="L17" s="68" t="n">
+      <c r="L17" s="69" t="n">
         <v>-7</v>
       </c>
-      <c r="M17" s="68" t="n">
+      <c r="M17" s="69" t="n">
         <v>-20</v>
       </c>
-      <c r="N17" s="67" t="n">
+      <c r="N17" s="68" t="n">
         <v>20</v>
       </c>
       <c r="O17" s="30" t="inlineStr"/>
@@ -10385,43 +10390,43 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="B18" s="66" t="n">
+      <c r="B18" s="67" t="n">
         <v>23.6</v>
       </c>
-      <c r="C18" s="66" t="n">
+      <c r="C18" s="67" t="n">
         <v>7.68</v>
       </c>
-      <c r="D18" s="69" t="n">
+      <c r="D18" s="70" t="n">
         <v>-15</v>
       </c>
-      <c r="E18" s="66" t="n">
+      <c r="E18" s="67" t="n">
         <v>0.79</v>
       </c>
-      <c r="F18" s="68" t="n">
+      <c r="F18" s="69" t="n">
         <v>-18</v>
       </c>
-      <c r="G18" s="68" t="n">
+      <c r="G18" s="69" t="n">
         <v>-94</v>
       </c>
-      <c r="H18" s="68" t="n">
+      <c r="H18" s="69" t="n">
         <v>-112</v>
       </c>
-      <c r="I18" s="67" t="n">
+      <c r="I18" s="68" t="n">
         <v>103</v>
       </c>
-      <c r="J18" s="68" t="n">
+      <c r="J18" s="69" t="n">
         <v>-136</v>
       </c>
-      <c r="K18" s="68" t="n">
+      <c r="K18" s="69" t="n">
         <v>-52</v>
       </c>
-      <c r="L18" s="68" t="n">
+      <c r="L18" s="69" t="n">
         <v>-5</v>
       </c>
-      <c r="M18" s="67" t="n">
+      <c r="M18" s="68" t="n">
         <v>92</v>
       </c>
-      <c r="N18" s="67" t="n">
+      <c r="N18" s="68" t="n">
         <v>19</v>
       </c>
       <c r="O18" s="30" t="inlineStr"/>
@@ -10432,46 +10437,46 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="B19" s="66" t="n">
+      <c r="B19" s="67" t="n">
         <v>5.92</v>
       </c>
-      <c r="C19" s="66" t="n">
+      <c r="C19" s="67" t="n">
         <v>4.56</v>
       </c>
-      <c r="D19" s="66" t="n">
+      <c r="D19" s="67" t="n">
         <v>2.71</v>
       </c>
-      <c r="E19" s="66" t="n">
+      <c r="E19" s="67" t="n">
         <v>0.78</v>
       </c>
-      <c r="F19" s="68" t="n">
+      <c r="F19" s="69" t="n">
         <v>-157</v>
       </c>
-      <c r="G19" s="68" t="n">
+      <c r="G19" s="69" t="n">
         <v>-20</v>
       </c>
-      <c r="H19" s="68" t="n">
+      <c r="H19" s="69" t="n">
         <v>-178</v>
       </c>
-      <c r="I19" s="67" t="n">
+      <c r="I19" s="68" t="n">
         <v>61</v>
       </c>
-      <c r="J19" s="68" t="n">
+      <c r="J19" s="69" t="n">
         <v>-61</v>
       </c>
-      <c r="K19" s="68" t="n">
+      <c r="K19" s="69" t="n">
         <v>-6</v>
       </c>
-      <c r="L19" s="68" t="n">
+      <c r="L19" s="69" t="n">
         <v>-14</v>
       </c>
-      <c r="M19" s="67" t="n">
+      <c r="M19" s="68" t="n">
         <v>146</v>
       </c>
-      <c r="N19" s="67" t="n">
+      <c r="N19" s="68" t="n">
         <v>32</v>
       </c>
-      <c r="O19" s="72" t="inlineStr">
+      <c r="O19" s="73" t="inlineStr">
         <is>
           <t>수급이탈</t>
         </is>
@@ -10483,46 +10488,46 @@
           <t>전기·가스</t>
         </is>
       </c>
-      <c r="B20" s="69" t="n">
+      <c r="B20" s="70" t="n">
         <v>-29.36</v>
       </c>
-      <c r="C20" s="69" t="n">
+      <c r="C20" s="70" t="n">
         <v>-22</v>
       </c>
-      <c r="D20" s="69" t="n">
+      <c r="D20" s="70" t="n">
         <v>-15.23</v>
       </c>
-      <c r="E20" s="66" t="n">
+      <c r="E20" s="67" t="n">
         <v>0.7</v>
       </c>
-      <c r="F20" s="68" t="n">
+      <c r="F20" s="69" t="n">
         <v>-67</v>
       </c>
-      <c r="G20" s="68" t="n">
+      <c r="G20" s="69" t="n">
         <v>-51</v>
       </c>
-      <c r="H20" s="68" t="n">
+      <c r="H20" s="69" t="n">
         <v>-118</v>
       </c>
-      <c r="I20" s="68" t="n">
+      <c r="I20" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="J20" s="67" t="n">
+      <c r="J20" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K20" s="68" t="n">
+      <c r="K20" s="69" t="n">
         <v>-51</v>
       </c>
-      <c r="L20" s="68" t="n">
+      <c r="L20" s="69" t="n">
         <v>-1</v>
       </c>
-      <c r="M20" s="67" t="n">
+      <c r="M20" s="68" t="n">
         <v>113</v>
       </c>
-      <c r="N20" s="67" t="n">
+      <c r="N20" s="68" t="n">
         <v>5</v>
       </c>
-      <c r="O20" s="60" t="inlineStr">
+      <c r="O20" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10534,46 +10539,46 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="B21" s="66" t="n">
+      <c r="B21" s="67" t="n">
         <v>42.04</v>
       </c>
-      <c r="C21" s="66" t="n">
+      <c r="C21" s="67" t="n">
         <v>21.12</v>
       </c>
-      <c r="D21" s="69" t="n">
+      <c r="D21" s="70" t="n">
         <v>-8.58</v>
       </c>
-      <c r="E21" s="66" t="n">
+      <c r="E21" s="67" t="n">
         <v>0.47</v>
       </c>
-      <c r="F21" s="67" t="n">
+      <c r="F21" s="68" t="n">
         <v>3983</v>
       </c>
-      <c r="G21" s="67" t="n">
+      <c r="G21" s="68" t="n">
         <v>1778</v>
       </c>
-      <c r="H21" s="67" t="n">
+      <c r="H21" s="68" t="n">
         <v>5761</v>
       </c>
-      <c r="I21" s="67" t="n">
+      <c r="I21" s="68" t="n">
         <v>1893</v>
       </c>
-      <c r="J21" s="68" t="n">
+      <c r="J21" s="69" t="n">
         <v>-465</v>
       </c>
-      <c r="K21" s="67" t="n">
+      <c r="K21" s="68" t="n">
         <v>130</v>
       </c>
-      <c r="L21" s="68" t="n">
+      <c r="L21" s="69" t="n">
         <v>-79</v>
       </c>
-      <c r="M21" s="67" t="n">
+      <c r="M21" s="68" t="n">
         <v>895</v>
       </c>
-      <c r="N21" s="68" t="n">
+      <c r="N21" s="69" t="n">
         <v>-6656</v>
       </c>
-      <c r="O21" s="59" t="inlineStr">
+      <c r="O21" s="60" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10585,43 +10590,43 @@
           <t>종이·목재</t>
         </is>
       </c>
-      <c r="B22" s="69" t="n">
+      <c r="B22" s="70" t="n">
         <v>-22.75</v>
       </c>
-      <c r="C22" s="69" t="n">
+      <c r="C22" s="70" t="n">
         <v>-23.09</v>
       </c>
-      <c r="D22" s="69" t="n">
+      <c r="D22" s="70" t="n">
         <v>-0.16</v>
       </c>
-      <c r="E22" s="66" t="n">
+      <c r="E22" s="67" t="n">
         <v>0.38</v>
       </c>
-      <c r="F22" s="68" t="n">
+      <c r="F22" s="69" t="n">
         <v>-2</v>
       </c>
-      <c r="G22" s="67" t="n">
+      <c r="G22" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="68" t="n">
+      <c r="H22" s="69" t="n">
         <v>-1</v>
       </c>
-      <c r="I22" s="67" t="n">
+      <c r="I22" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="67" t="n">
+      <c r="J22" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="K22" s="71" t="n">
+      <c r="K22" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="71" t="n">
+      <c r="L22" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="67" t="n">
+      <c r="M22" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="71" t="n">
+      <c r="N22" s="72" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="30" t="inlineStr"/>
@@ -10632,46 +10637,46 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="B23" s="69" t="n">
+      <c r="B23" s="70" t="n">
         <v>-15.08</v>
       </c>
-      <c r="C23" s="69" t="n">
+      <c r="C23" s="70" t="n">
         <v>-11.38</v>
       </c>
-      <c r="D23" s="69" t="n">
+      <c r="D23" s="70" t="n">
         <v>-0.23</v>
       </c>
-      <c r="E23" s="66" t="n">
+      <c r="E23" s="67" t="n">
         <v>0.35</v>
       </c>
-      <c r="F23" s="68" t="n">
+      <c r="F23" s="69" t="n">
         <v>-302</v>
       </c>
-      <c r="G23" s="67" t="n">
+      <c r="G23" s="68" t="n">
         <v>145</v>
       </c>
-      <c r="H23" s="68" t="n">
+      <c r="H23" s="69" t="n">
         <v>-157</v>
       </c>
-      <c r="I23" s="67" t="n">
+      <c r="I23" s="68" t="n">
         <v>138</v>
       </c>
-      <c r="J23" s="68" t="n">
+      <c r="J23" s="69" t="n">
         <v>-43</v>
       </c>
-      <c r="K23" s="67" t="n">
+      <c r="K23" s="68" t="n">
         <v>33</v>
       </c>
-      <c r="L23" s="67" t="n">
+      <c r="L23" s="68" t="n">
         <v>18</v>
       </c>
-      <c r="M23" s="68" t="n">
+      <c r="M23" s="69" t="n">
         <v>-44</v>
       </c>
-      <c r="N23" s="67" t="n">
+      <c r="N23" s="68" t="n">
         <v>201</v>
       </c>
-      <c r="O23" s="60" t="inlineStr">
+      <c r="O23" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10683,43 +10688,43 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="B24" s="69" t="n">
+      <c r="B24" s="70" t="n">
         <v>-10.34</v>
       </c>
-      <c r="C24" s="69" t="n">
+      <c r="C24" s="70" t="n">
         <v>-12.79</v>
       </c>
-      <c r="D24" s="66" t="n">
+      <c r="D24" s="67" t="n">
         <v>3.41</v>
       </c>
-      <c r="E24" s="66" t="n">
+      <c r="E24" s="67" t="n">
         <v>0.29</v>
       </c>
-      <c r="F24" s="68" t="n">
+      <c r="F24" s="69" t="n">
         <v>-23</v>
       </c>
-      <c r="G24" s="67" t="n">
+      <c r="G24" s="68" t="n">
         <v>32</v>
       </c>
-      <c r="H24" s="67" t="n">
+      <c r="H24" s="68" t="n">
         <v>9</v>
       </c>
-      <c r="I24" s="67" t="n">
+      <c r="I24" s="68" t="n">
         <v>39</v>
       </c>
-      <c r="J24" s="68" t="n">
+      <c r="J24" s="69" t="n">
         <v>-11</v>
       </c>
-      <c r="K24" s="67" t="n">
+      <c r="K24" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="L24" s="68" t="n">
+      <c r="L24" s="69" t="n">
         <v>-4</v>
       </c>
-      <c r="M24" s="68" t="n">
+      <c r="M24" s="69" t="n">
         <v>-8</v>
       </c>
-      <c r="N24" s="68" t="n">
+      <c r="N24" s="69" t="n">
         <v>-1</v>
       </c>
       <c r="O24" s="30" t="inlineStr"/>
@@ -10730,46 +10735,46 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="B25" s="66" t="n">
+      <c r="B25" s="67" t="n">
         <v>3.36</v>
       </c>
-      <c r="C25" s="69" t="n">
+      <c r="C25" s="70" t="n">
         <v>-0.49</v>
       </c>
-      <c r="D25" s="69" t="n">
+      <c r="D25" s="70" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E25" s="69" t="n">
+      <c r="E25" s="70" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F25" s="68" t="n">
+      <c r="F25" s="69" t="n">
         <v>-317</v>
       </c>
-      <c r="G25" s="67" t="n">
+      <c r="G25" s="68" t="n">
         <v>41</v>
       </c>
-      <c r="H25" s="68" t="n">
+      <c r="H25" s="69" t="n">
         <v>-276</v>
       </c>
-      <c r="I25" s="67" t="n">
+      <c r="I25" s="68" t="n">
         <v>61</v>
       </c>
-      <c r="J25" s="68" t="n">
+      <c r="J25" s="69" t="n">
         <v>-11</v>
       </c>
-      <c r="K25" s="67" t="n">
+      <c r="K25" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="L25" s="68" t="n">
+      <c r="L25" s="69" t="n">
         <v>-22</v>
       </c>
-      <c r="M25" s="67" t="n">
+      <c r="M25" s="68" t="n">
         <v>125</v>
       </c>
-      <c r="N25" s="67" t="n">
+      <c r="N25" s="68" t="n">
         <v>150</v>
       </c>
-      <c r="O25" s="60" t="inlineStr">
+      <c r="O25" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10781,43 +10786,43 @@
           <t>비금속</t>
         </is>
       </c>
-      <c r="B26" s="69" t="n">
+      <c r="B26" s="70" t="n">
         <v>-14.58</v>
       </c>
-      <c r="C26" s="69" t="n">
+      <c r="C26" s="70" t="n">
         <v>-14.92</v>
       </c>
-      <c r="D26" s="69" t="n">
+      <c r="D26" s="70" t="n">
         <v>-3.16</v>
       </c>
-      <c r="E26" s="69" t="n">
+      <c r="E26" s="70" t="n">
         <v>-0.18</v>
       </c>
-      <c r="F26" s="68" t="n">
+      <c r="F26" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="G26" s="71" t="n">
+      <c r="G26" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="68" t="n">
+      <c r="H26" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="I26" s="67" t="n">
+      <c r="I26" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="J26" s="68" t="n">
+      <c r="J26" s="69" t="n">
         <v>-1</v>
       </c>
-      <c r="K26" s="68" t="n">
+      <c r="K26" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="L26" s="71" t="n">
+      <c r="L26" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="67" t="n">
+      <c r="M26" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="N26" s="71" t="n">
+      <c r="N26" s="72" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="30" t="inlineStr"/>
@@ -10828,46 +10833,46 @@
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="B27" s="69" t="n">
+      <c r="B27" s="70" t="n">
         <v>-45.95</v>
       </c>
-      <c r="C27" s="69" t="n">
+      <c r="C27" s="70" t="n">
         <v>-33.87</v>
       </c>
-      <c r="D27" s="69" t="n">
+      <c r="D27" s="70" t="n">
         <v>-19.97</v>
       </c>
-      <c r="E27" s="69" t="n">
+      <c r="E27" s="70" t="n">
         <v>-0.64</v>
       </c>
-      <c r="F27" s="68" t="n">
+      <c r="F27" s="69" t="n">
         <v>-43</v>
       </c>
-      <c r="G27" s="68" t="n">
+      <c r="G27" s="69" t="n">
         <v>-46</v>
       </c>
-      <c r="H27" s="68" t="n">
+      <c r="H27" s="69" t="n">
         <v>-89</v>
       </c>
-      <c r="I27" s="67" t="n">
+      <c r="I27" s="68" t="n">
         <v>29</v>
       </c>
-      <c r="J27" s="68" t="n">
+      <c r="J27" s="69" t="n">
         <v>-10</v>
       </c>
-      <c r="K27" s="68" t="n">
+      <c r="K27" s="69" t="n">
         <v>-60</v>
       </c>
-      <c r="L27" s="68" t="n">
+      <c r="L27" s="69" t="n">
         <v>-5</v>
       </c>
-      <c r="M27" s="67" t="n">
+      <c r="M27" s="68" t="n">
         <v>91</v>
       </c>
-      <c r="N27" s="68" t="n">
+      <c r="N27" s="69" t="n">
         <v>-3</v>
       </c>
-      <c r="O27" s="60" t="inlineStr">
+      <c r="O27" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10879,46 +10884,46 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="B28" s="66" t="n">
+      <c r="B28" s="67" t="n">
         <v>64.83</v>
       </c>
-      <c r="C28" s="69" t="n">
+      <c r="C28" s="70" t="n">
         <v>-9.380000000000001</v>
       </c>
-      <c r="D28" s="69" t="n">
+      <c r="D28" s="70" t="n">
         <v>-0.09</v>
       </c>
-      <c r="E28" s="69" t="n">
+      <c r="E28" s="70" t="n">
         <v>-1.38</v>
       </c>
-      <c r="F28" s="68" t="n">
+      <c r="F28" s="69" t="n">
         <v>-31</v>
       </c>
-      <c r="G28" s="68" t="n">
+      <c r="G28" s="69" t="n">
         <v>-676</v>
       </c>
-      <c r="H28" s="68" t="n">
+      <c r="H28" s="69" t="n">
         <v>-707</v>
       </c>
-      <c r="I28" s="68" t="n">
+      <c r="I28" s="69" t="n">
         <v>-90</v>
       </c>
-      <c r="J28" s="68" t="n">
+      <c r="J28" s="69" t="n">
         <v>-310</v>
       </c>
-      <c r="K28" s="68" t="n">
+      <c r="K28" s="69" t="n">
         <v>-270</v>
       </c>
-      <c r="L28" s="68" t="n">
+      <c r="L28" s="69" t="n">
         <v>-7</v>
       </c>
-      <c r="M28" s="67" t="n">
+      <c r="M28" s="68" t="n">
         <v>698</v>
       </c>
-      <c r="N28" s="67" t="n">
+      <c r="N28" s="68" t="n">
         <v>9</v>
       </c>
-      <c r="O28" s="60" t="inlineStr">
+      <c r="O28" s="61" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10956,7 +10961,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{78E98288-0344-4A60-9B39-1D1E339E244E}</x14:id>
+          <x14:id>{6CD521CA-D918-438E-999E-05C26505930C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10970,7 +10975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9E280221-0FBF-43A1-B589-BF3EB2F722EC}</x14:id>
+          <x14:id>{1B06462A-3059-4D99-A20C-186316D70E02}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10984,7 +10989,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{527064BF-9651-4594-9C22-A81BFB03544D}</x14:id>
+          <x14:id>{B4C26B67-C91C-4822-B5EC-D152FA0ABC0D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10998,7 +11003,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D1A25360-E261-4215-B208-0F2F1201DBE1}</x14:id>
+          <x14:id>{C37EC435-C9AE-4F13-A936-D9F98ADE9638}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11008,7 +11013,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{78E98288-0344-4A60-9B39-1D1E339E244E}">
+          <x14:cfRule type="dataBar" id="{6CD521CA-D918-438E-999E-05C26505930C}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11021,7 +11026,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9E280221-0FBF-43A1-B589-BF3EB2F722EC}">
+          <x14:cfRule type="dataBar" id="{1B06462A-3059-4D99-A20C-186316D70E02}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11034,7 +11039,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{527064BF-9651-4594-9C22-A81BFB03544D}">
+          <x14:cfRule type="dataBar" id="{B4C26B67-C91C-4822-B5EC-D152FA0ABC0D}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11047,7 +11052,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D1A25360-E261-4215-B208-0F2F1201DBE1}">
+          <x14:cfRule type="dataBar" id="{C37EC435-C9AE-4F13-A936-D9F98ADE9638}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/reports/monthly_review/2026-10.xlsx
+++ b/public/reports/monthly_review/2026-10.xlsx
@@ -321,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -416,9 +416,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1020,7 +1017,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/07, %</t>
+          <t>미국 종가 기준 09/30 → 10/08, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1090,19 +1087,19 @@
         <v>-16253</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2.52</v>
+        <v>1.24</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>-7.71</v>
-      </c>
-      <c r="I8" s="28" t="n">
-        <v>3.46</v>
+        <v>-5.69</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="9">
@@ -1161,7 +1158,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>3.02</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="13">
@@ -1177,11 +1174,11 @@
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
-          <t>기술</t>
+          <t>임의소비재</t>
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="14">
@@ -1197,11 +1194,11 @@
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>반도체</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>2.63</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="15">
@@ -1221,7 +1218,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-4.72</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="16">
@@ -1237,13 +1234,11 @@
       </c>
       <c r="C16" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D16" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>반도체</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="17">
@@ -1259,13 +1254,11 @@
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D17" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>헬스케어</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="18">
@@ -2314,7 +2307,7 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="D53" s="35" t="inlineStr">
+      <c r="D53" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2355,7 +2348,7 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="D54" s="35" t="inlineStr">
+      <c r="D54" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2396,7 +2389,7 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="D55" s="35" t="inlineStr">
+      <c r="D55" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2437,7 +2430,7 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="D56" s="35" t="inlineStr">
+      <c r="D56" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2478,7 +2471,7 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="D57" s="35" t="inlineStr">
+      <c r="D57" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -2519,7 +2512,7 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="D58" s="35" t="inlineStr">
+      <c r="D58" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
@@ -2560,7 +2553,7 @@
           <t>고영</t>
         </is>
       </c>
-      <c r="D59" s="35" t="inlineStr">
+      <c r="D59" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2601,7 +2594,7 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="D60" s="35" t="inlineStr">
+      <c r="D60" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2642,7 +2635,7 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="D61" s="35" t="inlineStr">
+      <c r="D61" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -2683,7 +2676,7 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="D62" s="35" t="inlineStr">
+      <c r="D62" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2724,7 +2717,7 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="D63" s="35" t="inlineStr">
+      <c r="D63" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2765,7 +2758,7 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="D64" s="35" t="inlineStr">
+      <c r="D64" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2806,7 +2799,7 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="D65" s="35" t="inlineStr">
+      <c r="D65" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -2847,7 +2840,7 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="D66" s="35" t="inlineStr">
+      <c r="D66" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -2888,7 +2881,7 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="D67" s="35" t="inlineStr">
+      <c r="D67" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -2929,7 +2922,7 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="D68" s="35" t="inlineStr">
+      <c r="D68" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -2970,7 +2963,7 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="D69" s="35" t="inlineStr">
+      <c r="D69" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
@@ -3011,7 +3004,7 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="D70" s="35" t="inlineStr">
+      <c r="D70" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -3052,7 +3045,7 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="D71" s="35" t="inlineStr">
+      <c r="D71" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -3093,7 +3086,7 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="D72" s="35" t="inlineStr">
+      <c r="D72" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3147,7 +3140,7 @@
       <c r="K74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="36" t="inlineStr">
+      <c r="A75" s="35" t="inlineStr">
         <is>
           <t>● 동반강세 — 추세 지속형 상방 관찰</t>
         </is>
@@ -3164,12 +3157,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="B76" s="35" t="inlineStr">
+      <c r="B76" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C76" s="37" t="n">
+      <c r="C76" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D76" s="31" t="inlineStr"/>
@@ -3179,12 +3172,12 @@
           <t>에스엠</t>
         </is>
       </c>
-      <c r="H76" s="35" t="inlineStr">
+      <c r="H76" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="I76" s="38" t="n">
+      <c r="I76" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J76" s="31" t="inlineStr"/>
@@ -3208,12 +3201,12 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="B78" s="35" t="inlineStr">
+      <c r="B78" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C78" s="37" t="n">
+      <c r="C78" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D78" s="31" t="inlineStr"/>
@@ -3223,12 +3216,12 @@
           <t>하이브</t>
         </is>
       </c>
-      <c r="H78" s="35" t="inlineStr">
+      <c r="H78" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="I78" s="38" t="n">
+      <c r="I78" s="37" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="31" t="inlineStr"/>
@@ -3252,12 +3245,12 @@
           <t>LG화학</t>
         </is>
       </c>
-      <c r="B80" s="35" t="inlineStr">
+      <c r="B80" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C80" s="37" t="n">
+      <c r="C80" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D80" s="31" t="inlineStr"/>
@@ -3267,12 +3260,12 @@
           <t>파라다이스</t>
         </is>
       </c>
-      <c r="H80" s="35" t="inlineStr">
+      <c r="H80" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="I80" s="38" t="n">
+      <c r="I80" s="37" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="31" t="inlineStr"/>
@@ -3296,12 +3289,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="B82" s="35" t="inlineStr">
+      <c r="B82" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C82" s="37" t="n">
+      <c r="C82" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D82" s="31" t="inlineStr"/>
@@ -3311,12 +3304,12 @@
           <t>CJ CGV</t>
         </is>
       </c>
-      <c r="H82" s="35" t="inlineStr">
+      <c r="H82" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="I82" s="38" t="n">
+      <c r="I82" s="37" t="n">
         <v>1</v>
       </c>
       <c r="J82" s="31" t="inlineStr"/>
@@ -3340,12 +3333,12 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="B84" s="35" t="inlineStr">
+      <c r="B84" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="C84" s="37" t="n">
+      <c r="C84" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D84" s="31" t="inlineStr"/>
@@ -3360,12 +3353,12 @@
     </row>
     <row r="86"/>
     <row r="87">
-      <c r="A87" s="39" t="inlineStr">
+      <c r="A87" s="38" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G87" s="40" t="inlineStr">
+      <c r="G87" s="39" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
@@ -3377,17 +3370,17 @@
           <t>해당 섹터·조건 충족 종목 없음</t>
         </is>
       </c>
-      <c r="G88" s="41" t="inlineStr">
+      <c r="G88" s="40" t="inlineStr">
         <is>
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="H88" s="35" t="inlineStr">
+      <c r="H88" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="I88" s="42" t="n">
+      <c r="I88" s="41" t="n">
         <v>-3</v>
       </c>
       <c r="J88" s="31" t="inlineStr"/>
@@ -3406,12 +3399,12 @@
           <t>카카오</t>
         </is>
       </c>
-      <c r="H90" s="35" t="inlineStr">
+      <c r="H90" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="I90" s="42" t="n">
+      <c r="I90" s="41" t="n">
         <v>-3</v>
       </c>
       <c r="J90" s="31" t="inlineStr"/>
@@ -3430,12 +3423,12 @@
           <t>에이비엘바이오</t>
         </is>
       </c>
-      <c r="H92" s="35" t="inlineStr">
+      <c r="H92" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="I92" s="42" t="n">
+      <c r="I92" s="41" t="n">
         <v>-3</v>
       </c>
       <c r="J92" s="31" t="inlineStr"/>
@@ -3454,12 +3447,12 @@
           <t>한화투자증권</t>
         </is>
       </c>
-      <c r="H94" s="35" t="inlineStr">
+      <c r="H94" s="34" t="inlineStr">
         <is>
           <t>증권</t>
         </is>
       </c>
-      <c r="I94" s="42" t="n">
+      <c r="I94" s="41" t="n">
         <v>-3</v>
       </c>
       <c r="J94" s="31" t="inlineStr"/>
@@ -3478,12 +3471,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="H96" s="43" t="inlineStr">
+      <c r="H96" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I96" s="42" t="n">
+      <c r="I96" s="41" t="n">
         <v>-2</v>
       </c>
       <c r="J96" s="31" t="inlineStr"/>
@@ -3498,7 +3491,7 @@
     </row>
     <row r="98"/>
     <row r="99" ht="31" customHeight="1" s="15">
-      <c r="A99" s="44" t="inlineStr">
+      <c r="A99" s="43" t="inlineStr">
         <is>
           <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
@@ -3709,7 +3702,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D118" s="35" t="inlineStr">
+      <c r="D118" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -3744,7 +3737,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D119" s="35" t="inlineStr">
+      <c r="D119" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -3779,7 +3772,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D120" s="35" t="inlineStr">
+      <c r="D120" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -3814,7 +3807,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D121" s="35" t="inlineStr">
+      <c r="D121" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -3849,7 +3842,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D122" s="35" t="inlineStr">
+      <c r="D122" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -3884,7 +3877,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D123" s="35" t="inlineStr">
+      <c r="D123" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -3919,7 +3912,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D124" s="35" t="inlineStr">
+      <c r="D124" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -3954,7 +3947,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D125" s="35" t="inlineStr">
+      <c r="D125" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -3989,7 +3982,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D126" s="35" t="inlineStr">
+      <c r="D126" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -4025,7 +4018,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D127" s="35" t="inlineStr">
+      <c r="D127" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -4060,7 +4053,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D128" s="35" t="inlineStr">
+      <c r="D128" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -4095,7 +4088,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D129" s="35" t="inlineStr">
+      <c r="D129" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -4335,62 +4328,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="I5" s="45" t="inlineStr">
+      <c r="I5" s="44" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="44" t="inlineStr">
         <is>
           <t>월간등락(%)</t>
         </is>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="44" t="inlineStr">
         <is>
           <t>신고가대비(%)</t>
         </is>
@@ -4407,36 +4400,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D6" s="46" t="n">
+      <c r="D6" s="45" t="n">
         <v>1589</v>
       </c>
-      <c r="E6" s="46" t="n">
+      <c r="E6" s="45" t="n">
         <v>1580</v>
       </c>
-      <c r="F6" s="46" t="n">
+      <c r="F6" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="46" t="n">
         <v>-1499</v>
       </c>
-      <c r="H6" s="48" t="n">
+      <c r="H6" s="47" t="n">
         <v>1255.8</v>
       </c>
-      <c r="I6" s="48" t="n">
+      <c r="I6" s="47" t="n">
         <v>19079.1</v>
       </c>
-      <c r="J6" s="49" t="n">
+      <c r="J6" s="48" t="n">
         <v>1944.9</v>
       </c>
-      <c r="K6" s="50" t="n">
+      <c r="K6" s="49" t="n">
         <v>14.19</v>
       </c>
-      <c r="L6" s="51" t="n">
+      <c r="L6" s="50" t="n">
         <v>-6.37</v>
       </c>
     </row>
@@ -4451,36 +4444,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D7" s="46" t="n">
+      <c r="D7" s="45" t="n">
         <v>1399</v>
       </c>
-      <c r="E7" s="46" t="n">
+      <c r="E7" s="45" t="n">
         <v>819</v>
       </c>
-      <c r="F7" s="46" t="n">
+      <c r="F7" s="45" t="n">
         <v>580</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="46" t="n">
         <v>-1416</v>
       </c>
-      <c r="H7" s="48" t="n">
+      <c r="H7" s="47" t="n">
         <v>512.7</v>
       </c>
-      <c r="I7" s="48" t="n">
+      <c r="I7" s="47" t="n">
         <v>4991.6</v>
       </c>
-      <c r="J7" s="49" t="n">
+      <c r="J7" s="48" t="n">
         <v>1217.6</v>
       </c>
-      <c r="K7" s="50" t="n">
+      <c r="K7" s="49" t="n">
         <v>8.18</v>
       </c>
-      <c r="L7" s="52" t="n">
+      <c r="L7" s="51" t="n">
         <v>-1.98</v>
       </c>
     </row>
@@ -4495,36 +4488,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D8" s="46" t="n">
+      <c r="D8" s="45" t="n">
         <v>517</v>
       </c>
-      <c r="E8" s="46" t="n">
+      <c r="E8" s="45" t="n">
         <v>1125</v>
       </c>
-      <c r="F8" s="47" t="n">
+      <c r="F8" s="46" t="n">
         <v>-607</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="46" t="n">
         <v>-517</v>
       </c>
-      <c r="H8" s="48" t="n">
+      <c r="H8" s="47" t="n">
         <v>353.5</v>
       </c>
-      <c r="I8" s="48" t="n">
+      <c r="I8" s="47" t="n">
         <v>10727.2</v>
       </c>
-      <c r="J8" s="49" t="n">
+      <c r="J8" s="48" t="n">
         <v>1167.1</v>
       </c>
-      <c r="K8" s="50" t="n">
+      <c r="K8" s="49" t="n">
         <v>14.16</v>
       </c>
-      <c r="L8" s="51" t="n">
+      <c r="L8" s="50" t="n">
         <v>-5.98</v>
       </c>
     </row>
@@ -4539,36 +4532,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="D9" s="46" t="n">
+      <c r="D9" s="45" t="n">
         <v>15</v>
       </c>
-      <c r="E9" s="46" t="n">
+      <c r="E9" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="45" t="n">
         <v>15</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="46" t="n">
         <v>-15</v>
       </c>
-      <c r="H9" s="48" t="n">
+      <c r="H9" s="47" t="n">
         <v>4.9</v>
       </c>
-      <c r="I9" s="48" t="n">
+      <c r="I9" s="47" t="n">
         <v>30.4</v>
       </c>
-      <c r="J9" s="49" t="n">
+      <c r="J9" s="48" t="n">
         <v>1.4</v>
       </c>
-      <c r="K9" s="50" t="n">
+      <c r="K9" s="49" t="n">
         <v>38.7</v>
       </c>
-      <c r="L9" s="53" t="n">
+      <c r="L9" s="52" t="n">
         <v>-4.14</v>
       </c>
     </row>
@@ -4583,36 +4576,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="46" t="n">
         <v>-69</v>
       </c>
-      <c r="E10" s="46" t="n">
+      <c r="E10" s="45" t="n">
         <v>228</v>
       </c>
-      <c r="F10" s="47" t="n">
+      <c r="F10" s="46" t="n">
         <v>-297</v>
       </c>
-      <c r="G10" s="46" t="n">
+      <c r="G10" s="45" t="n">
         <v>53</v>
       </c>
-      <c r="H10" s="48" t="n">
+      <c r="H10" s="47" t="n">
         <v>55.2</v>
       </c>
-      <c r="I10" s="48" t="n">
+      <c r="I10" s="47" t="n">
         <v>1952.5</v>
       </c>
-      <c r="J10" s="54" t="n">
+      <c r="J10" s="53" t="n">
         <v>-53.9</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="54" t="n">
         <v>-4.21</v>
       </c>
-      <c r="L10" s="51" t="n">
+      <c r="L10" s="50" t="n">
         <v>-6.04</v>
       </c>
     </row>
@@ -4627,36 +4620,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D11" s="46" t="n">
+      <c r="D11" s="45" t="n">
         <v>118</v>
       </c>
-      <c r="E11" s="46" t="n">
+      <c r="E11" s="45" t="n">
         <v>119</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="F11" s="46" t="n">
         <v>-1</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="46" t="n">
         <v>-119</v>
       </c>
-      <c r="H11" s="48" t="n">
+      <c r="H11" s="47" t="n">
         <v>21.2</v>
       </c>
-      <c r="I11" s="48" t="n">
+      <c r="I11" s="47" t="n">
         <v>185.8</v>
       </c>
-      <c r="J11" s="49" t="n">
+      <c r="J11" s="48" t="n">
         <v>5.7</v>
       </c>
-      <c r="K11" s="50" t="n">
+      <c r="K11" s="49" t="n">
         <v>12.75</v>
       </c>
-      <c r="L11" s="51" t="n">
+      <c r="L11" s="50" t="n">
         <v>-6.21</v>
       </c>
     </row>
@@ -4671,36 +4664,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="45" t="n">
         <v>60</v>
       </c>
-      <c r="E12" s="46" t="n">
+      <c r="E12" s="45" t="n">
         <v>329</v>
       </c>
-      <c r="F12" s="47" t="n">
+      <c r="F12" s="46" t="n">
         <v>-268</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="46" t="n">
         <v>-77</v>
       </c>
-      <c r="H12" s="48" t="n">
+      <c r="H12" s="47" t="n">
         <v>78.7</v>
       </c>
-      <c r="I12" s="48" t="n">
+      <c r="I12" s="47" t="n">
         <v>1091.8</v>
       </c>
-      <c r="J12" s="54" t="n">
+      <c r="J12" s="53" t="n">
         <v>-62.3</v>
       </c>
-      <c r="K12" s="50" t="n">
+      <c r="K12" s="49" t="n">
         <v>7.61</v>
       </c>
-      <c r="L12" s="51" t="n">
+      <c r="L12" s="50" t="n">
         <v>-6.55</v>
       </c>
     </row>
@@ -4715,36 +4708,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="46" t="n">
+      <c r="E13" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="56" t="n">
+      <c r="F13" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="46" t="n">
         <v>-1</v>
       </c>
-      <c r="H13" s="48" t="n">
+      <c r="H13" s="47" t="n">
         <v>0.8</v>
       </c>
-      <c r="I13" s="48" t="n">
+      <c r="I13" s="47" t="n">
         <v>27.8</v>
       </c>
-      <c r="J13" s="54" t="n">
+      <c r="J13" s="53" t="n">
         <v>-0.8</v>
       </c>
-      <c r="K13" s="50" t="n">
+      <c r="K13" s="49" t="n">
         <v>26.86</v>
       </c>
-      <c r="L13" s="51" t="n">
+      <c r="L13" s="50" t="n">
         <v>-6.94</v>
       </c>
     </row>
@@ -4759,36 +4752,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D14" s="46" t="n">
+      <c r="D14" s="45" t="n">
         <v>590</v>
       </c>
-      <c r="E14" s="46" t="n">
+      <c r="E14" s="45" t="n">
         <v>265</v>
       </c>
-      <c r="F14" s="46" t="n">
+      <c r="F14" s="45" t="n">
         <v>325</v>
       </c>
-      <c r="G14" s="47" t="n">
+      <c r="G14" s="46" t="n">
         <v>-594</v>
       </c>
-      <c r="H14" s="48" t="n">
+      <c r="H14" s="47" t="n">
         <v>239.7</v>
       </c>
-      <c r="I14" s="48" t="n">
+      <c r="I14" s="47" t="n">
         <v>4078.4</v>
       </c>
-      <c r="J14" s="49" t="n">
+      <c r="J14" s="48" t="n">
         <v>216.8</v>
       </c>
-      <c r="K14" s="50" t="n">
+      <c r="K14" s="49" t="n">
         <v>3.95</v>
       </c>
-      <c r="L14" s="51" t="n">
+      <c r="L14" s="50" t="n">
         <v>-5.29</v>
       </c>
     </row>
@@ -4803,36 +4796,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D15" s="46" t="n">
+      <c r="D15" s="45" t="n">
         <v>66</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="46" t="n">
         <v>-282</v>
       </c>
-      <c r="F15" s="46" t="n">
+      <c r="F15" s="45" t="n">
         <v>349</v>
       </c>
-      <c r="G15" s="47" t="n">
+      <c r="G15" s="46" t="n">
         <v>-77</v>
       </c>
-      <c r="H15" s="48" t="n">
+      <c r="H15" s="47" t="n">
         <v>311.1</v>
       </c>
-      <c r="I15" s="48" t="n">
+      <c r="I15" s="47" t="n">
         <v>2746.4</v>
       </c>
-      <c r="J15" s="49" t="n">
+      <c r="J15" s="48" t="n">
         <v>445.6</v>
       </c>
-      <c r="K15" s="50" t="n">
+      <c r="K15" s="49" t="n">
         <v>13.01</v>
       </c>
-      <c r="L15" s="51" t="n">
+      <c r="L15" s="50" t="n">
         <v>-5.26</v>
       </c>
     </row>
@@ -4847,36 +4840,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D16" s="46" t="n">
+      <c r="D16" s="45" t="n">
         <v>98</v>
       </c>
-      <c r="E16" s="46" t="n">
+      <c r="E16" s="45" t="n">
         <v>163</v>
       </c>
-      <c r="F16" s="47" t="n">
+      <c r="F16" s="46" t="n">
         <v>-66</v>
       </c>
-      <c r="G16" s="47" t="n">
+      <c r="G16" s="46" t="n">
         <v>-78</v>
       </c>
-      <c r="H16" s="48" t="n">
+      <c r="H16" s="47" t="n">
         <v>100.5</v>
       </c>
-      <c r="I16" s="48" t="n">
+      <c r="I16" s="47" t="n">
         <v>2828.9</v>
       </c>
-      <c r="J16" s="49" t="n">
+      <c r="J16" s="48" t="n">
         <v>357.2</v>
       </c>
-      <c r="K16" s="50" t="n">
+      <c r="K16" s="49" t="n">
         <v>18.14</v>
       </c>
-      <c r="L16" s="53" t="n">
+      <c r="L16" s="52" t="n">
         <v>-4.04</v>
       </c>
     </row>
@@ -4891,36 +4884,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D17" s="46" t="n">
+      <c r="D17" s="45" t="n">
         <v>167</v>
       </c>
-      <c r="E17" s="46" t="n">
+      <c r="E17" s="45" t="n">
         <v>435</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="46" t="n">
         <v>-269</v>
       </c>
-      <c r="G17" s="47" t="n">
+      <c r="G17" s="46" t="n">
         <v>-152</v>
       </c>
-      <c r="H17" s="48" t="n">
+      <c r="H17" s="47" t="n">
         <v>34</v>
       </c>
-      <c r="I17" s="48" t="n">
+      <c r="I17" s="47" t="n">
         <v>630.3</v>
       </c>
-      <c r="J17" s="49" t="n">
+      <c r="J17" s="48" t="n">
         <v>142.7</v>
       </c>
-      <c r="K17" s="50" t="n">
+      <c r="K17" s="49" t="n">
         <v>13.58</v>
       </c>
-      <c r="L17" s="51" t="n">
+      <c r="L17" s="50" t="n">
         <v>-5.21</v>
       </c>
     </row>
@@ -4935,36 +4928,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="45" t="n">
         <v>413</v>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="E18" s="45" t="n">
         <v>133</v>
       </c>
-      <c r="F18" s="46" t="n">
+      <c r="F18" s="45" t="n">
         <v>279</v>
       </c>
-      <c r="G18" s="47" t="n">
+      <c r="G18" s="46" t="n">
         <v>-409</v>
       </c>
-      <c r="H18" s="48" t="n">
+      <c r="H18" s="47" t="n">
         <v>58.2</v>
       </c>
-      <c r="I18" s="48" t="n">
+      <c r="I18" s="47" t="n">
         <v>955.7</v>
       </c>
-      <c r="J18" s="49" t="n">
+      <c r="J18" s="48" t="n">
         <v>256</v>
       </c>
-      <c r="K18" s="50" t="n">
+      <c r="K18" s="49" t="n">
         <v>39.21</v>
       </c>
-      <c r="L18" s="51" t="n">
+      <c r="L18" s="50" t="n">
         <v>-8.94</v>
       </c>
     </row>
@@ -4979,36 +4972,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D19" s="47" t="n">
+      <c r="D19" s="46" t="n">
         <v>-85</v>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="46" t="n">
         <v>-60</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="F19" s="46" t="n">
         <v>-25</v>
       </c>
-      <c r="G19" s="47" t="n">
+      <c r="G19" s="46" t="n">
         <v>-130</v>
       </c>
-      <c r="H19" s="48" t="n">
+      <c r="H19" s="47" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="I19" s="48" t="n">
+      <c r="I19" s="47" t="n">
         <v>2581</v>
       </c>
-      <c r="J19" s="54" t="n">
+      <c r="J19" s="53" t="n">
         <v>-136.7</v>
       </c>
-      <c r="K19" s="50" t="n">
+      <c r="K19" s="49" t="n">
         <v>0.79</v>
       </c>
-      <c r="L19" s="51" t="n">
+      <c r="L19" s="50" t="n">
         <v>-8.33</v>
       </c>
     </row>
@@ -5023,36 +5016,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="D20" s="46" t="n">
+      <c r="D20" s="45" t="n">
         <v>103</v>
       </c>
-      <c r="E20" s="46" t="n">
+      <c r="E20" s="45" t="n">
         <v>70</v>
       </c>
-      <c r="F20" s="46" t="n">
+      <c r="F20" s="45" t="n">
         <v>34</v>
       </c>
-      <c r="G20" s="47" t="n">
+      <c r="G20" s="46" t="n">
         <v>-115</v>
       </c>
-      <c r="H20" s="48" t="n">
+      <c r="H20" s="47" t="n">
         <v>190.3</v>
       </c>
-      <c r="I20" s="48" t="n">
+      <c r="I20" s="47" t="n">
         <v>2065.1</v>
       </c>
-      <c r="J20" s="49" t="n">
+      <c r="J20" s="48" t="n">
         <v>272.8</v>
       </c>
-      <c r="K20" s="50" t="n">
+      <c r="K20" s="49" t="n">
         <v>7.8</v>
       </c>
-      <c r="L20" s="51" t="n">
+      <c r="L20" s="50" t="n">
         <v>-8.210000000000001</v>
       </c>
     </row>
@@ -5067,36 +5060,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D21" s="46" t="n">
+      <c r="D21" s="45" t="n">
         <v>64</v>
       </c>
-      <c r="E21" s="46" t="n">
+      <c r="E21" s="45" t="n">
         <v>21</v>
       </c>
-      <c r="F21" s="46" t="n">
+      <c r="F21" s="45" t="n">
         <v>43</v>
       </c>
-      <c r="G21" s="47" t="n">
+      <c r="G21" s="46" t="n">
         <v>-60</v>
       </c>
-      <c r="H21" s="48" t="n">
+      <c r="H21" s="47" t="n">
         <v>19.9</v>
       </c>
-      <c r="I21" s="48" t="n">
+      <c r="I21" s="47" t="n">
         <v>153.5</v>
       </c>
-      <c r="J21" s="54" t="n">
+      <c r="J21" s="53" t="n">
         <v>-4.6</v>
       </c>
-      <c r="K21" s="50" t="n">
+      <c r="K21" s="49" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="L21" s="53" t="n">
+      <c r="L21" s="52" t="n">
         <v>-2.61</v>
       </c>
     </row>
@@ -5111,36 +5104,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D22" s="46" t="n">
+      <c r="D22" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="47" t="n">
+      <c r="E22" s="46" t="n">
         <v>-1</v>
       </c>
-      <c r="F22" s="46" t="n">
+      <c r="F22" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="G22" s="47" t="n">
+      <c r="G22" s="46" t="n">
         <v>-3</v>
       </c>
-      <c r="H22" s="48" t="n">
+      <c r="H22" s="47" t="n">
         <v>61.9</v>
       </c>
-      <c r="I22" s="48" t="n">
+      <c r="I22" s="47" t="n">
         <v>890.9</v>
       </c>
-      <c r="J22" s="49" t="n">
+      <c r="J22" s="48" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="K22" s="50" t="n">
+      <c r="K22" s="49" t="n">
         <v>1.61</v>
       </c>
-      <c r="L22" s="51" t="n">
+      <c r="L22" s="50" t="n">
         <v>-7.69</v>
       </c>
     </row>
@@ -5155,36 +5148,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D23" s="46" t="n">
+      <c r="D23" s="45" t="n">
         <v>220</v>
       </c>
-      <c r="E23" s="46" t="n">
+      <c r="E23" s="45" t="n">
         <v>161</v>
       </c>
-      <c r="F23" s="46" t="n">
+      <c r="F23" s="45" t="n">
         <v>58</v>
       </c>
-      <c r="G23" s="47" t="n">
+      <c r="G23" s="46" t="n">
         <v>-217</v>
       </c>
-      <c r="H23" s="48" t="n">
+      <c r="H23" s="47" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="I23" s="48" t="n">
+      <c r="I23" s="47" t="n">
         <v>913.4</v>
       </c>
-      <c r="J23" s="49" t="n">
+      <c r="J23" s="48" t="n">
         <v>127.6</v>
       </c>
-      <c r="K23" s="50" t="n">
+      <c r="K23" s="49" t="n">
         <v>7.04</v>
       </c>
-      <c r="L23" s="51" t="n">
+      <c r="L23" s="50" t="n">
         <v>-6.59</v>
       </c>
     </row>
@@ -5199,36 +5192,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D24" s="46" t="n">
+      <c r="D24" s="45" t="n">
         <v>25</v>
       </c>
-      <c r="E24" s="46" t="n">
+      <c r="E24" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="F24" s="46" t="n">
+      <c r="F24" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="G24" s="47" t="n">
+      <c r="G24" s="46" t="n">
         <v>-24</v>
       </c>
-      <c r="H24" s="48" t="n">
+      <c r="H24" s="47" t="n">
         <v>0.9</v>
       </c>
-      <c r="I24" s="48" t="n">
+      <c r="I24" s="47" t="n">
         <v>31.7</v>
       </c>
-      <c r="J24" s="54" t="n">
+      <c r="J24" s="53" t="n">
         <v>-1.8</v>
       </c>
-      <c r="K24" s="50" t="n">
+      <c r="K24" s="49" t="n">
         <v>25.93</v>
       </c>
-      <c r="L24" s="51" t="n">
+      <c r="L24" s="50" t="n">
         <v>-5.45</v>
       </c>
     </row>
@@ -5243,36 +5236,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="46" t="n">
         <v>-19</v>
       </c>
-      <c r="E25" s="47" t="n">
+      <c r="E25" s="46" t="n">
         <v>-10</v>
       </c>
-      <c r="F25" s="47" t="n">
+      <c r="F25" s="46" t="n">
         <v>-9</v>
       </c>
-      <c r="G25" s="46" t="n">
+      <c r="G25" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="H25" s="48" t="n">
+      <c r="H25" s="47" t="n">
         <v>6.6</v>
       </c>
-      <c r="I25" s="48" t="n">
+      <c r="I25" s="47" t="n">
         <v>49</v>
       </c>
-      <c r="J25" s="49" t="n">
+      <c r="J25" s="48" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="K25" s="50" t="n">
+      <c r="K25" s="49" t="n">
         <v>24.84</v>
       </c>
-      <c r="L25" s="52" t="n">
+      <c r="L25" s="51" t="n">
         <v>-1.92</v>
       </c>
     </row>
@@ -5287,36 +5280,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D26" s="46" t="n">
+      <c r="D26" s="45" t="n">
         <v>134</v>
       </c>
-      <c r="E26" s="46" t="n">
+      <c r="E26" s="45" t="n">
         <v>44</v>
       </c>
-      <c r="F26" s="46" t="n">
+      <c r="F26" s="45" t="n">
         <v>90</v>
       </c>
-      <c r="G26" s="47" t="n">
+      <c r="G26" s="46" t="n">
         <v>-129</v>
       </c>
-      <c r="H26" s="48" t="n">
+      <c r="H26" s="47" t="n">
         <v>33.7</v>
       </c>
-      <c r="I26" s="48" t="n">
+      <c r="I26" s="47" t="n">
         <v>1296.7</v>
       </c>
-      <c r="J26" s="49" t="n">
+      <c r="J26" s="48" t="n">
         <v>70.2</v>
       </c>
-      <c r="K26" s="50" t="n">
+      <c r="K26" s="49" t="n">
         <v>4.87</v>
       </c>
-      <c r="L26" s="51" t="n">
+      <c r="L26" s="50" t="n">
         <v>-9.09</v>
       </c>
     </row>
@@ -5331,36 +5324,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="46" t="n">
         <v>-10</v>
       </c>
-      <c r="E27" s="47" t="n">
+      <c r="E27" s="46" t="n">
         <v>-7</v>
       </c>
-      <c r="F27" s="47" t="n">
+      <c r="F27" s="46" t="n">
         <v>-3</v>
       </c>
-      <c r="G27" s="46" t="n">
+      <c r="G27" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="H27" s="48" t="n">
+      <c r="H27" s="47" t="n">
         <v>5.3</v>
       </c>
-      <c r="I27" s="48" t="n">
+      <c r="I27" s="47" t="n">
         <v>52.3</v>
       </c>
-      <c r="J27" s="54" t="n">
+      <c r="J27" s="53" t="n">
         <v>-1.6</v>
       </c>
-      <c r="K27" s="55" t="n">
+      <c r="K27" s="54" t="n">
         <v>-1.34</v>
       </c>
-      <c r="L27" s="51" t="n">
+      <c r="L27" s="50" t="n">
         <v>-7.37</v>
       </c>
     </row>
@@ -5375,36 +5368,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D28" s="46" t="n">
+      <c r="D28" s="45" t="n">
         <v>83</v>
       </c>
-      <c r="E28" s="46" t="n">
+      <c r="E28" s="45" t="n">
         <v>87</v>
       </c>
-      <c r="F28" s="47" t="n">
+      <c r="F28" s="46" t="n">
         <v>-4</v>
       </c>
-      <c r="G28" s="47" t="n">
+      <c r="G28" s="46" t="n">
         <v>-67</v>
       </c>
-      <c r="H28" s="48" t="n">
+      <c r="H28" s="47" t="n">
         <v>22.1</v>
       </c>
-      <c r="I28" s="48" t="n">
+      <c r="I28" s="47" t="n">
         <v>278.2</v>
       </c>
-      <c r="J28" s="49" t="n">
+      <c r="J28" s="48" t="n">
         <v>17.6</v>
       </c>
-      <c r="K28" s="50" t="n">
+      <c r="K28" s="49" t="n">
         <v>13.27</v>
       </c>
-      <c r="L28" s="51" t="n">
+      <c r="L28" s="50" t="n">
         <v>-6.5</v>
       </c>
     </row>
@@ -5419,36 +5412,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D29" s="46" t="n">
+      <c r="D29" s="45" t="n">
         <v>35</v>
       </c>
-      <c r="E29" s="47" t="n">
+      <c r="E29" s="46" t="n">
         <v>-32</v>
       </c>
-      <c r="F29" s="46" t="n">
+      <c r="F29" s="45" t="n">
         <v>66</v>
       </c>
-      <c r="G29" s="47" t="n">
+      <c r="G29" s="46" t="n">
         <v>-38</v>
       </c>
-      <c r="H29" s="48" t="n">
+      <c r="H29" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="I29" s="48" t="n">
+      <c r="I29" s="47" t="n">
         <v>169</v>
       </c>
-      <c r="J29" s="54" t="n">
+      <c r="J29" s="53" t="n">
         <v>-20</v>
       </c>
-      <c r="K29" s="50" t="n">
+      <c r="K29" s="49" t="n">
         <v>5.38</v>
       </c>
-      <c r="L29" s="51" t="n">
+      <c r="L29" s="50" t="n">
         <v>-6.96</v>
       </c>
     </row>
@@ -5463,36 +5456,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C30" s="35" t="inlineStr">
+      <c r="C30" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D30" s="46" t="n">
+      <c r="D30" s="45" t="n">
         <v>30</v>
       </c>
-      <c r="E30" s="47" t="n">
+      <c r="E30" s="46" t="n">
         <v>-26</v>
       </c>
-      <c r="F30" s="46" t="n">
+      <c r="F30" s="45" t="n">
         <v>55</v>
       </c>
-      <c r="G30" s="47" t="n">
+      <c r="G30" s="46" t="n">
         <v>-30</v>
       </c>
-      <c r="H30" s="48" t="n">
+      <c r="H30" s="47" t="n">
         <v>28.5</v>
       </c>
-      <c r="I30" s="48" t="n">
+      <c r="I30" s="47" t="n">
         <v>388.3</v>
       </c>
-      <c r="J30" s="49" t="n">
+      <c r="J30" s="48" t="n">
         <v>78.7</v>
       </c>
-      <c r="K30" s="50" t="n">
+      <c r="K30" s="49" t="n">
         <v>5.64</v>
       </c>
-      <c r="L30" s="51" t="n">
+      <c r="L30" s="50" t="n">
         <v>-7.18</v>
       </c>
     </row>
@@ -5507,36 +5500,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C31" s="35" t="inlineStr">
+      <c r="C31" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D31" s="46" t="n">
+      <c r="D31" s="45" t="n">
         <v>68</v>
       </c>
-      <c r="E31" s="46" t="n">
+      <c r="E31" s="45" t="n">
         <v>24</v>
       </c>
-      <c r="F31" s="46" t="n">
+      <c r="F31" s="45" t="n">
         <v>43</v>
       </c>
-      <c r="G31" s="47" t="n">
+      <c r="G31" s="46" t="n">
         <v>-64</v>
       </c>
-      <c r="H31" s="48" t="n">
+      <c r="H31" s="47" t="n">
         <v>5.5</v>
       </c>
-      <c r="I31" s="48" t="n">
+      <c r="I31" s="47" t="n">
         <v>36.5</v>
       </c>
-      <c r="J31" s="49" t="n">
+      <c r="J31" s="48" t="n">
         <v>2.6</v>
       </c>
-      <c r="K31" s="50" t="n">
+      <c r="K31" s="49" t="n">
         <v>13.56</v>
       </c>
-      <c r="L31" s="53" t="n">
+      <c r="L31" s="52" t="n">
         <v>-3.9</v>
       </c>
     </row>
@@ -5551,36 +5544,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C32" s="35" t="inlineStr">
+      <c r="C32" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D32" s="46" t="n">
+      <c r="D32" s="45" t="n">
         <v>65</v>
       </c>
-      <c r="E32" s="47" t="n">
+      <c r="E32" s="46" t="n">
         <v>-12</v>
       </c>
-      <c r="F32" s="46" t="n">
+      <c r="F32" s="45" t="n">
         <v>77</v>
       </c>
-      <c r="G32" s="47" t="n">
+      <c r="G32" s="46" t="n">
         <v>-61</v>
       </c>
-      <c r="H32" s="48" t="n">
+      <c r="H32" s="47" t="n">
         <v>12.4</v>
       </c>
-      <c r="I32" s="48" t="n">
+      <c r="I32" s="47" t="n">
         <v>587.3</v>
       </c>
-      <c r="J32" s="49" t="n">
+      <c r="J32" s="48" t="n">
         <v>11.9</v>
       </c>
-      <c r="K32" s="50" t="n">
+      <c r="K32" s="49" t="n">
         <v>3.92</v>
       </c>
-      <c r="L32" s="53" t="n">
+      <c r="L32" s="52" t="n">
         <v>-4.48</v>
       </c>
     </row>
@@ -5595,36 +5588,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C33" s="35" t="inlineStr">
+      <c r="C33" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D33" s="46" t="n">
+      <c r="D33" s="45" t="n">
         <v>21</v>
       </c>
-      <c r="E33" s="46" t="n">
+      <c r="E33" s="45" t="n">
         <v>27</v>
       </c>
-      <c r="F33" s="47" t="n">
+      <c r="F33" s="46" t="n">
         <v>-6</v>
       </c>
-      <c r="G33" s="47" t="n">
+      <c r="G33" s="46" t="n">
         <v>-22</v>
       </c>
-      <c r="H33" s="48" t="n">
+      <c r="H33" s="47" t="n">
         <v>10.4</v>
       </c>
-      <c r="I33" s="48" t="n">
+      <c r="I33" s="47" t="n">
         <v>312.5</v>
       </c>
-      <c r="J33" s="49" t="n">
+      <c r="J33" s="48" t="n">
         <v>72.3</v>
       </c>
-      <c r="K33" s="50" t="n">
+      <c r="K33" s="49" t="n">
         <v>16.94</v>
       </c>
-      <c r="L33" s="52" t="n">
+      <c r="L33" s="51" t="n">
         <v>-0.7</v>
       </c>
     </row>
@@ -5639,36 +5632,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="C34" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="46" t="n">
         <v>-20</v>
       </c>
-      <c r="E34" s="47" t="n">
+      <c r="E34" s="46" t="n">
         <v>-28</v>
       </c>
-      <c r="F34" s="46" t="n">
+      <c r="F34" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="G34" s="46" t="n">
+      <c r="G34" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="H34" s="48" t="n">
+      <c r="H34" s="47" t="n">
         <v>10.3</v>
       </c>
-      <c r="I34" s="48" t="n">
+      <c r="I34" s="47" t="n">
         <v>810.5</v>
       </c>
-      <c r="J34" s="49" t="n">
+      <c r="J34" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="K34" s="55" t="n">
+      <c r="K34" s="54" t="n">
         <v>-0.75</v>
       </c>
-      <c r="L34" s="51" t="n">
+      <c r="L34" s="50" t="n">
         <v>-7.7</v>
       </c>
     </row>
@@ -5683,36 +5676,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D35" s="46" t="n">
+      <c r="D35" s="45" t="n">
         <v>115</v>
       </c>
-      <c r="E35" s="46" t="n">
+      <c r="E35" s="45" t="n">
         <v>33</v>
       </c>
-      <c r="F35" s="46" t="n">
+      <c r="F35" s="45" t="n">
         <v>82</v>
       </c>
-      <c r="G35" s="47" t="n">
+      <c r="G35" s="46" t="n">
         <v>-116</v>
       </c>
-      <c r="H35" s="48" t="n">
+      <c r="H35" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="I35" s="48" t="n">
+      <c r="I35" s="47" t="n">
         <v>201.3</v>
       </c>
-      <c r="J35" s="49" t="n">
+      <c r="J35" s="48" t="n">
         <v>30.8</v>
       </c>
-      <c r="K35" s="50" t="n">
+      <c r="K35" s="49" t="n">
         <v>14.12</v>
       </c>
-      <c r="L35" s="51" t="n">
+      <c r="L35" s="50" t="n">
         <v>-8.949999999999999</v>
       </c>
     </row>
@@ -5790,7 +5783,7 @@
           <t>F1 외국인</t>
         </is>
       </c>
-      <c r="E3" s="57" t="inlineStr">
+      <c r="E3" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -5800,111 +5793,111 @@
           <t>F2 기관계</t>
         </is>
       </c>
-      <c r="N3" s="57" t="inlineStr">
+      <c r="N3" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr">
+      <c r="E4" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J4" s="58" t="inlineStr">
+      <c r="J4" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N4" s="59" t="inlineStr">
+      <c r="N4" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M5" s="45" t="inlineStr">
+      <c r="M5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N5" s="45" t="inlineStr">
+      <c r="N5" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O5" s="45" t="inlineStr">
+      <c r="O5" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P5" s="45" t="inlineStr">
+      <c r="P5" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q5" s="45" t="inlineStr">
+      <c r="Q5" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -5919,12 +5912,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="46" t="n">
         <v>3135</v>
       </c>
       <c r="E6" s="30" t="n">
@@ -5935,12 +5928,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H6" s="60" t="n">
+      <c r="H6" s="59" t="n">
         <v>-40638</v>
       </c>
       <c r="J6" s="30" t="n">
@@ -5951,12 +5944,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L6" s="35" t="inlineStr">
+      <c r="L6" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M6" s="47" t="n">
+      <c r="M6" s="46" t="n">
         <v>3029</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -5967,12 +5960,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P6" s="35" t="inlineStr">
+      <c r="P6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q6" s="60" t="n">
+      <c r="Q6" s="59" t="n">
         <v>-11560</v>
       </c>
     </row>
@@ -5985,12 +5978,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="46" t="n">
         <v>1738</v>
       </c>
       <c r="E7" s="30" t="n">
@@ -6001,12 +5994,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G7" s="35" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H7" s="60" t="n">
+      <c r="H7" s="59" t="n">
         <v>-11910</v>
       </c>
       <c r="J7" s="30" t="n">
@@ -6017,12 +6010,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L7" s="35" t="inlineStr">
+      <c r="L7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M7" s="47" t="n">
+      <c r="M7" s="46" t="n">
         <v>1656</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -6033,12 +6026,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P7" s="35" t="inlineStr">
+      <c r="P7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q7" s="60" t="n">
+      <c r="Q7" s="59" t="n">
         <v>-2845</v>
       </c>
     </row>
@@ -6051,12 +6044,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="46" t="n">
         <v>1101</v>
       </c>
       <c r="E8" s="30" t="n">
@@ -6067,12 +6060,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G8" s="35" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H8" s="60" t="n">
+      <c r="H8" s="59" t="n">
         <v>-4836</v>
       </c>
       <c r="J8" s="30" t="n">
@@ -6083,12 +6076,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L8" s="35" t="inlineStr">
+      <c r="L8" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M8" s="47" t="n">
+      <c r="M8" s="46" t="n">
         <v>1632</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -6099,12 +6092,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P8" s="35" t="inlineStr">
+      <c r="P8" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q8" s="60" t="n">
+      <c r="Q8" s="59" t="n">
         <v>-1629</v>
       </c>
     </row>
@@ -6117,12 +6110,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="46" t="n">
         <v>932</v>
       </c>
       <c r="E9" s="30" t="n">
@@ -6133,12 +6126,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G9" s="35" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H9" s="60" t="n">
+      <c r="H9" s="59" t="n">
         <v>-2585</v>
       </c>
       <c r="J9" s="30" t="n">
@@ -6149,12 +6142,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L9" s="35" t="inlineStr">
+      <c r="L9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M9" s="47" t="n">
+      <c r="M9" s="46" t="n">
         <v>1294</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -6165,12 +6158,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P9" s="43" t="inlineStr">
+      <c r="P9" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q9" s="60" t="n">
+      <c r="Q9" s="59" t="n">
         <v>-1244</v>
       </c>
     </row>
@@ -6183,12 +6176,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="46" t="n">
         <v>908</v>
       </c>
       <c r="E10" s="30" t="n">
@@ -6199,12 +6192,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G10" s="35" t="inlineStr">
+      <c r="G10" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H10" s="60" t="n">
+      <c r="H10" s="59" t="n">
         <v>-2196</v>
       </c>
       <c r="J10" s="30" t="n">
@@ -6215,12 +6208,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="L10" s="35" t="inlineStr">
+      <c r="L10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M10" s="47" t="n">
+      <c r="M10" s="46" t="n">
         <v>812</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -6231,12 +6224,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="P10" s="43" t="inlineStr">
+      <c r="P10" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q10" s="60" t="n">
+      <c r="Q10" s="59" t="n">
         <v>-846</v>
       </c>
     </row>
@@ -6249,12 +6242,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="46" t="n">
         <v>679</v>
       </c>
       <c r="E11" s="30" t="n">
@@ -6265,12 +6258,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="G11" s="35" t="inlineStr">
+      <c r="G11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H11" s="60" t="n">
+      <c r="H11" s="59" t="n">
         <v>-1885</v>
       </c>
       <c r="J11" s="30" t="n">
@@ -6281,12 +6274,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="L11" s="35" t="inlineStr">
+      <c r="L11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M11" s="47" t="n">
+      <c r="M11" s="46" t="n">
         <v>752</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -6297,12 +6290,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr">
+      <c r="P11" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q11" s="60" t="n">
+      <c r="Q11" s="59" t="n">
         <v>-830</v>
       </c>
     </row>
@@ -6315,12 +6308,12 @@
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="46" t="n">
         <v>625</v>
       </c>
       <c r="E12" s="30" t="n">
@@ -6331,12 +6324,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="G12" s="35" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H12" s="60" t="n">
+      <c r="H12" s="59" t="n">
         <v>-1568</v>
       </c>
       <c r="J12" s="30" t="n">
@@ -6347,12 +6340,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L12" s="35" t="inlineStr">
+      <c r="L12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M12" s="47" t="n">
+      <c r="M12" s="46" t="n">
         <v>730</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -6363,12 +6356,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q12" s="60" t="n">
+      <c r="Q12" s="59" t="n">
         <v>-776</v>
       </c>
     </row>
@@ -6381,12 +6374,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="46" t="n">
         <v>600</v>
       </c>
       <c r="E13" s="30" t="n">
@@ -6397,12 +6390,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G13" s="43" t="inlineStr">
+      <c r="G13" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H13" s="60" t="n">
+      <c r="H13" s="59" t="n">
         <v>-1346</v>
       </c>
       <c r="J13" s="30" t="n">
@@ -6413,12 +6406,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="L13" s="35" t="inlineStr">
+      <c r="L13" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M13" s="47" t="n">
+      <c r="M13" s="46" t="n">
         <v>602</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -6429,12 +6422,12 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="P13" s="35" t="inlineStr">
+      <c r="P13" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q13" s="60" t="n">
+      <c r="Q13" s="59" t="n">
         <v>-749</v>
       </c>
     </row>
@@ -6447,12 +6440,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="46" t="n">
         <v>566</v>
       </c>
       <c r="E14" s="30" t="n">
@@ -6463,12 +6456,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G14" s="35" t="inlineStr">
+      <c r="G14" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H14" s="60" t="n">
+      <c r="H14" s="59" t="n">
         <v>-1341</v>
       </c>
       <c r="J14" s="30" t="n">
@@ -6479,12 +6472,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="L14" s="35" t="inlineStr">
+      <c r="L14" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M14" s="47" t="n">
+      <c r="M14" s="46" t="n">
         <v>535</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -6495,12 +6488,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P14" s="43" t="inlineStr">
+      <c r="P14" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q14" s="60" t="n">
+      <c r="Q14" s="59" t="n">
         <v>-739</v>
       </c>
     </row>
@@ -6513,12 +6506,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="46" t="n">
         <v>553</v>
       </c>
       <c r="E15" s="30" t="n">
@@ -6529,12 +6522,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="G15" s="35" t="inlineStr">
+      <c r="G15" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H15" s="60" t="n">
+      <c r="H15" s="59" t="n">
         <v>-1155</v>
       </c>
       <c r="J15" s="30" t="n">
@@ -6545,12 +6538,12 @@
           <t>NC</t>
         </is>
       </c>
-      <c r="L15" s="35" t="inlineStr">
+      <c r="L15" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M15" s="47" t="n">
+      <c r="M15" s="46" t="n">
         <v>507</v>
       </c>
       <c r="N15" s="30" t="n">
@@ -6561,12 +6554,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="P15" s="35" t="inlineStr">
+      <c r="P15" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q15" s="60" t="n">
+      <c r="Q15" s="59" t="n">
         <v>-682</v>
       </c>
     </row>
@@ -6577,7 +6570,7 @@
           <t>F3 외인+기관</t>
         </is>
       </c>
-      <c r="E17" s="57" t="inlineStr">
+      <c r="E17" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -6587,111 +6580,111 @@
           <t>F4 개인</t>
         </is>
       </c>
-      <c r="N17" s="57" t="inlineStr">
+      <c r="N17" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="58" t="inlineStr">
+      <c r="A18" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E18" s="59" t="inlineStr">
+      <c r="E18" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J18" s="58" t="inlineStr">
+      <c r="J18" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N18" s="59" t="inlineStr">
+      <c r="N18" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C19" s="45" t="inlineStr">
+      <c r="C19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D19" s="45" t="inlineStr">
+      <c r="D19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E19" s="45" t="inlineStr">
+      <c r="E19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F19" s="45" t="inlineStr">
+      <c r="F19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G19" s="45" t="inlineStr">
+      <c r="G19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H19" s="45" t="inlineStr">
+      <c r="H19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J19" s="45" t="inlineStr">
+      <c r="J19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K19" s="45" t="inlineStr">
+      <c r="K19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L19" s="45" t="inlineStr">
+      <c r="L19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M19" s="45" t="inlineStr">
+      <c r="M19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N19" s="45" t="inlineStr">
+      <c r="N19" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O19" s="45" t="inlineStr">
+      <c r="O19" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P19" s="45" t="inlineStr">
+      <c r="P19" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q19" s="45" t="inlineStr">
+      <c r="Q19" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -6706,12 +6699,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D20" s="46" t="n">
         <v>2790</v>
       </c>
       <c r="E20" s="30" t="n">
@@ -6722,12 +6715,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G20" s="35" t="inlineStr">
+      <c r="G20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H20" s="60" t="n">
+      <c r="H20" s="59" t="n">
         <v>-43484</v>
       </c>
       <c r="J20" s="30" t="n">
@@ -6738,12 +6731,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L20" s="35" t="inlineStr">
+      <c r="L20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M20" s="47" t="n">
+      <c r="M20" s="46" t="n">
         <v>9614</v>
       </c>
       <c r="N20" s="30" t="n">
@@ -6754,12 +6747,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="P20" s="35" t="inlineStr">
+      <c r="P20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q20" s="60" t="n">
+      <c r="Q20" s="59" t="n">
         <v>-2942</v>
       </c>
     </row>
@@ -6772,12 +6765,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="D21" s="46" t="n">
         <v>2564</v>
       </c>
       <c r="E21" s="30" t="n">
@@ -6788,12 +6781,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G21" s="35" t="inlineStr">
+      <c r="G21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H21" s="60" t="n">
+      <c r="H21" s="59" t="n">
         <v>-23470</v>
       </c>
       <c r="J21" s="30" t="n">
@@ -6804,12 +6797,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="L21" s="35" t="inlineStr">
+      <c r="L21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M21" s="47" t="n">
+      <c r="M21" s="46" t="n">
         <v>3244</v>
       </c>
       <c r="N21" s="30" t="n">
@@ -6820,12 +6813,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="P21" s="35" t="inlineStr">
+      <c r="P21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q21" s="60" t="n">
+      <c r="Q21" s="59" t="n">
         <v>-2573</v>
       </c>
     </row>
@@ -6838,12 +6831,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="D22" s="46" t="n">
         <v>1859</v>
       </c>
       <c r="E22" s="30" t="n">
@@ -6854,12 +6847,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G22" s="35" t="inlineStr">
+      <c r="G22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H22" s="60" t="n">
+      <c r="H22" s="59" t="n">
         <v>-3243</v>
       </c>
       <c r="J22" s="30" t="n">
@@ -6870,12 +6863,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L22" s="35" t="inlineStr">
+      <c r="L22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M22" s="47" t="n">
+      <c r="M22" s="46" t="n">
         <v>2660</v>
       </c>
       <c r="N22" s="30" t="n">
@@ -6886,12 +6879,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="P22" s="35" t="inlineStr">
+      <c r="P22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q22" s="60" t="n">
+      <c r="Q22" s="59" t="n">
         <v>-1820</v>
       </c>
     </row>
@@ -6904,12 +6897,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="46" t="n">
         <v>1646</v>
       </c>
       <c r="E23" s="30" t="n">
@@ -6920,12 +6913,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G23" s="43" t="inlineStr">
+      <c r="G23" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H23" s="60" t="n">
+      <c r="H23" s="59" t="n">
         <v>-2591</v>
       </c>
       <c r="J23" s="30" t="n">
@@ -6936,12 +6929,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="L23" s="43" t="inlineStr">
+      <c r="L23" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M23" s="47" t="n">
+      <c r="M23" s="46" t="n">
         <v>2569</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -6952,12 +6945,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="P23" s="35" t="inlineStr">
+      <c r="P23" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q23" s="60" t="n">
+      <c r="Q23" s="59" t="n">
         <v>-1562</v>
       </c>
     </row>
@@ -6970,12 +6963,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="D24" s="46" t="n">
         <v>1202</v>
       </c>
       <c r="E24" s="30" t="n">
@@ -6986,12 +6979,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G24" s="35" t="inlineStr">
+      <c r="G24" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H24" s="60" t="n">
+      <c r="H24" s="59" t="n">
         <v>-2340</v>
       </c>
       <c r="J24" s="30" t="n">
@@ -7002,12 +6995,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="L24" s="35" t="inlineStr">
+      <c r="L24" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M24" s="47" t="n">
+      <c r="M24" s="46" t="n">
         <v>2328</v>
       </c>
       <c r="N24" s="30" t="n">
@@ -7018,12 +7011,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P24" s="35" t="inlineStr">
+      <c r="P24" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q24" s="60" t="n">
+      <c r="Q24" s="59" t="n">
         <v>-1206</v>
       </c>
     </row>
@@ -7036,12 +7029,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="46" t="n">
         <v>856</v>
       </c>
       <c r="E25" s="30" t="n">
@@ -7052,12 +7045,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G25" s="35" t="inlineStr">
+      <c r="G25" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H25" s="60" t="n">
+      <c r="H25" s="59" t="n">
         <v>-2171</v>
       </c>
       <c r="J25" s="30" t="n">
@@ -7068,12 +7061,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="L25" s="35" t="inlineStr">
+      <c r="L25" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M25" s="47" t="n">
+      <c r="M25" s="46" t="n">
         <v>2168</v>
       </c>
       <c r="N25" s="30" t="n">
@@ -7084,12 +7077,12 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="P25" s="35" t="inlineStr">
+      <c r="P25" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="Q25" s="60" t="n">
+      <c r="Q25" s="59" t="n">
         <v>-857</v>
       </c>
     </row>
@@ -7102,12 +7095,12 @@
           <t>고영</t>
         </is>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D26" s="47" t="n">
+      <c r="D26" s="46" t="n">
         <v>606</v>
       </c>
       <c r="E26" s="30" t="n">
@@ -7118,12 +7111,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G26" s="35" t="inlineStr">
+      <c r="G26" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H26" s="60" t="n">
+      <c r="H26" s="59" t="n">
         <v>-1807</v>
       </c>
       <c r="J26" s="30" t="n">
@@ -7134,12 +7127,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L26" s="35" t="inlineStr">
+      <c r="L26" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M26" s="47" t="n">
+      <c r="M26" s="46" t="n">
         <v>1914</v>
       </c>
       <c r="N26" s="30" t="n">
@@ -7150,12 +7143,12 @@
           <t>고영</t>
         </is>
       </c>
-      <c r="P26" s="35" t="inlineStr">
+      <c r="P26" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q26" s="60" t="n">
+      <c r="Q26" s="59" t="n">
         <v>-632</v>
       </c>
     </row>
@@ -7168,12 +7161,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="46" t="n">
         <v>600</v>
       </c>
       <c r="E27" s="30" t="n">
@@ -7184,12 +7177,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="G27" s="43" t="inlineStr">
+      <c r="G27" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H27" s="60" t="n">
+      <c r="H27" s="59" t="n">
         <v>-1766</v>
       </c>
       <c r="J27" s="30" t="n">
@@ -7200,12 +7193,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="L27" s="43" t="inlineStr">
+      <c r="L27" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M27" s="47" t="n">
+      <c r="M27" s="46" t="n">
         <v>1753</v>
       </c>
       <c r="N27" s="30" t="n">
@@ -7216,12 +7209,12 @@
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="P27" s="35" t="inlineStr">
+      <c r="P27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q27" s="60" t="n">
+      <c r="Q27" s="59" t="n">
         <v>-604</v>
       </c>
     </row>
@@ -7234,12 +7227,12 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D28" s="47" t="n">
+      <c r="D28" s="46" t="n">
         <v>574</v>
       </c>
       <c r="E28" s="30" t="n">
@@ -7250,12 +7243,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="G28" s="35" t="inlineStr">
+      <c r="G28" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H28" s="60" t="n">
+      <c r="H28" s="59" t="n">
         <v>-1292</v>
       </c>
       <c r="J28" s="30" t="n">
@@ -7266,12 +7259,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="L28" s="35" t="inlineStr">
+      <c r="L28" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M28" s="47" t="n">
+      <c r="M28" s="46" t="n">
         <v>1248</v>
       </c>
       <c r="N28" s="30" t="n">
@@ -7282,12 +7275,12 @@
           <t>한화솔루션</t>
         </is>
       </c>
-      <c r="P28" s="35" t="inlineStr">
+      <c r="P28" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q28" s="60" t="n">
+      <c r="Q28" s="59" t="n">
         <v>-591</v>
       </c>
     </row>
@@ -7300,12 +7293,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D29" s="47" t="n">
+      <c r="D29" s="46" t="n">
         <v>490</v>
       </c>
       <c r="E29" s="30" t="n">
@@ -7316,12 +7309,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="G29" s="35" t="inlineStr">
+      <c r="G29" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H29" s="60" t="n">
+      <c r="H29" s="59" t="n">
         <v>-1133</v>
       </c>
       <c r="J29" s="30" t="n">
@@ -7332,12 +7325,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="L29" s="35" t="inlineStr">
+      <c r="L29" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M29" s="47" t="n">
+      <c r="M29" s="46" t="n">
         <v>1067</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -7348,12 +7341,12 @@
           <t>에이피알</t>
         </is>
       </c>
-      <c r="P29" s="35" t="inlineStr">
+      <c r="P29" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q29" s="60" t="n">
+      <c r="Q29" s="59" t="n">
         <v>-485</v>
       </c>
     </row>
@@ -7364,7 +7357,7 @@
           <t>F5 금융투자</t>
         </is>
       </c>
-      <c r="E31" s="57" t="inlineStr">
+      <c r="E31" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -7374,111 +7367,111 @@
           <t>F6 투신(사모)</t>
         </is>
       </c>
-      <c r="N31" s="57" t="inlineStr">
+      <c r="N31" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="58" t="inlineStr">
+      <c r="A32" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E32" s="59" t="inlineStr">
+      <c r="E32" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J32" s="58" t="inlineStr">
+      <c r="J32" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N32" s="59" t="inlineStr">
+      <c r="N32" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="45" t="inlineStr">
+      <c r="A33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C33" s="45" t="inlineStr">
+      <c r="C33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D33" s="45" t="inlineStr">
+      <c r="D33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E33" s="45" t="inlineStr">
+      <c r="E33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F33" s="45" t="inlineStr">
+      <c r="F33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G33" s="45" t="inlineStr">
+      <c r="G33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H33" s="45" t="inlineStr">
+      <c r="H33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J33" s="45" t="inlineStr">
+      <c r="J33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K33" s="45" t="inlineStr">
+      <c r="K33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L33" s="45" t="inlineStr">
+      <c r="L33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M33" s="45" t="inlineStr">
+      <c r="M33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N33" s="45" t="inlineStr">
+      <c r="N33" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O33" s="45" t="inlineStr">
+      <c r="O33" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P33" s="45" t="inlineStr">
+      <c r="P33" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q33" s="45" t="inlineStr">
+      <c r="Q33" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -7493,12 +7486,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="C34" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="46" t="n">
         <v>1090</v>
       </c>
       <c r="E34" s="30" t="n">
@@ -7509,12 +7502,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G34" s="35" t="inlineStr">
+      <c r="G34" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H34" s="60" t="n">
+      <c r="H34" s="59" t="n">
         <v>-10388</v>
       </c>
       <c r="J34" s="30" t="n">
@@ -7525,12 +7518,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L34" s="35" t="inlineStr">
+      <c r="L34" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M34" s="47" t="n">
+      <c r="M34" s="46" t="n">
         <v>4098</v>
       </c>
       <c r="N34" s="30" t="n">
@@ -7541,12 +7534,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P34" s="35" t="inlineStr">
+      <c r="P34" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q34" s="60" t="n">
+      <c r="Q34" s="59" t="n">
         <v>-2236</v>
       </c>
     </row>
@@ -7559,12 +7552,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D35" s="47" t="n">
+      <c r="D35" s="46" t="n">
         <v>988</v>
       </c>
       <c r="E35" s="30" t="n">
@@ -7575,12 +7568,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G35" s="35" t="inlineStr">
+      <c r="G35" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H35" s="60" t="n">
+      <c r="H35" s="59" t="n">
         <v>-5967</v>
       </c>
       <c r="J35" s="30" t="n">
@@ -7591,12 +7584,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L35" s="35" t="inlineStr">
+      <c r="L35" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M35" s="47" t="n">
+      <c r="M35" s="46" t="n">
         <v>2746</v>
       </c>
       <c r="N35" s="30" t="n">
@@ -7607,12 +7600,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="P35" s="35" t="inlineStr">
+      <c r="P35" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q35" s="60" t="n">
+      <c r="Q35" s="59" t="n">
         <v>-982</v>
       </c>
     </row>
@@ -7625,12 +7618,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C36" s="35" t="inlineStr">
+      <c r="C36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D36" s="47" t="n">
+      <c r="D36" s="46" t="n">
         <v>540</v>
       </c>
       <c r="E36" s="30" t="n">
@@ -7641,12 +7634,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G36" s="35" t="inlineStr">
+      <c r="G36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H36" s="60" t="n">
+      <c r="H36" s="59" t="n">
         <v>-1700</v>
       </c>
       <c r="J36" s="30" t="n">
@@ -7657,12 +7650,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L36" s="35" t="inlineStr">
+      <c r="L36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M36" s="47" t="n">
+      <c r="M36" s="46" t="n">
         <v>983</v>
       </c>
       <c r="N36" s="30" t="n">
@@ -7673,12 +7666,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="P36" s="35" t="inlineStr">
+      <c r="P36" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q36" s="60" t="n">
+      <c r="Q36" s="59" t="n">
         <v>-947</v>
       </c>
     </row>
@@ -7691,12 +7684,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C37" s="35" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D37" s="47" t="n">
+      <c r="D37" s="46" t="n">
         <v>507</v>
       </c>
       <c r="E37" s="30" t="n">
@@ -7707,12 +7700,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G37" s="35" t="inlineStr">
+      <c r="G37" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H37" s="60" t="n">
+      <c r="H37" s="59" t="n">
         <v>-929</v>
       </c>
       <c r="J37" s="30" t="n">
@@ -7723,12 +7716,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L37" s="35" t="inlineStr">
+      <c r="L37" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M37" s="47" t="n">
+      <c r="M37" s="46" t="n">
         <v>901</v>
       </c>
       <c r="N37" s="30" t="n">
@@ -7739,12 +7732,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="P37" s="35" t="inlineStr">
+      <c r="P37" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q37" s="60" t="n">
+      <c r="Q37" s="59" t="n">
         <v>-882</v>
       </c>
     </row>
@@ -7757,12 +7750,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="C38" s="35" t="inlineStr">
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D38" s="47" t="n">
+      <c r="D38" s="46" t="n">
         <v>480</v>
       </c>
       <c r="E38" s="30" t="n">
@@ -7773,12 +7766,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="G38" s="35" t="inlineStr">
+      <c r="G38" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H38" s="60" t="n">
+      <c r="H38" s="59" t="n">
         <v>-437</v>
       </c>
       <c r="J38" s="30" t="n">
@@ -7789,12 +7782,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L38" s="35" t="inlineStr">
+      <c r="L38" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M38" s="47" t="n">
+      <c r="M38" s="46" t="n">
         <v>823</v>
       </c>
       <c r="N38" s="30" t="n">
@@ -7805,12 +7798,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="P38" s="35" t="inlineStr">
+      <c r="P38" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q38" s="60" t="n">
+      <c r="Q38" s="59" t="n">
         <v>-707</v>
       </c>
     </row>
@@ -7823,12 +7816,12 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="C39" s="35" t="inlineStr">
+      <c r="C39" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="D39" s="47" t="n">
+      <c r="D39" s="46" t="n">
         <v>447</v>
       </c>
       <c r="E39" s="30" t="n">
@@ -7839,12 +7832,12 @@
           <t>대한항공</t>
         </is>
       </c>
-      <c r="G39" s="35" t="inlineStr">
+      <c r="G39" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="H39" s="60" t="n">
+      <c r="H39" s="59" t="n">
         <v>-361</v>
       </c>
       <c r="J39" s="30" t="n">
@@ -7855,12 +7848,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L39" s="35" t="inlineStr">
+      <c r="L39" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M39" s="47" t="n">
+      <c r="M39" s="46" t="n">
         <v>728</v>
       </c>
       <c r="N39" s="30" t="n">
@@ -7871,12 +7864,12 @@
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="P39" s="35" t="inlineStr">
+      <c r="P39" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q39" s="60" t="n">
+      <c r="Q39" s="59" t="n">
         <v>-663</v>
       </c>
     </row>
@@ -7889,12 +7882,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="C40" s="35" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D40" s="47" t="n">
+      <c r="D40" s="46" t="n">
         <v>425</v>
       </c>
       <c r="E40" s="30" t="n">
@@ -7905,12 +7898,12 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="G40" s="35" t="inlineStr">
+      <c r="G40" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H40" s="60" t="n">
+      <c r="H40" s="59" t="n">
         <v>-318</v>
       </c>
       <c r="J40" s="30" t="n">
@@ -7921,12 +7914,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="L40" s="35" t="inlineStr">
+      <c r="L40" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M40" s="47" t="n">
+      <c r="M40" s="46" t="n">
         <v>524</v>
       </c>
       <c r="N40" s="30" t="n">
@@ -7937,12 +7930,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P40" s="35" t="inlineStr">
+      <c r="P40" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q40" s="60" t="n">
+      <c r="Q40" s="59" t="n">
         <v>-574</v>
       </c>
     </row>
@@ -7955,12 +7948,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="C41" s="35" t="inlineStr">
+      <c r="C41" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D41" s="47" t="n">
+      <c r="D41" s="46" t="n">
         <v>405</v>
       </c>
       <c r="E41" s="30" t="n">
@@ -7971,12 +7964,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="G41" s="43" t="inlineStr">
+      <c r="G41" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H41" s="60" t="n">
+      <c r="H41" s="59" t="n">
         <v>-259</v>
       </c>
       <c r="J41" s="30" t="n">
@@ -7987,12 +7980,12 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="L41" s="35" t="inlineStr">
+      <c r="L41" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M41" s="47" t="n">
+      <c r="M41" s="46" t="n">
         <v>454</v>
       </c>
       <c r="N41" s="30" t="n">
@@ -8003,12 +7996,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="P41" s="35" t="inlineStr">
+      <c r="P41" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q41" s="60" t="n">
+      <c r="Q41" s="59" t="n">
         <v>-567</v>
       </c>
     </row>
@@ -8021,12 +8014,12 @@
           <t>LG화학</t>
         </is>
       </c>
-      <c r="C42" s="35" t="inlineStr">
+      <c r="C42" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D42" s="47" t="n">
+      <c r="D42" s="46" t="n">
         <v>382</v>
       </c>
       <c r="E42" s="30" t="n">
@@ -8037,12 +8030,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="G42" s="35" t="inlineStr">
+      <c r="G42" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H42" s="60" t="n">
+      <c r="H42" s="59" t="n">
         <v>-255</v>
       </c>
       <c r="J42" s="30" t="n">
@@ -8053,12 +8046,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="L42" s="35" t="inlineStr">
+      <c r="L42" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M42" s="47" t="n">
+      <c r="M42" s="46" t="n">
         <v>422</v>
       </c>
       <c r="N42" s="30" t="n">
@@ -8069,12 +8062,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="P42" s="43" t="inlineStr">
+      <c r="P42" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q42" s="60" t="n">
+      <c r="Q42" s="59" t="n">
         <v>-542</v>
       </c>
     </row>
@@ -8087,12 +8080,12 @@
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="C43" s="35" t="inlineStr">
+      <c r="C43" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D43" s="47" t="n">
+      <c r="D43" s="46" t="n">
         <v>245</v>
       </c>
       <c r="E43" s="30" t="n">
@@ -8103,12 +8096,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G43" s="35" t="inlineStr">
+      <c r="G43" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H43" s="60" t="n">
+      <c r="H43" s="59" t="n">
         <v>-220</v>
       </c>
       <c r="J43" s="30" t="n">
@@ -8119,12 +8112,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="L43" s="35" t="inlineStr">
+      <c r="L43" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M43" s="47" t="n">
+      <c r="M43" s="46" t="n">
         <v>360</v>
       </c>
       <c r="N43" s="30" t="n">
@@ -8135,12 +8128,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P43" s="35" t="inlineStr">
+      <c r="P43" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q43" s="60" t="n">
+      <c r="Q43" s="59" t="n">
         <v>-469</v>
       </c>
     </row>
@@ -8151,7 +8144,7 @@
           <t>F7 연기금</t>
         </is>
       </c>
-      <c r="E45" s="57" t="inlineStr">
+      <c r="E45" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -8161,111 +8154,111 @@
           <t>F8 보험</t>
         </is>
       </c>
-      <c r="N45" s="57" t="inlineStr">
+      <c r="N45" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="58" t="inlineStr">
+      <c r="A46" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E46" s="59" t="inlineStr">
+      <c r="E46" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J46" s="58" t="inlineStr">
+      <c r="J46" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N46" s="59" t="inlineStr">
+      <c r="N46" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="45" t="inlineStr">
+      <c r="A47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B47" s="45" t="inlineStr">
+      <c r="B47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C47" s="45" t="inlineStr">
+      <c r="C47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D47" s="45" t="inlineStr">
+      <c r="D47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E47" s="45" t="inlineStr">
+      <c r="E47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F47" s="45" t="inlineStr">
+      <c r="F47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G47" s="45" t="inlineStr">
+      <c r="G47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H47" s="45" t="inlineStr">
+      <c r="H47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J47" s="45" t="inlineStr">
+      <c r="J47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K47" s="45" t="inlineStr">
+      <c r="K47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L47" s="45" t="inlineStr">
+      <c r="L47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M47" s="45" t="inlineStr">
+      <c r="M47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N47" s="45" t="inlineStr">
+      <c r="N47" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O47" s="45" t="inlineStr">
+      <c r="O47" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P47" s="45" t="inlineStr">
+      <c r="P47" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q47" s="45" t="inlineStr">
+      <c r="Q47" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -8280,12 +8273,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C48" s="35" t="inlineStr">
+      <c r="C48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D48" s="47" t="n">
+      <c r="D48" s="46" t="n">
         <v>1194</v>
       </c>
       <c r="E48" s="30" t="n">
@@ -8296,12 +8289,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="G48" s="35" t="inlineStr">
+      <c r="G48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H48" s="60" t="n">
+      <c r="H48" s="59" t="n">
         <v>-1149</v>
       </c>
       <c r="J48" s="30" t="n">
@@ -8312,12 +8305,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L48" s="35" t="inlineStr">
+      <c r="L48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M48" s="47" t="n">
+      <c r="M48" s="46" t="n">
         <v>241</v>
       </c>
       <c r="N48" s="30" t="n">
@@ -8328,12 +8321,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P48" s="35" t="inlineStr">
+      <c r="P48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q48" s="60" t="n">
+      <c r="Q48" s="59" t="n">
         <v>-170</v>
       </c>
     </row>
@@ -8346,12 +8339,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C49" s="35" t="inlineStr">
+      <c r="C49" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D49" s="47" t="n">
+      <c r="D49" s="46" t="n">
         <v>925</v>
       </c>
       <c r="E49" s="30" t="n">
@@ -8362,12 +8355,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G49" s="43" t="inlineStr">
+      <c r="G49" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H49" s="60" t="n">
+      <c r="H49" s="59" t="n">
         <v>-839</v>
       </c>
       <c r="J49" s="30" t="n">
@@ -8378,12 +8371,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L49" s="35" t="inlineStr">
+      <c r="L49" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M49" s="47" t="n">
+      <c r="M49" s="46" t="n">
         <v>237</v>
       </c>
       <c r="N49" s="30" t="n">
@@ -8394,12 +8387,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P49" s="35" t="inlineStr">
+      <c r="P49" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q49" s="60" t="n">
+      <c r="Q49" s="59" t="n">
         <v>-101</v>
       </c>
     </row>
@@ -8412,12 +8405,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C50" s="35" t="inlineStr">
+      <c r="C50" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D50" s="47" t="n">
+      <c r="D50" s="46" t="n">
         <v>602</v>
       </c>
       <c r="E50" s="30" t="n">
@@ -8428,12 +8421,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="G50" s="43" t="inlineStr">
+      <c r="G50" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H50" s="60" t="n">
+      <c r="H50" s="59" t="n">
         <v>-580</v>
       </c>
       <c r="J50" s="30" t="n">
@@ -8444,12 +8437,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L50" s="35" t="inlineStr">
+      <c r="L50" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M50" s="47" t="n">
+      <c r="M50" s="46" t="n">
         <v>95</v>
       </c>
       <c r="N50" s="30" t="n">
@@ -8460,12 +8453,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P50" s="35" t="inlineStr">
+      <c r="P50" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q50" s="60" t="n">
+      <c r="Q50" s="59" t="n">
         <v>-70</v>
       </c>
     </row>
@@ -8478,12 +8471,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="C51" s="35" t="inlineStr">
+      <c r="C51" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D51" s="47" t="n">
+      <c r="D51" s="46" t="n">
         <v>585</v>
       </c>
       <c r="E51" s="30" t="n">
@@ -8494,12 +8487,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G51" s="35" t="inlineStr">
+      <c r="G51" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H51" s="60" t="n">
+      <c r="H51" s="59" t="n">
         <v>-557</v>
       </c>
       <c r="J51" s="30" t="n">
@@ -8510,12 +8503,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="L51" s="35" t="inlineStr">
+      <c r="L51" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M51" s="47" t="n">
+      <c r="M51" s="46" t="n">
         <v>82</v>
       </c>
       <c r="N51" s="30" t="n">
@@ -8526,12 +8519,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P51" s="43" t="inlineStr">
+      <c r="P51" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q51" s="60" t="n">
+      <c r="Q51" s="59" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -8544,12 +8537,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C52" s="35" t="inlineStr">
+      <c r="C52" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D52" s="47" t="n">
+      <c r="D52" s="46" t="n">
         <v>447</v>
       </c>
       <c r="E52" s="30" t="n">
@@ -8560,12 +8553,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="G52" s="35" t="inlineStr">
+      <c r="G52" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="H52" s="60" t="n">
+      <c r="H52" s="59" t="n">
         <v>-429</v>
       </c>
       <c r="J52" s="30" t="n">
@@ -8576,12 +8569,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L52" s="35" t="inlineStr">
+      <c r="L52" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M52" s="47" t="n">
+      <c r="M52" s="46" t="n">
         <v>79</v>
       </c>
       <c r="N52" s="30" t="n">
@@ -8592,12 +8585,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="P52" s="35" t="inlineStr">
+      <c r="P52" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q52" s="60" t="n">
+      <c r="Q52" s="59" t="n">
         <v>-58</v>
       </c>
     </row>
@@ -8610,12 +8603,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="C53" s="35" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D53" s="47" t="n">
+      <c r="D53" s="46" t="n">
         <v>432</v>
       </c>
       <c r="E53" s="30" t="n">
@@ -8626,12 +8619,12 @@
           <t>HD한국조선해양</t>
         </is>
       </c>
-      <c r="G53" s="35" t="inlineStr">
+      <c r="G53" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H53" s="60" t="n">
+      <c r="H53" s="59" t="n">
         <v>-352</v>
       </c>
       <c r="J53" s="30" t="n">
@@ -8642,12 +8635,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L53" s="35" t="inlineStr">
+      <c r="L53" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M53" s="47" t="n">
+      <c r="M53" s="46" t="n">
         <v>77</v>
       </c>
       <c r="N53" s="30" t="n">
@@ -8658,12 +8651,12 @@
           <t>신한지주</t>
         </is>
       </c>
-      <c r="P53" s="35" t="inlineStr">
+      <c r="P53" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q53" s="60" t="n">
+      <c r="Q53" s="59" t="n">
         <v>-55</v>
       </c>
     </row>
@@ -8676,12 +8669,12 @@
           <t>NC</t>
         </is>
       </c>
-      <c r="C54" s="35" t="inlineStr">
+      <c r="C54" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D54" s="47" t="n">
+      <c r="D54" s="46" t="n">
         <v>385</v>
       </c>
       <c r="E54" s="30" t="n">
@@ -8692,12 +8685,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G54" s="43" t="inlineStr">
+      <c r="G54" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H54" s="60" t="n">
+      <c r="H54" s="59" t="n">
         <v>-330</v>
       </c>
       <c r="J54" s="30" t="n">
@@ -8708,12 +8701,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="L54" s="35" t="inlineStr">
+      <c r="L54" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M54" s="47" t="n">
+      <c r="M54" s="46" t="n">
         <v>73</v>
       </c>
       <c r="N54" s="30" t="n">
@@ -8724,12 +8717,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="P54" s="43" t="inlineStr">
+      <c r="P54" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q54" s="60" t="n">
+      <c r="Q54" s="59" t="n">
         <v>-51</v>
       </c>
     </row>
@@ -8742,12 +8735,12 @@
           <t>우리금융지주</t>
         </is>
       </c>
-      <c r="C55" s="35" t="inlineStr">
+      <c r="C55" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D55" s="47" t="n">
+      <c r="D55" s="46" t="n">
         <v>217</v>
       </c>
       <c r="E55" s="30" t="n">
@@ -8758,12 +8751,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="G55" s="35" t="inlineStr">
+      <c r="G55" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H55" s="60" t="n">
+      <c r="H55" s="59" t="n">
         <v>-324</v>
       </c>
       <c r="J55" s="30" t="n">
@@ -8774,12 +8767,12 @@
           <t>포스코퓨처엠</t>
         </is>
       </c>
-      <c r="L55" s="35" t="inlineStr">
+      <c r="L55" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M55" s="47" t="n">
+      <c r="M55" s="46" t="n">
         <v>49</v>
       </c>
       <c r="N55" s="30" t="n">
@@ -8790,12 +8783,12 @@
           <t>LS</t>
         </is>
       </c>
-      <c r="P55" s="35" t="inlineStr">
+      <c r="P55" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q55" s="60" t="n">
+      <c r="Q55" s="59" t="n">
         <v>-46</v>
       </c>
     </row>
@@ -8808,12 +8801,12 @@
           <t>LG화학</t>
         </is>
       </c>
-      <c r="C56" s="35" t="inlineStr">
+      <c r="C56" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D56" s="47" t="n">
+      <c r="D56" s="46" t="n">
         <v>198</v>
       </c>
       <c r="E56" s="30" t="n">
@@ -8824,12 +8817,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="G56" s="35" t="inlineStr">
+      <c r="G56" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H56" s="60" t="n">
+      <c r="H56" s="59" t="n">
         <v>-268</v>
       </c>
       <c r="J56" s="30" t="n">
@@ -8840,12 +8833,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="L56" s="43" t="inlineStr">
+      <c r="L56" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M56" s="47" t="n">
+      <c r="M56" s="46" t="n">
         <v>33</v>
       </c>
       <c r="N56" s="30" t="n">
@@ -8856,12 +8849,12 @@
           <t>HD한국조선해양</t>
         </is>
       </c>
-      <c r="P56" s="35" t="inlineStr">
+      <c r="P56" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q56" s="60" t="n">
+      <c r="Q56" s="59" t="n">
         <v>-38</v>
       </c>
     </row>
@@ -8874,12 +8867,12 @@
           <t>올릭스</t>
         </is>
       </c>
-      <c r="C57" s="35" t="inlineStr">
+      <c r="C57" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D57" s="47" t="n">
+      <c r="D57" s="46" t="n">
         <v>170</v>
       </c>
       <c r="E57" s="30" t="n">
@@ -8890,12 +8883,12 @@
           <t>LS ELECTRIC</t>
         </is>
       </c>
-      <c r="G57" s="35" t="inlineStr">
+      <c r="G57" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H57" s="60" t="n">
+      <c r="H57" s="59" t="n">
         <v>-217</v>
       </c>
       <c r="J57" s="30" t="n">
@@ -8906,12 +8899,12 @@
           <t>NC</t>
         </is>
       </c>
-      <c r="L57" s="35" t="inlineStr">
+      <c r="L57" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M57" s="47" t="n">
+      <c r="M57" s="46" t="n">
         <v>32</v>
       </c>
       <c r="N57" s="30" t="n">
@@ -8922,12 +8915,12 @@
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="P57" s="35" t="inlineStr">
+      <c r="P57" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q57" s="60" t="n">
+      <c r="Q57" s="59" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -8938,61 +8931,61 @@
           <t>F9 기타법인</t>
         </is>
       </c>
-      <c r="E59" s="57" t="inlineStr">
+      <c r="E59" s="56" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="58" t="inlineStr">
+      <c r="A60" s="57" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E60" s="59" t="inlineStr">
+      <c r="E60" s="58" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="45" t="inlineStr">
+      <c r="A61" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B61" s="45" t="inlineStr">
+      <c r="B61" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C61" s="45" t="inlineStr">
+      <c r="C61" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D61" s="45" t="inlineStr">
+      <c r="D61" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E61" s="45" t="inlineStr">
+      <c r="E61" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F61" s="45" t="inlineStr">
+      <c r="F61" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G61" s="45" t="inlineStr">
+      <c r="G61" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H61" s="45" t="inlineStr">
+      <c r="H61" s="44" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -9007,12 +9000,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C62" s="35" t="inlineStr">
+      <c r="C62" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D62" s="47" t="n">
+      <c r="D62" s="46" t="n">
         <v>40824</v>
       </c>
       <c r="E62" s="30" t="n">
@@ -9023,12 +9016,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="G62" s="35" t="inlineStr">
+      <c r="G62" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H62" s="60" t="n">
+      <c r="H62" s="59" t="n">
         <v>-222</v>
       </c>
     </row>
@@ -9041,12 +9034,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C63" s="35" t="inlineStr">
+      <c r="C63" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D63" s="47" t="n">
+      <c r="D63" s="46" t="n">
         <v>13856</v>
       </c>
       <c r="E63" s="30" t="n">
@@ -9057,12 +9050,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G63" s="35" t="inlineStr">
+      <c r="G63" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H63" s="60" t="n">
+      <c r="H63" s="59" t="n">
         <v>-107</v>
       </c>
     </row>
@@ -9075,12 +9068,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="C64" s="35" t="inlineStr">
+      <c r="C64" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D64" s="47" t="n">
+      <c r="D64" s="46" t="n">
         <v>185</v>
       </c>
       <c r="E64" s="30" t="n">
@@ -9091,12 +9084,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="G64" s="35" t="inlineStr">
+      <c r="G64" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H64" s="60" t="n">
+      <c r="H64" s="59" t="n">
         <v>-86</v>
       </c>
     </row>
@@ -9109,12 +9102,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C65" s="35" t="inlineStr">
+      <c r="C65" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D65" s="47" t="n">
+      <c r="D65" s="46" t="n">
         <v>152</v>
       </c>
       <c r="E65" s="30" t="n">
@@ -9125,12 +9118,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="G65" s="35" t="inlineStr">
+      <c r="G65" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H65" s="60" t="n">
+      <c r="H65" s="59" t="n">
         <v>-84</v>
       </c>
     </row>
@@ -9143,12 +9136,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C66" s="35" t="inlineStr">
+      <c r="C66" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D66" s="47" t="n">
+      <c r="D66" s="46" t="n">
         <v>83</v>
       </c>
       <c r="E66" s="30" t="n">
@@ -9159,12 +9152,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="G66" s="35" t="inlineStr">
+      <c r="G66" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H66" s="60" t="n">
+      <c r="H66" s="59" t="n">
         <v>-44</v>
       </c>
     </row>
@@ -9177,12 +9170,12 @@
           <t>KT&amp;G</t>
         </is>
       </c>
-      <c r="C67" s="35" t="inlineStr">
+      <c r="C67" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D67" s="47" t="n">
+      <c r="D67" s="46" t="n">
         <v>74</v>
       </c>
       <c r="E67" s="30" t="n">
@@ -9193,12 +9186,12 @@
           <t>피노</t>
         </is>
       </c>
-      <c r="G67" s="35" t="inlineStr">
+      <c r="G67" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H67" s="60" t="n">
+      <c r="H67" s="59" t="n">
         <v>-43</v>
       </c>
     </row>
@@ -9211,12 +9204,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="C68" s="43" t="inlineStr">
+      <c r="C68" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D68" s="47" t="n">
+      <c r="D68" s="46" t="n">
         <v>71</v>
       </c>
       <c r="E68" s="30" t="n">
@@ -9227,12 +9220,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="G68" s="35" t="inlineStr">
+      <c r="G68" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H68" s="60" t="n">
+      <c r="H68" s="59" t="n">
         <v>-39</v>
       </c>
     </row>
@@ -9245,12 +9238,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C69" s="35" t="inlineStr">
+      <c r="C69" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D69" s="47" t="n">
+      <c r="D69" s="46" t="n">
         <v>66</v>
       </c>
       <c r="E69" s="30" t="n">
@@ -9261,12 +9254,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="G69" s="35" t="inlineStr">
+      <c r="G69" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H69" s="60" t="n">
+      <c r="H69" s="59" t="n">
         <v>-29</v>
       </c>
     </row>
@@ -9279,12 +9272,12 @@
           <t>리노공업</t>
         </is>
       </c>
-      <c r="C70" s="35" t="inlineStr">
+      <c r="C70" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D70" s="47" t="n">
+      <c r="D70" s="46" t="n">
         <v>58</v>
       </c>
       <c r="E70" s="30" t="n">
@@ -9295,12 +9288,12 @@
           <t>포스코퓨처엠</t>
         </is>
       </c>
-      <c r="G70" s="35" t="inlineStr">
+      <c r="G70" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H70" s="60" t="n">
+      <c r="H70" s="59" t="n">
         <v>-22</v>
       </c>
     </row>
@@ -9313,12 +9306,12 @@
           <t>서진시스템</t>
         </is>
       </c>
-      <c r="C71" s="35" t="inlineStr">
+      <c r="C71" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D71" s="47" t="n">
+      <c r="D71" s="46" t="n">
         <v>54</v>
       </c>
       <c r="E71" s="30" t="n">
@@ -9329,18 +9322,18 @@
           <t>롯데쇼핑</t>
         </is>
       </c>
-      <c r="G71" s="35" t="inlineStr">
+      <c r="G71" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="H71" s="60" t="n">
+      <c r="H71" s="59" t="n">
         <v>-22</v>
       </c>
     </row>
     <row r="72"/>
     <row r="73" ht="31" customHeight="1" s="15">
-      <c r="A73" s="61" t="inlineStr">
+      <c r="A73" s="60" t="inlineStr">
         <is>
           <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드, 기타법인=일반법인(자사주 매입 등) (확정 병합분) · 외인+기관=합산 카드와 동일</t>
         </is>
@@ -9458,87 +9451,87 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>금액(억)</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="44" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="44" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="44" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="N4" s="44" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O4" s="45" t="inlineStr">
+      <c r="O4" s="44" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P4" s="45" t="inlineStr">
+      <c r="P4" s="44" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q4" s="45" t="inlineStr">
+      <c r="Q4" s="44" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="R4" s="45" t="inlineStr">
+      <c r="R4" s="44" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="S4" s="45" t="inlineStr">
+      <c r="S4" s="44" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
@@ -9553,15 +9546,15 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D5" s="62" t="n">
+      <c r="D5" s="61" t="n">
         <v>13947</v>
       </c>
-      <c r="E5" s="63" t="n">
+      <c r="E5" s="62" t="n">
         <v>0.11</v>
       </c>
       <c r="G5" s="30" t="n">
@@ -9572,18 +9565,18 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J5" s="47" t="n">
+      <c r="J5" s="46" t="n">
         <v>18929.1</v>
       </c>
-      <c r="K5" s="64" t="n">
+      <c r="K5" s="63" t="n">
         <v>218646.7</v>
       </c>
-      <c r="L5" s="63" t="n">
+      <c r="L5" s="62" t="n">
         <v>1.39</v>
       </c>
       <c r="N5" s="30" t="n">
@@ -9594,18 +9587,18 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P5" s="35" t="inlineStr">
+      <c r="P5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q5" s="60" t="n">
+      <c r="Q5" s="59" t="n">
         <v>-23343.8</v>
       </c>
-      <c r="R5" s="64" t="n">
+      <c r="R5" s="63" t="n">
         <v>202373.3</v>
       </c>
-      <c r="S5" s="63" t="n">
+      <c r="S5" s="62" t="n">
         <v>1.61</v>
       </c>
     </row>
@@ -9618,15 +9611,15 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="62" t="n">
+      <c r="D6" s="61" t="n">
         <v>9931</v>
       </c>
-      <c r="E6" s="63" t="n">
+      <c r="E6" s="62" t="n">
         <v>0.06</v>
       </c>
       <c r="G6" s="30" t="n">
@@ -9637,18 +9630,18 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="I6" s="43" t="inlineStr">
+      <c r="I6" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="J6" s="47" t="n">
+      <c r="J6" s="46" t="n">
         <v>3387.4</v>
       </c>
-      <c r="K6" s="64" t="n">
+      <c r="K6" s="63" t="n">
         <v>8326.6</v>
       </c>
-      <c r="L6" s="63" t="n">
+      <c r="L6" s="62" t="n">
         <v>2.48</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -9659,18 +9652,18 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P6" s="43" t="inlineStr">
+      <c r="P6" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q6" s="60" t="n">
+      <c r="Q6" s="59" t="n">
         <v>-2385.4</v>
       </c>
-      <c r="R6" s="64" t="n">
+      <c r="R6" s="63" t="n">
         <v>25550.3</v>
       </c>
-      <c r="S6" s="63" t="n">
+      <c r="S6" s="62" t="n">
         <v>6.09</v>
       </c>
     </row>
@@ -9683,15 +9676,15 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D7" s="62" t="n">
+      <c r="D7" s="61" t="n">
         <v>2690</v>
       </c>
-      <c r="E7" s="63" t="n">
+      <c r="E7" s="62" t="n">
         <v>0.52</v>
       </c>
       <c r="G7" s="30" t="n">
@@ -9702,18 +9695,18 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="I7" s="35" t="inlineStr">
+      <c r="I7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="46" t="n">
         <v>2945.2</v>
       </c>
-      <c r="K7" s="64" t="n">
+      <c r="K7" s="63" t="n">
         <v>35913.1</v>
       </c>
-      <c r="L7" s="63" t="n">
+      <c r="L7" s="62" t="n">
         <v>3.93</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -9724,14 +9717,14 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P7" s="35" t="inlineStr"/>
-      <c r="Q7" s="60" t="n">
+      <c r="P7" s="34" t="inlineStr"/>
+      <c r="Q7" s="59" t="n">
         <v>-907.3</v>
       </c>
-      <c r="R7" s="64" t="n">
+      <c r="R7" s="63" t="n">
         <v>28562</v>
       </c>
-      <c r="S7" s="63" t="n">
+      <c r="S7" s="62" t="n">
         <v>4.18</v>
       </c>
     </row>
@@ -9744,15 +9737,15 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D8" s="62" t="n">
+      <c r="D8" s="61" t="n">
         <v>2272</v>
       </c>
-      <c r="E8" s="63" t="n">
+      <c r="E8" s="62" t="n">
         <v>0.15</v>
       </c>
       <c r="G8" s="30" t="n">
@@ -9763,18 +9756,18 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="I8" s="35" t="inlineStr">
+      <c r="I8" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="46" t="n">
         <v>2933.8</v>
       </c>
-      <c r="K8" s="64" t="n">
+      <c r="K8" s="63" t="n">
         <v>52517.2</v>
       </c>
-      <c r="L8" s="63" t="n">
+      <c r="L8" s="62" t="n">
         <v>20.83</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -9785,18 +9778,18 @@
           <t>한국항공우주</t>
         </is>
       </c>
-      <c r="P8" s="43" t="inlineStr">
+      <c r="P8" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q8" s="60" t="n">
+      <c r="Q8" s="59" t="n">
         <v>-800.3</v>
       </c>
-      <c r="R8" s="64" t="n">
+      <c r="R8" s="63" t="n">
         <v>13808</v>
       </c>
-      <c r="S8" s="63" t="n">
+      <c r="S8" s="62" t="n">
         <v>11.63</v>
       </c>
     </row>
@@ -9809,15 +9802,15 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D9" s="62" t="n">
+      <c r="D9" s="61" t="n">
         <v>1855</v>
       </c>
-      <c r="E9" s="63" t="n">
+      <c r="E9" s="62" t="n">
         <v>0.74</v>
       </c>
       <c r="G9" s="30" t="n">
@@ -9828,14 +9821,14 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="I9" s="35" t="inlineStr"/>
-      <c r="J9" s="47" t="n">
+      <c r="I9" s="34" t="inlineStr"/>
+      <c r="J9" s="46" t="n">
         <v>2847.6</v>
       </c>
-      <c r="K9" s="64" t="n">
+      <c r="K9" s="63" t="n">
         <v>27382.6</v>
       </c>
-      <c r="L9" s="63" t="n">
+      <c r="L9" s="62" t="n">
         <v>1.72</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -9846,18 +9839,18 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="P9" s="35" t="inlineStr">
+      <c r="P9" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="Q9" s="60" t="n">
+      <c r="Q9" s="59" t="n">
         <v>-794.2</v>
       </c>
-      <c r="R9" s="64" t="n">
+      <c r="R9" s="63" t="n">
         <v>8488.700000000001</v>
       </c>
-      <c r="S9" s="63" t="n">
+      <c r="S9" s="62" t="n">
         <v>1.44</v>
       </c>
     </row>
@@ -9870,15 +9863,15 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D10" s="62" t="n">
+      <c r="D10" s="61" t="n">
         <v>1622</v>
       </c>
-      <c r="E10" s="63" t="n">
+      <c r="E10" s="62" t="n">
         <v>0.18</v>
       </c>
       <c r="G10" s="30" t="n">
@@ -9889,18 +9882,18 @@
           <t>삼양식품</t>
         </is>
       </c>
-      <c r="I10" s="35" t="inlineStr">
+      <c r="I10" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="J10" s="47" t="n">
+      <c r="J10" s="46" t="n">
         <v>2317.4</v>
       </c>
-      <c r="K10" s="64" t="n">
+      <c r="K10" s="63" t="n">
         <v>9495.4</v>
       </c>
-      <c r="L10" s="63" t="n">
+      <c r="L10" s="62" t="n">
         <v>10.36</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -9911,18 +9904,18 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="P10" s="43" t="inlineStr">
+      <c r="P10" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q10" s="60" t="n">
+      <c r="Q10" s="59" t="n">
         <v>-583.6</v>
       </c>
-      <c r="R10" s="64" t="n">
+      <c r="R10" s="63" t="n">
         <v>12458</v>
       </c>
-      <c r="S10" s="63" t="n">
+      <c r="S10" s="62" t="n">
         <v>2.49</v>
       </c>
     </row>
@@ -9935,11 +9928,11 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr"/>
-      <c r="D11" s="62" t="n">
+      <c r="C11" s="34" t="inlineStr"/>
+      <c r="D11" s="61" t="n">
         <v>1519</v>
       </c>
-      <c r="E11" s="63" t="n">
+      <c r="E11" s="62" t="n">
         <v>0.22</v>
       </c>
       <c r="G11" s="30" t="n">
@@ -9950,18 +9943,18 @@
           <t>에코프로</t>
         </is>
       </c>
-      <c r="I11" s="35" t="inlineStr">
+      <c r="I11" s="34" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="J11" s="47" t="n">
+      <c r="J11" s="46" t="n">
         <v>2255.8</v>
       </c>
-      <c r="K11" s="64" t="n">
+      <c r="K11" s="63" t="n">
         <v>19712.3</v>
       </c>
-      <c r="L11" s="63" t="n">
+      <c r="L11" s="62" t="n">
         <v>15.8</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -9972,18 +9965,18 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr">
+      <c r="P11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q11" s="60" t="n">
+      <c r="Q11" s="59" t="n">
         <v>-549.4</v>
       </c>
-      <c r="R11" s="64" t="n">
+      <c r="R11" s="63" t="n">
         <v>9135.6</v>
       </c>
-      <c r="S11" s="63" t="n">
+      <c r="S11" s="62" t="n">
         <v>2.7</v>
       </c>
     </row>
@@ -9996,15 +9989,15 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="62" t="n">
+      <c r="D12" s="61" t="n">
         <v>1390</v>
       </c>
-      <c r="E12" s="63" t="n">
+      <c r="E12" s="62" t="n">
         <v>0.41</v>
       </c>
       <c r="G12" s="30" t="n">
@@ -10015,18 +10008,18 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
+      <c r="I12" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="46" t="n">
         <v>1944.9</v>
       </c>
-      <c r="K12" s="64" t="n">
+      <c r="K12" s="63" t="n">
         <v>19079.1</v>
       </c>
-      <c r="L12" s="63" t="n">
+      <c r="L12" s="62" t="n">
         <v>16.58</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -10037,18 +10030,18 @@
           <t>삼성에스디에스</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q12" s="60" t="n">
+      <c r="Q12" s="59" t="n">
         <v>-415.5</v>
       </c>
-      <c r="R12" s="64" t="n">
+      <c r="R12" s="63" t="n">
         <v>4930.2</v>
       </c>
-      <c r="S12" s="63" t="n">
+      <c r="S12" s="62" t="n">
         <v>3.08</v>
       </c>
     </row>
@@ -10061,15 +10054,15 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D13" s="62" t="n">
+      <c r="D13" s="61" t="n">
         <v>1354</v>
       </c>
-      <c r="E13" s="63" t="n">
+      <c r="E13" s="62" t="n">
         <v>0.11</v>
       </c>
       <c r="G13" s="30" t="n">
@@ -10080,18 +10073,18 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="I13" s="35" t="inlineStr">
+      <c r="I13" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="46" t="n">
         <v>1590.6</v>
       </c>
-      <c r="K13" s="64" t="n">
+      <c r="K13" s="63" t="n">
         <v>38072.8</v>
       </c>
-      <c r="L13" s="63" t="n">
+      <c r="L13" s="62" t="n">
         <v>3.18</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -10102,18 +10095,18 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="P13" s="43" t="inlineStr">
+      <c r="P13" s="42" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q13" s="60" t="n">
+      <c r="Q13" s="59" t="n">
         <v>-396.1</v>
       </c>
-      <c r="R13" s="64" t="n">
+      <c r="R13" s="63" t="n">
         <v>6786.8</v>
       </c>
-      <c r="S13" s="63" t="n">
+      <c r="S13" s="62" t="n">
         <v>2.99</v>
       </c>
     </row>
@@ -10126,15 +10119,15 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D14" s="62" t="n">
+      <c r="D14" s="61" t="n">
         <v>1256</v>
       </c>
-      <c r="E14" s="63" t="n">
+      <c r="E14" s="62" t="n">
         <v>1.09</v>
       </c>
       <c r="G14" s="30" t="n">
@@ -10145,18 +10138,18 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="I14" s="35" t="inlineStr">
+      <c r="I14" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="J14" s="47" t="n">
+      <c r="J14" s="46" t="n">
         <v>1413.7</v>
       </c>
-      <c r="K14" s="64" t="n">
+      <c r="K14" s="63" t="n">
         <v>7584.7</v>
       </c>
-      <c r="L14" s="63" t="n">
+      <c r="L14" s="62" t="n">
         <v>12.41</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -10167,24 +10160,24 @@
           <t>DB손해보험</t>
         </is>
       </c>
-      <c r="P14" s="35" t="inlineStr">
+      <c r="P14" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="Q14" s="60" t="n">
+      <c r="Q14" s="59" t="n">
         <v>-394.9</v>
       </c>
-      <c r="R14" s="64" t="n">
+      <c r="R14" s="63" t="n">
         <v>2387.2</v>
       </c>
-      <c r="S14" s="63" t="n">
+      <c r="S14" s="62" t="n">
         <v>1.95</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16" ht="31" customHeight="1" s="15">
-      <c r="A16" s="61" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>랭킹 유니버스(순매수 상위 30 등재 종목) 한정 · 대차 증감=전월말 대비 최신 잔고 · 시총대비(%)=공매도 누적 금액÷시가총액, 대차잔고÷시가총액(KIS 마스터 시총(주 1회 갱신))</t>
         </is>
@@ -10277,77 +10270,77 @@
       <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="44" t="inlineStr">
         <is>
           <t>기관(합)</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>외인+기관</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="44" t="inlineStr">
         <is>
           <t>금융투자</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="44" t="inlineStr">
         <is>
           <t>투신(사모)</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="44" t="inlineStr">
         <is>
           <t>연기금</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="44" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="M4" s="45" t="inlineStr">
+      <c r="M4" s="44" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="N4" s="44" t="inlineStr">
         <is>
           <t>기타법인</t>
         </is>
       </c>
-      <c r="O4" s="45" t="inlineStr">
+      <c r="O4" s="44" t="inlineStr">
         <is>
           <t>신호</t>
         </is>
@@ -10359,46 +10352,46 @@
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="B5" s="65" t="n">
+      <c r="B5" s="64" t="n">
         <v>51.3</v>
       </c>
-      <c r="C5" s="65" t="n">
+      <c r="C5" s="64" t="n">
         <v>41</v>
       </c>
-      <c r="D5" s="65" t="n">
+      <c r="D5" s="64" t="n">
         <v>37.51</v>
       </c>
-      <c r="E5" s="65" t="n">
+      <c r="E5" s="64" t="n">
         <v>19.03</v>
       </c>
-      <c r="F5" s="66" t="n">
+      <c r="F5" s="65" t="n">
         <v>444</v>
       </c>
-      <c r="G5" s="67" t="n">
+      <c r="G5" s="66" t="n">
         <v>-15</v>
       </c>
-      <c r="H5" s="66" t="n">
+      <c r="H5" s="65" t="n">
         <v>429</v>
       </c>
-      <c r="I5" s="66" t="n">
+      <c r="I5" s="65" t="n">
         <v>11</v>
       </c>
-      <c r="J5" s="66" t="n">
+      <c r="J5" s="65" t="n">
         <v>19</v>
       </c>
-      <c r="K5" s="67" t="n">
+      <c r="K5" s="66" t="n">
         <v>-45</v>
       </c>
-      <c r="L5" s="66" t="n">
+      <c r="L5" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="67" t="n">
+      <c r="M5" s="66" t="n">
         <v>-417</v>
       </c>
-      <c r="N5" s="67" t="n">
+      <c r="N5" s="66" t="n">
         <v>-12</v>
       </c>
-      <c r="O5" s="58" t="inlineStr">
+      <c r="O5" s="57" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10410,43 +10403,43 @@
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="B6" s="68" t="n">
+      <c r="B6" s="67" t="n">
         <v>-1.49</v>
       </c>
-      <c r="C6" s="68" t="n">
+      <c r="C6" s="67" t="n">
         <v>-1.4</v>
       </c>
-      <c r="D6" s="68" t="n">
+      <c r="D6" s="67" t="n">
         <v>-2.14</v>
       </c>
-      <c r="E6" s="65" t="n">
+      <c r="E6" s="64" t="n">
         <v>4.43</v>
       </c>
-      <c r="F6" s="66" t="n">
+      <c r="F6" s="65" t="n">
         <v>11</v>
       </c>
-      <c r="G6" s="67" t="n">
+      <c r="G6" s="66" t="n">
         <v>-8</v>
       </c>
-      <c r="H6" s="66" t="n">
+      <c r="H6" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="66" t="n">
+      <c r="I6" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="66" t="n">
+      <c r="J6" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="67" t="n">
+      <c r="K6" s="66" t="n">
         <v>-14</v>
       </c>
-      <c r="L6" s="67" t="n">
+      <c r="L6" s="66" t="n">
         <v>-3</v>
       </c>
-      <c r="M6" s="67" t="n">
+      <c r="M6" s="66" t="n">
         <v>-62</v>
       </c>
-      <c r="N6" s="66" t="n">
+      <c r="N6" s="65" t="n">
         <v>59</v>
       </c>
       <c r="O6" s="30" t="inlineStr"/>
@@ -10457,46 +10450,46 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="B7" s="65" t="n">
+      <c r="B7" s="64" t="n">
         <v>22.47</v>
       </c>
-      <c r="C7" s="65" t="n">
+      <c r="C7" s="64" t="n">
         <v>2.05</v>
       </c>
-      <c r="D7" s="65" t="n">
+      <c r="D7" s="64" t="n">
         <v>14.15</v>
       </c>
-      <c r="E7" s="65" t="n">
+      <c r="E7" s="64" t="n">
         <v>3.85</v>
       </c>
-      <c r="F7" s="66" t="n">
+      <c r="F7" s="65" t="n">
         <v>914</v>
       </c>
-      <c r="G7" s="66" t="n">
+      <c r="G7" s="65" t="n">
         <v>2380</v>
       </c>
-      <c r="H7" s="66" t="n">
+      <c r="H7" s="65" t="n">
         <v>3295</v>
       </c>
-      <c r="I7" s="66" t="n">
+      <c r="I7" s="65" t="n">
         <v>647</v>
       </c>
-      <c r="J7" s="66" t="n">
+      <c r="J7" s="65" t="n">
         <v>642</v>
       </c>
-      <c r="K7" s="66" t="n">
+      <c r="K7" s="65" t="n">
         <v>1050</v>
       </c>
-      <c r="L7" s="66" t="n">
+      <c r="L7" s="65" t="n">
         <v>47</v>
       </c>
-      <c r="M7" s="67" t="n">
+      <c r="M7" s="66" t="n">
         <v>-3340</v>
       </c>
-      <c r="N7" s="66" t="n">
+      <c r="N7" s="65" t="n">
         <v>46</v>
       </c>
-      <c r="O7" s="58" t="inlineStr">
+      <c r="O7" s="57" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10508,46 +10501,46 @@
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="B8" s="68" t="n">
+      <c r="B8" s="67" t="n">
         <v>-44.2</v>
       </c>
-      <c r="C8" s="68" t="n">
+      <c r="C8" s="67" t="n">
         <v>-29.91</v>
       </c>
-      <c r="D8" s="68" t="n">
+      <c r="D8" s="67" t="n">
         <v>-20.22</v>
       </c>
-      <c r="E8" s="65" t="n">
+      <c r="E8" s="64" t="n">
         <v>2.56</v>
       </c>
-      <c r="F8" s="66" t="n">
+      <c r="F8" s="65" t="n">
         <v>45</v>
       </c>
-      <c r="G8" s="66" t="n">
+      <c r="G8" s="65" t="n">
         <v>107</v>
       </c>
-      <c r="H8" s="66" t="n">
+      <c r="H8" s="65" t="n">
         <v>152</v>
       </c>
-      <c r="I8" s="67" t="n">
+      <c r="I8" s="66" t="n">
         <v>-80</v>
       </c>
-      <c r="J8" s="66" t="n">
+      <c r="J8" s="65" t="n">
         <v>112</v>
       </c>
-      <c r="K8" s="66" t="n">
+      <c r="K8" s="65" t="n">
         <v>73</v>
       </c>
-      <c r="L8" s="66" t="n">
+      <c r="L8" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="M8" s="67" t="n">
+      <c r="M8" s="66" t="n">
         <v>-147</v>
       </c>
-      <c r="N8" s="67" t="n">
+      <c r="N8" s="66" t="n">
         <v>-5</v>
       </c>
-      <c r="O8" s="69" t="inlineStr">
+      <c r="O8" s="68" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -10559,43 +10552,43 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="B9" s="68" t="n">
+      <c r="B9" s="67" t="n">
         <v>-10.48</v>
       </c>
-      <c r="C9" s="68" t="n">
+      <c r="C9" s="67" t="n">
         <v>-14.05</v>
       </c>
-      <c r="D9" s="65" t="n">
+      <c r="D9" s="64" t="n">
         <v>1.15</v>
       </c>
-      <c r="E9" s="65" t="n">
+      <c r="E9" s="64" t="n">
         <v>0.14</v>
       </c>
-      <c r="F9" s="67" t="n">
+      <c r="F9" s="66" t="n">
         <v>-24</v>
       </c>
-      <c r="G9" s="66" t="n">
+      <c r="G9" s="65" t="n">
         <v>45</v>
       </c>
-      <c r="H9" s="66" t="n">
+      <c r="H9" s="65" t="n">
         <v>21</v>
       </c>
-      <c r="I9" s="66" t="n">
+      <c r="I9" s="65" t="n">
         <v>70</v>
       </c>
-      <c r="J9" s="67" t="n">
+      <c r="J9" s="66" t="n">
         <v>-33</v>
       </c>
-      <c r="K9" s="66" t="n">
+      <c r="K9" s="65" t="n">
         <v>16</v>
       </c>
-      <c r="L9" s="67" t="n">
+      <c r="L9" s="66" t="n">
         <v>-8</v>
       </c>
-      <c r="M9" s="67" t="n">
+      <c r="M9" s="66" t="n">
         <v>-19</v>
       </c>
-      <c r="N9" s="67" t="n">
+      <c r="N9" s="66" t="n">
         <v>-2</v>
       </c>
       <c r="O9" s="30" t="inlineStr"/>
@@ -10606,43 +10599,43 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="B10" s="65" t="n">
+      <c r="B10" s="64" t="n">
         <v>2.86</v>
       </c>
-      <c r="C10" s="68" t="n">
+      <c r="C10" s="67" t="n">
         <v>-1</v>
       </c>
-      <c r="D10" s="68" t="n">
+      <c r="D10" s="67" t="n">
         <v>-3.59</v>
       </c>
-      <c r="E10" s="68" t="n">
+      <c r="E10" s="67" t="n">
         <v>-0.54</v>
       </c>
-      <c r="F10" s="67" t="n">
+      <c r="F10" s="66" t="n">
         <v>-73</v>
       </c>
-      <c r="G10" s="67" t="n">
+      <c r="G10" s="66" t="n">
         <v>-15</v>
       </c>
-      <c r="H10" s="67" t="n">
+      <c r="H10" s="66" t="n">
         <v>-89</v>
       </c>
-      <c r="I10" s="67" t="n">
+      <c r="I10" s="66" t="n">
         <v>-5</v>
       </c>
-      <c r="J10" s="67" t="n">
+      <c r="J10" s="66" t="n">
         <v>-129</v>
       </c>
-      <c r="K10" s="66" t="n">
+      <c r="K10" s="65" t="n">
         <v>139</v>
       </c>
-      <c r="L10" s="67" t="n">
+      <c r="L10" s="66" t="n">
         <v>-26</v>
       </c>
-      <c r="M10" s="67" t="n">
+      <c r="M10" s="66" t="n">
         <v>-130</v>
       </c>
-      <c r="N10" s="66" t="n">
+      <c r="N10" s="65" t="n">
         <v>219</v>
       </c>
       <c r="O10" s="30" t="inlineStr"/>
@@ -10653,43 +10646,43 @@
           <t>비금속</t>
         </is>
       </c>
-      <c r="B11" s="68" t="n">
+      <c r="B11" s="67" t="n">
         <v>-15.1</v>
       </c>
-      <c r="C11" s="68" t="n">
+      <c r="C11" s="67" t="n">
         <v>-18.29</v>
       </c>
-      <c r="D11" s="68" t="n">
+      <c r="D11" s="67" t="n">
         <v>-3.05</v>
       </c>
-      <c r="E11" s="68" t="n">
+      <c r="E11" s="67" t="n">
         <v>-0.78</v>
       </c>
-      <c r="F11" s="67" t="n">
+      <c r="F11" s="66" t="n">
         <v>-2</v>
       </c>
-      <c r="G11" s="70" t="n">
+      <c r="G11" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="67" t="n">
+      <c r="H11" s="66" t="n">
         <v>-3</v>
       </c>
-      <c r="I11" s="66" t="n">
+      <c r="I11" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="70" t="n">
+      <c r="J11" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="67" t="n">
+      <c r="K11" s="66" t="n">
         <v>-5</v>
       </c>
-      <c r="L11" s="70" t="n">
+      <c r="L11" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="66" t="n">
+      <c r="M11" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="70" t="n">
+      <c r="N11" s="69" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="30" t="inlineStr"/>
@@ -10700,43 +10693,43 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="B12" s="65" t="n">
+      <c r="B12" s="64" t="n">
         <v>4.23</v>
       </c>
-      <c r="C12" s="68" t="n">
+      <c r="C12" s="67" t="n">
         <v>-7</v>
       </c>
-      <c r="D12" s="65" t="n">
+      <c r="D12" s="64" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="E12" s="68" t="n">
+      <c r="E12" s="67" t="n">
         <v>-0.83</v>
       </c>
-      <c r="F12" s="67" t="n">
+      <c r="F12" s="66" t="n">
         <v>-106</v>
       </c>
-      <c r="G12" s="67" t="n">
+      <c r="G12" s="66" t="n">
         <v>-164</v>
       </c>
-      <c r="H12" s="67" t="n">
+      <c r="H12" s="66" t="n">
         <v>-270</v>
       </c>
-      <c r="I12" s="66" t="n">
+      <c r="I12" s="65" t="n">
         <v>96</v>
       </c>
-      <c r="J12" s="67" t="n">
+      <c r="J12" s="66" t="n">
         <v>-67</v>
       </c>
-      <c r="K12" s="67" t="n">
+      <c r="K12" s="66" t="n">
         <v>-176</v>
       </c>
-      <c r="L12" s="67" t="n">
+      <c r="L12" s="66" t="n">
         <v>-16</v>
       </c>
-      <c r="M12" s="66" t="n">
+      <c r="M12" s="65" t="n">
         <v>221</v>
       </c>
-      <c r="N12" s="66" t="n">
+      <c r="N12" s="65" t="n">
         <v>49</v>
       </c>
       <c r="O12" s="30" t="inlineStr"/>
@@ -10747,43 +10740,43 @@
           <t>통신</t>
         </is>
       </c>
-      <c r="B13" s="65" t="n">
+      <c r="B13" s="64" t="n">
         <v>21.84</v>
       </c>
-      <c r="C13" s="68" t="n">
+      <c r="C13" s="67" t="n">
         <v>-9.789999999999999</v>
       </c>
-      <c r="D13" s="68" t="n">
+      <c r="D13" s="67" t="n">
         <v>-2.51</v>
       </c>
-      <c r="E13" s="68" t="n">
+      <c r="E13" s="67" t="n">
         <v>-1.13</v>
       </c>
-      <c r="F13" s="66" t="n">
+      <c r="F13" s="65" t="n">
         <v>225</v>
       </c>
-      <c r="G13" s="67" t="n">
+      <c r="G13" s="66" t="n">
         <v>-227</v>
       </c>
-      <c r="H13" s="67" t="n">
+      <c r="H13" s="66" t="n">
         <v>-2</v>
       </c>
-      <c r="I13" s="67" t="n">
+      <c r="I13" s="66" t="n">
         <v>-160</v>
       </c>
-      <c r="J13" s="66" t="n">
+      <c r="J13" s="65" t="n">
         <v>121</v>
       </c>
-      <c r="K13" s="67" t="n">
+      <c r="K13" s="66" t="n">
         <v>-168</v>
       </c>
-      <c r="L13" s="67" t="n">
+      <c r="L13" s="66" t="n">
         <v>-19</v>
       </c>
-      <c r="M13" s="66" t="n">
+      <c r="M13" s="65" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="67" t="n">
+      <c r="N13" s="66" t="n">
         <v>-13</v>
       </c>
       <c r="O13" s="30" t="inlineStr"/>
@@ -10794,43 +10787,43 @@
           <t>종이·목재</t>
         </is>
       </c>
-      <c r="B14" s="68" t="n">
+      <c r="B14" s="67" t="n">
         <v>-24.1</v>
       </c>
-      <c r="C14" s="68" t="n">
+      <c r="C14" s="67" t="n">
         <v>-24.32</v>
       </c>
-      <c r="D14" s="68" t="n">
+      <c r="D14" s="67" t="n">
         <v>-2.17</v>
       </c>
-      <c r="E14" s="68" t="n">
+      <c r="E14" s="67" t="n">
         <v>-1.37</v>
       </c>
-      <c r="F14" s="67" t="n">
+      <c r="F14" s="66" t="n">
         <v>-2</v>
       </c>
-      <c r="G14" s="66" t="n">
+      <c r="G14" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="66" t="n">
+      <c r="H14" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="66" t="n">
+      <c r="I14" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="J14" s="70" t="n">
+      <c r="J14" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="70" t="n">
+      <c r="K14" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="70" t="n">
+      <c r="L14" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="66" t="n">
+      <c r="M14" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="N14" s="67" t="n">
+      <c r="N14" s="66" t="n">
         <v>-8</v>
       </c>
       <c r="O14" s="30" t="inlineStr"/>
@@ -10841,46 +10834,46 @@
           <t>전기·가스</t>
         </is>
       </c>
-      <c r="B15" s="68" t="n">
+      <c r="B15" s="67" t="n">
         <v>-31.19</v>
       </c>
-      <c r="C15" s="68" t="n">
+      <c r="C15" s="67" t="n">
         <v>-28.09</v>
       </c>
-      <c r="D15" s="68" t="n">
+      <c r="D15" s="67" t="n">
         <v>-15.01</v>
       </c>
-      <c r="E15" s="68" t="n">
+      <c r="E15" s="67" t="n">
         <v>-1.91</v>
       </c>
-      <c r="F15" s="67" t="n">
+      <c r="F15" s="66" t="n">
         <v>-233</v>
       </c>
-      <c r="G15" s="66" t="n">
+      <c r="G15" s="65" t="n">
         <v>31</v>
       </c>
-      <c r="H15" s="67" t="n">
+      <c r="H15" s="66" t="n">
         <v>-202</v>
       </c>
-      <c r="I15" s="66" t="n">
+      <c r="I15" s="65" t="n">
         <v>68</v>
       </c>
-      <c r="J15" s="66" t="n">
+      <c r="J15" s="65" t="n">
         <v>69</v>
       </c>
-      <c r="K15" s="67" t="n">
+      <c r="K15" s="66" t="n">
         <v>-94</v>
       </c>
-      <c r="L15" s="67" t="n">
+      <c r="L15" s="66" t="n">
         <v>-9</v>
       </c>
-      <c r="M15" s="66" t="n">
+      <c r="M15" s="65" t="n">
         <v>196</v>
       </c>
-      <c r="N15" s="66" t="n">
+      <c r="N15" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="O15" s="59" t="inlineStr">
+      <c r="O15" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10892,43 +10885,43 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="B16" s="65" t="n">
+      <c r="B16" s="64" t="n">
         <v>7.47</v>
       </c>
-      <c r="C16" s="68" t="n">
+      <c r="C16" s="67" t="n">
         <v>-2.62</v>
       </c>
-      <c r="D16" s="65" t="n">
+      <c r="D16" s="64" t="n">
         <v>3.53</v>
       </c>
-      <c r="E16" s="68" t="n">
+      <c r="E16" s="67" t="n">
         <v>-2.35</v>
       </c>
-      <c r="F16" s="66" t="n">
+      <c r="F16" s="65" t="n">
         <v>478</v>
       </c>
-      <c r="G16" s="67" t="n">
+      <c r="G16" s="66" t="n">
         <v>-537</v>
       </c>
-      <c r="H16" s="67" t="n">
+      <c r="H16" s="66" t="n">
         <v>-59</v>
       </c>
-      <c r="I16" s="67" t="n">
+      <c r="I16" s="66" t="n">
         <v>-480</v>
       </c>
-      <c r="J16" s="66" t="n">
+      <c r="J16" s="65" t="n">
         <v>54</v>
       </c>
-      <c r="K16" s="67" t="n">
+      <c r="K16" s="66" t="n">
         <v>-76</v>
       </c>
-      <c r="L16" s="67" t="n">
+      <c r="L16" s="66" t="n">
         <v>-35</v>
       </c>
-      <c r="M16" s="66" t="n">
+      <c r="M16" s="65" t="n">
         <v>22</v>
       </c>
-      <c r="N16" s="66" t="n">
+      <c r="N16" s="65" t="n">
         <v>37</v>
       </c>
       <c r="O16" s="30" t="inlineStr"/>
@@ -10939,43 +10932,43 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="B17" s="65" t="n">
+      <c r="B17" s="64" t="n">
         <v>10.19</v>
       </c>
-      <c r="C17" s="68" t="n">
+      <c r="C17" s="67" t="n">
         <v>-19.81</v>
       </c>
-      <c r="D17" s="65" t="n">
+      <c r="D17" s="64" t="n">
         <v>6.7</v>
       </c>
-      <c r="E17" s="68" t="n">
+      <c r="E17" s="67" t="n">
         <v>-2.59</v>
       </c>
-      <c r="F17" s="67" t="n">
+      <c r="F17" s="66" t="n">
         <v>-2414</v>
       </c>
-      <c r="G17" s="67" t="n">
+      <c r="G17" s="66" t="n">
         <v>-667</v>
       </c>
-      <c r="H17" s="67" t="n">
+      <c r="H17" s="66" t="n">
         <v>-3081</v>
       </c>
-      <c r="I17" s="66" t="n">
+      <c r="I17" s="65" t="n">
         <v>1474</v>
       </c>
-      <c r="J17" s="67" t="n">
+      <c r="J17" s="66" t="n">
         <v>-1982</v>
       </c>
-      <c r="K17" s="67" t="n">
+      <c r="K17" s="66" t="n">
         <v>-21</v>
       </c>
-      <c r="L17" s="67" t="n">
+      <c r="L17" s="66" t="n">
         <v>-114</v>
       </c>
-      <c r="M17" s="66" t="n">
+      <c r="M17" s="65" t="n">
         <v>3147</v>
       </c>
-      <c r="N17" s="67" t="n">
+      <c r="N17" s="66" t="n">
         <v>-66</v>
       </c>
       <c r="O17" s="30" t="inlineStr"/>
@@ -10986,43 +10979,43 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="B18" s="65" t="n">
+      <c r="B18" s="64" t="n">
         <v>110.02</v>
       </c>
-      <c r="C18" s="65" t="n">
+      <c r="C18" s="64" t="n">
         <v>35.2</v>
       </c>
-      <c r="D18" s="68" t="n">
+      <c r="D18" s="67" t="n">
         <v>-9.06</v>
       </c>
-      <c r="E18" s="68" t="n">
+      <c r="E18" s="67" t="n">
         <v>-2.76</v>
       </c>
-      <c r="F18" s="67" t="n">
+      <c r="F18" s="66" t="n">
         <v>-53546</v>
       </c>
-      <c r="G18" s="67" t="n">
+      <c r="G18" s="66" t="n">
         <v>-12018</v>
       </c>
-      <c r="H18" s="67" t="n">
+      <c r="H18" s="66" t="n">
         <v>-65563</v>
       </c>
-      <c r="I18" s="67" t="n">
+      <c r="I18" s="66" t="n">
         <v>-17432</v>
       </c>
-      <c r="J18" s="66" t="n">
+      <c r="J18" s="65" t="n">
         <v>2148</v>
       </c>
-      <c r="K18" s="66" t="n">
+      <c r="K18" s="65" t="n">
         <v>2521</v>
       </c>
-      <c r="L18" s="66" t="n">
+      <c r="L18" s="65" t="n">
         <v>734</v>
       </c>
-      <c r="M18" s="66" t="n">
+      <c r="M18" s="65" t="n">
         <v>10820</v>
       </c>
-      <c r="N18" s="66" t="n">
+      <c r="N18" s="65" t="n">
         <v>54744</v>
       </c>
       <c r="O18" s="30" t="inlineStr"/>
@@ -11033,43 +11026,43 @@
           <t>제조</t>
         </is>
       </c>
-      <c r="B19" s="65" t="n">
+      <c r="B19" s="64" t="n">
         <v>67.84</v>
       </c>
-      <c r="C19" s="65" t="n">
+      <c r="C19" s="64" t="n">
         <v>17.63</v>
       </c>
-      <c r="D19" s="68" t="n">
+      <c r="D19" s="67" t="n">
         <v>-8.789999999999999</v>
       </c>
-      <c r="E19" s="68" t="n">
+      <c r="E19" s="67" t="n">
         <v>-2.83</v>
       </c>
-      <c r="F19" s="67" t="n">
+      <c r="F19" s="66" t="n">
         <v>-62481</v>
       </c>
-      <c r="G19" s="67" t="n">
+      <c r="G19" s="66" t="n">
         <v>-15087</v>
       </c>
-      <c r="H19" s="67" t="n">
+      <c r="H19" s="66" t="n">
         <v>-77567</v>
       </c>
-      <c r="I19" s="67" t="n">
+      <c r="I19" s="66" t="n">
         <v>-16292</v>
       </c>
-      <c r="J19" s="66" t="n">
+      <c r="J19" s="65" t="n">
         <v>17</v>
       </c>
-      <c r="K19" s="66" t="n">
+      <c r="K19" s="65" t="n">
         <v>784</v>
       </c>
-      <c r="L19" s="66" t="n">
+      <c r="L19" s="65" t="n">
         <v>452</v>
       </c>
-      <c r="M19" s="66" t="n">
+      <c r="M19" s="65" t="n">
         <v>21838</v>
       </c>
-      <c r="N19" s="66" t="n">
+      <c r="N19" s="65" t="n">
         <v>55730</v>
       </c>
       <c r="O19" s="30" t="inlineStr"/>
@@ -11080,43 +11073,43 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="B20" s="65" t="n">
+      <c r="B20" s="64" t="n">
         <v>48.04</v>
       </c>
-      <c r="C20" s="65" t="n">
+      <c r="C20" s="64" t="n">
         <v>16.5</v>
       </c>
-      <c r="D20" s="68" t="n">
+      <c r="D20" s="67" t="n">
         <v>-10.54</v>
       </c>
-      <c r="E20" s="68" t="n">
+      <c r="E20" s="67" t="n">
         <v>-2.92</v>
       </c>
-      <c r="F20" s="66" t="n">
+      <c r="F20" s="65" t="n">
         <v>519</v>
       </c>
-      <c r="G20" s="67" t="n">
+      <c r="G20" s="66" t="n">
         <v>-547</v>
       </c>
-      <c r="H20" s="67" t="n">
+      <c r="H20" s="66" t="n">
         <v>-28</v>
       </c>
-      <c r="I20" s="67" t="n">
+      <c r="I20" s="66" t="n">
         <v>-336</v>
       </c>
-      <c r="J20" s="66" t="n">
+      <c r="J20" s="65" t="n">
         <v>102</v>
       </c>
-      <c r="K20" s="67" t="n">
+      <c r="K20" s="66" t="n">
         <v>-276</v>
       </c>
-      <c r="L20" s="67" t="n">
+      <c r="L20" s="66" t="n">
         <v>-35</v>
       </c>
-      <c r="M20" s="67" t="n">
+      <c r="M20" s="66" t="n">
         <v>-12</v>
       </c>
-      <c r="N20" s="66" t="n">
+      <c r="N20" s="65" t="n">
         <v>40</v>
       </c>
       <c r="O20" s="30" t="inlineStr"/>
@@ -11127,46 +11120,46 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="B21" s="68" t="n">
+      <c r="B21" s="67" t="n">
         <v>-3.14</v>
       </c>
-      <c r="C21" s="68" t="n">
+      <c r="C21" s="67" t="n">
         <v>-25.55</v>
       </c>
-      <c r="D21" s="65" t="n">
+      <c r="D21" s="64" t="n">
         <v>0.43</v>
       </c>
-      <c r="E21" s="68" t="n">
+      <c r="E21" s="67" t="n">
         <v>-2.93</v>
       </c>
-      <c r="F21" s="67" t="n">
+      <c r="F21" s="66" t="n">
         <v>-2319</v>
       </c>
-      <c r="G21" s="66" t="n">
+      <c r="G21" s="65" t="n">
         <v>393</v>
       </c>
-      <c r="H21" s="67" t="n">
+      <c r="H21" s="66" t="n">
         <v>-1926</v>
       </c>
-      <c r="I21" s="66" t="n">
+      <c r="I21" s="65" t="n">
         <v>319</v>
       </c>
-      <c r="J21" s="66" t="n">
+      <c r="J21" s="65" t="n">
         <v>290</v>
       </c>
-      <c r="K21" s="67" t="n">
+      <c r="K21" s="66" t="n">
         <v>-211</v>
       </c>
-      <c r="L21" s="67" t="n">
+      <c r="L21" s="66" t="n">
         <v>-5</v>
       </c>
-      <c r="M21" s="66" t="n">
+      <c r="M21" s="65" t="n">
         <v>1891</v>
       </c>
-      <c r="N21" s="66" t="n">
+      <c r="N21" s="65" t="n">
         <v>36</v>
       </c>
-      <c r="O21" s="59" t="inlineStr">
+      <c r="O21" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11178,46 +11171,46 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="B22" s="65" t="n">
+      <c r="B22" s="64" t="n">
         <v>8.51</v>
       </c>
-      <c r="C22" s="68" t="n">
+      <c r="C22" s="67" t="n">
         <v>-42.32</v>
       </c>
-      <c r="D22" s="68" t="n">
+      <c r="D22" s="67" t="n">
         <v>-21.43</v>
       </c>
-      <c r="E22" s="68" t="n">
+      <c r="E22" s="67" t="n">
         <v>-3.45</v>
       </c>
-      <c r="F22" s="67" t="n">
+      <c r="F22" s="66" t="n">
         <v>-390</v>
       </c>
-      <c r="G22" s="66" t="n">
+      <c r="G22" s="65" t="n">
         <v>115</v>
       </c>
-      <c r="H22" s="67" t="n">
+      <c r="H22" s="66" t="n">
         <v>-275</v>
       </c>
-      <c r="I22" s="66" t="n">
+      <c r="I22" s="65" t="n">
         <v>42</v>
       </c>
-      <c r="J22" s="67" t="n">
+      <c r="J22" s="66" t="n">
         <v>-22</v>
       </c>
-      <c r="K22" s="66" t="n">
+      <c r="K22" s="65" t="n">
         <v>14</v>
       </c>
-      <c r="L22" s="67" t="n">
+      <c r="L22" s="66" t="n">
         <v>-6</v>
       </c>
-      <c r="M22" s="66" t="n">
+      <c r="M22" s="65" t="n">
         <v>249</v>
       </c>
-      <c r="N22" s="66" t="n">
+      <c r="N22" s="65" t="n">
         <v>26</v>
       </c>
-      <c r="O22" s="59" t="inlineStr">
+      <c r="O22" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11229,43 +11222,43 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="B23" s="65" t="n">
+      <c r="B23" s="64" t="n">
         <v>17.88</v>
       </c>
-      <c r="C23" s="68" t="n">
+      <c r="C23" s="67" t="n">
         <v>-4.15</v>
       </c>
-      <c r="D23" s="68" t="n">
+      <c r="D23" s="67" t="n">
         <v>-16.18</v>
       </c>
-      <c r="E23" s="68" t="n">
+      <c r="E23" s="67" t="n">
         <v>-3.88</v>
       </c>
-      <c r="F23" s="66" t="n">
+      <c r="F23" s="65" t="n">
         <v>372</v>
       </c>
-      <c r="G23" s="67" t="n">
+      <c r="G23" s="66" t="n">
         <v>-422</v>
       </c>
-      <c r="H23" s="67" t="n">
+      <c r="H23" s="66" t="n">
         <v>-49</v>
       </c>
-      <c r="I23" s="66" t="n">
+      <c r="I23" s="65" t="n">
         <v>48</v>
       </c>
-      <c r="J23" s="67" t="n">
+      <c r="J23" s="66" t="n">
         <v>-305</v>
       </c>
-      <c r="K23" s="67" t="n">
+      <c r="K23" s="66" t="n">
         <v>-122</v>
       </c>
-      <c r="L23" s="67" t="n">
+      <c r="L23" s="66" t="n">
         <v>-30</v>
       </c>
-      <c r="M23" s="66" t="n">
+      <c r="M23" s="65" t="n">
         <v>51</v>
       </c>
-      <c r="N23" s="67" t="n">
+      <c r="N23" s="66" t="n">
         <v>-1</v>
       </c>
       <c r="O23" s="30" t="inlineStr"/>
@@ -11276,46 +11269,46 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="B24" s="68" t="n">
+      <c r="B24" s="67" t="n">
         <v>-18.16</v>
       </c>
-      <c r="C24" s="68" t="n">
+      <c r="C24" s="67" t="n">
         <v>-9.33</v>
       </c>
-      <c r="D24" s="68" t="n">
+      <c r="D24" s="67" t="n">
         <v>-7.38</v>
       </c>
-      <c r="E24" s="68" t="n">
+      <c r="E24" s="67" t="n">
         <v>-4.2</v>
       </c>
-      <c r="F24" s="67" t="n">
+      <c r="F24" s="66" t="n">
         <v>-1750</v>
       </c>
-      <c r="G24" s="67" t="n">
+      <c r="G24" s="66" t="n">
         <v>-946</v>
       </c>
-      <c r="H24" s="67" t="n">
+      <c r="H24" s="66" t="n">
         <v>-2695</v>
       </c>
-      <c r="I24" s="67" t="n">
+      <c r="I24" s="66" t="n">
         <v>-37</v>
       </c>
-      <c r="J24" s="67" t="n">
+      <c r="J24" s="66" t="n">
         <v>-240</v>
       </c>
-      <c r="K24" s="67" t="n">
+      <c r="K24" s="66" t="n">
         <v>-624</v>
       </c>
-      <c r="L24" s="67" t="n">
+      <c r="L24" s="66" t="n">
         <v>-45</v>
       </c>
-      <c r="M24" s="66" t="n">
+      <c r="M24" s="65" t="n">
         <v>2693</v>
       </c>
-      <c r="N24" s="66" t="n">
+      <c r="N24" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="O24" s="59" t="inlineStr">
+      <c r="O24" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11327,43 +11320,43 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="B25" s="65" t="n">
+      <c r="B25" s="64" t="n">
         <v>34.72</v>
       </c>
-      <c r="C25" s="65" t="n">
+      <c r="C25" s="64" t="n">
         <v>5.78</v>
       </c>
-      <c r="D25" s="68" t="n">
+      <c r="D25" s="67" t="n">
         <v>-8.85</v>
       </c>
-      <c r="E25" s="68" t="n">
+      <c r="E25" s="67" t="n">
         <v>-4.7</v>
       </c>
-      <c r="F25" s="67" t="n">
+      <c r="F25" s="66" t="n">
         <v>-235</v>
       </c>
-      <c r="G25" s="66" t="n">
+      <c r="G25" s="65" t="n">
         <v>2007</v>
       </c>
-      <c r="H25" s="66" t="n">
+      <c r="H25" s="65" t="n">
         <v>1772</v>
       </c>
-      <c r="I25" s="67" t="n">
+      <c r="I25" s="66" t="n">
         <v>-356</v>
       </c>
-      <c r="J25" s="66" t="n">
+      <c r="J25" s="65" t="n">
         <v>3749</v>
       </c>
-      <c r="K25" s="67" t="n">
+      <c r="K25" s="66" t="n">
         <v>-1789</v>
       </c>
-      <c r="L25" s="67" t="n">
+      <c r="L25" s="66" t="n">
         <v>-342</v>
       </c>
-      <c r="M25" s="66" t="n">
+      <c r="M25" s="65" t="n">
         <v>4733</v>
       </c>
-      <c r="N25" s="67" t="n">
+      <c r="N25" s="66" t="n">
         <v>-6505</v>
       </c>
       <c r="O25" s="30" t="inlineStr"/>
@@ -11374,46 +11367,46 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="B26" s="68" t="n">
+      <c r="B26" s="67" t="n">
         <v>-19.75</v>
       </c>
-      <c r="C26" s="68" t="n">
+      <c r="C26" s="67" t="n">
         <v>-16.91</v>
       </c>
-      <c r="D26" s="68" t="n">
+      <c r="D26" s="67" t="n">
         <v>-3.96</v>
       </c>
-      <c r="E26" s="68" t="n">
+      <c r="E26" s="67" t="n">
         <v>-5.16</v>
       </c>
-      <c r="F26" s="67" t="n">
+      <c r="F26" s="66" t="n">
         <v>-1790</v>
       </c>
-      <c r="G26" s="67" t="n">
+      <c r="G26" s="66" t="n">
         <v>-385</v>
       </c>
-      <c r="H26" s="67" t="n">
+      <c r="H26" s="66" t="n">
         <v>-2175</v>
       </c>
-      <c r="I26" s="67" t="n">
+      <c r="I26" s="66" t="n">
         <v>-321</v>
       </c>
-      <c r="J26" s="67" t="n">
+      <c r="J26" s="66" t="n">
         <v>-110</v>
       </c>
-      <c r="K26" s="66" t="n">
+      <c r="K26" s="65" t="n">
         <v>64</v>
       </c>
-      <c r="L26" s="67" t="n">
+      <c r="L26" s="66" t="n">
         <v>-16</v>
       </c>
-      <c r="M26" s="66" t="n">
+      <c r="M26" s="65" t="n">
         <v>1664</v>
       </c>
-      <c r="N26" s="66" t="n">
+      <c r="N26" s="65" t="n">
         <v>511</v>
       </c>
-      <c r="O26" s="59" t="inlineStr">
+      <c r="O26" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11425,43 +11418,43 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="B27" s="65" t="n">
+      <c r="B27" s="64" t="n">
         <v>56.14</v>
       </c>
-      <c r="C27" s="68" t="n">
+      <c r="C27" s="67" t="n">
         <v>-31.48</v>
       </c>
-      <c r="D27" s="65" t="n">
+      <c r="D27" s="64" t="n">
         <v>5.49</v>
       </c>
-      <c r="E27" s="68" t="n">
+      <c r="E27" s="67" t="n">
         <v>-6.58</v>
       </c>
-      <c r="F27" s="66" t="n">
+      <c r="F27" s="65" t="n">
         <v>143</v>
       </c>
-      <c r="G27" s="67" t="n">
+      <c r="G27" s="66" t="n">
         <v>-1193</v>
       </c>
-      <c r="H27" s="67" t="n">
+      <c r="H27" s="66" t="n">
         <v>-1049</v>
       </c>
-      <c r="I27" s="66" t="n">
+      <c r="I27" s="65" t="n">
         <v>222</v>
       </c>
-      <c r="J27" s="67" t="n">
+      <c r="J27" s="66" t="n">
         <v>-600</v>
       </c>
-      <c r="K27" s="67" t="n">
+      <c r="K27" s="66" t="n">
         <v>-744</v>
       </c>
-      <c r="L27" s="67" t="n">
+      <c r="L27" s="66" t="n">
         <v>-69</v>
       </c>
-      <c r="M27" s="66" t="n">
+      <c r="M27" s="65" t="n">
         <v>1049</v>
       </c>
-      <c r="N27" s="66" t="n">
+      <c r="N27" s="65" t="n">
         <v>1</v>
       </c>
       <c r="O27" s="30" t="inlineStr"/>
@@ -11472,46 +11465,46 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="B28" s="68" t="n">
+      <c r="B28" s="67" t="n">
         <v>-13.62</v>
       </c>
-      <c r="C28" s="68" t="n">
+      <c r="C28" s="67" t="n">
         <v>-33.4</v>
       </c>
-      <c r="D28" s="68" t="n">
+      <c r="D28" s="67" t="n">
         <v>-24.03</v>
       </c>
-      <c r="E28" s="68" t="n">
+      <c r="E28" s="67" t="n">
         <v>-6.9</v>
       </c>
-      <c r="F28" s="67" t="n">
+      <c r="F28" s="66" t="n">
         <v>-3703</v>
       </c>
-      <c r="G28" s="67" t="n">
+      <c r="G28" s="66" t="n">
         <v>-4755</v>
       </c>
-      <c r="H28" s="67" t="n">
+      <c r="H28" s="66" t="n">
         <v>-8458</v>
       </c>
-      <c r="I28" s="67" t="n">
+      <c r="I28" s="66" t="n">
         <v>-1001</v>
       </c>
-      <c r="J28" s="67" t="n">
+      <c r="J28" s="66" t="n">
         <v>-864</v>
       </c>
-      <c r="K28" s="67" t="n">
+      <c r="K28" s="66" t="n">
         <v>-2693</v>
       </c>
-      <c r="L28" s="67" t="n">
+      <c r="L28" s="66" t="n">
         <v>-166</v>
       </c>
-      <c r="M28" s="66" t="n">
+      <c r="M28" s="65" t="n">
         <v>8255</v>
       </c>
-      <c r="N28" s="66" t="n">
+      <c r="N28" s="65" t="n">
         <v>203</v>
       </c>
-      <c r="O28" s="59" t="inlineStr">
+      <c r="O28" s="58" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11549,7 +11542,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0D4C6A1E-F7FE-4DE1-B2AA-ADDC72A63605}</x14:id>
+          <x14:id>{9B1C3070-3572-4D81-8A66-1BC99CA687C5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11563,7 +11556,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16DECA37-5710-49E5-9394-06FDB9D260B0}</x14:id>
+          <x14:id>{17AAADF9-BE9D-43FF-A751-2A495D7488BE}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11577,7 +11570,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C2FDB5A1-6905-4C92-9877-BC4BF3B8AE60}</x14:id>
+          <x14:id>{32E06E48-B94A-4A7C-9DA0-213F5DEDFE98}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11591,7 +11584,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DD1D4DAC-E86C-4CCF-9C2C-EEABB1F2C487}</x14:id>
+          <x14:id>{3DDAAE57-4197-4CEF-A486-C72E3676F308}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11601,7 +11594,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0D4C6A1E-F7FE-4DE1-B2AA-ADDC72A63605}">
+          <x14:cfRule type="dataBar" id="{9B1C3070-3572-4D81-8A66-1BC99CA687C5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11614,7 +11607,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{16DECA37-5710-49E5-9394-06FDB9D260B0}">
+          <x14:cfRule type="dataBar" id="{17AAADF9-BE9D-43FF-A751-2A495D7488BE}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11627,7 +11620,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C2FDB5A1-6905-4C92-9877-BC4BF3B8AE60}">
+          <x14:cfRule type="dataBar" id="{32E06E48-B94A-4A7C-9DA0-213F5DEDFE98}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11640,7 +11633,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DD1D4DAC-E86C-4CCF-9C2C-EEABB1F2C487}">
+          <x14:cfRule type="dataBar" id="{3DDAAE57-4197-4CEF-A486-C72E3676F308}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/reports/monthly_review/2026-10.xlsx
+++ b/public/reports/monthly_review/2026-10.xlsx
@@ -1017,7 +1017,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/15, %</t>
+          <t>미국 종가 기준 09/30 → 10/16, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1087,19 +1087,19 @@
         <v>17552</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>1.21</v>
+        <v>0.1</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>-0.55</v>
+        <v>-2.68</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>0.73</v>
+        <v>22.34</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>-8.289999999999999</v>
+        <v>-11.81</v>
       </c>
     </row>
     <row r="9">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>8.23</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="13">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>5.21</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="14">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>임의소비재</t>
+          <t>소재</t>
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>4.2</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="15">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-8.24</v>
+        <v>-11.36</v>
       </c>
     </row>
     <row r="16">
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>-5.01</v>
+        <v>-8.470000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="D17" s="33" t="n">
-        <v>-3.35</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="18">
@@ -12533,7 +12533,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AB47F3FC-5441-4FE8-B215-48B830804BA6}</x14:id>
+          <x14:id>{40A2E205-7BF6-4C09-8140-C3F41D75636F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12547,7 +12547,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55B9D2AF-090A-4EE5-B7E0-83B6089E4D60}</x14:id>
+          <x14:id>{C100B728-7B8D-457F-81E1-20D696C32C49}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12561,7 +12561,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29B392F9-3102-4824-87F6-3BA5B176FBCC}</x14:id>
+          <x14:id>{A61BA63B-1A8F-4DE7-B648-B79413466258}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12575,7 +12575,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91E2FA3B-AB1C-4819-9657-8AFF238486EB}</x14:id>
+          <x14:id>{05DE62AC-C0A4-4A94-9A6A-9ABBB0334F65}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12585,7 +12585,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AB47F3FC-5441-4FE8-B215-48B830804BA6}">
+          <x14:cfRule type="dataBar" id="{40A2E205-7BF6-4C09-8140-C3F41D75636F}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12598,7 +12598,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55B9D2AF-090A-4EE5-B7E0-83B6089E4D60}">
+          <x14:cfRule type="dataBar" id="{C100B728-7B8D-457F-81E1-20D696C32C49}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12611,7 +12611,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{29B392F9-3102-4824-87F6-3BA5B176FBCC}">
+          <x14:cfRule type="dataBar" id="{A61BA63B-1A8F-4DE7-B648-B79413466258}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12624,7 +12624,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{91E2FA3B-AB1C-4819-9657-8AFF238486EB}">
+          <x14:cfRule type="dataBar" id="{05DE62AC-C0A4-4A94-9A6A-9ABBB0334F65}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/reports/monthly_review/2026-10.xlsx
+++ b/public/reports/monthly_review/2026-10.xlsx
@@ -517,10 +517,10 @@
     <xf numFmtId="169" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -931,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K185"/>
+  <dimension ref="A1:K186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -960,7 +960,7 @@
       </c>
       <c r="I1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-01 ~ 2026-10-22</t>
+          <t>2026-10-01 ~ 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-10-22 16:28 KST</t>
+          <t>2026-10-23 16:26 KST</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>10월은 견조한 수출 펀더멘털에도 불구하고 미국발 인플레이션 우려와 외국인의 대규모 매도세가 겹치며 극심한 변동성을 보인 한 달이었습니다.</t>
+          <t>10월은 견조한 수출 펀더멘털에도 불구하고 미국발 인플레이션 우려와 외국인 수급 변동성으로 인해 급락과 반등이 교차하는 변동성 장세를 보였습니다.</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/21, %</t>
+          <t>미국 종가 기준 09/30 → 10/22, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1081,28 +1081,28 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>63230</v>
+        <v>63678</v>
       </c>
       <c r="C8" s="29" t="n">
-        <v>-178876</v>
+        <v>-188702</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>8012</v>
+        <v>16699</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>1.38</v>
+        <v>0.16</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>-0.59</v>
+        <v>-3.17</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>2.08</v>
+        <v>16.46</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>-8.890000000000001</v>
+        <v>-15.02</v>
       </c>
     </row>
     <row r="9">
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>5656</v>
+        <v>6292</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>-6379</v>
+        <v>-6798</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>461</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10"/>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>10.83</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>6.25</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="14">
@@ -1197,11 +1197,11 @@
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>임의소비재</t>
+          <t>소재</t>
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="15">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-8.59</v>
+        <v>-14.06</v>
       </c>
     </row>
     <row r="16">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>-3.68</v>
+        <v>-6.85</v>
       </c>
     </row>
     <row r="17">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="D17" s="33" t="n">
-        <v>-3.11</v>
+        <v>-3.83</v>
       </c>
     </row>
     <row r="18">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="D18" s="32" t="n">
-        <v>6.87</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="19">
@@ -1297,11 +1297,11 @@
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D19" s="32" t="n">
-        <v>4.07</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="20">
@@ -1317,11 +1317,11 @@
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>음식료·담배</t>
         </is>
       </c>
       <c r="D20" s="32" t="n">
-        <v>1.21</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="21">
@@ -1337,11 +1337,11 @@
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>기계·장비</t>
         </is>
       </c>
       <c r="D21" s="33" t="n">
-        <v>-23.56</v>
+        <v>-23.88</v>
       </c>
     </row>
     <row r="22">
@@ -1357,11 +1357,11 @@
       </c>
       <c r="C22" s="31" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="D22" s="33" t="n">
-        <v>-21.87</v>
+        <v>-22.59</v>
       </c>
     </row>
     <row r="23">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="D23" s="33" t="n">
-        <v>-20.97</v>
+        <v>-20.46</v>
       </c>
     </row>
     <row r="24"/>
@@ -2468,75 +2468,111 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57" ht="31" customHeight="1" s="15">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B57" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>신규 실업수당청구건수</t>
+        </is>
+      </c>
+      <c r="D57" s="31" t="n">
+        <v>194</v>
+      </c>
+      <c r="E57" s="31" t="n">
+        <v>200</v>
+      </c>
+      <c r="F57" s="31" t="n">
+        <v>199</v>
+      </c>
+      <c r="G57" s="31" t="inlineStr">
+        <is>
+          <t>Kpers</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>예상 하회</t>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>일별 요약</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr"/>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="3" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr"/>
-      <c r="K58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>코스피(%)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>코스피 ▲/▼</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>코스닥(%)</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>코스닥 ▲/▼</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>주도 섹터</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>그날 지수·수급 반응 요인</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="31" customHeight="1" s="15">
-      <c r="A60" s="31" t="inlineStr">
+    <row r="61" ht="31" customHeight="1" s="15">
+      <c r="A61" s="31" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B60" s="28" t="n">
+      <c r="B61" s="28" t="n">
         <v>1.95</v>
       </c>
-      <c r="C60" s="31" t="inlineStr">
+      <c r="C61" s="31" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2559,10 +2595,10 @@
           </r>
         </is>
       </c>
-      <c r="D60" s="28" t="n">
+      <c r="D61" s="28" t="n">
         <v>4.48</v>
       </c>
-      <c r="E60" s="17" t="inlineStr">
+      <c r="E61" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2585,27 +2621,27 @@
           </r>
         </is>
       </c>
-      <c r="F60" s="17" t="inlineStr">
+      <c r="F61" s="17" t="inlineStr">
         <is>
           <t>의료·정밀기기, 제약</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
-        <is>
-          <t>수출 급증과 기관 매수로 코스피 7,000선 돌파.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="31" customHeight="1" s="15">
-      <c r="A61" s="31" t="inlineStr">
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>수출 급증과 기관 매수로 지수 동반 급등.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="31" customHeight="1" s="15">
+      <c r="A62" s="31" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B61" s="28" t="n">
+      <c r="B62" s="28" t="n">
         <v>0.46</v>
       </c>
-      <c r="C61" s="17" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2628,10 +2664,10 @@
           </r>
         </is>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D62" s="29" t="n">
         <v>-0.11</v>
       </c>
-      <c r="E61" s="17" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2654,27 +2690,27 @@
           </r>
         </is>
       </c>
-      <c r="F61" s="17" t="inlineStr">
+      <c r="F62" s="17" t="inlineStr">
         <is>
           <t>화학, 금속</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
-        <is>
-          <t>기관 매수세로 코스피 7,000선 안착 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="31" customHeight="1" s="15">
-      <c r="A62" s="31" t="inlineStr">
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>기관 매수세로 코스피 7,000선 돌파.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="31" customHeight="1" s="15">
+      <c r="A63" s="31" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B62" s="29" t="n">
+      <c r="B63" s="29" t="n">
         <v>-0.89</v>
       </c>
-      <c r="C62" s="31" t="inlineStr">
+      <c r="C63" s="31" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2697,10 +2733,10 @@
           </r>
         </is>
       </c>
-      <c r="D62" s="28" t="n">
+      <c r="D63" s="28" t="n">
         <v>2.98</v>
       </c>
-      <c r="E62" s="17" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2723,27 +2759,27 @@
           </r>
         </is>
       </c>
-      <c r="F62" s="17" t="inlineStr">
+      <c r="F63" s="17" t="inlineStr">
         <is>
           <t>의료·정밀기기, 화학</t>
         </is>
       </c>
-      <c r="G62" s="17" t="inlineStr">
-        <is>
-          <t>외국인 1.8조 매도로 코스피 하락, 코스닥은 상승.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="31" customHeight="1" s="15">
-      <c r="A63" s="31" t="inlineStr">
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>외국인 1.8조 매도로 코스피 하락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="31" customHeight="1" s="15">
+      <c r="A64" s="31" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B63" s="29" t="n">
+      <c r="B64" s="29" t="n">
         <v>-1.98</v>
       </c>
-      <c r="C63" s="17" t="inlineStr">
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2766,10 +2802,10 @@
           </r>
         </is>
       </c>
-      <c r="D63" s="29" t="n">
+      <c r="D64" s="29" t="n">
         <v>-2.34</v>
       </c>
-      <c r="E63" s="17" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2792,27 +2828,27 @@
           </r>
         </is>
       </c>
-      <c r="F63" s="17" t="inlineStr">
+      <c r="F64" s="17" t="inlineStr">
         <is>
           <t>의료·정밀기기, 오락·문화</t>
         </is>
       </c>
-      <c r="G63" s="17" t="inlineStr">
-        <is>
-          <t>외국인 2.6조 매도에 양 시장 동반 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="31" customHeight="1" s="15">
-      <c r="A64" s="31" t="inlineStr">
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>외국인 2.6조 매도로 양 시장 하락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="31" customHeight="1" s="15">
+      <c r="A65" s="31" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B64" s="29" t="n">
+      <c r="B65" s="29" t="n">
         <v>-2.62</v>
       </c>
-      <c r="C64" s="17" t="inlineStr">
+      <c r="C65" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2835,10 +2871,10 @@
           </r>
         </is>
       </c>
-      <c r="D64" s="29" t="n">
+      <c r="D65" s="29" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="E64" s="17" t="inlineStr">
+      <c r="E65" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2861,27 +2897,27 @@
           </r>
         </is>
       </c>
-      <c r="F64" s="17" t="inlineStr">
+      <c r="F65" s="17" t="inlineStr">
         <is>
           <t>섬유·의류, 종이·목재</t>
         </is>
       </c>
-      <c r="G64" s="17" t="inlineStr">
-        <is>
-          <t>외국인·기관 동반 매도로 코스피 2.62% 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="31" customHeight="1" s="15">
-      <c r="A65" s="31" t="inlineStr">
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>외국인·기관 동반 매도로 코스피 급락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="31" customHeight="1" s="15">
+      <c r="A66" s="31" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B65" s="29" t="n">
+      <c r="B66" s="29" t="n">
         <v>-3.65</v>
       </c>
-      <c r="C65" s="17" t="inlineStr">
+      <c r="C66" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2904,10 +2940,10 @@
           </r>
         </is>
       </c>
-      <c r="D65" s="29" t="n">
+      <c r="D66" s="29" t="n">
         <v>-4.83</v>
       </c>
-      <c r="E65" s="17" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2930,27 +2966,27 @@
           </r>
         </is>
       </c>
-      <c r="F65" s="17" t="inlineStr">
+      <c r="F66" s="17" t="inlineStr">
         <is>
           <t>운송·창고, 음식료·담배</t>
         </is>
       </c>
-      <c r="G65" s="17" t="inlineStr">
-        <is>
-          <t>외국인 2조 매도에 코스피 3.65% 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="31" customHeight="1" s="15">
-      <c r="A66" s="31" t="inlineStr">
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>외국인 2조 매도로 코스피 3.65% 급락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="31" customHeight="1" s="15">
+      <c r="A67" s="31" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B66" s="29" t="n">
+      <c r="B67" s="29" t="n">
         <v>-5.46</v>
       </c>
-      <c r="C66" s="31" t="inlineStr">
+      <c r="C67" s="31" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2973,10 +3009,10 @@
           </r>
         </is>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="D67" s="29" t="n">
         <v>-1.43</v>
       </c>
-      <c r="E66" s="17" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2999,27 +3035,27 @@
           </r>
         </is>
       </c>
-      <c r="F66" s="17" t="inlineStr">
+      <c r="F67" s="17" t="inlineStr">
         <is>
           <t>오락·문화, 의료·정밀기기</t>
         </is>
       </c>
-      <c r="G66" s="17" t="inlineStr">
+      <c r="G67" s="17" t="inlineStr">
         <is>
           <t>외국인 4.5조 매도로 코스피 5.46% 급락.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="31" customHeight="1" s="15">
-      <c r="A67" s="31" t="inlineStr">
+    <row r="68" ht="31" customHeight="1" s="15">
+      <c r="A68" s="31" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B67" s="29" t="n">
+      <c r="B68" s="29" t="n">
         <v>-0.44</v>
       </c>
-      <c r="C67" s="17" t="inlineStr">
+      <c r="C68" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3042,10 +3078,10 @@
           </r>
         </is>
       </c>
-      <c r="D67" s="29" t="n">
+      <c r="D68" s="29" t="n">
         <v>-1.57</v>
       </c>
-      <c r="E67" s="17" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3068,27 +3104,27 @@
           </r>
         </is>
       </c>
-      <c r="F67" s="17" t="inlineStr">
+      <c r="F68" s="17" t="inlineStr">
         <is>
           <t>운송·창고, 화학</t>
         </is>
       </c>
-      <c r="G67" s="17" t="inlineStr">
-        <is>
-          <t>외국인 매도 지속으로 코스피 6,000선 위협.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="31" customHeight="1" s="15">
-      <c r="A68" s="31" t="inlineStr">
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>외국인 매도 지속으로 코스피 하락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="31" customHeight="1" s="15">
+      <c r="A69" s="31" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B68" s="29" t="n">
+      <c r="B69" s="29" t="n">
         <v>-7.57</v>
       </c>
-      <c r="C68" s="17" t="inlineStr">
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3111,10 +3147,10 @@
           </r>
         </is>
       </c>
-      <c r="D68" s="29" t="n">
+      <c r="D69" s="29" t="n">
         <v>-7.65</v>
       </c>
-      <c r="E68" s="17" t="inlineStr">
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3137,27 +3173,27 @@
           </r>
         </is>
       </c>
-      <c r="F68" s="17" t="inlineStr">
+      <c r="F69" s="17" t="inlineStr">
         <is>
           <t>제약, 음식료·담배</t>
         </is>
       </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>인플레이션 우려로 코스피 7.57% 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="31" customHeight="1" s="15">
-      <c r="A69" s="31" t="inlineStr">
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>외국인 3.6조 매도로 코스피 7.57% 급락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="31" customHeight="1" s="15">
+      <c r="A70" s="31" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B69" s="28" t="n">
+      <c r="B70" s="28" t="n">
         <v>2.05</v>
       </c>
-      <c r="C69" s="17" t="inlineStr">
+      <c r="C70" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3180,10 +3216,10 @@
           </r>
         </is>
       </c>
-      <c r="D69" s="28" t="n">
+      <c r="D70" s="28" t="n">
         <v>4.46</v>
       </c>
-      <c r="E69" s="17" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3206,27 +3242,27 @@
           </r>
         </is>
       </c>
-      <c r="F69" s="17" t="inlineStr">
+      <c r="F70" s="17" t="inlineStr">
         <is>
           <t>의료·정밀기기, 제약</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
-        <is>
-          <t>저가 매수세 유입으로 코스피 2.05% 반등.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="31" customHeight="1" s="15">
-      <c r="A70" s="31" t="inlineStr">
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>저가 매수세 유입으로 지수 반등.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="31" customHeight="1" s="15">
+      <c r="A71" s="31" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B70" s="28" t="n">
+      <c r="B71" s="28" t="n">
         <v>1.76</v>
       </c>
-      <c r="C70" s="17" t="inlineStr">
+      <c r="C71" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3249,10 +3285,10 @@
           </r>
         </is>
       </c>
-      <c r="D70" s="28" t="n">
+      <c r="D71" s="28" t="n">
         <v>1.78</v>
       </c>
-      <c r="E70" s="17" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3275,27 +3311,27 @@
           </r>
         </is>
       </c>
-      <c r="F70" s="17" t="inlineStr">
+      <c r="F71" s="17" t="inlineStr">
         <is>
           <t>제약, 금속</t>
         </is>
       </c>
-      <c r="G70" s="17" t="inlineStr">
-        <is>
-          <t>기관 매수세 유입으로 코스피 1.76% 상승.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="31" customHeight="1" s="15">
-      <c r="A71" s="31" t="inlineStr">
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>기관 매수세로 지수 상승 전환.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="31" customHeight="1" s="15">
+      <c r="A72" s="31" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B71" s="29" t="n">
+      <c r="B72" s="29" t="n">
         <v>-3.73</v>
       </c>
-      <c r="C71" s="17" t="inlineStr">
+      <c r="C72" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3318,10 +3354,10 @@
           </r>
         </is>
       </c>
-      <c r="D71" s="29" t="n">
+      <c r="D72" s="29" t="n">
         <v>-3.33</v>
       </c>
-      <c r="E71" s="17" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3344,27 +3380,27 @@
           </r>
         </is>
       </c>
-      <c r="F71" s="17" t="inlineStr">
+      <c r="F72" s="17" t="inlineStr">
         <is>
           <t>음식료·담배, 부동산</t>
         </is>
       </c>
-      <c r="G71" s="17" t="inlineStr">
-        <is>
-          <t>외국인·기관 동반 매도로 코스피 3.73% 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="31" customHeight="1" s="15">
-      <c r="A72" s="31" t="inlineStr">
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>외국인·기관 동반 매도로 지수 급락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="31" customHeight="1" s="15">
+      <c r="A73" s="31" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B72" s="28" t="n">
+      <c r="B73" s="28" t="n">
         <v>3.29</v>
       </c>
-      <c r="C72" s="17" t="inlineStr">
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3387,10 +3423,10 @@
           </r>
         </is>
       </c>
-      <c r="D72" s="28" t="n">
+      <c r="D73" s="28" t="n">
         <v>1.38</v>
       </c>
-      <c r="E72" s="17" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3413,27 +3449,27 @@
           </r>
         </is>
       </c>
-      <c r="F72" s="17" t="inlineStr">
+      <c r="F73" s="17" t="inlineStr">
         <is>
           <t>의료·정밀기기, 전기·전자</t>
         </is>
       </c>
-      <c r="G72" s="17" t="inlineStr">
-        <is>
-          <t>외국인 매수세로 코스피 3.29% 급등.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="31" customHeight="1" s="15">
-      <c r="A73" s="31" t="inlineStr">
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>외국인 매수세로 반도체 중심 반등.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="31" customHeight="1" s="15">
+      <c r="A74" s="31" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B73" s="29" t="n">
+      <c r="B74" s="29" t="n">
         <v>-3.52</v>
       </c>
-      <c r="C73" s="31" t="inlineStr">
+      <c r="C74" s="31" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3456,10 +3492,10 @@
           </r>
         </is>
       </c>
-      <c r="D73" s="29" t="n">
+      <c r="D74" s="29" t="n">
         <v>-3.62</v>
       </c>
-      <c r="E73" s="17" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3482,242 +3518,227 @@
           </r>
         </is>
       </c>
-      <c r="F73" s="17" t="inlineStr">
+      <c r="F74" s="17" t="inlineStr">
         <is>
           <t>일반서비스, 비금속</t>
         </is>
       </c>
-      <c r="G73" s="17" t="inlineStr">
-        <is>
-          <t>기관 매도세로 코스피 3.52% 급락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>외국인·기관 매도로 지수 급락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="31" customHeight="1" s="15">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B75" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C75" s="31" t="inlineStr">
+        <is>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="D75" s="29" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>제약, 의료·정밀기기</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>기관 매수로 코스피 상승 마감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>월간 종합 코멘트 — 매크로·수급</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" s="3" t="inlineStr"/>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
-      <c r="K75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="15">
-      <c r="A77" s="17" t="inlineStr">
-        <is>
-          <t>- 미국 소비자물가지수(3.7%)와 생산자물가지수(1.3%)가 예상치를 상회하며 인플레이션 압력이 재확인된 매크로 환경이었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="15">
-      <c r="A78" s="17" t="inlineStr">
-        <is>
-          <t>- 외국인은 전기·전자 섹터에 대규모 순매도를 집중하며 지수 하락을 주도했고, 기관은 일부 섹터에서 방어적 매수를 보였습니다.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="31" customHeight="1" s="15">
       <c r="A79" s="17" t="inlineStr">
         <is>
-          <t>- 시장 전반은 AI 인프라 투자 지속성과 수익성 사이에서 방향성을 탐색 중이며, 대형주 중심의 수급 변화가 지수 등락을 결정짓고 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1" s="15">
+          <t>- 매크로 환경: 9월 수출이 83.5% 급증하며 펀더멘털은 견조했으나, 미국 CPI(3.7%)와 PPI(1.3%)가 예상치를 상회하며 고금리 장기화 우려가 시장을 압박함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="31" customHeight="1" s="15">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t>- 수출 펀더멘털은 견조하나, 고금리 장기화 우려가 기술주 중심의 수급 이탈을 가속화하며 변동성을 키우고 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81"/>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+          <t>- 수급 구도: 외국인의 대규모 순매도가 전기·전자 섹터에 집중되며 지수 하락을 주도했고, 기관은 제약 및 오락·문화 섹터에서 순매수를 기록하며 방어함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="31" customHeight="1" s="15">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>- 종합 관점: 시장은 AI 인프라 투자 지속성과 수익성 사이에서 방향성을 탐색 중이며, 대형주 중심의 외국인 수급 변화가 지수 등락의 핵심 변수로 작용함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>투자자 합산 순매수 상위/하위</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr"/>
-      <c r="D82" s="3" t="inlineStr"/>
-      <c r="E82" s="3" t="inlineStr"/>
-      <c r="F82" s="3" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr"/>
-      <c r="H82" s="3" t="inlineStr"/>
-      <c r="I82" s="3" t="inlineStr"/>
-      <c r="J82" s="18" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="18" t="inlineStr">
         <is>
           <t>외인+기관계, 억원</t>
         </is>
       </c>
-      <c r="K82" s="3" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="K83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
+      <c r="K84" s="4" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="31" customHeight="1" s="15">
-      <c r="A84" s="8" t="inlineStr">
+    <row r="85" ht="31" customHeight="1" s="15">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="B84" s="31" t="n">
+      <c r="B85" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="C84" s="17" t="inlineStr">
+      <c r="C85" s="17" t="inlineStr">
         <is>
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="D84" s="34" t="inlineStr">
+      <c r="D85" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E84" s="28" t="n">
+      <c r="E85" s="28" t="n">
         <v>3473</v>
       </c>
-      <c r="F84" s="29" t="n">
+      <c r="F85" s="29" t="n">
         <v>-1026</v>
       </c>
-      <c r="G84" s="28" t="n">
+      <c r="G85" s="28" t="n">
         <v>4498</v>
       </c>
-      <c r="H84" s="29" t="n">
+      <c r="H85" s="29" t="n">
         <v>-3450</v>
       </c>
-      <c r="I84" s="31" t="n">
+      <c r="I85" s="31" t="n">
         <v>6262.4</v>
       </c>
-      <c r="J84" s="31" t="n">
-        <v>42022.8</v>
-      </c>
-      <c r="K84" s="31" t="n">
-        <v>9054.9</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
-        </is>
-      </c>
-      <c r="B85" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C85" s="31" t="inlineStr">
-        <is>
-          <t>삼성E&amp;A</t>
-        </is>
-      </c>
-      <c r="D85" s="34" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="E85" s="28" t="n">
-        <v>2656</v>
-      </c>
-      <c r="F85" s="28" t="n">
-        <v>1314</v>
-      </c>
-      <c r="G85" s="28" t="n">
-        <v>1342</v>
-      </c>
-      <c r="H85" s="29" t="n">
-        <v>-2649</v>
-      </c>
-      <c r="I85" s="31" t="n">
-        <v>475.9</v>
-      </c>
       <c r="J85" s="31" t="n">
-        <v>3191.1</v>
+        <v>39744.6</v>
       </c>
       <c r="K85" s="31" t="n">
-        <v>-7.8</v>
+        <v>6776.7</v>
       </c>
     </row>
     <row r="86">
@@ -3727,38 +3748,38 @@
         </is>
       </c>
       <c r="B86" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C86" s="31" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="D86" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E86" s="28" t="n">
-        <v>2653</v>
+        <v>2656</v>
       </c>
       <c r="F86" s="28" t="n">
-        <v>295</v>
+        <v>1314</v>
       </c>
       <c r="G86" s="28" t="n">
-        <v>2357</v>
+        <v>1342</v>
       </c>
       <c r="H86" s="29" t="n">
-        <v>-3245</v>
+        <v>-2649</v>
       </c>
       <c r="I86" s="31" t="n">
-        <v>816.4</v>
+        <v>475.9</v>
       </c>
       <c r="J86" s="31" t="n">
-        <v>13600.9</v>
+        <v>3704.9</v>
       </c>
       <c r="K86" s="31" t="n">
-        <v>885.7</v>
+        <v>506</v>
       </c>
     </row>
     <row r="87">
@@ -3768,38 +3789,38 @@
         </is>
       </c>
       <c r="B87" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C87" s="31" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D87" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E87" s="28" t="n">
-        <v>2251</v>
+        <v>2653</v>
       </c>
       <c r="F87" s="28" t="n">
-        <v>13</v>
+        <v>295</v>
       </c>
       <c r="G87" s="28" t="n">
-        <v>2239</v>
+        <v>2357</v>
       </c>
       <c r="H87" s="29" t="n">
-        <v>-1986</v>
+        <v>-3245</v>
       </c>
       <c r="I87" s="31" t="n">
-        <v>1762.9</v>
+        <v>816.4</v>
       </c>
       <c r="J87" s="31" t="n">
-        <v>6885.6</v>
+        <v>13339.6</v>
       </c>
       <c r="K87" s="31" t="n">
-        <v>3111.6</v>
+        <v>624.4</v>
       </c>
     </row>
     <row r="88">
@@ -3809,38 +3830,38 @@
         </is>
       </c>
       <c r="B88" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C88" s="31" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="D88" s="34" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E88" s="28" t="n">
-        <v>1683</v>
+        <v>2251</v>
       </c>
       <c r="F88" s="28" t="n">
-        <v>1042</v>
+        <v>13</v>
       </c>
       <c r="G88" s="28" t="n">
-        <v>641</v>
+        <v>2239</v>
       </c>
       <c r="H88" s="29" t="n">
-        <v>-1670</v>
+        <v>-1986</v>
       </c>
       <c r="I88" s="31" t="n">
-        <v>144.4</v>
+        <v>1762.9</v>
       </c>
       <c r="J88" s="31" t="n">
-        <v>3589.1</v>
+        <v>6369.2</v>
       </c>
       <c r="K88" s="31" t="n">
-        <v>178.6</v>
+        <v>2595.2</v>
       </c>
     </row>
     <row r="89">
@@ -3850,38 +3871,38 @@
         </is>
       </c>
       <c r="B89" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89" s="31" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="D89" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="E89" s="28" t="n">
-        <v>1537</v>
+        <v>1683</v>
       </c>
       <c r="F89" s="28" t="n">
-        <v>1125</v>
+        <v>1042</v>
       </c>
       <c r="G89" s="28" t="n">
-        <v>412</v>
+        <v>641</v>
       </c>
       <c r="H89" s="29" t="n">
-        <v>-1522</v>
+        <v>-1670</v>
       </c>
       <c r="I89" s="31" t="n">
-        <v>908.6</v>
+        <v>144.4</v>
       </c>
       <c r="J89" s="31" t="n">
-        <v>9403.5</v>
+        <v>3589.1</v>
       </c>
       <c r="K89" s="31" t="n">
-        <v>-1589.8</v>
+        <v>178.6</v>
       </c>
     </row>
     <row r="90">
@@ -3891,38 +3912,38 @@
         </is>
       </c>
       <c r="B90" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C90" s="31" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="D90" s="34" t="inlineStr">
         <is>
-          <t>오락·문화</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E90" s="28" t="n">
-        <v>1295</v>
+        <v>1537</v>
       </c>
       <c r="F90" s="28" t="n">
-        <v>62</v>
+        <v>1125</v>
       </c>
       <c r="G90" s="28" t="n">
-        <v>1233</v>
+        <v>412</v>
       </c>
       <c r="H90" s="29" t="n">
-        <v>-1342</v>
+        <v>-1522</v>
       </c>
       <c r="I90" s="31" t="n">
-        <v>407.3</v>
+        <v>908.6</v>
       </c>
       <c r="J90" s="31" t="n">
-        <v>4399.6</v>
+        <v>9403.5</v>
       </c>
       <c r="K90" s="31" t="n">
-        <v>640.9</v>
+        <v>-1589.8</v>
       </c>
     </row>
     <row r="91">
@@ -3932,38 +3953,38 @@
         </is>
       </c>
       <c r="B91" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C91" s="31" t="inlineStr">
         <is>
-          <t>LG씨엔에스</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="D91" s="34" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>오락·문화</t>
         </is>
       </c>
       <c r="E91" s="28" t="n">
-        <v>1136</v>
+        <v>1295</v>
       </c>
       <c r="F91" s="28" t="n">
-        <v>559</v>
+        <v>62</v>
       </c>
       <c r="G91" s="28" t="n">
-        <v>577</v>
+        <v>1233</v>
       </c>
       <c r="H91" s="29" t="n">
-        <v>-1108</v>
+        <v>-1342</v>
       </c>
       <c r="I91" s="31" t="n">
-        <v>165.1</v>
+        <v>407.3</v>
       </c>
       <c r="J91" s="31" t="n">
-        <v>2007.4</v>
+        <v>4399.6</v>
       </c>
       <c r="K91" s="31" t="n">
-        <v>-406.2</v>
+        <v>640.9</v>
       </c>
     </row>
     <row r="92">
@@ -3973,38 +3994,38 @@
         </is>
       </c>
       <c r="B92" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C92" s="31" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>LG씨엔에스</t>
         </is>
       </c>
       <c r="D92" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E92" s="28" t="n">
-        <v>688</v>
+        <v>1136</v>
       </c>
       <c r="F92" s="28" t="n">
-        <v>271</v>
+        <v>559</v>
       </c>
       <c r="G92" s="28" t="n">
-        <v>417</v>
+        <v>577</v>
       </c>
       <c r="H92" s="29" t="n">
-        <v>-675</v>
+        <v>-1108</v>
       </c>
       <c r="I92" s="31" t="n">
-        <v>139.8</v>
+        <v>165.1</v>
       </c>
       <c r="J92" s="31" t="n">
-        <v>9538.200000000001</v>
+        <v>2038.6</v>
       </c>
       <c r="K92" s="31" t="n">
-        <v>1057.6</v>
+        <v>-375</v>
       </c>
     </row>
     <row r="93">
@@ -4014,79 +4035,79 @@
         </is>
       </c>
       <c r="B93" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C93" s="31" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="D93" s="34" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="E93" s="28" t="n">
+        <v>688</v>
+      </c>
+      <c r="F93" s="28" t="n">
+        <v>271</v>
+      </c>
+      <c r="G93" s="28" t="n">
+        <v>417</v>
+      </c>
+      <c r="H93" s="29" t="n">
+        <v>-675</v>
+      </c>
+      <c r="I93" s="31" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="J93" s="31" t="n">
+        <v>9145.9</v>
+      </c>
+      <c r="K93" s="31" t="n">
+        <v>665.3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B94" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="C93" s="31" t="inlineStr">
+      <c r="C94" s="31" t="inlineStr">
         <is>
           <t>고영</t>
         </is>
       </c>
-      <c r="D93" s="34" t="inlineStr">
+      <c r="D94" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="E93" s="28" t="n">
+      <c r="E94" s="28" t="n">
         <v>596</v>
       </c>
-      <c r="F93" s="28" t="n">
+      <c r="F94" s="28" t="n">
         <v>551</v>
       </c>
-      <c r="G93" s="28" t="n">
+      <c r="G94" s="28" t="n">
         <v>45</v>
       </c>
-      <c r="H93" s="29" t="n">
+      <c r="H94" s="29" t="n">
         <v>-620</v>
       </c>
-      <c r="I93" s="31" t="n">
+      <c r="I94" s="31" t="n">
         <v>93.3</v>
       </c>
-      <c r="J93" s="31" t="n">
+      <c r="J94" s="31" t="n">
         <v>1436.3</v>
       </c>
-      <c r="K93" s="31" t="n">
+      <c r="K94" s="31" t="n">
         <v>-107.4</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B94" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" s="31" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="D94" s="34" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E94" s="29" t="n">
-        <v>-100163</v>
-      </c>
-      <c r="F94" s="29" t="n">
-        <v>-97475</v>
-      </c>
-      <c r="G94" s="29" t="n">
-        <v>-2688</v>
-      </c>
-      <c r="H94" s="28" t="n">
-        <v>9900</v>
-      </c>
-      <c r="I94" s="31" t="n">
-        <v>28973.6</v>
-      </c>
-      <c r="J94" s="31" t="n">
-        <v>154505.1</v>
-      </c>
-      <c r="K94" s="31" t="n">
-        <v>-71212</v>
       </c>
     </row>
     <row r="95">
@@ -4096,11 +4117,11 @@
         </is>
       </c>
       <c r="B95" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D95" s="34" t="inlineStr">
@@ -4109,25 +4130,25 @@
         </is>
       </c>
       <c r="E95" s="29" t="n">
-        <v>-52943</v>
+        <v>-100163</v>
       </c>
       <c r="F95" s="29" t="n">
-        <v>-36199</v>
+        <v>-97475</v>
       </c>
       <c r="G95" s="29" t="n">
-        <v>-16744</v>
+        <v>-2688</v>
       </c>
       <c r="H95" s="28" t="n">
-        <v>38513</v>
+        <v>9900</v>
       </c>
       <c r="I95" s="31" t="n">
-        <v>20083.2</v>
+        <v>28973.6</v>
       </c>
       <c r="J95" s="31" t="n">
-        <v>185130.7</v>
+        <v>144905.4</v>
       </c>
       <c r="K95" s="31" t="n">
-        <v>-14586.9</v>
+        <v>-80811.7</v>
       </c>
     </row>
     <row r="96">
@@ -4137,11 +4158,11 @@
         </is>
       </c>
       <c r="B96" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C96" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D96" s="34" t="inlineStr">
@@ -4150,25 +4171,25 @@
         </is>
       </c>
       <c r="E96" s="29" t="n">
-        <v>-5814</v>
+        <v>-52943</v>
       </c>
       <c r="F96" s="29" t="n">
-        <v>-3168</v>
+        <v>-36199</v>
       </c>
       <c r="G96" s="29" t="n">
-        <v>-2646</v>
+        <v>-16744</v>
       </c>
       <c r="H96" s="28" t="n">
-        <v>5683</v>
+        <v>38513</v>
       </c>
       <c r="I96" s="31" t="n">
-        <v>3750.9</v>
+        <v>20083.2</v>
       </c>
       <c r="J96" s="31" t="n">
-        <v>28767.9</v>
+        <v>175096.2</v>
       </c>
       <c r="K96" s="31" t="n">
-        <v>-7714.3</v>
+        <v>-24621.4</v>
       </c>
     </row>
     <row r="97">
@@ -4178,38 +4199,38 @@
         </is>
       </c>
       <c r="B97" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C97" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D97" s="34" t="inlineStr">
         <is>
-          <t>기타금융</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E97" s="29" t="n">
-        <v>-5132</v>
+        <v>-5814</v>
       </c>
       <c r="F97" s="29" t="n">
-        <v>-7020</v>
-      </c>
-      <c r="G97" s="28" t="n">
-        <v>1888</v>
+        <v>-3168</v>
+      </c>
+      <c r="G97" s="29" t="n">
+        <v>-2646</v>
       </c>
       <c r="H97" s="28" t="n">
-        <v>5087</v>
+        <v>5683</v>
       </c>
       <c r="I97" s="31" t="n">
-        <v>5124.2</v>
+        <v>3750.9</v>
       </c>
       <c r="J97" s="31" t="n">
-        <v>21826.9</v>
+        <v>28267.5</v>
       </c>
       <c r="K97" s="31" t="n">
-        <v>-9609.5</v>
+        <v>-8214.700000000001</v>
       </c>
     </row>
     <row r="98">
@@ -4219,38 +4240,38 @@
         </is>
       </c>
       <c r="B98" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D98" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="E98" s="29" t="n">
-        <v>-4840</v>
+        <v>-5132</v>
       </c>
       <c r="F98" s="29" t="n">
-        <v>-3611</v>
-      </c>
-      <c r="G98" s="29" t="n">
-        <v>-1229</v>
+        <v>-7020</v>
+      </c>
+      <c r="G98" s="28" t="n">
+        <v>1888</v>
       </c>
       <c r="H98" s="28" t="n">
-        <v>4425</v>
+        <v>5087</v>
       </c>
       <c r="I98" s="31" t="n">
-        <v>820.2</v>
+        <v>5124.2</v>
       </c>
       <c r="J98" s="31" t="n">
-        <v>25343.8</v>
+        <v>20822.3</v>
       </c>
       <c r="K98" s="31" t="n">
-        <v>808.8</v>
+        <v>-10614.1</v>
       </c>
     </row>
     <row r="99">
@@ -4260,11 +4281,11 @@
         </is>
       </c>
       <c r="B99" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C99" s="31" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D99" s="34" t="inlineStr">
@@ -4273,25 +4294,25 @@
         </is>
       </c>
       <c r="E99" s="29" t="n">
-        <v>-4681</v>
+        <v>-4840</v>
       </c>
       <c r="F99" s="29" t="n">
-        <v>-3795</v>
+        <v>-3611</v>
       </c>
       <c r="G99" s="29" t="n">
-        <v>-885</v>
+        <v>-1229</v>
       </c>
       <c r="H99" s="28" t="n">
-        <v>4665</v>
+        <v>4425</v>
       </c>
       <c r="I99" s="31" t="n">
-        <v>1777.7</v>
+        <v>820.2</v>
       </c>
       <c r="J99" s="31" t="n">
-        <v>3861</v>
+        <v>24488.6</v>
       </c>
       <c r="K99" s="31" t="n">
-        <v>-1554.2</v>
+        <v>-46.4</v>
       </c>
     </row>
     <row r="100">
@@ -4301,38 +4322,38 @@
         </is>
       </c>
       <c r="B100" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C100" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="D100" s="34" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E100" s="29" t="n">
-        <v>-3163</v>
+        <v>-4681</v>
       </c>
       <c r="F100" s="29" t="n">
-        <v>-3072</v>
+        <v>-3795</v>
       </c>
       <c r="G100" s="29" t="n">
-        <v>-91</v>
+        <v>-885</v>
       </c>
       <c r="H100" s="28" t="n">
-        <v>3151</v>
+        <v>4665</v>
       </c>
       <c r="I100" s="31" t="n">
-        <v>4413.7</v>
+        <v>1777.7</v>
       </c>
       <c r="J100" s="31" t="n">
-        <v>16844.8</v>
+        <v>3630.1</v>
       </c>
       <c r="K100" s="31" t="n">
-        <v>-3574.9</v>
+        <v>-1785.1</v>
       </c>
     </row>
     <row r="101">
@@ -4342,599 +4363,633 @@
         </is>
       </c>
       <c r="B101" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C101" s="31" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="D101" s="34" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="E101" s="29" t="n">
+        <v>-3163</v>
+      </c>
+      <c r="F101" s="29" t="n">
+        <v>-3072</v>
+      </c>
+      <c r="G101" s="29" t="n">
+        <v>-91</v>
+      </c>
+      <c r="H101" s="28" t="n">
+        <v>3151</v>
+      </c>
+      <c r="I101" s="31" t="n">
+        <v>4413.7</v>
+      </c>
+      <c r="J101" s="31" t="n">
+        <v>16084</v>
+      </c>
+      <c r="K101" s="31" t="n">
+        <v>-4335.7</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+      <c r="B102" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="C101" s="31" t="inlineStr">
+      <c r="C102" s="31" t="inlineStr">
         <is>
           <t>LG전자</t>
         </is>
       </c>
-      <c r="D101" s="34" t="inlineStr">
+      <c r="D102" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E101" s="29" t="n">
+      <c r="E102" s="29" t="n">
         <v>-2517</v>
       </c>
-      <c r="F101" s="29" t="n">
+      <c r="F102" s="29" t="n">
         <v>-2354</v>
       </c>
-      <c r="G101" s="29" t="n">
+      <c r="G102" s="29" t="n">
         <v>-163</v>
       </c>
-      <c r="H101" s="28" t="n">
+      <c r="H102" s="28" t="n">
         <v>2440</v>
       </c>
-      <c r="I101" s="31" t="n">
+      <c r="I102" s="31" t="n">
         <v>2503.8</v>
       </c>
-      <c r="J101" s="31" t="n">
-        <v>7545.3</v>
-      </c>
-      <c r="K101" s="31" t="n">
-        <v>-2139.7</v>
-      </c>
-    </row>
-    <row r="102" ht="31" customHeight="1" s="15">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="J102" s="31" t="n">
+        <v>7245.5</v>
+      </c>
+      <c r="K102" s="31" t="n">
+        <v>-2439.5</v>
+      </c>
+    </row>
+    <row r="103" ht="31" customHeight="1" s="15">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B102" s="31" t="n">
+      <c r="B103" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="C102" s="17" t="inlineStr">
+      <c r="C103" s="17" t="inlineStr">
         <is>
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="D102" s="34" t="inlineStr">
+      <c r="D103" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="E102" s="29" t="n">
+      <c r="E103" s="29" t="n">
         <v>-1653</v>
       </c>
-      <c r="F102" s="29" t="n">
+      <c r="F103" s="29" t="n">
         <v>-1503</v>
       </c>
-      <c r="G102" s="29" t="n">
+      <c r="G103" s="29" t="n">
         <v>-151</v>
       </c>
-      <c r="H102" s="28" t="n">
+      <c r="H103" s="28" t="n">
         <v>1665</v>
       </c>
-      <c r="I102" s="31" t="n">
+      <c r="I103" s="31" t="n">
         <v>2181.3</v>
       </c>
-      <c r="J102" s="31" t="n">
-        <v>9770.4</v>
-      </c>
-      <c r="K102" s="31" t="n">
-        <v>-3271.2</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="J103" s="31" t="n">
+        <v>9947.6</v>
+      </c>
+      <c r="K103" s="31" t="n">
+        <v>-3094</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="B103" s="31" t="n">
+      <c r="B104" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="C103" s="31" t="inlineStr">
+      <c r="C104" s="31" t="inlineStr">
         <is>
           <t>LS ELECTRIC</t>
         </is>
       </c>
-      <c r="D103" s="34" t="inlineStr">
+      <c r="D104" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E103" s="29" t="n">
+      <c r="E104" s="29" t="n">
         <v>-1549</v>
       </c>
-      <c r="F103" s="29" t="n">
+      <c r="F104" s="29" t="n">
         <v>-1140</v>
       </c>
-      <c r="G103" s="29" t="n">
+      <c r="G104" s="29" t="n">
         <v>-409</v>
       </c>
-      <c r="H103" s="28" t="n">
+      <c r="H104" s="28" t="n">
         <v>1505</v>
       </c>
-      <c r="I103" s="31" t="n">
+      <c r="I104" s="31" t="n">
         <v>2040.7</v>
       </c>
-      <c r="J103" s="31" t="n">
-        <v>8093.8</v>
-      </c>
-      <c r="K103" s="31" t="n">
-        <v>-725.7</v>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="J104" s="31" t="n">
+        <v>7824.1</v>
+      </c>
+      <c r="K104" s="31" t="n">
+        <v>-995.4</v>
+      </c>
+    </row>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>섹터 시그널 종목 관찰</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr"/>
-      <c r="D105" s="3" t="inlineStr"/>
-      <c r="E105" s="3" t="inlineStr"/>
-      <c r="F105" s="3" t="inlineStr"/>
-      <c r="G105" s="18" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr"/>
+      <c r="D106" s="3" t="inlineStr"/>
+      <c r="E106" s="3" t="inlineStr"/>
+      <c r="F106" s="3" t="inlineStr"/>
+      <c r="G106" s="18" t="inlineStr">
         <is>
           <t>섹터 상태 x 수급 x 공매도·대차 x 촉매</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr"/>
-      <c r="I105" s="3" t="inlineStr"/>
-      <c r="J105" s="3" t="inlineStr"/>
-      <c r="K105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="35" t="inlineStr">
+      <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="35" t="inlineStr">
         <is>
           <t>● 동반강세 — 추세 지속형 상방 관찰</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr">
+      <c r="G107" s="3" t="inlineStr">
         <is>
           <t>● 수급유입 — 초기 유입형 상방 관찰</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B108" s="34" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="C108" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" s="31" t="inlineStr"/>
+      <c r="E108" s="31" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>아모레퍼시픽</t>
+        </is>
+      </c>
+      <c r="H108" s="34" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="I108" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J108" s="31" t="inlineStr"/>
+      <c r="K108" s="31" t="inlineStr"/>
+    </row>
+    <row r="109" ht="44.5" customHeight="1" s="15">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +1,125억 순매수, 기관 +412억 순매수, 대차잔고 -1,590억 감소 — 일반서비스(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G109" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +67억 순매수, 기관 +155억 순매수, 대차잔고 -373억 감소 — 화학(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>케이씨텍</t>
         </is>
       </c>
-      <c r="B107" s="34" t="inlineStr">
+      <c r="B110" s="34" t="inlineStr">
         <is>
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="C107" s="36" t="n">
+      <c r="C110" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="D107" s="31" t="inlineStr"/>
-      <c r="E107" s="31" t="inlineStr"/>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>아모레퍼시픽</t>
-        </is>
-      </c>
-      <c r="H107" s="34" t="inlineStr">
+      <c r="D110" s="31" t="inlineStr"/>
+      <c r="E110" s="31" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>F&amp;F</t>
+        </is>
+      </c>
+      <c r="H110" s="34" t="inlineStr">
+        <is>
+          <t>섬유·의류</t>
+        </is>
+      </c>
+      <c r="I110" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J110" s="31" t="inlineStr"/>
+      <c r="K110" s="31" t="inlineStr"/>
+    </row>
+    <row r="111" ht="44.5" customHeight="1" s="15">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +233억 순매수, 기관 +547억 순매수, 대차잔고 -57억 감소 — 의료·정밀기기(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G111" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +136억 순매수, 기관 +47억 순매수, 대차잔고 -19억 감소 — 섬유·의류(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>CJ제일제당</t>
+        </is>
+      </c>
+      <c r="B112" s="34" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="C112" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" s="31" t="inlineStr"/>
+      <c r="E112" s="31" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>LG생활건강</t>
+        </is>
+      </c>
+      <c r="H112" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="I107" s="37" t="n">
+      <c r="I112" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="J107" s="31" t="inlineStr"/>
-      <c r="K107" s="31" t="inlineStr"/>
-    </row>
-    <row r="108" ht="44.5" customHeight="1" s="15">
-      <c r="A108" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +312억 순매수, 기관 +500억 순매수, 대차잔고 0억 감소 — 의료·정밀기기(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G108" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +53억 순매수, 기관 +172억 순매수, 대차잔고 -296억 감소 — 화학(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>CJ제일제당</t>
-        </is>
-      </c>
-      <c r="B109" s="34" t="inlineStr">
+      <c r="J112" s="31" t="inlineStr"/>
+      <c r="K112" s="31" t="inlineStr"/>
+    </row>
+    <row r="113" ht="44.5" customHeight="1" s="15">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +120억 순매수, 기관 +244억 순매수, 대차잔고 -214억 감소 — 음식료·담배(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G113" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +145억 순매수, 기관 +37억 순매수, 대차잔고 -76억 감소 — 화학(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>한전기술</t>
+        </is>
+      </c>
+      <c r="B114" s="34" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="C114" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" s="31" t="inlineStr"/>
+      <c r="E114" s="31" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>에스엠국일</t>
+        </is>
+      </c>
+      <c r="H114" s="34" t="inlineStr">
+        <is>
+          <t>종이·목재</t>
+        </is>
+      </c>
+      <c r="I114" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J114" s="31" t="inlineStr"/>
+      <c r="K114" s="31" t="inlineStr"/>
+    </row>
+    <row r="115" ht="44.5" customHeight="1" s="15">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +320억 순매수, 기관 +30억 순매수, 대차잔고 -1,082억 감소 — 일반서비스(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G115" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +4억 순매수, 기관 +8억 순매수, 대차잔고 0억 감소 — 종이·목재(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>빙그레</t>
+        </is>
+      </c>
+      <c r="B116" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="C109" s="36" t="n">
+      <c r="C116" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="D109" s="31" t="inlineStr"/>
-      <c r="E109" s="31" t="inlineStr"/>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>LG생활건강</t>
-        </is>
-      </c>
-      <c r="H109" s="34" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="I109" s="37" t="n">
+      <c r="D116" s="31" t="inlineStr"/>
+      <c r="E116" s="31" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>동화기업</t>
+        </is>
+      </c>
+      <c r="H116" s="34" t="inlineStr">
+        <is>
+          <t>종이·목재</t>
+        </is>
+      </c>
+      <c r="I116" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="J109" s="31" t="inlineStr"/>
-      <c r="K109" s="31" t="inlineStr"/>
-    </row>
-    <row r="110" ht="44.5" customHeight="1" s="15">
-      <c r="A110" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +141억 순매수, 기관 +223억 순매수, 대차잔고 -182억 감소 — 음식료·담배(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G110" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +147억 순매수, 기관 +34억 순매수, 대차잔고 -114억 감소 — 화학(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>빙그레</t>
-        </is>
-      </c>
-      <c r="B111" s="34" t="inlineStr">
-        <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="C111" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D111" s="31" t="inlineStr"/>
-      <c r="E111" s="31" t="inlineStr"/>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>F&amp;F</t>
-        </is>
-      </c>
-      <c r="H111" s="34" t="inlineStr">
-        <is>
-          <t>섬유·의류</t>
-        </is>
-      </c>
-      <c r="I111" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="J111" s="31" t="inlineStr"/>
-      <c r="K111" s="31" t="inlineStr"/>
-    </row>
-    <row r="112" ht="44.5" customHeight="1" s="15">
-      <c r="A112" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +113억 순매수, 기관 +45억 순매수, 대차잔고 -31억 감소 — 음식료·담배(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G112" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +135억 순매수, 기관 +42억 순매수, 대차잔고 -10억 감소 — 섬유·의류(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>인바디</t>
-        </is>
-      </c>
-      <c r="B113" s="34" t="inlineStr">
-        <is>
-          <t>의료·정밀기기</t>
-        </is>
-      </c>
-      <c r="C113" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D113" s="31" t="inlineStr"/>
-      <c r="E113" s="31" t="inlineStr"/>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>SGC에너지</t>
-        </is>
-      </c>
-      <c r="H113" s="34" t="inlineStr">
-        <is>
-          <t>전기·가스</t>
-        </is>
-      </c>
-      <c r="I113" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="J113" s="31" t="inlineStr"/>
-      <c r="K113" s="31" t="inlineStr"/>
-    </row>
-    <row r="114" ht="44.5" customHeight="1" s="15">
-      <c r="A114" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +5억 순매수, 기관 +17억 순매수, 대차잔고 -22억 감소 — 의료·정밀기기(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G114" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +11억 순매수, 기관 +7억 순매수, 대차잔고 -52억 감소 — 전기·가스(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>롯데웰푸드</t>
-        </is>
-      </c>
-      <c r="B115" s="34" t="inlineStr">
-        <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="C115" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D115" s="31" t="inlineStr"/>
-      <c r="E115" s="31" t="inlineStr"/>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>에스엠국일</t>
-        </is>
-      </c>
-      <c r="H115" s="34" t="inlineStr">
-        <is>
-          <t>종이·목재</t>
-        </is>
-      </c>
-      <c r="I115" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="J115" s="31" t="inlineStr"/>
-      <c r="K115" s="31" t="inlineStr"/>
-    </row>
-    <row r="116" ht="44.5" customHeight="1" s="15">
-      <c r="A116" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +4억 순매수, 기관 +15억 순매수, 대차잔고 -49억 감소 — 음식료·담배(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G116" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +4억 순매수, 기관 +8억 순매수, 대차잔고 -1억 감소 — 종이·목재(수급유입) 섹터 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="117"/>
-    <row r="118">
-      <c r="A118" s="38" t="inlineStr">
+      <c r="J116" s="31" t="inlineStr"/>
+      <c r="K116" s="31" t="inlineStr"/>
+    </row>
+    <row r="117" ht="44.5" customHeight="1" s="15">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +121억 순매수, 기관 +43억 순매수, 대차잔고 -42억 감소 — 음식료·담배(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G117" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +6억 순매수, 기관 +2억 순매수, 대차잔고 -10억 감소 — 종이·목재(수급유입) 섹터 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="118"/>
+    <row r="119">
+      <c r="A119" s="38" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G118" s="39" t="inlineStr">
+      <c r="G119" s="39" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="31" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="31" t="inlineStr">
         <is>
           <t>해당 섹터·조건 충족 종목 없음</t>
         </is>
       </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>삼성전자우</t>
-        </is>
-      </c>
-      <c r="H119" s="34" t="inlineStr">
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>포스코퓨처엠</t>
+        </is>
+      </c>
+      <c r="H120" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I119" s="40" t="n">
+      <c r="I120" s="40" t="n">
         <v>-3</v>
       </c>
-      <c r="J119" s="31" t="inlineStr"/>
-      <c r="K119" s="31" t="inlineStr"/>
-    </row>
-    <row r="120" ht="44.5" customHeight="1" s="15">
-      <c r="G120" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -3,611억 순매도, 기관 -1,229억 순매도, 대차잔고 +809억 증가 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>포스코퓨처엠</t>
-        </is>
-      </c>
-      <c r="H121" s="34" t="inlineStr">
+      <c r="J120" s="31" t="inlineStr"/>
+      <c r="K120" s="31" t="inlineStr"/>
+    </row>
+    <row r="121" ht="44.5" customHeight="1" s="15">
+      <c r="G121" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -641억 순매도, 기관 -67억 순매도, 대차잔고 +864억 증가 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="H122" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I121" s="40" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J121" s="31" t="inlineStr"/>
-      <c r="K121" s="31" t="inlineStr"/>
-    </row>
-    <row r="122" ht="44.5" customHeight="1" s="15">
-      <c r="G122" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -553억 순매도, 기관 -58억 순매도, 대차잔고 +1,549억 증가 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="H123" s="34" t="inlineStr">
+      <c r="I122" s="40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J122" s="31" t="inlineStr"/>
+      <c r="K122" s="31" t="inlineStr"/>
+    </row>
+    <row r="123" ht="44.5" customHeight="1" s="15">
+      <c r="G123" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -97,475억 순매도, 기관 -2,688억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="H124" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I123" s="40" t="n">
+      <c r="I124" s="40" t="n">
         <v>-2</v>
       </c>
-      <c r="J123" s="31" t="inlineStr"/>
-      <c r="K123" s="31" t="inlineStr"/>
-    </row>
-    <row r="124" ht="44.5" customHeight="1" s="15">
-      <c r="G124" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -97,475억 순매도, 기관 -2,688억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="H125" s="34" t="inlineStr">
+      <c r="J124" s="31" t="inlineStr"/>
+      <c r="K124" s="31" t="inlineStr"/>
+    </row>
+    <row r="125" ht="44.5" customHeight="1" s="15">
+      <c r="G125" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -36,199억 순매도, 기관 -16,744억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="H126" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I125" s="40" t="n">
+      <c r="I126" s="40" t="n">
         <v>-2</v>
       </c>
-      <c r="J125" s="31" t="inlineStr"/>
-      <c r="K125" s="31" t="inlineStr"/>
-    </row>
-    <row r="126" ht="44.5" customHeight="1" s="15">
-      <c r="G126" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -36,199억 순매도, 기관 -16,744억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="H127" s="34" t="inlineStr">
+      <c r="J126" s="31" t="inlineStr"/>
+      <c r="K126" s="31" t="inlineStr"/>
+    </row>
+    <row r="127" ht="44.5" customHeight="1" s="15">
+      <c r="G127" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -3,168억 순매도, 기관 -2,646억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="H128" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="I127" s="40" t="n">
+      <c r="I128" s="40" t="n">
         <v>-2</v>
       </c>
-      <c r="J127" s="31" t="inlineStr"/>
-      <c r="K127" s="31" t="inlineStr"/>
-    </row>
-    <row r="128" ht="44.5" customHeight="1" s="15">
-      <c r="G128" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -3,168억 순매도, 기관 -2,646억 순매도, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="129"/>
-    <row r="130" ht="31" customHeight="1" s="15">
-      <c r="A130" s="41" t="inlineStr">
+      <c r="J128" s="31" t="inlineStr"/>
+      <c r="K128" s="31" t="inlineStr"/>
+    </row>
+    <row r="129" ht="44.5" customHeight="1" s="15">
+      <c r="G129" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -1,026억 순매도, 대차잔고 +6,777억 증가, 공매도 누적 상위 등재 — 전기·전자(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="130"/>
+    <row r="131" ht="31" customHeight="1" s="15">
+      <c r="A131" s="41" t="inlineStr">
         <is>
           <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
       </c>
     </row>
-    <row r="131"/>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="132"/>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>월간 시장 흐름</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr"/>
-      <c r="D132" s="3" t="inlineStr"/>
-      <c r="E132" s="3" t="inlineStr"/>
-      <c r="F132" s="3" t="inlineStr"/>
-      <c r="G132" s="3" t="inlineStr"/>
-      <c r="H132" s="3" t="inlineStr"/>
-      <c r="I132" s="3" t="inlineStr"/>
-      <c r="J132" s="3" t="inlineStr"/>
-      <c r="K132" s="3" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr"/>
+      <c r="D133" s="3" t="inlineStr"/>
+      <c r="E133" s="3" t="inlineStr"/>
+      <c r="F133" s="3" t="inlineStr"/>
+      <c r="G133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>Market Flow</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="15" customHeight="1" s="15">
-      <c r="A134" s="17" t="inlineStr">
-        <is>
-          <t>- 월 초 9월 수출이 전년 대비 83.5% 급증하는 등 견조한 펀더멘털을 확인하며 코스피가 7,000선을 돌파하는 강세를 보였습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="31" customHeight="1" s="15">
+    <row r="135" ht="15" customHeight="1" s="15">
       <c r="A135" s="17" t="inlineStr">
         <is>
-          <t>- 월 중순 미국 소비자물가지수(CPI)와 생산자물가지수(PPI)가 예상치를 상회하며 인플레이션 우려가 재점화되어 기술주 중심의 투매가 발생했습니다.</t>
+          <t>- 월 초 9월 수출이 전년 대비 83.5% 급증하는 등 견조한 펀더멘털이 확인되며 코스피 7,000선 회복을 시도함.</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="15">
       <c r="A136" s="17" t="inlineStr">
         <is>
-          <t>- 외국인은 코스피 시장에서 대규모 순매도를 지속하며 지수 하락을 주도했고, 특히 전기·전자 섹터에 매도세가 집중되었습니다.</t>
+          <t>- 중순 이후 미국 소비자물가지수(CPI)와 생산자물가지수(PPI)가 예상치를 상회하며 인플레이션 우려가 재점화됨.</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="15">
       <c r="A137" s="17" t="inlineStr">
         <is>
-          <t>- 월 후반 미국 물가 지표의 서프라이즈가 고금리 장기화 공포를 키우며 시장의 변동성을 극대화했습니다.</t>
+          <t>- 외국인의 대규모 순매도세가 전기·전자 섹터에 집중되며 코스피 지수가 5,500선까지 밀리는 급락장이 연출됨.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="15">
       <c r="A138" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 대형주를 중심으로 외국인 수급에 따른 급등락이 반복되며 지수 방향성을 결정짓는 핵심 요인으로 작용했습니다.</t>
+          <t>- 주 후반 저가 매수세와 기관의 수급 유입으로 반등을 시도했으나, AI 수익성 우려와 매크로 불확실성으로 변동성이 지속됨.</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="15">
       <c r="A139" s="17" t="inlineStr">
         <is>
-          <t>- 제약, 오락·문화 등 일부 섹터는 개별 모멘텀과 수급 유입으로 시장 하락 속에서도 상대적 강세를 유지했습니다.</t>
+          <t>- 외국인은 월중 대규모 매도세를 보였으나, 기관은 제약 및 오락·문화 섹터 중심으로 방어적인 수급을 형성함.</t>
         </is>
       </c>
     </row>
@@ -4963,28 +5018,28 @@
     <row r="142" ht="15" customHeight="1" s="15">
       <c r="A142" s="17" t="inlineStr">
         <is>
-          <t>- 월 초 반도체·바이오 섹터가 수출 데이터 호조에 힘입어 시장 상승을 주도했습니다.</t>
+          <t>- 월 초 반도체 수출 데이터 호조로 전기·전자 및 의료·정밀기기 섹터가 주도주로 부상함.</t>
         </is>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="15">
       <c r="A143" s="17" t="inlineStr">
         <is>
-          <t>- 월 중순 이후 미국 인플레이션 우려로 전기·전자 및 반도체 섹터가 지속적인 약세를 보였습니다.</t>
+          <t>- 중순 이후 미국발 인플레이션 공포로 기술주 투매가 발생하며 전기·전자 섹터가 급락함.</t>
         </is>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" s="15">
       <c r="A144" s="17" t="inlineStr">
         <is>
-          <t>- 운송·창고 섹터는 중동 지정학적 리스크에 따른 해상 운임 상승 기대감으로 강세를 유지했습니다.</t>
+          <t>- 운송·창고 섹터는 중동 지정학적 리스크에 따른 해상 운임 상승 기대감으로 강세를 유지함.</t>
         </is>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" s="15">
       <c r="A145" s="17" t="inlineStr">
         <is>
-          <t>- 제약 및 오락·문화 섹터는 신약 모멘텀과 IP 가치 부각으로 수급이 유입되며 방어적인 흐름을 보였습니다.</t>
+          <t>- 제약 섹터는 신약 모멘텀과 기관의 순매수세가 집중되며 시장 하락기에도 상대적 강세를 보임.</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5133,7 @@
         </is>
       </c>
       <c r="F149" s="29" t="n">
-        <v>-2.1</v>
+        <v>-6.18</v>
       </c>
       <c r="G149" s="17" t="inlineStr">
         <is>
@@ -5113,7 +5168,7 @@
         </is>
       </c>
       <c r="F150" s="28" t="n">
-        <v>37.42</v>
+        <v>31.02</v>
       </c>
       <c r="G150" s="17" t="inlineStr">
         <is>
@@ -5148,7 +5203,7 @@
         </is>
       </c>
       <c r="F151" s="29" t="n">
-        <v>-8.02</v>
+        <v>-9.92</v>
       </c>
       <c r="G151" s="17" t="inlineStr">
         <is>
@@ -5183,7 +5238,7 @@
         </is>
       </c>
       <c r="F152" s="29" t="n">
-        <v>-14.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G152" s="17" t="inlineStr">
         <is>
@@ -5218,7 +5273,7 @@
         </is>
       </c>
       <c r="F153" s="28" t="n">
-        <v>76.95999999999999</v>
+        <v>100.61</v>
       </c>
       <c r="G153" s="17" t="inlineStr">
         <is>
@@ -5253,7 +5308,7 @@
         </is>
       </c>
       <c r="F154" s="28" t="n">
-        <v>54.54</v>
+        <v>51.93</v>
       </c>
       <c r="G154" s="17" t="inlineStr">
         <is>
@@ -5288,7 +5343,7 @@
         </is>
       </c>
       <c r="F155" s="28" t="n">
-        <v>34.54</v>
+        <v>36.03</v>
       </c>
       <c r="G155" s="17" t="inlineStr">
         <is>
@@ -5358,7 +5413,7 @@
         </is>
       </c>
       <c r="F157" s="28" t="n">
-        <v>200.88</v>
+        <v>158.26</v>
       </c>
       <c r="G157" s="17" t="inlineStr">
         <is>
@@ -5393,7 +5448,7 @@
         </is>
       </c>
       <c r="F158" s="28" t="n">
-        <v>180.94</v>
+        <v>114.09</v>
       </c>
       <c r="G158" s="17" t="inlineStr">
         <is>
@@ -5428,7 +5483,7 @@
         </is>
       </c>
       <c r="F159" s="28" t="n">
-        <v>43.36</v>
+        <v>48.31</v>
       </c>
       <c r="G159" s="17" t="inlineStr">
         <is>
@@ -5464,7 +5519,7 @@
         </is>
       </c>
       <c r="F160" s="28" t="n">
-        <v>28.51</v>
+        <v>23.83</v>
       </c>
       <c r="G160" s="17" t="inlineStr">
         <is>
@@ -5499,7 +5554,7 @@
         </is>
       </c>
       <c r="F161" s="28" t="n">
-        <v>150.52</v>
+        <v>134.86</v>
       </c>
       <c r="G161" s="17" t="inlineStr">
         <is>
@@ -5535,7 +5590,7 @@
         </is>
       </c>
       <c r="F162" s="28" t="n">
-        <v>21.9</v>
+        <v>25.86</v>
       </c>
       <c r="G162" s="17" t="inlineStr">
         <is>
@@ -5544,15 +5599,15 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="31" customHeight="1" s="15">
+    <row r="163" ht="44.5" customHeight="1" s="15">
       <c r="A163" s="31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B163" s="31" t="inlineStr">
         <is>
-          <t>유니켐</t>
+          <t>국제약품 (2회)</t>
         </is>
       </c>
       <c r="C163" s="31" t="inlineStr">
@@ -5562,7 +5617,7 @@
       </c>
       <c r="D163" s="34" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E163" s="14" t="inlineStr">
@@ -5571,129 +5626,130 @@
         </is>
       </c>
       <c r="F163" s="28" t="n">
-        <v>83.27</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G163" s="17" t="inlineStr">
         <is>
-          <t>미국 유연전자 기업 인수 및 로봇 신사업 진출이라는 대형 재료로 상한가 기록.</t>
+          <t>러시아 페스트 우려 관련 이슈에 따른 테마성 매수세 유입
+(10-07) 러시아 페스트 관련 진단키트 수요 급증 및 경영권 승계 기대감 복합 작용.</t>
         </is>
       </c>
     </row>
     <row r="164" ht="31" customHeight="1" s="15">
       <c r="A164" s="31" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B164" s="31" t="inlineStr">
+        <is>
+          <t>유니켐</t>
+        </is>
+      </c>
+      <c r="C164" s="31" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="D164" s="34" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="E164" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F164" s="28" t="n">
+        <v>75.16</v>
+      </c>
+      <c r="G164" s="17" t="inlineStr">
+        <is>
+          <t>미국 유연전자 기업 인수 및 로봇 신사업 진출이라는 대형 재료로 상한가 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="31" customHeight="1" s="15">
+      <c r="A165" s="31" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B164" s="31" t="inlineStr">
+      <c r="B165" s="31" t="inlineStr">
         <is>
           <t>에스엠벡셀</t>
         </is>
       </c>
-      <c r="C164" s="31" t="inlineStr">
+      <c r="C165" s="31" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D164" s="34" t="inlineStr">
+      <c r="D165" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="E164" s="14" t="inlineStr">
+      <c r="E165" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F164" s="28" t="n">
-        <v>45.84</v>
-      </c>
-      <c r="G164" s="17" t="inlineStr">
+      <c r="F165" s="28" t="n">
+        <v>38.81</v>
+      </c>
+      <c r="G165" s="17" t="inlineStr">
         <is>
           <t>서울대와 공동으로 저궤도 위성용 리튬이온 배터리 제조 기술 확보</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="58" customHeight="1" s="15">
-      <c r="A165" s="31" t="inlineStr">
+    <row r="166" ht="58" customHeight="1" s="15">
+      <c r="A166" s="31" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B165" s="17" t="inlineStr">
+      <c r="B166" s="17" t="inlineStr">
         <is>
           <t>하이퍼코퍼레이션 (2회)</t>
         </is>
       </c>
-      <c r="C165" s="31" t="inlineStr">
+      <c r="C166" s="31" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D165" s="34" t="inlineStr">
+      <c r="D166" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="E165" s="14" t="inlineStr">
+      <c r="E166" s="14" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="F165" s="28" t="n">
-        <v>37.01</v>
-      </c>
-      <c r="G165" s="17" t="inlineStr">
+      <c r="F166" s="28" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="G166" s="17" t="inlineStr">
         <is>
           <t>100억 규모 유상증자를 통한 최대주주 변경 소식에 따른 기대감 반영
 (10-14) 110억원 규모 제3자배정 유상증자 및 최대주주 변경이라는 경영권 관련 대형 공시로 상한가 기록.</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="31" customHeight="1" s="15">
-      <c r="A166" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B166" s="31" t="inlineStr">
-        <is>
-          <t>듀켐바이오</t>
-        </is>
-      </c>
-      <c r="C166" s="31" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="D166" s="34" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="E166" s="14" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="F166" s="28" t="n">
-        <v>21.61</v>
-      </c>
-      <c r="G166" s="17" t="inlineStr">
-        <is>
-          <t>미국 일라이 릴리의 알츠하이머 치료제 국내 허가 기대감 부각</t>
-        </is>
-      </c>
-    </row>
     <row r="167" ht="31" customHeight="1" s="15">
       <c r="A167" s="31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B167" s="31" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>듀켐바이오</t>
         </is>
       </c>
       <c r="C167" s="31" t="inlineStr">
@@ -5703,7 +5759,7 @@
       </c>
       <c r="D167" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E167" s="14" t="inlineStr">
@@ -5712,11 +5768,11 @@
         </is>
       </c>
       <c r="F167" s="28" t="n">
-        <v>21.64</v>
+        <v>12.12</v>
       </c>
       <c r="G167" s="17" t="inlineStr">
         <is>
-          <t>대규모 AI 데이터센터 공동개발 사업 참여 소식에 따른 강력한 매수세 유입</t>
+          <t>미국 일라이 릴리의 알츠하이머 치료제 국내 허가 기대감 부각</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5784,7 @@
       </c>
       <c r="B168" s="31" t="inlineStr">
         <is>
-          <t>형지글로벌</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="C168" s="31" t="inlineStr">
@@ -5738,20 +5794,20 @@
       </c>
       <c r="D168" s="34" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>▼★★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F168" s="28" t="n">
-        <v>17.12</v>
+        <v>12.66</v>
       </c>
       <c r="G168" s="17" t="inlineStr">
         <is>
-          <t>주가 미달에 따른 상장폐지 우려 관련 안내 공시 및 주가 급락 발생</t>
+          <t>대규모 AI 데이터센터 공동개발 사업 참여 소식에 따른 강력한 매수세 유입</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5838,7 @@
         </is>
       </c>
       <c r="F169" s="28" t="n">
-        <v>45.84</v>
+        <v>38.81</v>
       </c>
       <c r="G169" s="17" t="inlineStr">
         <is>
@@ -5793,35 +5849,35 @@
     <row r="170" ht="31" customHeight="1" s="15">
       <c r="A170" s="31" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B170" s="17" t="inlineStr">
-        <is>
-          <t>휴니드테크놀러지스</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B170" s="31" t="inlineStr">
+        <is>
+          <t>파이온엑스</t>
         </is>
       </c>
       <c r="C170" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D170" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>▼★★★★★</t>
         </is>
       </c>
       <c r="F170" s="28" t="n">
-        <v>9.720000000000001</v>
+        <v>29.93</v>
       </c>
       <c r="G170" s="17" t="inlineStr">
         <is>
-          <t>미국 항공기 업체와 1,031억 원 규모의 대규모 공급계약을 체결했습니다.</t>
+          <t>파산 신청으로 인해 주권매매거래정지 기간이 변경되는 등 심각한 경영 위기가 확인되었습니다.</t>
         </is>
       </c>
     </row>
@@ -5833,17 +5889,17 @@
       </c>
       <c r="B171" s="31" t="inlineStr">
         <is>
-          <t>형지엘리트</t>
+          <t>플리토</t>
         </is>
       </c>
       <c r="C171" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D171" s="34" t="inlineStr">
         <is>
-          <t>섬유·의류</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E171" s="14" t="inlineStr">
@@ -5852,23 +5908,23 @@
         </is>
       </c>
       <c r="F171" s="28" t="n">
-        <v>40.88</v>
+        <v>24.97</v>
       </c>
       <c r="G171" s="17" t="inlineStr">
         <is>
-          <t>시가총액 미달 기업 상장폐지 절차 잠정 유예 소식에 투자심리가 급격히 개선되었습니다.</t>
+          <t>3분기 창사 이래 최대 실적 달성이라는 확정적 호재가 주가 급등을 이끌었습니다.</t>
         </is>
       </c>
     </row>
     <row r="172" ht="31" customHeight="1" s="15">
       <c r="A172" s="31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B172" s="31" t="inlineStr">
         <is>
-          <t>플리토</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C172" s="31" t="inlineStr">
@@ -5878,7 +5934,7 @@
       </c>
       <c r="D172" s="34" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr">
@@ -5887,23 +5943,23 @@
         </is>
       </c>
       <c r="F172" s="28" t="n">
-        <v>26.09</v>
+        <v>40.9</v>
       </c>
       <c r="G172" s="17" t="inlineStr">
         <is>
-          <t>3분기 창사 이래 최대 실적 달성이라는 확정적 호재가 주가 급등을 이끌었습니다.</t>
+          <t>중국 UBT와 장기지속형 주사제 플랫폼 평가 계약 체결이라는 구체적 성과 발생.</t>
         </is>
       </c>
     </row>
     <row r="173" ht="31" customHeight="1" s="15">
       <c r="A173" s="31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B173" s="31" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C173" s="31" t="inlineStr">
@@ -5913,7 +5969,7 @@
       </c>
       <c r="D173" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E173" s="14" t="inlineStr">
@@ -5922,58 +5978,58 @@
         </is>
       </c>
       <c r="F173" s="28" t="n">
-        <v>16.08</v>
+        <v>27.95</v>
       </c>
       <c r="G173" s="17" t="inlineStr">
         <is>
-          <t>중국 UBT와 장기지속형 주사제 플랫폼 평가 계약 체결이라는 구체적 성과 발생.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="31" customHeight="1" s="15">
+          <t>데이터센터용 슈퍼커패시터 1,200억 원 규모 대규모 공급계약 체결.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="15" customHeight="1" s="15">
       <c r="A174" s="31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B174" s="31" t="inlineStr">
         <is>
-          <t>서한</t>
+          <t>뉴인텍</t>
         </is>
       </c>
       <c r="C174" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D174" s="34" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>▼★★★★★</t>
         </is>
       </c>
       <c r="F174" s="28" t="n">
-        <v>15.3</v>
+        <v>39.85</v>
       </c>
       <c r="G174" s="17" t="inlineStr">
         <is>
-          <t>강남 대치동 데이터센터 신축공사 수주라는 대규모 계약 체결.</t>
+          <t>주권매매거래정지 공시로 인한 투자자 거래 제한.</t>
         </is>
       </c>
     </row>
     <row r="175" ht="31" customHeight="1" s="15">
       <c r="A175" s="31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B175" s="31" t="inlineStr">
-        <is>
-          <t>비나텍</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B175" s="17" t="inlineStr">
+        <is>
+          <t>아이패밀리에스씨</t>
         </is>
       </c>
       <c r="C175" s="31" t="inlineStr">
@@ -5983,7 +6039,7 @@
       </c>
       <c r="D175" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E175" s="14" t="inlineStr">
@@ -5992,33 +6048,33 @@
         </is>
       </c>
       <c r="F175" s="28" t="n">
-        <v>16.36</v>
+        <v>34.07</v>
       </c>
       <c r="G175" s="17" t="inlineStr">
         <is>
-          <t>데이터센터용 슈퍼커패시터 1,200억 원 규모 대규모 공급계약 체결.</t>
+          <t>일본 종합상사 마루베니의 지분 공개매수 추진 소식.</t>
         </is>
       </c>
     </row>
     <row r="176" ht="31" customHeight="1" s="15">
       <c r="A176" s="31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B176" s="31" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>퓨쳐켐</t>
         </is>
       </c>
       <c r="C176" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D176" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="E176" s="14" t="inlineStr">
@@ -6027,11 +6083,11 @@
         </is>
       </c>
       <c r="F176" s="28" t="n">
-        <v>15.03</v>
+        <v>29.91</v>
       </c>
       <c r="G176" s="17" t="inlineStr">
         <is>
-          <t>3분기 영업이익 5,006억 원 어닝 서프라이즈 및 대규모 자사주 소각 결정.</t>
+          <t>전립선암 치료제 미국 제2a상 임상시험 Topline data 수령.</t>
         </is>
       </c>
     </row>
@@ -6060,146 +6116,153 @@
     <row r="179" ht="15" customHeight="1" s="15">
       <c r="A179" s="17" t="inlineStr">
         <is>
-          <t>- 미국 물가 지표 안정화에 따른 기술주 반등</t>
+          <t>- 주요 기업들의 실적 서프라이즈 발표</t>
         </is>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1" s="15">
       <c r="A180" s="17" t="inlineStr">
         <is>
-          <t>- 주요 대형주 실적 발표 서프라이즈</t>
+          <t>- 미국 인플레이션 우려 완화 및 금리 경로 안정화</t>
         </is>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" s="15">
       <c r="A181" s="17" t="inlineStr">
         <is>
-          <t>- 고금리 장기화 우려 지속</t>
+          <t>- 외국인의 반도체 섹터 매도세 지속</t>
         </is>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1" s="15">
       <c r="A182" s="17" t="inlineStr">
         <is>
-          <t>- 외국인 매도세 지속에 따른 수급 공백</t>
+          <t>- 미국 연준의 매파적 통화정책 시그널</t>
         </is>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1" s="15">
       <c r="A183" s="17" t="inlineStr">
         <is>
-          <t>- 외국인의 반도체 대형주 순매수 전환 여부를 확인해야 합니다.</t>
+          <t>- 외국인의 코스피 전기·전자 섹터 순매수 전환 여부를 확인해야 함.</t>
         </is>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1" s="15">
       <c r="A184" s="17" t="inlineStr">
         <is>
-          <t>- 2026-10-29 03:00 미국 중앙은행 기준금리 결정</t>
+          <t>- 10-29 03:00 미국 중앙은행 기준금리 결정</t>
         </is>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" s="15">
       <c r="A185" s="17" t="inlineStr">
         <is>
-          <t>- 2026-10-27~30 주요 기업 실적 발표(삼성전자, SK하이닉스 등)</t>
+          <t>- 10-30 08:00 한국 광공업생산 발표</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="15" customHeight="1" s="15">
+      <c r="A186" s="17" t="inlineStr">
+        <is>
+          <t>- 10-29~30 삼성SDS, 현대건설 등 주요 기업 실적 발표</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="93">
     <mergeCell ref="G158:K158"/>
-    <mergeCell ref="G59:K59"/>
+    <mergeCell ref="A186:K186"/>
+    <mergeCell ref="G117:K117"/>
     <mergeCell ref="G169:K169"/>
     <mergeCell ref="G151:K151"/>
     <mergeCell ref="G67:K67"/>
-    <mergeCell ref="B133:K133"/>
     <mergeCell ref="G61:K61"/>
-    <mergeCell ref="G126:K126"/>
     <mergeCell ref="G70:K70"/>
-    <mergeCell ref="G116:K116"/>
-    <mergeCell ref="G112:K112"/>
+    <mergeCell ref="G125:K125"/>
     <mergeCell ref="G62:K62"/>
-    <mergeCell ref="G118:K118"/>
+    <mergeCell ref="B134:K134"/>
+    <mergeCell ref="G127:K127"/>
     <mergeCell ref="G167:K167"/>
+    <mergeCell ref="A113:E113"/>
     <mergeCell ref="G65:K65"/>
     <mergeCell ref="G73:K73"/>
     <mergeCell ref="A135:K135"/>
     <mergeCell ref="G153:K153"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="G129:K129"/>
     <mergeCell ref="G63:K63"/>
+    <mergeCell ref="A115:E115"/>
     <mergeCell ref="G173:K173"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="G60:K60"/>
+    <mergeCell ref="G115:K115"/>
     <mergeCell ref="G155:K155"/>
     <mergeCell ref="A142:K142"/>
     <mergeCell ref="A182:K182"/>
     <mergeCell ref="A119:E119"/>
     <mergeCell ref="G170:K170"/>
     <mergeCell ref="A79:K79"/>
-    <mergeCell ref="B76:K76"/>
     <mergeCell ref="G157:K157"/>
-    <mergeCell ref="G122:K122"/>
     <mergeCell ref="G166:K166"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="G172:K172"/>
-    <mergeCell ref="A118:E118"/>
     <mergeCell ref="A137:K137"/>
     <mergeCell ref="G69:K69"/>
+    <mergeCell ref="A120:E120"/>
     <mergeCell ref="A136:K136"/>
     <mergeCell ref="A145:K145"/>
     <mergeCell ref="G152:K152"/>
     <mergeCell ref="A139:K139"/>
     <mergeCell ref="A179:K179"/>
     <mergeCell ref="A181:K181"/>
-    <mergeCell ref="A106:E106"/>
     <mergeCell ref="G64:K64"/>
     <mergeCell ref="A184:K184"/>
+    <mergeCell ref="A131:K131"/>
     <mergeCell ref="A180:K180"/>
+    <mergeCell ref="G119:K119"/>
     <mergeCell ref="G159:K159"/>
     <mergeCell ref="G164:K164"/>
-    <mergeCell ref="G106:K106"/>
     <mergeCell ref="A143:K143"/>
     <mergeCell ref="G161:K161"/>
     <mergeCell ref="A1:G2"/>
-    <mergeCell ref="G120:K120"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A78:K78"/>
+    <mergeCell ref="G107:K107"/>
     <mergeCell ref="G174:K174"/>
     <mergeCell ref="G156:K156"/>
-    <mergeCell ref="A108:E108"/>
     <mergeCell ref="G66:K66"/>
     <mergeCell ref="A80:K80"/>
+    <mergeCell ref="G74:K74"/>
     <mergeCell ref="G68:K68"/>
-    <mergeCell ref="G108:K108"/>
-    <mergeCell ref="G124:K124"/>
     <mergeCell ref="A185:K185"/>
-    <mergeCell ref="G110:K110"/>
     <mergeCell ref="G168:K168"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="G109:K109"/>
     <mergeCell ref="G150:K150"/>
-    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="B78:K78"/>
+    <mergeCell ref="G111:K111"/>
     <mergeCell ref="G72:K72"/>
-    <mergeCell ref="A130:K130"/>
-    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="A107:E107"/>
     <mergeCell ref="G71:K71"/>
     <mergeCell ref="A138:K138"/>
     <mergeCell ref="G176:K176"/>
     <mergeCell ref="G160:K160"/>
     <mergeCell ref="G175:K175"/>
     <mergeCell ref="A183:K183"/>
-    <mergeCell ref="G128:K128"/>
     <mergeCell ref="G162:K162"/>
     <mergeCell ref="G171:K171"/>
+    <mergeCell ref="G121:K121"/>
     <mergeCell ref="G148:K148"/>
-    <mergeCell ref="A116:E116"/>
-    <mergeCell ref="G114:K114"/>
+    <mergeCell ref="G123:K123"/>
     <mergeCell ref="G154:K154"/>
     <mergeCell ref="G163:K163"/>
     <mergeCell ref="A144:K144"/>
-    <mergeCell ref="A134:K134"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="G113:K113"/>
+    <mergeCell ref="A81:K81"/>
     <mergeCell ref="G165:K165"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="G75:K75"/>
     <mergeCell ref="G149:K149"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6242,7 +6305,7 @@
       </c>
       <c r="K1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-01 ~ 2026-10-22</t>
+          <t>2026-10-01 ~ 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -6401,28 +6464,28 @@
         </is>
       </c>
       <c r="D7" s="44" t="n">
-        <v>165</v>
+        <v>39</v>
       </c>
       <c r="E7" s="43" t="n">
-        <v>-564</v>
+        <v>-604</v>
       </c>
       <c r="F7" s="44" t="n">
-        <v>729</v>
+        <v>643</v>
       </c>
       <c r="G7" s="43" t="n">
-        <v>-570</v>
+        <v>-540</v>
       </c>
       <c r="H7" s="46" t="n">
-        <v>413.3</v>
+        <v>474.8</v>
       </c>
       <c r="I7" s="46" t="n">
-        <v>2812.4</v>
+        <v>2770.1</v>
       </c>
       <c r="J7" s="50" t="n">
-        <v>94.7</v>
+        <v>52.4</v>
       </c>
       <c r="K7" s="51" t="n">
-        <v>9.699999999999999</v>
+        <v>7.26</v>
       </c>
       <c r="L7" s="52" t="n">
         <v>-1.34</v>
@@ -6445,28 +6508,28 @@
         </is>
       </c>
       <c r="D8" s="44" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E8" s="43" t="n">
-        <v>-15</v>
+        <v>-27</v>
       </c>
       <c r="F8" s="44" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G8" s="43" t="n">
-        <v>-38</v>
+        <v>-29</v>
       </c>
       <c r="H8" s="46" t="n">
-        <v>20.2</v>
+        <v>21.2</v>
       </c>
       <c r="I8" s="46" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="J8" s="53" t="n">
-        <v>-5.4</v>
+        <v>72.8</v>
+      </c>
+      <c r="J8" s="50" t="n">
+        <v>6.6</v>
       </c>
       <c r="K8" s="51" t="n">
-        <v>17.44</v>
+        <v>10.11</v>
       </c>
       <c r="L8" s="49" t="n">
         <v>-7.18</v>
@@ -6489,28 +6552,28 @@
         </is>
       </c>
       <c r="D9" s="44" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E9" s="43" t="n">
-        <v>-97</v>
+        <v>-133</v>
       </c>
       <c r="F9" s="44" t="n">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-86</v>
+        <v>-70</v>
       </c>
       <c r="H9" s="46" t="n">
-        <v>130.1</v>
+        <v>136.5</v>
       </c>
       <c r="I9" s="46" t="n">
-        <v>151.5</v>
+        <v>150.4</v>
       </c>
       <c r="J9" s="53" t="n">
-        <v>-6.6</v>
+        <v>-7.7</v>
       </c>
       <c r="K9" s="51" t="n">
-        <v>4.65</v>
+        <v>5.58</v>
       </c>
       <c r="L9" s="49" t="n">
         <v>-9.43</v>
@@ -6533,28 +6596,28 @@
         </is>
       </c>
       <c r="D10" s="44" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E10" s="43" t="n">
-        <v>-139</v>
+        <v>-156</v>
       </c>
       <c r="F10" s="44" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-69</v>
+        <v>-71</v>
       </c>
       <c r="H10" s="46" t="n">
-        <v>318.6</v>
+        <v>342.8</v>
       </c>
       <c r="I10" s="46" t="n">
-        <v>1378.8</v>
+        <v>1406.5</v>
       </c>
       <c r="J10" s="50" t="n">
-        <v>555.5</v>
+        <v>583.2</v>
       </c>
       <c r="K10" s="51" t="n">
-        <v>6.02</v>
+        <v>6.43</v>
       </c>
       <c r="L10" s="49" t="n">
         <v>-5.17</v>
@@ -6577,28 +6640,28 @@
         </is>
       </c>
       <c r="D11" s="44" t="n">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="E11" s="44" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-207</v>
+        <v>-171</v>
       </c>
       <c r="H11" s="46" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="I11" s="46" t="n">
-        <v>523.9</v>
+        <v>539.4</v>
       </c>
       <c r="J11" s="50" t="n">
-        <v>136.2</v>
+        <v>151.7</v>
       </c>
       <c r="K11" s="51" t="n">
-        <v>16.71</v>
+        <v>4.55</v>
       </c>
       <c r="L11" s="49" t="n">
         <v>-6.52</v>
@@ -6621,28 +6684,28 @@
         </is>
       </c>
       <c r="D12" s="44" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>-115</v>
+        <v>-239</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>242</v>
+        <v>367</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-126</v>
+        <v>-127</v>
       </c>
       <c r="H12" s="46" t="n">
-        <v>99.5</v>
+        <v>110.2</v>
       </c>
       <c r="I12" s="46" t="n">
-        <v>2775.9</v>
+        <v>2941.5</v>
       </c>
       <c r="J12" s="50" t="n">
-        <v>1563</v>
+        <v>1728.6</v>
       </c>
       <c r="K12" s="51" t="n">
-        <v>16.93</v>
+        <v>16.08</v>
       </c>
       <c r="L12" s="49" t="n">
         <v>-6.63</v>
@@ -6665,28 +6728,28 @@
         </is>
       </c>
       <c r="D13" s="44" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E13" s="43" t="n">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="F13" s="44" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G13" s="43" t="n">
-        <v>-102</v>
+        <v>-99</v>
       </c>
       <c r="H13" s="46" t="n">
-        <v>17.3</v>
+        <v>20.4</v>
       </c>
       <c r="I13" s="46" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="J13" s="50" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="K13" s="51" t="n">
-        <v>15.29</v>
+        <v>11.38</v>
       </c>
       <c r="L13" s="54" t="n">
         <v>-4.8</v>
@@ -6709,28 +6772,28 @@
         </is>
       </c>
       <c r="D14" s="44" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E14" s="43" t="n">
-        <v>-76</v>
+        <v>-71</v>
       </c>
       <c r="F14" s="44" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G14" s="43" t="n">
-        <v>-17</v>
+        <v>-30</v>
       </c>
       <c r="H14" s="46" t="n">
-        <v>77.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="I14" s="46" t="n">
-        <v>384.1</v>
+        <v>390.1</v>
       </c>
       <c r="J14" s="50" t="n">
-        <v>74.5</v>
+        <v>80.5</v>
       </c>
       <c r="K14" s="51" t="n">
-        <v>10.95</v>
+        <v>11.27</v>
       </c>
       <c r="L14" s="49" t="n">
         <v>-6.09</v>
@@ -6753,28 +6816,28 @@
         </is>
       </c>
       <c r="D15" s="44" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E15" s="44" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F15" s="44" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="G15" s="43" t="n">
-        <v>-137</v>
+        <v>-140</v>
       </c>
       <c r="H15" s="46" t="n">
-        <v>63.3</v>
+        <v>67.3</v>
       </c>
       <c r="I15" s="46" t="n">
-        <v>606</v>
+        <v>605.9</v>
       </c>
       <c r="J15" s="53" t="n">
-        <v>-22.8</v>
-      </c>
-      <c r="K15" s="55" t="n">
-        <v>-1</v>
+        <v>-22.9</v>
+      </c>
+      <c r="K15" s="51" t="n">
+        <v>0.4</v>
       </c>
       <c r="L15" s="49" t="n">
         <v>-6.52</v>
@@ -6800,25 +6863,25 @@
         <v>0</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>-62</v>
+        <v>-65</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="H16" s="46" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="I16" s="46" t="n">
-        <v>829.1</v>
+        <v>847.7</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>20.3</v>
+        <v>38.9</v>
       </c>
       <c r="K16" s="55" t="n">
-        <v>-2.26</v>
+        <v>-3.63</v>
       </c>
       <c r="L16" s="49" t="n">
         <v>-8.83</v>
@@ -6844,25 +6907,25 @@
         <v>21</v>
       </c>
       <c r="E17" s="43" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="F17" s="44" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" s="43" t="n">
         <v>-21</v>
       </c>
       <c r="H17" s="46" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I17" s="46" t="n">
-        <v>211.2</v>
+        <v>213.8</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="K17" s="51" t="n">
-        <v>6.5</v>
+        <v>5.62</v>
       </c>
       <c r="L17" s="49" t="n">
         <v>-7.81</v>
@@ -6885,28 +6948,28 @@
         </is>
       </c>
       <c r="D18" s="43" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="E18" s="43" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="F18" s="43" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G18" s="43" t="n">
-        <v>-47</v>
+        <v>-50</v>
       </c>
       <c r="H18" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I18" s="46" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K18" s="51" t="n">
-        <v>8.609999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L18" s="49" t="n">
         <v>-7.05</v>
@@ -6975,7 +7038,7 @@
       </c>
       <c r="O1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-01 ~ 2026-10-22</t>
+          <t>2026-10-01 ~ 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10694,7 @@
       </c>
       <c r="Q1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-01 ~ 2026-10-22</t>
+          <t>2026-10-01 ~ 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -10755,10 +10818,10 @@
         </is>
       </c>
       <c r="D5" s="62" t="n">
-        <v>30475</v>
+        <v>32412</v>
       </c>
       <c r="E5" s="63" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="G5" s="30" t="n">
         <v>1</v>
@@ -10774,10 +10837,10 @@
         </is>
       </c>
       <c r="J5" s="43" t="n">
-        <v>9054.9</v>
+        <v>6776.7</v>
       </c>
       <c r="K5" s="64" t="n">
-        <v>42022.8</v>
+        <v>39744.6</v>
       </c>
       <c r="L5" s="63" t="n">
         <v>4.36</v>
@@ -10796,13 +10859,13 @@
         </is>
       </c>
       <c r="Q5" s="59" t="n">
-        <v>-71212</v>
+        <v>-80811.7</v>
       </c>
       <c r="R5" s="64" t="n">
-        <v>154505.1</v>
+        <v>144905.4</v>
       </c>
       <c r="S5" s="63" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="6">
@@ -10820,10 +10883,10 @@
         </is>
       </c>
       <c r="D6" s="62" t="n">
-        <v>20167</v>
+        <v>20542</v>
       </c>
       <c r="E6" s="63" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G6" s="30" t="n">
         <v>2</v>
@@ -10839,13 +10902,13 @@
         </is>
       </c>
       <c r="J6" s="43" t="n">
-        <v>3111.6</v>
+        <v>2595.2</v>
       </c>
       <c r="K6" s="64" t="n">
-        <v>6885.6</v>
+        <v>6369.2</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="N6" s="30" t="n">
         <v>2</v>
@@ -10861,13 +10924,13 @@
         </is>
       </c>
       <c r="Q6" s="59" t="n">
-        <v>-14586.9</v>
+        <v>-24621.4</v>
       </c>
       <c r="R6" s="64" t="n">
-        <v>185130.7</v>
+        <v>175096.2</v>
       </c>
       <c r="S6" s="63" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
@@ -10885,10 +10948,10 @@
         </is>
       </c>
       <c r="D7" s="62" t="n">
-        <v>6946</v>
+        <v>7315</v>
       </c>
       <c r="E7" s="63" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="G7" s="30" t="n">
         <v>3</v>
@@ -10904,13 +10967,13 @@
         </is>
       </c>
       <c r="J7" s="43" t="n">
-        <v>2905.2</v>
+        <v>2096.1</v>
       </c>
       <c r="K7" s="64" t="n">
-        <v>16513.2</v>
+        <v>15704.1</v>
       </c>
       <c r="L7" s="63" t="n">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="N7" s="30" t="n">
         <v>3</v>
@@ -10926,13 +10989,13 @@
         </is>
       </c>
       <c r="Q7" s="59" t="n">
-        <v>-9746.4</v>
+        <v>-11658.6</v>
       </c>
       <c r="R7" s="64" t="n">
-        <v>39837</v>
+        <v>37924.8</v>
       </c>
       <c r="S7" s="63" t="n">
-        <v>20.59</v>
+        <v>20.81</v>
       </c>
     </row>
     <row r="8">
@@ -10950,10 +11013,10 @@
         </is>
       </c>
       <c r="D8" s="62" t="n">
-        <v>5449</v>
+        <v>5789</v>
       </c>
       <c r="E8" s="63" t="n">
-        <v>2.82</v>
+        <v>3.18</v>
       </c>
       <c r="G8" s="30" t="n">
         <v>4</v>
@@ -10969,13 +11032,13 @@
         </is>
       </c>
       <c r="J8" s="43" t="n">
-        <v>1563</v>
+        <v>1728.6</v>
       </c>
       <c r="K8" s="64" t="n">
-        <v>2775.9</v>
+        <v>2941.5</v>
       </c>
       <c r="L8" s="63" t="n">
-        <v>7.52</v>
+        <v>8.01</v>
       </c>
       <c r="N8" s="30" t="n">
         <v>4</v>
@@ -10991,13 +11054,13 @@
         </is>
       </c>
       <c r="Q8" s="59" t="n">
-        <v>-9609.5</v>
+        <v>-10614.1</v>
       </c>
       <c r="R8" s="64" t="n">
-        <v>21826.9</v>
+        <v>20822.3</v>
       </c>
       <c r="S8" s="63" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9" ht="31" customHeight="1" s="15">
@@ -11015,32 +11078,32 @@
         </is>
       </c>
       <c r="D9" s="62" t="n">
-        <v>5178</v>
+        <v>5571</v>
       </c>
       <c r="E9" s="63" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G9" s="30" t="n">
         <v>5</v>
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="I9" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>오락·문화</t>
         </is>
       </c>
       <c r="J9" s="43" t="n">
-        <v>1548.6</v>
+        <v>1267.4</v>
       </c>
       <c r="K9" s="64" t="n">
-        <v>15566.7</v>
+        <v>4810.3</v>
       </c>
       <c r="L9" s="63" t="n">
-        <v>9.68</v>
+        <v>6.3</v>
       </c>
       <c r="N9" s="30" t="n">
         <v>5</v>
@@ -11056,13 +11119,13 @@
         </is>
       </c>
       <c r="Q9" s="59" t="n">
-        <v>-9282.5</v>
+        <v>-10085.5</v>
       </c>
       <c r="R9" s="64" t="n">
-        <v>18653.2</v>
+        <v>17850.2</v>
       </c>
       <c r="S9" s="63" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
@@ -11080,17 +11143,17 @@
         </is>
       </c>
       <c r="D10" s="62" t="n">
-        <v>4808</v>
+        <v>5135</v>
       </c>
       <c r="E10" s="63" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="G10" s="30" t="n">
         <v>6</v>
       </c>
       <c r="H10" s="31" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="I10" s="34" t="inlineStr">
@@ -11099,13 +11162,13 @@
         </is>
       </c>
       <c r="J10" s="43" t="n">
-        <v>1456.6</v>
+        <v>1158.2</v>
       </c>
       <c r="K10" s="64" t="n">
-        <v>10739.5</v>
+        <v>3528</v>
       </c>
       <c r="L10" s="63" t="n">
-        <v>1.64</v>
+        <v>7.5</v>
       </c>
       <c r="N10" s="30" t="n">
         <v>6</v>
@@ -11121,13 +11184,13 @@
         </is>
       </c>
       <c r="Q10" s="59" t="n">
-        <v>-7714.3</v>
+        <v>-8214.700000000001</v>
       </c>
       <c r="R10" s="64" t="n">
-        <v>28767.9</v>
+        <v>28267.5</v>
       </c>
       <c r="S10" s="63" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="11">
@@ -11145,32 +11208,32 @@
         </is>
       </c>
       <c r="D11" s="62" t="n">
-        <v>4282</v>
+        <v>4770</v>
       </c>
       <c r="E11" s="63" t="n">
-        <v>4.49</v>
+        <v>5.5</v>
       </c>
       <c r="G11" s="30" t="n">
         <v>7</v>
       </c>
       <c r="H11" s="31" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="I11" s="34" t="inlineStr">
         <is>
-          <t>오락·문화</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="J11" s="43" t="n">
-        <v>1404</v>
+        <v>1087.2</v>
       </c>
       <c r="K11" s="64" t="n">
-        <v>4946.9</v>
+        <v>10370.1</v>
       </c>
       <c r="L11" s="63" t="n">
-        <v>6.27</v>
+        <v>1.65</v>
       </c>
       <c r="N11" s="30" t="n">
         <v>7</v>
@@ -11182,13 +11245,13 @@
       </c>
       <c r="P11" s="34" t="inlineStr"/>
       <c r="Q11" s="59" t="n">
-        <v>-4371.8</v>
+        <v>-5037.5</v>
       </c>
       <c r="R11" s="64" t="n">
-        <v>25097.5</v>
+        <v>24431.8</v>
       </c>
       <c r="S11" s="63" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="12">
@@ -11206,10 +11269,10 @@
         </is>
       </c>
       <c r="D12" s="62" t="n">
-        <v>3820</v>
+        <v>4395</v>
       </c>
       <c r="E12" s="63" t="n">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="G12" s="30" t="n">
         <v>8</v>
@@ -11225,13 +11288,13 @@
         </is>
       </c>
       <c r="J12" s="43" t="n">
-        <v>1318.8</v>
+        <v>1086.7</v>
       </c>
       <c r="K12" s="64" t="n">
-        <v>9378</v>
+        <v>9145.9</v>
       </c>
       <c r="L12" s="63" t="n">
-        <v>14.71</v>
+        <v>14.79</v>
       </c>
       <c r="N12" s="30" t="n">
         <v>8</v>
@@ -11247,13 +11310,13 @@
         </is>
       </c>
       <c r="Q12" s="59" t="n">
-        <v>-3799.2</v>
+        <v>-4335.7</v>
       </c>
       <c r="R12" s="64" t="n">
-        <v>16620.5</v>
+        <v>16084</v>
       </c>
       <c r="S12" s="63" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="13" ht="31" customHeight="1" s="15">
@@ -11271,39 +11334,39 @@
         </is>
       </c>
       <c r="D13" s="62" t="n">
-        <v>3774</v>
+        <v>4280</v>
       </c>
       <c r="E13" s="63" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="G13" s="30" t="n">
         <v>9</v>
       </c>
       <c r="H13" s="31" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="I13" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="J13" s="43" t="n">
-        <v>1258.5</v>
+        <v>864.3</v>
       </c>
       <c r="K13" s="64" t="n">
-        <v>3628.3</v>
+        <v>14882.4</v>
       </c>
       <c r="L13" s="63" t="n">
-        <v>7.28</v>
+        <v>10.03</v>
       </c>
       <c r="N13" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="O13" s="17" t="inlineStr">
-        <is>
-          <t>한화에어로스페이스</t>
+      <c r="O13" s="31" t="inlineStr">
+        <is>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="P13" s="60" t="inlineStr">
@@ -11312,16 +11375,16 @@
         </is>
       </c>
       <c r="Q13" s="59" t="n">
-        <v>-3271.2</v>
+        <v>-3360.8</v>
       </c>
       <c r="R13" s="64" t="n">
-        <v>9770.4</v>
+        <v>11247.5</v>
       </c>
       <c r="S13" s="63" t="n">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="14" ht="31" customHeight="1" s="15">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="30" t="n">
         <v>10</v>
       </c>
@@ -11332,54 +11395,54 @@
       </c>
       <c r="C14" s="34" t="inlineStr"/>
       <c r="D14" s="62" t="n">
-        <v>3403</v>
+        <v>3611</v>
       </c>
       <c r="E14" s="63" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="G14" s="30" t="n">
         <v>10</v>
       </c>
       <c r="H14" s="31" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="I14" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="J14" s="43" t="n">
-        <v>885.7</v>
+        <v>787.5</v>
       </c>
       <c r="K14" s="64" t="n">
-        <v>13600.9</v>
+        <v>8555.5</v>
       </c>
       <c r="L14" s="63" t="n">
-        <v>2.97</v>
+        <v>6.13</v>
       </c>
       <c r="N14" s="30" t="n">
         <v>10</v>
       </c>
       <c r="O14" s="31" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
-        </is>
-      </c>
-      <c r="P14" s="60" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>LG이노텍</t>
+        </is>
+      </c>
+      <c r="P14" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="Q14" s="59" t="n">
-        <v>-2993</v>
+        <v>-3098.8</v>
       </c>
       <c r="R14" s="64" t="n">
-        <v>11615.3</v>
+        <v>4513.1</v>
       </c>
       <c r="S14" s="63" t="n">
-        <v>10.9</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="15"/>
@@ -11442,7 +11505,7 @@
       </c>
       <c r="L1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-01 ~ 2026-10-22</t>
+          <t>2026-10-01 ~ 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -11560,43 +11623,43 @@
         </is>
       </c>
       <c r="B5" s="65" t="n">
-        <v>-41.86</v>
+        <v>-42.22</v>
       </c>
       <c r="C5" s="65" t="n">
-        <v>-25.93</v>
+        <v>-25.61</v>
       </c>
       <c r="D5" s="65" t="n">
-        <v>-6.21</v>
+        <v>-10.93</v>
       </c>
       <c r="E5" s="66" t="n">
-        <v>6.87</v>
+        <v>6.21</v>
       </c>
       <c r="F5" s="67" t="n">
-        <v>19</v>
-      </c>
-      <c r="G5" s="67" t="n">
-        <v>1432</v>
-      </c>
-      <c r="H5" s="67" t="n">
-        <v>1451</v>
-      </c>
-      <c r="I5" s="68" t="n">
+        <v>-36</v>
+      </c>
+      <c r="G5" s="68" t="n">
+        <v>1534</v>
+      </c>
+      <c r="H5" s="68" t="n">
+        <v>1498</v>
+      </c>
+      <c r="I5" s="67" t="n">
         <v>-6</v>
       </c>
-      <c r="J5" s="67" t="n">
-        <v>790</v>
-      </c>
-      <c r="K5" s="67" t="n">
-        <v>568</v>
-      </c>
-      <c r="L5" s="67" t="n">
-        <v>76</v>
-      </c>
-      <c r="M5" s="68" t="n">
-        <v>-1486</v>
-      </c>
-      <c r="N5" s="67" t="n">
-        <v>35</v>
+      <c r="J5" s="68" t="n">
+        <v>796</v>
+      </c>
+      <c r="K5" s="68" t="n">
+        <v>653</v>
+      </c>
+      <c r="L5" s="68" t="n">
+        <v>87</v>
+      </c>
+      <c r="M5" s="67" t="n">
+        <v>-1531</v>
+      </c>
+      <c r="N5" s="68" t="n">
+        <v>32</v>
       </c>
       <c r="O5" s="69" t="inlineStr">
         <is>
@@ -11607,192 +11670,196 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
-        </is>
-      </c>
-      <c r="B6" s="66" t="n">
-        <v>7.62</v>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="n">
+        <v>-11.38</v>
       </c>
       <c r="C6" s="65" t="n">
-        <v>-3.69</v>
+        <v>-6.86</v>
       </c>
       <c r="D6" s="66" t="n">
-        <v>5.6</v>
+        <v>7.16</v>
       </c>
       <c r="E6" s="66" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="F6" s="68" t="n">
-        <v>-940</v>
-      </c>
-      <c r="G6" s="67" t="n">
-        <v>2579</v>
-      </c>
-      <c r="H6" s="67" t="n">
-        <v>1639</v>
+        <v>4.73</v>
+      </c>
+      <c r="F6" s="67" t="n">
+        <v>-2081</v>
+      </c>
+      <c r="G6" s="68" t="n">
+        <v>6140</v>
+      </c>
+      <c r="H6" s="68" t="n">
+        <v>4059</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>188</v>
-      </c>
-      <c r="J6" s="67" t="n">
-        <v>1107</v>
-      </c>
-      <c r="K6" s="67" t="n">
-        <v>1116</v>
-      </c>
-      <c r="L6" s="67" t="n">
-        <v>173</v>
-      </c>
-      <c r="M6" s="68" t="n">
-        <v>-2036</v>
-      </c>
-      <c r="N6" s="67" t="n">
-        <v>397</v>
-      </c>
-      <c r="O6" s="57" t="inlineStr">
-        <is>
-          <t>동반강세</t>
-        </is>
-      </c>
+        <v>-441</v>
+      </c>
+      <c r="J6" s="68" t="n">
+        <v>2082</v>
+      </c>
+      <c r="K6" s="68" t="n">
+        <v>4011</v>
+      </c>
+      <c r="L6" s="68" t="n">
+        <v>490</v>
+      </c>
+      <c r="M6" s="67" t="n">
+        <v>-4926</v>
+      </c>
+      <c r="N6" s="68" t="n">
+        <v>868</v>
+      </c>
+      <c r="O6" s="30" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B7" s="65" t="n">
-        <v>-14.35</v>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="B7" s="66" t="n">
+        <v>6.32</v>
       </c>
       <c r="C7" s="65" t="n">
-        <v>-10.97</v>
+        <v>-5.16</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>4.93</v>
+        <v>2.41</v>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="F7" s="68" t="n">
-        <v>-1917</v>
-      </c>
-      <c r="G7" s="67" t="n">
-        <v>5305</v>
-      </c>
-      <c r="H7" s="67" t="n">
-        <v>3388</v>
+        <v>2.81</v>
+      </c>
+      <c r="F7" s="67" t="n">
+        <v>-1206</v>
+      </c>
+      <c r="G7" s="68" t="n">
+        <v>2741</v>
+      </c>
+      <c r="H7" s="68" t="n">
+        <v>1535</v>
       </c>
       <c r="I7" s="68" t="n">
-        <v>-248</v>
-      </c>
-      <c r="J7" s="67" t="n">
-        <v>1767</v>
-      </c>
-      <c r="K7" s="67" t="n">
-        <v>3371</v>
-      </c>
-      <c r="L7" s="67" t="n">
-        <v>419</v>
-      </c>
-      <c r="M7" s="68" t="n">
-        <v>-4270</v>
-      </c>
-      <c r="N7" s="67" t="n">
-        <v>882</v>
-      </c>
-      <c r="O7" s="30" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="J7" s="68" t="n">
+        <v>1246</v>
+      </c>
+      <c r="K7" s="68" t="n">
+        <v>1160</v>
+      </c>
+      <c r="L7" s="68" t="n">
+        <v>193</v>
+      </c>
+      <c r="M7" s="67" t="n">
+        <v>-2028</v>
+      </c>
+      <c r="N7" s="68" t="n">
+        <v>493</v>
+      </c>
+      <c r="O7" s="57" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>의료·정밀기기</t>
         </is>
       </c>
       <c r="B8" s="66" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="C8" s="65" t="n">
-        <v>-13.11</v>
+        <v>29.04</v>
+      </c>
+      <c r="C8" s="66" t="n">
+        <v>5.27</v>
       </c>
       <c r="D8" s="66" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="E8" s="65" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="F8" s="67" t="n">
-        <v>1365</v>
-      </c>
-      <c r="G8" s="67" t="n">
-        <v>1844</v>
-      </c>
-      <c r="H8" s="67" t="n">
-        <v>3210</v>
-      </c>
-      <c r="I8" s="67" t="n">
-        <v>741</v>
-      </c>
-      <c r="J8" s="67" t="n">
-        <v>520</v>
+        <v>16.51</v>
+      </c>
+      <c r="E8" s="66" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F8" s="68" t="n">
+        <v>465</v>
+      </c>
+      <c r="G8" s="68" t="n">
+        <v>264</v>
+      </c>
+      <c r="H8" s="68" t="n">
+        <v>729</v>
+      </c>
+      <c r="I8" s="68" t="n">
+        <v>119</v>
+      </c>
+      <c r="J8" s="68" t="n">
+        <v>201</v>
       </c>
       <c r="K8" s="67" t="n">
-        <v>553</v>
+        <v>-40</v>
       </c>
       <c r="L8" s="67" t="n">
-        <v>33</v>
-      </c>
-      <c r="M8" s="68" t="n">
-        <v>-3335</v>
+        <v>-15</v>
+      </c>
+      <c r="M8" s="67" t="n">
+        <v>-705</v>
       </c>
       <c r="N8" s="67" t="n">
-        <v>125</v>
-      </c>
-      <c r="O8" s="30" t="inlineStr"/>
+        <v>-23</v>
+      </c>
+      <c r="O8" s="57" t="inlineStr">
+        <is>
+          <t>동반강세</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>의료·정밀기기</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="B9" s="66" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="C9" s="66" t="n">
-        <v>3.03</v>
+        <v>5.38</v>
+      </c>
+      <c r="C9" s="65" t="n">
+        <v>-12.06</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="E9" s="65" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="F9" s="67" t="n">
-        <v>535</v>
-      </c>
-      <c r="G9" s="67" t="n">
-        <v>203</v>
-      </c>
-      <c r="H9" s="67" t="n">
-        <v>738</v>
-      </c>
-      <c r="I9" s="67" t="n">
-        <v>106</v>
-      </c>
-      <c r="J9" s="67" t="n">
-        <v>153</v>
+        <v>6.73</v>
+      </c>
+      <c r="E9" s="66" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F9" s="68" t="n">
+        <v>2932</v>
+      </c>
+      <c r="G9" s="68" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H9" s="68" t="n">
+        <v>4952</v>
+      </c>
+      <c r="I9" s="68" t="n">
+        <v>953</v>
+      </c>
+      <c r="J9" s="68" t="n">
+        <v>539</v>
       </c>
       <c r="K9" s="68" t="n">
-        <v>-33</v>
+        <v>496</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>-22</v>
-      </c>
-      <c r="M9" s="68" t="n">
-        <v>-713</v>
+        <v>38</v>
+      </c>
+      <c r="M9" s="67" t="n">
+        <v>-5206</v>
       </c>
       <c r="N9" s="68" t="n">
-        <v>-24</v>
+        <v>254</v>
       </c>
       <c r="O9" s="57" t="inlineStr">
         <is>
@@ -11803,47 +11870,47 @@
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>비금속</t>
+          <t>부동산</t>
         </is>
       </c>
       <c r="B10" s="65" t="n">
-        <v>-16.06</v>
+        <v>-12.09</v>
       </c>
       <c r="C10" s="65" t="n">
-        <v>-21.63</v>
+        <v>-20.98</v>
       </c>
       <c r="D10" s="66" t="n">
-        <v>2.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>-1.91</v>
+        <v>-1.67</v>
       </c>
       <c r="F10" s="67" t="n">
-        <v>49</v>
-      </c>
-      <c r="G10" s="67" t="n">
-        <v>39</v>
-      </c>
-      <c r="H10" s="67" t="n">
-        <v>88</v>
-      </c>
-      <c r="I10" s="67" t="n">
-        <v>17</v>
-      </c>
-      <c r="J10" s="68" t="n">
-        <v>-3</v>
+        <v>-1</v>
+      </c>
+      <c r="G10" s="68" t="n">
+        <v>55</v>
+      </c>
+      <c r="H10" s="68" t="n">
+        <v>54</v>
+      </c>
+      <c r="I10" s="68" t="n">
+        <v>221</v>
+      </c>
+      <c r="J10" s="67" t="n">
+        <v>-99</v>
       </c>
       <c r="K10" s="67" t="n">
-        <v>26</v>
-      </c>
-      <c r="L10" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="68" t="n">
-        <v>-88</v>
-      </c>
-      <c r="N10" s="70" t="n">
-        <v>0</v>
+        <v>-36</v>
+      </c>
+      <c r="L10" s="67" t="n">
+        <v>-27</v>
+      </c>
+      <c r="M10" s="67" t="n">
+        <v>-39</v>
+      </c>
+      <c r="N10" s="67" t="n">
+        <v>-15</v>
       </c>
       <c r="O10" s="69" t="inlineStr">
         <is>
@@ -11854,47 +11921,47 @@
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>부동산</t>
+          <t>비금속</t>
         </is>
       </c>
       <c r="B11" s="65" t="n">
-        <v>-12.45</v>
+        <v>-17.18</v>
       </c>
       <c r="C11" s="65" t="n">
-        <v>-21.17</v>
-      </c>
-      <c r="D11" s="66" t="n">
-        <v>2.56</v>
+        <v>-22.18</v>
+      </c>
+      <c r="D11" s="65" t="n">
+        <v>-2.32</v>
       </c>
       <c r="E11" s="65" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="F11" s="67" t="n">
-        <v>19</v>
-      </c>
-      <c r="G11" s="67" t="n">
-        <v>43</v>
-      </c>
-      <c r="H11" s="67" t="n">
-        <v>62</v>
-      </c>
-      <c r="I11" s="67" t="n">
-        <v>204</v>
-      </c>
-      <c r="J11" s="68" t="n">
-        <v>-90</v>
+        <v>-3.22</v>
+      </c>
+      <c r="F11" s="68" t="n">
+        <v>42</v>
+      </c>
+      <c r="G11" s="68" t="n">
+        <v>42</v>
+      </c>
+      <c r="H11" s="68" t="n">
+        <v>84</v>
+      </c>
+      <c r="I11" s="68" t="n">
+        <v>18</v>
+      </c>
+      <c r="J11" s="67" t="n">
+        <v>-3</v>
       </c>
       <c r="K11" s="68" t="n">
-        <v>-43</v>
-      </c>
-      <c r="L11" s="68" t="n">
-        <v>-25</v>
-      </c>
-      <c r="M11" s="68" t="n">
-        <v>-44</v>
-      </c>
-      <c r="N11" s="68" t="n">
-        <v>-18</v>
+        <v>26</v>
+      </c>
+      <c r="L11" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="67" t="n">
+        <v>-84</v>
+      </c>
+      <c r="N11" s="70" t="n">
+        <v>0</v>
       </c>
       <c r="O11" s="69" t="inlineStr">
         <is>
@@ -11905,94 +11972,98 @@
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="B12" s="66" t="n">
-        <v>6.57</v>
+          <t>전기·가스</t>
+        </is>
+      </c>
+      <c r="B12" s="65" t="n">
+        <v>-32.58</v>
       </c>
       <c r="C12" s="65" t="n">
-        <v>-6.67</v>
-      </c>
-      <c r="D12" s="66" t="n">
-        <v>4.54</v>
+        <v>-33.23</v>
+      </c>
+      <c r="D12" s="65" t="n">
+        <v>-15.53</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>-3.17</v>
+        <v>-3.89</v>
       </c>
       <c r="F12" s="67" t="n">
-        <v>1065</v>
-      </c>
-      <c r="G12" s="67" t="n">
-        <v>798</v>
-      </c>
-      <c r="H12" s="67" t="n">
-        <v>1863</v>
+        <v>-14</v>
+      </c>
+      <c r="G12" s="68" t="n">
+        <v>562</v>
+      </c>
+      <c r="H12" s="68" t="n">
+        <v>549</v>
       </c>
       <c r="I12" s="68" t="n">
-        <v>-139</v>
-      </c>
-      <c r="J12" s="67" t="n">
-        <v>6</v>
+        <v>313</v>
+      </c>
+      <c r="J12" s="68" t="n">
+        <v>248</v>
       </c>
       <c r="K12" s="67" t="n">
-        <v>876</v>
-      </c>
-      <c r="L12" s="67" t="n">
-        <v>60</v>
-      </c>
-      <c r="M12" s="68" t="n">
-        <v>-3074</v>
+        <v>-23</v>
+      </c>
+      <c r="L12" s="68" t="n">
+        <v>29</v>
+      </c>
+      <c r="M12" s="67" t="n">
+        <v>-529</v>
       </c>
       <c r="N12" s="67" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O12" s="30" t="inlineStr"/>
+        <v>-20</v>
+      </c>
+      <c r="O12" s="69" t="inlineStr">
+        <is>
+          <t>수급유입</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>전기·가스</t>
-        </is>
-      </c>
-      <c r="B13" s="65" t="n">
-        <v>-32.12</v>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="B13" s="66" t="n">
+        <v>5.41</v>
       </c>
       <c r="C13" s="65" t="n">
-        <v>-32.7</v>
+        <v>-6.41</v>
       </c>
       <c r="D13" s="65" t="n">
-        <v>-10.32</v>
+        <v>-0.58</v>
       </c>
       <c r="E13" s="65" t="n">
-        <v>-3.23</v>
+        <v>-4.22</v>
       </c>
       <c r="F13" s="68" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G13" s="67" t="n">
-        <v>455</v>
-      </c>
-      <c r="H13" s="67" t="n">
-        <v>441</v>
+        <v>1052</v>
+      </c>
+      <c r="G13" s="68" t="n">
+        <v>769</v>
+      </c>
+      <c r="H13" s="68" t="n">
+        <v>1821</v>
       </c>
       <c r="I13" s="67" t="n">
-        <v>325</v>
+        <v>-114</v>
       </c>
       <c r="J13" s="67" t="n">
-        <v>228</v>
+        <v>-29</v>
       </c>
       <c r="K13" s="68" t="n">
-        <v>-98</v>
-      </c>
-      <c r="L13" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" s="68" t="n">
-        <v>-424</v>
+        <v>853</v>
+      </c>
+      <c r="L13" s="68" t="n">
+        <v>65</v>
+      </c>
+      <c r="M13" s="67" t="n">
+        <v>-3044</v>
       </c>
       <c r="N13" s="68" t="n">
-        <v>-17</v>
+        <v>1223</v>
       </c>
       <c r="O13" s="69" t="inlineStr">
         <is>
@@ -12007,43 +12078,43 @@
         </is>
       </c>
       <c r="B14" s="65" t="n">
-        <v>-9.07</v>
+        <v>-10.67</v>
       </c>
       <c r="C14" s="65" t="n">
-        <v>-13.65</v>
+        <v>-15.08</v>
       </c>
       <c r="D14" s="65" t="n">
-        <v>-5.01</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="F14" s="67" t="n">
-        <v>119</v>
-      </c>
-      <c r="G14" s="67" t="n">
-        <v>82</v>
-      </c>
-      <c r="H14" s="67" t="n">
-        <v>201</v>
-      </c>
-      <c r="I14" s="67" t="n">
-        <v>96</v>
-      </c>
-      <c r="J14" s="68" t="n">
-        <v>-10</v>
+        <v>-5.3</v>
+      </c>
+      <c r="F14" s="68" t="n">
+        <v>115</v>
+      </c>
+      <c r="G14" s="68" t="n">
+        <v>81</v>
+      </c>
+      <c r="H14" s="68" t="n">
+        <v>196</v>
+      </c>
+      <c r="I14" s="68" t="n">
+        <v>95</v>
+      </c>
+      <c r="J14" s="67" t="n">
+        <v>-2</v>
       </c>
       <c r="K14" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="68" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M14" s="68" t="n">
-        <v>-344</v>
-      </c>
-      <c r="N14" s="67" t="n">
-        <v>143</v>
+        <v>-3</v>
+      </c>
+      <c r="L14" s="67" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M14" s="67" t="n">
+        <v>-375</v>
+      </c>
+      <c r="N14" s="68" t="n">
+        <v>180</v>
       </c>
       <c r="O14" s="69" t="inlineStr">
         <is>
@@ -12058,43 +12129,43 @@
         </is>
       </c>
       <c r="B15" s="65" t="n">
-        <v>-19.54</v>
+        <v>-20.33</v>
       </c>
       <c r="C15" s="65" t="n">
-        <v>-17.35</v>
+        <v>-18.22</v>
       </c>
       <c r="D15" s="65" t="n">
-        <v>-6.62</v>
+        <v>-14.2</v>
       </c>
       <c r="E15" s="65" t="n">
-        <v>-5.82</v>
-      </c>
-      <c r="F15" s="67" t="n">
-        <v>451</v>
-      </c>
-      <c r="G15" s="67" t="n">
-        <v>626</v>
-      </c>
-      <c r="H15" s="67" t="n">
-        <v>1077</v>
-      </c>
-      <c r="I15" s="67" t="n">
-        <v>756</v>
-      </c>
-      <c r="J15" s="67" t="n">
-        <v>147</v>
-      </c>
-      <c r="K15" s="68" t="n">
-        <v>-395</v>
-      </c>
-      <c r="L15" s="67" t="n">
-        <v>128</v>
-      </c>
-      <c r="M15" s="68" t="n">
-        <v>-977</v>
-      </c>
-      <c r="N15" s="68" t="n">
-        <v>-100</v>
+        <v>-6.74</v>
+      </c>
+      <c r="F15" s="68" t="n">
+        <v>262</v>
+      </c>
+      <c r="G15" s="68" t="n">
+        <v>945</v>
+      </c>
+      <c r="H15" s="68" t="n">
+        <v>1207</v>
+      </c>
+      <c r="I15" s="68" t="n">
+        <v>720</v>
+      </c>
+      <c r="J15" s="68" t="n">
+        <v>194</v>
+      </c>
+      <c r="K15" s="67" t="n">
+        <v>-162</v>
+      </c>
+      <c r="L15" s="68" t="n">
+        <v>200</v>
+      </c>
+      <c r="M15" s="67" t="n">
+        <v>-1089</v>
+      </c>
+      <c r="N15" s="67" t="n">
+        <v>-118</v>
       </c>
       <c r="O15" s="30" t="inlineStr"/>
     </row>
@@ -12105,42 +12176,42 @@
         </is>
       </c>
       <c r="B16" s="65" t="n">
-        <v>-29.22</v>
+        <v>-30.03</v>
       </c>
       <c r="C16" s="65" t="n">
-        <v>-34.09</v>
+        <v>-33.76</v>
       </c>
       <c r="D16" s="65" t="n">
-        <v>-5.3</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="E16" s="65" t="n">
-        <v>-8.029999999999999</v>
-      </c>
-      <c r="F16" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" s="67" t="n">
+        <v>-9.07</v>
+      </c>
+      <c r="F16" s="68" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="68" t="n">
         <v>7</v>
       </c>
-      <c r="H16" s="67" t="n">
-        <v>10</v>
-      </c>
-      <c r="I16" s="67" t="n">
+      <c r="H16" s="68" t="n">
         <v>11</v>
       </c>
-      <c r="J16" s="68" t="n">
+      <c r="I16" s="68" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" s="67" t="n">
         <v>-1</v>
       </c>
-      <c r="K16" s="68" t="n">
+      <c r="K16" s="67" t="n">
         <v>-3</v>
       </c>
       <c r="L16" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="67" t="n">
-        <v>9</v>
-      </c>
-      <c r="N16" s="68" t="n">
+      <c r="M16" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="N16" s="67" t="n">
         <v>-19</v>
       </c>
       <c r="O16" s="69" t="inlineStr">
@@ -12152,98 +12223,94 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>보험</t>
         </is>
       </c>
       <c r="B17" s="66" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="C17" s="65" t="n">
-        <v>-21.99</v>
+        <v>38.21</v>
+      </c>
+      <c r="C17" s="66" t="n">
+        <v>4.63</v>
       </c>
       <c r="D17" s="65" t="n">
-        <v>-12.79</v>
+        <v>-13.99</v>
       </c>
       <c r="E17" s="65" t="n">
-        <v>-8.59</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="F17" s="67" t="n">
-        <v>293</v>
-      </c>
-      <c r="G17" s="67" t="n">
-        <v>196</v>
-      </c>
-      <c r="H17" s="67" t="n">
-        <v>489</v>
-      </c>
-      <c r="I17" s="67" t="n">
-        <v>17</v>
-      </c>
-      <c r="J17" s="67" t="n">
-        <v>277</v>
+        <v>-1940</v>
+      </c>
+      <c r="G17" s="68" t="n">
+        <v>2428</v>
+      </c>
+      <c r="H17" s="68" t="n">
+        <v>488</v>
+      </c>
+      <c r="I17" s="68" t="n">
+        <v>485</v>
+      </c>
+      <c r="J17" s="68" t="n">
+        <v>1529</v>
       </c>
       <c r="K17" s="68" t="n">
-        <v>-302</v>
+        <v>480</v>
       </c>
       <c r="L17" s="67" t="n">
-        <v>198</v>
-      </c>
-      <c r="M17" s="68" t="n">
-        <v>-471</v>
+        <v>-50</v>
+      </c>
+      <c r="M17" s="67" t="n">
+        <v>-549</v>
       </c>
       <c r="N17" s="68" t="n">
-        <v>-17</v>
-      </c>
-      <c r="O17" s="69" t="inlineStr">
-        <is>
-          <t>수급유입</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="O17" s="30" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="B18" s="66" t="n">
-        <v>6.92</v>
+        <v>10.45</v>
       </c>
       <c r="C18" s="65" t="n">
-        <v>-19.74</v>
+        <v>-23.05</v>
       </c>
       <c r="D18" s="65" t="n">
-        <v>-0.18</v>
+        <v>-17.25</v>
       </c>
       <c r="E18" s="65" t="n">
-        <v>-9.33</v>
-      </c>
-      <c r="F18" s="67" t="n">
-        <v>287</v>
-      </c>
-      <c r="G18" s="67" t="n">
-        <v>3443</v>
-      </c>
-      <c r="H18" s="67" t="n">
-        <v>3730</v>
-      </c>
-      <c r="I18" s="67" t="n">
-        <v>1314</v>
-      </c>
-      <c r="J18" s="67" t="n">
-        <v>606</v>
+        <v>-10.37</v>
+      </c>
+      <c r="F18" s="68" t="n">
+        <v>219</v>
+      </c>
+      <c r="G18" s="68" t="n">
+        <v>239</v>
+      </c>
+      <c r="H18" s="68" t="n">
+        <v>458</v>
+      </c>
+      <c r="I18" s="68" t="n">
+        <v>85</v>
+      </c>
+      <c r="J18" s="68" t="n">
+        <v>199</v>
       </c>
       <c r="K18" s="67" t="n">
-        <v>1271</v>
-      </c>
-      <c r="L18" s="67" t="n">
-        <v>272</v>
-      </c>
-      <c r="M18" s="68" t="n">
-        <v>-3473</v>
-      </c>
-      <c r="N18" s="68" t="n">
-        <v>-256</v>
+        <v>-238</v>
+      </c>
+      <c r="L18" s="68" t="n">
+        <v>192</v>
+      </c>
+      <c r="M18" s="67" t="n">
+        <v>-449</v>
+      </c>
+      <c r="N18" s="67" t="n">
+        <v>-10</v>
       </c>
       <c r="O18" s="69" t="inlineStr">
         <is>
@@ -12254,94 +12321,98 @@
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>보험</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="B19" s="66" t="n">
-        <v>38.08</v>
-      </c>
-      <c r="C19" s="66" t="n">
-        <v>6.25</v>
+        <v>8.789999999999999</v>
+      </c>
+      <c r="C19" s="65" t="n">
+        <v>-16.35</v>
       </c>
       <c r="D19" s="65" t="n">
-        <v>-12.13</v>
+        <v>-18.36</v>
       </c>
       <c r="E19" s="65" t="n">
-        <v>-9.449999999999999</v>
+        <v>-11.28</v>
       </c>
       <c r="F19" s="68" t="n">
-        <v>-1843</v>
-      </c>
-      <c r="G19" s="67" t="n">
-        <v>2294</v>
-      </c>
-      <c r="H19" s="67" t="n">
-        <v>451</v>
-      </c>
-      <c r="I19" s="67" t="n">
-        <v>524</v>
+        <v>733</v>
+      </c>
+      <c r="G19" s="68" t="n">
+        <v>1240</v>
+      </c>
+      <c r="H19" s="68" t="n">
+        <v>1973</v>
+      </c>
+      <c r="I19" s="68" t="n">
+        <v>594</v>
       </c>
       <c r="J19" s="67" t="n">
-        <v>1438</v>
-      </c>
-      <c r="K19" s="67" t="n">
-        <v>400</v>
+        <v>-320</v>
+      </c>
+      <c r="K19" s="68" t="n">
+        <v>820</v>
       </c>
       <c r="L19" s="68" t="n">
-        <v>-55</v>
-      </c>
-      <c r="M19" s="68" t="n">
-        <v>-509</v>
-      </c>
-      <c r="N19" s="67" t="n">
-        <v>57</v>
-      </c>
-      <c r="O19" s="30" t="inlineStr"/>
+        <v>180</v>
+      </c>
+      <c r="M19" s="67" t="n">
+        <v>-2008</v>
+      </c>
+      <c r="N19" s="68" t="n">
+        <v>36</v>
+      </c>
+      <c r="O19" s="69" t="inlineStr">
+        <is>
+          <t>수급유입</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="B20" s="66" t="n">
-        <v>10.16</v>
+        <v>3.67</v>
       </c>
       <c r="C20" s="65" t="n">
-        <v>-12.69</v>
+        <v>-22.38</v>
       </c>
       <c r="D20" s="65" t="n">
-        <v>-15.28</v>
+        <v>-9</v>
       </c>
       <c r="E20" s="65" t="n">
-        <v>-10.17</v>
-      </c>
-      <c r="F20" s="67" t="n">
-        <v>957</v>
-      </c>
-      <c r="G20" s="67" t="n">
-        <v>1087</v>
-      </c>
-      <c r="H20" s="67" t="n">
-        <v>2044</v>
-      </c>
-      <c r="I20" s="67" t="n">
-        <v>489</v>
+        <v>-12.09</v>
+      </c>
+      <c r="F20" s="68" t="n">
+        <v>507</v>
+      </c>
+      <c r="G20" s="68" t="n">
+        <v>2914</v>
+      </c>
+      <c r="H20" s="68" t="n">
+        <v>3421</v>
+      </c>
+      <c r="I20" s="68" t="n">
+        <v>1413</v>
       </c>
       <c r="J20" s="68" t="n">
-        <v>-333</v>
-      </c>
-      <c r="K20" s="67" t="n">
-        <v>795</v>
-      </c>
-      <c r="L20" s="67" t="n">
-        <v>171</v>
-      </c>
-      <c r="M20" s="68" t="n">
-        <v>-2080</v>
+        <v>286</v>
+      </c>
+      <c r="K20" s="68" t="n">
+        <v>959</v>
+      </c>
+      <c r="L20" s="68" t="n">
+        <v>282</v>
+      </c>
+      <c r="M20" s="67" t="n">
+        <v>-3124</v>
       </c>
       <c r="N20" s="67" t="n">
-        <v>36</v>
+        <v>-297</v>
       </c>
       <c r="O20" s="69" t="inlineStr">
         <is>
@@ -12356,235 +12427,235 @@
         </is>
       </c>
       <c r="B21" s="65" t="n">
-        <v>-3.46</v>
+        <v>-4.65</v>
       </c>
       <c r="C21" s="65" t="n">
-        <v>-49.76</v>
+        <v>-49.97</v>
       </c>
       <c r="D21" s="65" t="n">
-        <v>-24.76</v>
+        <v>-28.36</v>
       </c>
       <c r="E21" s="65" t="n">
-        <v>-14.09</v>
-      </c>
-      <c r="F21" s="68" t="n">
-        <v>-270</v>
-      </c>
-      <c r="G21" s="67" t="n">
-        <v>285</v>
-      </c>
-      <c r="H21" s="67" t="n">
-        <v>14</v>
-      </c>
-      <c r="I21" s="67" t="n">
-        <v>38</v>
-      </c>
-      <c r="J21" s="67" t="n">
-        <v>233</v>
-      </c>
-      <c r="K21" s="68" t="n">
-        <v>-232</v>
-      </c>
-      <c r="L21" s="67" t="n">
-        <v>32</v>
-      </c>
-      <c r="M21" s="68" t="n">
-        <v>-77</v>
-      </c>
-      <c r="N21" s="67" t="n">
-        <v>63</v>
+        <v>-15.15</v>
+      </c>
+      <c r="F21" s="67" t="n">
+        <v>-354</v>
+      </c>
+      <c r="G21" s="68" t="n">
+        <v>362</v>
+      </c>
+      <c r="H21" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" s="68" t="n">
+        <v>82</v>
+      </c>
+      <c r="J21" s="68" t="n">
+        <v>277</v>
+      </c>
+      <c r="K21" s="67" t="n">
+        <v>-276</v>
+      </c>
+      <c r="L21" s="68" t="n">
+        <v>52</v>
+      </c>
+      <c r="M21" s="67" t="n">
+        <v>-70</v>
+      </c>
+      <c r="N21" s="68" t="n">
+        <v>62</v>
       </c>
       <c r="O21" s="30" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>금속</t>
-        </is>
-      </c>
-      <c r="B22" s="65" t="n">
-        <v>-14.43</v>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="B22" s="66" t="n">
+        <v>18.1</v>
       </c>
       <c r="C22" s="65" t="n">
-        <v>-41.35</v>
+        <v>-14.21</v>
       </c>
       <c r="D22" s="65" t="n">
-        <v>-8.66</v>
+        <v>-20.31</v>
       </c>
       <c r="E22" s="65" t="n">
-        <v>-14.25</v>
-      </c>
-      <c r="F22" s="68" t="n">
-        <v>-2476</v>
-      </c>
-      <c r="G22" s="67" t="n">
-        <v>1149</v>
+        <v>-16.46</v>
+      </c>
+      <c r="F22" s="67" t="n">
+        <v>-11085</v>
+      </c>
+      <c r="G22" s="68" t="n">
+        <v>11566</v>
       </c>
       <c r="H22" s="68" t="n">
-        <v>-1327</v>
-      </c>
-      <c r="I22" s="67" t="n">
-        <v>1389</v>
-      </c>
-      <c r="J22" s="67" t="n">
-        <v>155</v>
-      </c>
-      <c r="K22" s="68" t="n">
-        <v>-448</v>
-      </c>
-      <c r="L22" s="67" t="n">
-        <v>51</v>
-      </c>
-      <c r="M22" s="67" t="n">
-        <v>1343</v>
-      </c>
-      <c r="N22" s="68" t="n">
-        <v>-16</v>
-      </c>
-      <c r="O22" s="58" t="inlineStr">
-        <is>
-          <t>동반약세</t>
-        </is>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="I22" s="68" t="n">
+        <v>7862</v>
+      </c>
+      <c r="J22" s="68" t="n">
+        <v>6623</v>
+      </c>
+      <c r="K22" s="67" t="n">
+        <v>-4423</v>
+      </c>
+      <c r="L22" s="68" t="n">
+        <v>62</v>
+      </c>
+      <c r="M22" s="68" t="n">
+        <v>5597</v>
+      </c>
+      <c r="N22" s="67" t="n">
+        <v>-6078</v>
+      </c>
+      <c r="O22" s="30" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="B23" s="65" t="n">
-        <v>-21.66</v>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="B23" s="66" t="n">
+        <v>39.32</v>
       </c>
       <c r="C23" s="65" t="n">
-        <v>-43.83</v>
+        <v>-43.66</v>
       </c>
       <c r="D23" s="65" t="n">
-        <v>-26.63</v>
+        <v>-14.55</v>
       </c>
       <c r="E23" s="65" t="n">
-        <v>-15.57</v>
+        <v>-16.65</v>
       </c>
       <c r="F23" s="68" t="n">
-        <v>-4039</v>
+        <v>1675</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>5522</v>
+        <v>-2080</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1483</v>
+        <v>-405</v>
       </c>
       <c r="I23" s="67" t="n">
-        <v>7383</v>
+        <v>-88</v>
       </c>
       <c r="J23" s="67" t="n">
-        <v>1085</v>
-      </c>
-      <c r="K23" s="68" t="n">
-        <v>-3095</v>
+        <v>-792</v>
+      </c>
+      <c r="K23" s="67" t="n">
+        <v>-1088</v>
       </c>
       <c r="L23" s="67" t="n">
-        <v>195</v>
-      </c>
-      <c r="M23" s="67" t="n">
-        <v>3141</v>
-      </c>
-      <c r="N23" s="68" t="n">
-        <v>-4623</v>
+        <v>-109</v>
+      </c>
+      <c r="M23" s="68" t="n">
+        <v>408</v>
+      </c>
+      <c r="N23" s="67" t="n">
+        <v>-3</v>
       </c>
       <c r="O23" s="30" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="31" t="inlineStr">
         <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="B24" s="66" t="n">
-        <v>19.1</v>
+          <t>금속</t>
+        </is>
+      </c>
+      <c r="B24" s="65" t="n">
+        <v>-17.19</v>
       </c>
       <c r="C24" s="65" t="n">
-        <v>-12.52</v>
+        <v>-42.04</v>
       </c>
       <c r="D24" s="65" t="n">
-        <v>-17.92</v>
+        <v>-17.51</v>
       </c>
       <c r="E24" s="65" t="n">
-        <v>-15.75</v>
-      </c>
-      <c r="F24" s="68" t="n">
-        <v>-9105</v>
-      </c>
-      <c r="G24" s="67" t="n">
-        <v>9914</v>
+        <v>-17.01</v>
+      </c>
+      <c r="F24" s="67" t="n">
+        <v>-2490</v>
+      </c>
+      <c r="G24" s="68" t="n">
+        <v>939</v>
       </c>
       <c r="H24" s="67" t="n">
-        <v>808</v>
-      </c>
-      <c r="I24" s="67" t="n">
-        <v>7011</v>
-      </c>
-      <c r="J24" s="67" t="n">
-        <v>6008</v>
-      </c>
-      <c r="K24" s="68" t="n">
-        <v>-4476</v>
+        <v>-1551</v>
+      </c>
+      <c r="I24" s="68" t="n">
+        <v>1381</v>
+      </c>
+      <c r="J24" s="68" t="n">
+        <v>73</v>
+      </c>
+      <c r="K24" s="67" t="n">
+        <v>-570</v>
       </c>
       <c r="L24" s="68" t="n">
-        <v>-17</v>
-      </c>
-      <c r="M24" s="67" t="n">
-        <v>5294</v>
-      </c>
-      <c r="N24" s="68" t="n">
-        <v>-6103</v>
-      </c>
-      <c r="O24" s="30" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="M24" s="68" t="n">
+        <v>1570</v>
+      </c>
+      <c r="N24" s="67" t="n">
+        <v>-19</v>
+      </c>
+      <c r="O24" s="58" t="inlineStr">
+        <is>
+          <t>동반약세</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="B25" s="66" t="n">
-        <v>39.21</v>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="B25" s="65" t="n">
+        <v>-23.4</v>
       </c>
       <c r="C25" s="65" t="n">
-        <v>-42.45</v>
+        <v>-44.82</v>
       </c>
       <c r="D25" s="65" t="n">
-        <v>-5.68</v>
+        <v>-31.7</v>
       </c>
       <c r="E25" s="65" t="n">
-        <v>-16.71</v>
+        <v>-17.44</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>1613</v>
+        <v>-3631</v>
       </c>
       <c r="G25" s="68" t="n">
-        <v>-2126</v>
+        <v>5139</v>
       </c>
       <c r="H25" s="68" t="n">
-        <v>-513</v>
+        <v>1508</v>
       </c>
       <c r="I25" s="68" t="n">
-        <v>-90</v>
+        <v>7490</v>
       </c>
       <c r="J25" s="68" t="n">
-        <v>-887</v>
-      </c>
-      <c r="K25" s="68" t="n">
-        <v>-1021</v>
+        <v>848</v>
+      </c>
+      <c r="K25" s="67" t="n">
+        <v>-3340</v>
       </c>
       <c r="L25" s="68" t="n">
-        <v>-124</v>
-      </c>
-      <c r="M25" s="67" t="n">
-        <v>511</v>
+        <v>190</v>
+      </c>
+      <c r="M25" s="68" t="n">
+        <v>3108</v>
       </c>
       <c r="N25" s="67" t="n">
-        <v>2</v>
+        <v>-4616</v>
       </c>
       <c r="O25" s="30" t="inlineStr"/>
     </row>
@@ -12595,43 +12666,43 @@
         </is>
       </c>
       <c r="B26" s="66" t="n">
-        <v>36.52</v>
+        <v>37.4</v>
       </c>
       <c r="C26" s="65" t="n">
-        <v>-13.29</v>
+        <v>-13.51</v>
       </c>
       <c r="D26" s="65" t="n">
-        <v>-20.04</v>
+        <v>-23.17</v>
       </c>
       <c r="E26" s="65" t="n">
-        <v>-20.97</v>
-      </c>
-      <c r="F26" s="68" t="n">
-        <v>-170314</v>
+        <v>-20.46</v>
+      </c>
+      <c r="F26" s="67" t="n">
+        <v>-179426</v>
       </c>
       <c r="G26" s="68" t="n">
-        <v>-1214</v>
-      </c>
-      <c r="H26" s="68" t="n">
-        <v>-171528</v>
-      </c>
-      <c r="I26" s="67" t="n">
-        <v>7809</v>
-      </c>
-      <c r="J26" s="68" t="n">
-        <v>-18906</v>
-      </c>
-      <c r="K26" s="67" t="n">
-        <v>3473</v>
-      </c>
-      <c r="L26" s="67" t="n">
-        <v>6913</v>
-      </c>
-      <c r="M26" s="67" t="n">
-        <v>69556</v>
-      </c>
-      <c r="N26" s="67" t="n">
-        <v>101971</v>
+        <v>5056</v>
+      </c>
+      <c r="H26" s="67" t="n">
+        <v>-174370</v>
+      </c>
+      <c r="I26" s="68" t="n">
+        <v>12188</v>
+      </c>
+      <c r="J26" s="67" t="n">
+        <v>-17782</v>
+      </c>
+      <c r="K26" s="68" t="n">
+        <v>3607</v>
+      </c>
+      <c r="L26" s="68" t="n">
+        <v>7533</v>
+      </c>
+      <c r="M26" s="68" t="n">
+        <v>71598</v>
+      </c>
+      <c r="N26" s="68" t="n">
+        <v>102772</v>
       </c>
       <c r="O26" s="58" t="inlineStr">
         <is>
@@ -12642,47 +12713,47 @@
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="B27" s="65" t="n">
-        <v>-11.62</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="B27" s="66" t="n">
+        <v>67.19</v>
       </c>
       <c r="C27" s="65" t="n">
-        <v>-42.7</v>
+        <v>-4.69</v>
       </c>
       <c r="D27" s="65" t="n">
-        <v>-13.06</v>
+        <v>-24.77</v>
       </c>
       <c r="E27" s="65" t="n">
-        <v>-21.87</v>
-      </c>
-      <c r="F27" s="68" t="n">
-        <v>-4629</v>
-      </c>
-      <c r="G27" s="68" t="n">
-        <v>-652</v>
-      </c>
-      <c r="H27" s="68" t="n">
-        <v>-5281</v>
+        <v>-22.59</v>
+      </c>
+      <c r="F27" s="67" t="n">
+        <v>-166518</v>
+      </c>
+      <c r="G27" s="67" t="n">
+        <v>-12335</v>
+      </c>
+      <c r="H27" s="67" t="n">
+        <v>-178854</v>
       </c>
       <c r="I27" s="67" t="n">
-        <v>2608</v>
-      </c>
-      <c r="J27" s="68" t="n">
-        <v>-2724</v>
+        <v>-735</v>
+      </c>
+      <c r="J27" s="67" t="n">
+        <v>-19606</v>
       </c>
       <c r="K27" s="68" t="n">
-        <v>-408</v>
+        <v>1904</v>
       </c>
       <c r="L27" s="68" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M27" s="67" t="n">
-        <v>5319</v>
+        <v>6474</v>
+      </c>
+      <c r="M27" s="68" t="n">
+        <v>72582</v>
       </c>
       <c r="N27" s="68" t="n">
-        <v>-38</v>
+        <v>106272</v>
       </c>
       <c r="O27" s="58" t="inlineStr">
         <is>
@@ -12693,47 +12764,47 @@
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="B28" s="66" t="n">
-        <v>65.09999999999999</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="B28" s="65" t="n">
+        <v>-13.89</v>
       </c>
       <c r="C28" s="65" t="n">
-        <v>-4.62</v>
+        <v>-45.92</v>
       </c>
       <c r="D28" s="65" t="n">
-        <v>-22.18</v>
+        <v>-19.41</v>
       </c>
       <c r="E28" s="65" t="n">
-        <v>-23.56</v>
-      </c>
-      <c r="F28" s="68" t="n">
-        <v>-157305</v>
-      </c>
-      <c r="G28" s="68" t="n">
-        <v>-18890</v>
-      </c>
-      <c r="H28" s="68" t="n">
-        <v>-176195</v>
+        <v>-23.88</v>
+      </c>
+      <c r="F28" s="67" t="n">
+        <v>-4630</v>
+      </c>
+      <c r="G28" s="67" t="n">
+        <v>-875</v>
+      </c>
+      <c r="H28" s="67" t="n">
+        <v>-5505</v>
       </c>
       <c r="I28" s="68" t="n">
-        <v>-5056</v>
-      </c>
-      <c r="J28" s="68" t="n">
-        <v>-21041</v>
+        <v>2684</v>
+      </c>
+      <c r="J28" s="67" t="n">
+        <v>-2905</v>
       </c>
       <c r="K28" s="67" t="n">
-        <v>1672</v>
+        <v>-498</v>
       </c>
       <c r="L28" s="67" t="n">
-        <v>5930</v>
-      </c>
-      <c r="M28" s="67" t="n">
-        <v>70671</v>
+        <v>-129</v>
+      </c>
+      <c r="M28" s="68" t="n">
+        <v>5575</v>
       </c>
       <c r="N28" s="67" t="n">
-        <v>105524</v>
+        <v>-70</v>
       </c>
       <c r="O28" s="58" t="inlineStr">
         <is>
@@ -12773,7 +12844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{498F857D-4E8A-41BF-BB01-0B721C1554C1}</x14:id>
+          <x14:id>{2F344ED0-A658-487D-A766-E99678CDF991}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12787,7 +12858,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D40902B0-86CA-4661-87AF-954D35C6EDC7}</x14:id>
+          <x14:id>{3C1DB21E-98BF-41DD-B560-98F83A8FD4D8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12801,7 +12872,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D86E692A-5C4B-4E35-88D9-7A47DD6DBFBD}</x14:id>
+          <x14:id>{BF55AA5A-1708-403C-8444-1E5EDAD86509}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12815,7 +12886,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E61269CA-26B7-439D-B573-D540696E3B40}</x14:id>
+          <x14:id>{F7D5BF92-2C87-4CD6-8887-1E37C2DF85E6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12825,7 +12896,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{498F857D-4E8A-41BF-BB01-0B721C1554C1}">
+          <x14:cfRule type="dataBar" id="{2F344ED0-A658-487D-A766-E99678CDF991}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12838,7 +12909,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D40902B0-86CA-4661-87AF-954D35C6EDC7}">
+          <x14:cfRule type="dataBar" id="{3C1DB21E-98BF-41DD-B560-98F83A8FD4D8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12851,7 +12922,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D86E692A-5C4B-4E35-88D9-7A47DD6DBFBD}">
+          <x14:cfRule type="dataBar" id="{BF55AA5A-1708-403C-8444-1E5EDAD86509}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12864,7 +12935,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E61269CA-26B7-439D-B573-D540696E3B40}">
+          <x14:cfRule type="dataBar" id="{F7D5BF92-2C87-4CD6-8887-1E37C2DF85E6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/reports/monthly_review/2026-10.xlsx
+++ b/public/reports/monthly_review/2026-10.xlsx
@@ -1020,7 +1020,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/22, %</t>
+          <t>미국 종가 기준 09/30 → 10/23, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1089,20 +1089,20 @@
       <c r="D8" s="28" t="n">
         <v>16699</v>
       </c>
-      <c r="E8" s="28" t="n">
-        <v>0.16</v>
+      <c r="E8" s="29" t="n">
+        <v>-0.36</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>3.85</v>
+        <v>2.57</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>-3.17</v>
+        <v>-3.37</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>16.46</v>
+        <v>19.03</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>-15.02</v>
+        <v>-14.64</v>
       </c>
     </row>
     <row r="9">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>9.869999999999999</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="13">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>7.65</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="14">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>6.14</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="15">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-14.06</v>
+        <v>-13.43</v>
       </c>
     </row>
     <row r="16">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>-6.85</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="17">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="D17" s="33" t="n">
-        <v>-3.83</v>
+        <v>-5.16</v>
       </c>
     </row>
     <row r="18">
@@ -12844,7 +12844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2F344ED0-A658-487D-A766-E99678CDF991}</x14:id>
+          <x14:id>{3ECB61BD-7912-4801-80F6-2A1989E3C79E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12858,7 +12858,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3C1DB21E-98BF-41DD-B560-98F83A8FD4D8}</x14:id>
+          <x14:id>{858627A6-CEE7-4855-95DF-A1D63177C655}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12872,7 +12872,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BF55AA5A-1708-403C-8444-1E5EDAD86509}</x14:id>
+          <x14:id>{916D4678-8D43-48BE-A479-B19397C64FBC}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12886,7 +12886,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F7D5BF92-2C87-4CD6-8887-1E37C2DF85E6}</x14:id>
+          <x14:id>{0C47F868-80CF-4EE0-AC05-534E66F9F076}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12896,7 +12896,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2F344ED0-A658-487D-A766-E99678CDF991}">
+          <x14:cfRule type="dataBar" id="{3ECB61BD-7912-4801-80F6-2A1989E3C79E}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12909,7 +12909,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3C1DB21E-98BF-41DD-B560-98F83A8FD4D8}">
+          <x14:cfRule type="dataBar" id="{858627A6-CEE7-4855-95DF-A1D63177C655}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12922,7 +12922,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BF55AA5A-1708-403C-8444-1E5EDAD86509}">
+          <x14:cfRule type="dataBar" id="{916D4678-8D43-48BE-A479-B19397C64FBC}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -12935,7 +12935,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F7D5BF92-2C87-4CD6-8887-1E37C2DF85E6}">
+          <x14:cfRule type="dataBar" id="{0C47F868-80CF-4EE0-AC05-534E66F9F076}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/reports/monthly_review/2026-10.xlsx
+++ b/public/reports/monthly_review/2026-10.xlsx
@@ -321,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -416,9 +416,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1014,7 +1011,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/30 → 10/29, %</t>
+          <t>미국 종가 기준 09/30 → 10/30, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1083,20 +1080,20 @@
       <c r="D8" s="28" t="n">
         <v>38129</v>
       </c>
-      <c r="E8" s="28" t="n">
-        <v>0.9</v>
+      <c r="E8" s="29" t="n">
+        <v>-0.93</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>2.82</v>
+        <v>1.7</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>-2.52</v>
+        <v>-5.3</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>5.26</v>
+        <v>18.85</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>-8.789999999999999</v>
+        <v>-15.36</v>
       </c>
     </row>
     <row r="9">
@@ -1155,7 +1152,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>11.72</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="13">
@@ -1175,7 +1172,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>9.27</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="14">
@@ -1195,7 +1192,7 @@
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>7.86</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1215,7 +1212,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-7.77</v>
+        <v>-14.21</v>
       </c>
     </row>
     <row r="16">
@@ -1235,7 +1232,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>-3.58</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1251,13 +1248,11 @@
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
-        </is>
-      </c>
-      <c r="D17" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>바이오</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="18">
@@ -4357,7 +4352,7 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="D99" s="35" t="inlineStr">
+      <c r="D99" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -4398,7 +4393,7 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="D100" s="35" t="inlineStr">
+      <c r="D100" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4439,7 +4434,7 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="D101" s="35" t="inlineStr">
+      <c r="D101" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -4480,7 +4475,7 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="D102" s="35" t="inlineStr">
+      <c r="D102" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -4521,7 +4516,7 @@
           <t>LG씨엔에스</t>
         </is>
       </c>
-      <c r="D103" s="35" t="inlineStr">
+      <c r="D103" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -4562,7 +4557,7 @@
           <t>HMM</t>
         </is>
       </c>
-      <c r="D104" s="35" t="inlineStr">
+      <c r="D104" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -4603,7 +4598,7 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="D105" s="35" t="inlineStr">
+      <c r="D105" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -4644,7 +4639,7 @@
           <t>하이브</t>
         </is>
       </c>
-      <c r="D106" s="35" t="inlineStr">
+      <c r="D106" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
@@ -4685,7 +4680,7 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="D107" s="35" t="inlineStr">
+      <c r="D107" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4726,7 +4721,7 @@
           <t>삼성물산</t>
         </is>
       </c>
-      <c r="D108" s="35" t="inlineStr">
+      <c r="D108" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
@@ -4767,7 +4762,7 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="D109" s="35" t="inlineStr">
+      <c r="D109" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4808,7 +4803,7 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="D110" s="35" t="inlineStr">
+      <c r="D110" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4849,7 +4844,7 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="D111" s="35" t="inlineStr">
+      <c r="D111" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4890,7 +4885,7 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="D112" s="35" t="inlineStr">
+      <c r="D112" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4931,7 +4926,7 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="D113" s="35" t="inlineStr">
+      <c r="D113" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -4972,7 +4967,7 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="D114" s="35" t="inlineStr">
+      <c r="D114" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -5013,7 +5008,7 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="D115" s="35" t="inlineStr">
+      <c r="D115" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
@@ -5054,7 +5049,7 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="D116" s="35" t="inlineStr">
+      <c r="D116" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -5095,7 +5090,7 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="D117" s="35" t="inlineStr">
+      <c r="D117" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -5136,7 +5131,7 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="D118" s="35" t="inlineStr">
+      <c r="D118" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -5190,7 +5185,7 @@
       <c r="K120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="36" t="inlineStr">
+      <c r="A121" s="35" t="inlineStr">
         <is>
           <t>● 동반강세 — 추세 지속형 상방 관찰</t>
         </is>
@@ -5207,12 +5202,12 @@
           <t>삼성생명</t>
         </is>
       </c>
-      <c r="B122" s="35" t="inlineStr">
+      <c r="B122" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="C122" s="37" t="n">
+      <c r="C122" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D122" s="31" t="inlineStr"/>
@@ -5222,12 +5217,12 @@
           <t>아모레퍼시픽</t>
         </is>
       </c>
-      <c r="H122" s="35" t="inlineStr">
+      <c r="H122" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="I122" s="38" t="n">
+      <c r="I122" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J122" s="31" t="inlineStr"/>
@@ -5251,12 +5246,12 @@
           <t>롯데손해보험</t>
         </is>
       </c>
-      <c r="B124" s="35" t="inlineStr">
+      <c r="B124" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="C124" s="37" t="n">
+      <c r="C124" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D124" s="31" t="inlineStr"/>
@@ -5266,12 +5261,12 @@
           <t>LG생활건강</t>
         </is>
       </c>
-      <c r="H124" s="35" t="inlineStr">
+      <c r="H124" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="I124" s="38" t="n">
+      <c r="I124" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J124" s="31" t="inlineStr"/>
@@ -5295,12 +5290,12 @@
           <t>DB손해보험</t>
         </is>
       </c>
-      <c r="B126" s="35" t="inlineStr">
+      <c r="B126" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="C126" s="37" t="n">
+      <c r="C126" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D126" s="31" t="inlineStr"/>
@@ -5310,12 +5305,12 @@
           <t>한일시멘트</t>
         </is>
       </c>
-      <c r="H126" s="35" t="inlineStr">
+      <c r="H126" s="34" t="inlineStr">
         <is>
           <t>비금속</t>
         </is>
       </c>
-      <c r="I126" s="38" t="n">
+      <c r="I126" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J126" s="31" t="inlineStr"/>
@@ -5339,12 +5334,12 @@
           <t>미래에셋생명</t>
         </is>
       </c>
-      <c r="B128" s="35" t="inlineStr">
+      <c r="B128" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="C128" s="37" t="n">
+      <c r="C128" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D128" s="31" t="inlineStr"/>
@@ -5354,12 +5349,12 @@
           <t>CJ CGV</t>
         </is>
       </c>
-      <c r="H128" s="35" t="inlineStr">
+      <c r="H128" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="I128" s="38" t="n">
+      <c r="I128" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J128" s="31" t="inlineStr"/>
@@ -5383,12 +5378,12 @@
           <t>나이스정보통신</t>
         </is>
       </c>
-      <c r="H130" s="35" t="inlineStr">
+      <c r="H130" s="34" t="inlineStr">
         <is>
           <t>통신</t>
         </is>
       </c>
-      <c r="I130" s="38" t="n">
+      <c r="I130" s="37" t="n">
         <v>3</v>
       </c>
       <c r="J130" s="31" t="inlineStr"/>
@@ -5403,12 +5398,12 @@
     </row>
     <row r="132"/>
     <row r="133">
-      <c r="A133" s="39" t="inlineStr">
+      <c r="A133" s="38" t="inlineStr">
         <is>
           <t>● 수급이탈 — 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G133" s="40" t="inlineStr">
+      <c r="G133" s="39" t="inlineStr">
         <is>
           <t>● 동반약세 — 약세 지속형 하방 관찰</t>
         </is>
@@ -5425,12 +5420,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="H134" s="35" t="inlineStr">
+      <c r="H134" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I134" s="41" t="n">
+      <c r="I134" s="40" t="n">
         <v>-2</v>
       </c>
       <c r="J134" s="31" t="inlineStr"/>
@@ -5449,12 +5444,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="H136" s="35" t="inlineStr">
+      <c r="H136" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I136" s="41" t="n">
+      <c r="I136" s="40" t="n">
         <v>-2</v>
       </c>
       <c r="J136" s="31" t="inlineStr"/>
@@ -5473,12 +5468,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="H138" s="35" t="inlineStr">
+      <c r="H138" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="I138" s="41" t="n">
+      <c r="I138" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="J138" s="31" t="inlineStr"/>
@@ -5497,12 +5492,12 @@
           <t>고려아연</t>
         </is>
       </c>
-      <c r="H140" s="35" t="inlineStr">
+      <c r="H140" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="I140" s="41" t="n">
+      <c r="I140" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="J140" s="31" t="inlineStr"/>
@@ -5521,12 +5516,12 @@
           <t>풍산</t>
         </is>
       </c>
-      <c r="H142" s="35" t="inlineStr">
+      <c r="H142" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="I142" s="41" t="n">
+      <c r="I142" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="J142" s="31" t="inlineStr"/>
@@ -5541,7 +5536,7 @@
     </row>
     <row r="144"/>
     <row r="145" ht="31" customHeight="1" s="15">
-      <c r="A145" s="42" t="inlineStr">
+      <c r="A145" s="41" t="inlineStr">
         <is>
           <t>현재 확보된 월간 리뷰 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 월간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
@@ -5745,7 +5740,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D163" s="35" t="inlineStr">
+      <c r="D163" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
@@ -5780,7 +5775,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D164" s="35" t="inlineStr">
+      <c r="D164" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -5815,7 +5810,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D165" s="35" t="inlineStr">
+      <c r="D165" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -5850,7 +5845,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D166" s="35" t="inlineStr">
+      <c r="D166" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -5885,7 +5880,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D167" s="35" t="inlineStr">
+      <c r="D167" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -5920,7 +5915,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D168" s="35" t="inlineStr">
+      <c r="D168" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -5955,7 +5950,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D169" s="35" t="inlineStr">
+      <c r="D169" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -5990,7 +5985,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D170" s="35" t="inlineStr">
+      <c r="D170" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -6025,7 +6020,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D171" s="35" t="inlineStr">
+      <c r="D171" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -6060,7 +6055,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D172" s="35" t="inlineStr">
+      <c r="D172" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -6095,7 +6090,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D173" s="35" t="inlineStr">
+      <c r="D173" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -6130,7 +6125,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D174" s="35" t="inlineStr">
+      <c r="D174" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
@@ -6166,7 +6161,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D175" s="35" t="inlineStr">
+      <c r="D175" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -6202,7 +6197,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D176" s="35" t="inlineStr">
+      <c r="D176" s="34" t="inlineStr">
         <is>
           <t>비금속</t>
         </is>
@@ -6238,7 +6233,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D177" s="35" t="inlineStr">
+      <c r="D177" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -6274,7 +6269,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D178" s="35" t="inlineStr">
+      <c r="D178" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -6309,7 +6304,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D179" s="35" t="inlineStr">
+      <c r="D179" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -6344,7 +6339,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D180" s="35" t="inlineStr">
+      <c r="D180" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
@@ -6379,7 +6374,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D181" s="35" t="inlineStr">
+      <c r="D181" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -6414,7 +6409,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D182" s="35" t="inlineStr">
+      <c r="D182" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -6449,7 +6444,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D183" s="35" t="inlineStr">
+      <c r="D183" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -6484,7 +6479,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D184" s="35" t="inlineStr">
+      <c r="D184" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -6519,7 +6514,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D185" s="35" t="inlineStr">
+      <c r="D185" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
@@ -6554,7 +6549,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D186" s="35" t="inlineStr">
+      <c r="D186" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
@@ -6589,7 +6584,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D187" s="35" t="inlineStr">
+      <c r="D187" s="34" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
@@ -6624,7 +6619,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D188" s="35" t="inlineStr">
+      <c r="D188" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
@@ -6660,7 +6655,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D189" s="35" t="inlineStr">
+      <c r="D189" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
@@ -6695,7 +6690,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D190" s="35" t="inlineStr">
+      <c r="D190" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
@@ -6731,7 +6726,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D191" s="35" t="inlineStr">
+      <c r="D191" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6766,7 +6761,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D192" s="35" t="inlineStr">
+      <c r="D192" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6801,7 +6796,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D193" s="35" t="inlineStr">
+      <c r="D193" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6836,7 +6831,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D194" s="35" t="inlineStr">
+      <c r="D194" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6871,7 +6866,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D195" s="35" t="inlineStr">
+      <c r="D195" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6906,7 +6901,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D196" s="35" t="inlineStr">
+      <c r="D196" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
@@ -6941,7 +6936,7 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="D197" s="35" t="inlineStr">
+      <c r="D197" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
@@ -6976,7 +6971,7 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="D198" s="35" t="inlineStr">
+      <c r="D198" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
@@ -7270,62 +7265,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>합산</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="42" t="inlineStr">
         <is>
           <t>기관</t>
         </is>
       </c>
-      <c r="G5" s="43" t="inlineStr">
+      <c r="G5" s="42" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="H5" s="43" t="inlineStr">
+      <c r="H5" s="42" t="inlineStr">
         <is>
           <t>공매도</t>
         </is>
       </c>
-      <c r="I5" s="43" t="inlineStr">
+      <c r="I5" s="42" t="inlineStr">
         <is>
           <t>대차잔고</t>
         </is>
       </c>
-      <c r="J5" s="43" t="inlineStr">
+      <c r="J5" s="42" t="inlineStr">
         <is>
           <t>대차증감</t>
         </is>
       </c>
-      <c r="K5" s="43" t="inlineStr">
+      <c r="K5" s="42" t="inlineStr">
         <is>
           <t>월간등락(%)</t>
         </is>
       </c>
-      <c r="L5" s="43" t="inlineStr">
+      <c r="L5" s="42" t="inlineStr">
         <is>
           <t>신고가대비(%)</t>
         </is>
@@ -7342,36 +7337,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="43" t="n">
         <v>5656</v>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="43" t="n">
         <v>4711</v>
       </c>
-      <c r="F6" s="44" t="n">
+      <c r="F6" s="43" t="n">
         <v>945</v>
       </c>
-      <c r="G6" s="45" t="n">
+      <c r="G6" s="44" t="n">
         <v>-6515</v>
       </c>
-      <c r="H6" s="46" t="n">
+      <c r="H6" s="45" t="n">
         <v>1478.7</v>
       </c>
-      <c r="I6" s="46" t="n">
+      <c r="I6" s="45" t="n">
         <v>4245.9</v>
       </c>
-      <c r="J6" s="47" t="n">
+      <c r="J6" s="46" t="n">
         <v>1211</v>
       </c>
-      <c r="K6" s="48" t="n">
+      <c r="K6" s="47" t="n">
         <v>27.56</v>
       </c>
-      <c r="L6" s="49" t="n">
+      <c r="L6" s="48" t="n">
         <v>-9.789999999999999</v>
       </c>
     </row>
@@ -7386,36 +7381,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="43" t="n">
         <v>346</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="43" t="n">
         <v>136</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="43" t="n">
         <v>209</v>
       </c>
-      <c r="G7" s="45" t="n">
+      <c r="G7" s="44" t="n">
         <v>-340</v>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="45" t="n">
         <v>288.9</v>
       </c>
-      <c r="I7" s="46" t="n">
+      <c r="I7" s="45" t="n">
         <v>618.8</v>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="46" t="n">
         <v>231.1</v>
       </c>
-      <c r="K7" s="48" t="n">
+      <c r="K7" s="47" t="n">
         <v>64.84</v>
       </c>
-      <c r="L7" s="50" t="n">
+      <c r="L7" s="49" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -7430,36 +7425,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="D8" s="44" t="n">
         <v>-10</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="44" t="n">
         <v>-26</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="43" t="n">
         <v>16</v>
       </c>
-      <c r="G8" s="44" t="n">
+      <c r="G8" s="43" t="n">
         <v>21</v>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="45" t="n">
         <v>34.6</v>
       </c>
-      <c r="I8" s="46" t="n">
+      <c r="I8" s="45" t="n">
         <v>70.5</v>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="46" t="n">
         <v>22.4</v>
       </c>
-      <c r="K8" s="48" t="n">
+      <c r="K8" s="47" t="n">
         <v>45.89</v>
       </c>
-      <c r="L8" s="49" t="n">
+      <c r="L8" s="48" t="n">
         <v>-7.86</v>
       </c>
     </row>
@@ -7474,36 +7469,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="D9" s="44" t="n">
         <v>-242</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="44" t="n">
         <v>-887</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="43" t="n">
         <v>644</v>
       </c>
-      <c r="G9" s="45" t="n">
+      <c r="G9" s="44" t="n">
         <v>-647</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="45" t="n">
         <v>683.2</v>
       </c>
-      <c r="I9" s="46" t="n">
+      <c r="I9" s="45" t="n">
         <v>2602.9</v>
       </c>
-      <c r="J9" s="51" t="n">
+      <c r="J9" s="50" t="n">
         <v>-114.8</v>
       </c>
-      <c r="K9" s="48" t="n">
+      <c r="K9" s="47" t="n">
         <v>10.95</v>
       </c>
-      <c r="L9" s="50" t="n">
+      <c r="L9" s="49" t="n">
         <v>-0.41</v>
       </c>
     </row>
@@ -7518,36 +7513,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D10" s="44" t="n">
+      <c r="D10" s="43" t="n">
         <v>2215</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="43" t="n">
         <v>1600</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="43" t="n">
         <v>615</v>
       </c>
-      <c r="G10" s="45" t="n">
+      <c r="G10" s="44" t="n">
         <v>-3292</v>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="H10" s="45" t="n">
         <v>338.2</v>
       </c>
-      <c r="I10" s="46" t="n">
+      <c r="I10" s="45" t="n">
         <v>3203.8</v>
       </c>
-      <c r="J10" s="51" t="n">
+      <c r="J10" s="50" t="n">
         <v>-198.3</v>
       </c>
-      <c r="K10" s="48" t="n">
+      <c r="K10" s="47" t="n">
         <v>11.72</v>
       </c>
-      <c r="L10" s="49" t="n">
+      <c r="L10" s="48" t="n">
         <v>-7.08</v>
       </c>
     </row>
@@ -7562,36 +7557,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="43" t="n">
         <v>352</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="44" t="n">
         <v>-255</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="43" t="n">
         <v>607</v>
       </c>
-      <c r="G11" s="45" t="n">
+      <c r="G11" s="44" t="n">
         <v>-333</v>
       </c>
-      <c r="H11" s="46" t="n">
+      <c r="H11" s="45" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="I11" s="46" t="n">
+      <c r="I11" s="45" t="n">
         <v>225.8</v>
       </c>
-      <c r="J11" s="47" t="n">
+      <c r="J11" s="46" t="n">
         <v>48.5</v>
       </c>
-      <c r="K11" s="48" t="n">
+      <c r="K11" s="47" t="n">
         <v>40.19</v>
       </c>
-      <c r="L11" s="52" t="n">
+      <c r="L11" s="51" t="n">
         <v>-3.73</v>
       </c>
     </row>
@@ -7606,36 +7601,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D12" s="44" t="n">
         <v>-2</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="44" t="n">
         <v>-2</v>
       </c>
-      <c r="F12" s="53" t="n">
+      <c r="F12" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="53" t="n">
+      <c r="G12" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="H12" s="45" t="n">
         <v>0.9</v>
       </c>
-      <c r="I12" s="46" t="n">
+      <c r="I12" s="45" t="n">
         <v>9.1</v>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="46" t="n">
         <v>3.5</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K12" s="47" t="n">
         <v>76.27</v>
       </c>
-      <c r="L12" s="52" t="n">
+      <c r="L12" s="51" t="n">
         <v>-4.08</v>
       </c>
     </row>
@@ -7650,36 +7645,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D13" s="44" t="n">
+      <c r="D13" s="43" t="n">
         <v>88</v>
       </c>
-      <c r="E13" s="45" t="n">
+      <c r="E13" s="44" t="n">
         <v>-125</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="43" t="n">
         <v>213</v>
       </c>
-      <c r="G13" s="45" t="n">
+      <c r="G13" s="44" t="n">
         <v>-84</v>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="H13" s="45" t="n">
         <v>429.2</v>
       </c>
-      <c r="I13" s="46" t="n">
+      <c r="I13" s="45" t="n">
         <v>1272.8</v>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="46" t="n">
         <v>449.5</v>
       </c>
-      <c r="K13" s="48" t="n">
+      <c r="K13" s="47" t="n">
         <v>4.42</v>
       </c>
-      <c r="L13" s="49" t="n">
+      <c r="L13" s="48" t="n">
         <v>-7.5</v>
       </c>
     </row>
@@ -7694,36 +7689,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D14" s="45" t="n">
+      <c r="D14" s="44" t="n">
         <v>-69</v>
       </c>
-      <c r="E14" s="45" t="n">
+      <c r="E14" s="44" t="n">
         <v>-50</v>
       </c>
-      <c r="F14" s="45" t="n">
+      <c r="F14" s="44" t="n">
         <v>-19</v>
       </c>
-      <c r="G14" s="44" t="n">
+      <c r="G14" s="43" t="n">
         <v>72</v>
       </c>
-      <c r="H14" s="46" t="n">
+      <c r="H14" s="45" t="n">
         <v>27.2</v>
       </c>
-      <c r="I14" s="46" t="n">
+      <c r="I14" s="45" t="n">
         <v>56.2</v>
       </c>
-      <c r="J14" s="47" t="n">
+      <c r="J14" s="46" t="n">
         <v>15.9</v>
       </c>
-      <c r="K14" s="48" t="n">
+      <c r="K14" s="47" t="n">
         <v>29.52</v>
       </c>
-      <c r="L14" s="52" t="n">
+      <c r="L14" s="51" t="n">
         <v>-2.16</v>
       </c>
     </row>
@@ -7738,36 +7733,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="43" t="n">
         <v>130</v>
       </c>
-      <c r="E15" s="45" t="n">
+      <c r="E15" s="44" t="n">
         <v>-345</v>
       </c>
-      <c r="F15" s="44" t="n">
+      <c r="F15" s="43" t="n">
         <v>475</v>
       </c>
-      <c r="G15" s="45" t="n">
+      <c r="G15" s="44" t="n">
         <v>-128</v>
       </c>
-      <c r="H15" s="46" t="n">
+      <c r="H15" s="45" t="n">
         <v>161</v>
       </c>
-      <c r="I15" s="46" t="n">
+      <c r="I15" s="45" t="n">
         <v>3140.9</v>
       </c>
-      <c r="J15" s="47" t="n">
+      <c r="J15" s="46" t="n">
         <v>1928</v>
       </c>
-      <c r="K15" s="48" t="n">
+      <c r="K15" s="47" t="n">
         <v>18.14</v>
       </c>
-      <c r="L15" s="49" t="n">
+      <c r="L15" s="48" t="n">
         <v>-5.53</v>
       </c>
     </row>
@@ -7782,36 +7777,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D16" s="44" t="n">
+      <c r="D16" s="43" t="n">
         <v>47</v>
       </c>
-      <c r="E16" s="45" t="n">
+      <c r="E16" s="44" t="n">
         <v>-153</v>
       </c>
-      <c r="F16" s="44" t="n">
+      <c r="F16" s="43" t="n">
         <v>200</v>
       </c>
-      <c r="G16" s="45" t="n">
+      <c r="G16" s="44" t="n">
         <v>-48</v>
       </c>
-      <c r="H16" s="46" t="n">
+      <c r="H16" s="45" t="n">
         <v>16.9</v>
       </c>
-      <c r="I16" s="46" t="n">
+      <c r="I16" s="45" t="n">
         <v>471.2</v>
       </c>
-      <c r="J16" s="47" t="n">
+      <c r="J16" s="46" t="n">
         <v>169.8</v>
       </c>
-      <c r="K16" s="48" t="n">
+      <c r="K16" s="47" t="n">
         <v>37.21</v>
       </c>
-      <c r="L16" s="52" t="n">
+      <c r="L16" s="51" t="n">
         <v>-2.5</v>
       </c>
     </row>
@@ -7826,36 +7821,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D17" s="44" t="n">
+      <c r="D17" s="43" t="n">
         <v>127</v>
       </c>
-      <c r="E17" s="44" t="n">
+      <c r="E17" s="43" t="n">
         <v>78</v>
       </c>
-      <c r="F17" s="44" t="n">
+      <c r="F17" s="43" t="n">
         <v>49</v>
       </c>
-      <c r="G17" s="45" t="n">
+      <c r="G17" s="44" t="n">
         <v>-126</v>
       </c>
-      <c r="H17" s="46" t="n">
+      <c r="H17" s="45" t="n">
         <v>113.9</v>
       </c>
-      <c r="I17" s="46" t="n">
+      <c r="I17" s="45" t="n">
         <v>649.5</v>
       </c>
-      <c r="J17" s="47" t="n">
+      <c r="J17" s="46" t="n">
         <v>20.7</v>
       </c>
-      <c r="K17" s="48" t="n">
+      <c r="K17" s="47" t="n">
         <v>3.98</v>
       </c>
-      <c r="L17" s="52" t="n">
+      <c r="L17" s="51" t="n">
         <v>-2.12</v>
       </c>
     </row>
@@ -7870,36 +7865,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="D18" s="45" t="n">
+      <c r="D18" s="44" t="n">
         <v>-4</v>
       </c>
-      <c r="E18" s="45" t="n">
+      <c r="E18" s="44" t="n">
         <v>-5</v>
       </c>
-      <c r="F18" s="44" t="n">
+      <c r="F18" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="44" t="n">
+      <c r="G18" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="46" t="n">
+      <c r="H18" s="45" t="n">
         <v>1.1</v>
       </c>
-      <c r="I18" s="46" t="n">
+      <c r="I18" s="45" t="n">
         <v>7.2</v>
       </c>
-      <c r="J18" s="51" t="n">
+      <c r="J18" s="50" t="n">
         <v>-0.4</v>
       </c>
-      <c r="K18" s="48" t="n">
+      <c r="K18" s="47" t="n">
         <v>7.35</v>
       </c>
-      <c r="L18" s="49" t="n">
+      <c r="L18" s="48" t="n">
         <v>-7.53</v>
       </c>
     </row>
@@ -7914,36 +7909,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="D19" s="44" t="n">
+      <c r="D19" s="43" t="n">
         <v>86</v>
       </c>
-      <c r="E19" s="45" t="n">
+      <c r="E19" s="44" t="n">
         <v>-1</v>
       </c>
-      <c r="F19" s="44" t="n">
+      <c r="F19" s="43" t="n">
         <v>87</v>
       </c>
-      <c r="G19" s="45" t="n">
+      <c r="G19" s="44" t="n">
         <v>-130</v>
       </c>
-      <c r="H19" s="46" t="n">
+      <c r="H19" s="45" t="n">
         <v>56.9</v>
       </c>
-      <c r="I19" s="46" t="n">
+      <c r="I19" s="45" t="n">
         <v>499</v>
       </c>
-      <c r="J19" s="47" t="n">
+      <c r="J19" s="46" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="K19" s="48" t="n">
+      <c r="K19" s="47" t="n">
         <v>4.32</v>
       </c>
-      <c r="L19" s="52" t="n">
+      <c r="L19" s="51" t="n">
         <v>-4.55</v>
       </c>
     </row>
@@ -7958,36 +7953,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="D20" s="44" t="n">
+      <c r="D20" s="43" t="n">
         <v>71</v>
       </c>
-      <c r="E20" s="44" t="n">
+      <c r="E20" s="43" t="n">
         <v>36</v>
       </c>
-      <c r="F20" s="44" t="n">
+      <c r="F20" s="43" t="n">
         <v>35</v>
       </c>
-      <c r="G20" s="45" t="n">
+      <c r="G20" s="44" t="n">
         <v>-66</v>
       </c>
-      <c r="H20" s="46" t="n">
+      <c r="H20" s="45" t="n">
         <v>61.9</v>
       </c>
-      <c r="I20" s="46" t="n">
+      <c r="I20" s="45" t="n">
         <v>715.3</v>
       </c>
-      <c r="J20" s="47" t="n">
+      <c r="J20" s="46" t="n">
         <v>79.5</v>
       </c>
-      <c r="K20" s="48" t="n">
+      <c r="K20" s="47" t="n">
         <v>10.78</v>
       </c>
-      <c r="L20" s="49" t="n">
+      <c r="L20" s="48" t="n">
         <v>-9.359999999999999</v>
       </c>
     </row>
@@ -8002,36 +7997,36 @@
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D21" s="44" t="n">
+      <c r="D21" s="43" t="n">
         <v>26</v>
       </c>
-      <c r="E21" s="45" t="n">
+      <c r="E21" s="44" t="n">
         <v>-10</v>
       </c>
-      <c r="F21" s="44" t="n">
+      <c r="F21" s="43" t="n">
         <v>36</v>
       </c>
-      <c r="G21" s="45" t="n">
+      <c r="G21" s="44" t="n">
         <v>-25</v>
       </c>
-      <c r="H21" s="46" t="n">
+      <c r="H21" s="45" t="n">
         <v>13.1</v>
       </c>
-      <c r="I21" s="46" t="n">
+      <c r="I21" s="45" t="n">
         <v>215.2</v>
       </c>
-      <c r="J21" s="47" t="n">
+      <c r="J21" s="46" t="n">
         <v>10.8</v>
       </c>
-      <c r="K21" s="48" t="n">
+      <c r="K21" s="47" t="n">
         <v>8.44</v>
       </c>
-      <c r="L21" s="49" t="n">
+      <c r="L21" s="48" t="n">
         <v>-6.44</v>
       </c>
     </row>
@@ -8046,36 +8041,36 @@
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D22" s="44" t="n">
+      <c r="D22" s="43" t="n">
         <v>114</v>
       </c>
-      <c r="E22" s="44" t="n">
+      <c r="E22" s="43" t="n">
         <v>21</v>
       </c>
-      <c r="F22" s="44" t="n">
+      <c r="F22" s="43" t="n">
         <v>93</v>
       </c>
-      <c r="G22" s="45" t="n">
+      <c r="G22" s="44" t="n">
         <v>-110</v>
       </c>
-      <c r="H22" s="46" t="n">
+      <c r="H22" s="45" t="n">
         <v>7.2</v>
       </c>
-      <c r="I22" s="46" t="n">
+      <c r="I22" s="45" t="n">
         <v>39.4</v>
       </c>
-      <c r="J22" s="47" t="n">
+      <c r="J22" s="46" t="n">
         <v>5.8</v>
       </c>
-      <c r="K22" s="48" t="n">
+      <c r="K22" s="47" t="n">
         <v>25.06</v>
       </c>
-      <c r="L22" s="52" t="n">
+      <c r="L22" s="51" t="n">
         <v>-2.71</v>
       </c>
     </row>
@@ -8153,7 +8148,7 @@
           <t>F1 외국인</t>
         </is>
       </c>
-      <c r="E3" s="54" t="inlineStr">
+      <c r="E3" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -8163,111 +8158,111 @@
           <t>F2 기관계</t>
         </is>
       </c>
-      <c r="N3" s="54" t="inlineStr">
+      <c r="N3" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="E4" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J4" s="55" t="inlineStr">
+      <c r="J4" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N4" s="56" t="inlineStr">
+      <c r="N4" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="43" t="inlineStr">
+      <c r="G5" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H5" s="43" t="inlineStr">
+      <c r="H5" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J5" s="43" t="inlineStr">
+      <c r="J5" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K5" s="43" t="inlineStr">
+      <c r="K5" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L5" s="43" t="inlineStr">
+      <c r="L5" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M5" s="43" t="inlineStr">
+      <c r="M5" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N5" s="43" t="inlineStr">
+      <c r="N5" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O5" s="43" t="inlineStr">
+      <c r="O5" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P5" s="43" t="inlineStr">
+      <c r="P5" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q5" s="43" t="inlineStr">
+      <c r="Q5" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -8282,12 +8277,12 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D6" s="45" t="n">
+      <c r="D6" s="44" t="n">
         <v>3096</v>
       </c>
       <c r="E6" s="30" t="n">
@@ -8298,12 +8293,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H6" s="57" t="n">
+      <c r="H6" s="56" t="n">
         <v>-97751</v>
       </c>
       <c r="J6" s="30" t="n">
@@ -8314,12 +8309,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L6" s="35" t="inlineStr">
+      <c r="L6" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M6" s="45" t="n">
+      <c r="M6" s="44" t="n">
         <v>7111</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -8330,12 +8325,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P6" s="35" t="inlineStr">
+      <c r="P6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q6" s="57" t="n">
+      <c r="Q6" s="56" t="n">
         <v>-6142</v>
       </c>
     </row>
@@ -8348,12 +8343,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D7" s="45" t="n">
+      <c r="D7" s="44" t="n">
         <v>1579</v>
       </c>
       <c r="E7" s="30" t="n">
@@ -8364,12 +8359,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G7" s="35" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H7" s="57" t="n">
+      <c r="H7" s="56" t="n">
         <v>-35922</v>
       </c>
       <c r="J7" s="30" t="n">
@@ -8380,12 +8375,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L7" s="35" t="inlineStr">
+      <c r="L7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M7" s="45" t="n">
+      <c r="M7" s="44" t="n">
         <v>5633</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -8396,12 +8391,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="P7" s="35" t="inlineStr">
+      <c r="P7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q7" s="57" t="n">
+      <c r="Q7" s="56" t="n">
         <v>-1763</v>
       </c>
     </row>
@@ -8414,12 +8409,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="D8" s="44" t="n">
         <v>1337</v>
       </c>
       <c r="E8" s="30" t="n">
@@ -8430,12 +8425,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G8" s="35" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H8" s="57" t="n">
+      <c r="H8" s="56" t="n">
         <v>-10110</v>
       </c>
       <c r="J8" s="30" t="n">
@@ -8446,12 +8441,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L8" s="35" t="inlineStr">
+      <c r="L8" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M8" s="45" t="n">
+      <c r="M8" s="44" t="n">
         <v>4348</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -8462,12 +8457,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="P8" s="35" t="inlineStr">
+      <c r="P8" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="Q8" s="57" t="n">
+      <c r="Q8" s="56" t="n">
         <v>-1650</v>
       </c>
     </row>
@@ -8480,12 +8475,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="D9" s="44" t="n">
         <v>1267</v>
       </c>
       <c r="E9" s="30" t="n">
@@ -8496,12 +8491,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="G9" s="35" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H9" s="57" t="n">
+      <c r="H9" s="56" t="n">
         <v>-5245</v>
       </c>
       <c r="J9" s="30" t="n">
@@ -8512,12 +8507,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="L9" s="35" t="inlineStr">
+      <c r="L9" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M9" s="45" t="n">
+      <c r="M9" s="44" t="n">
         <v>3002</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -8528,12 +8523,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P9" s="58" t="inlineStr">
+      <c r="P9" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q9" s="57" t="n">
+      <c r="Q9" s="56" t="n">
         <v>-1485</v>
       </c>
     </row>
@@ -8546,12 +8541,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="C10" s="58" t="inlineStr">
+      <c r="C10" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D10" s="45" t="n">
+      <c r="D10" s="44" t="n">
         <v>1243</v>
       </c>
       <c r="E10" s="30" t="n">
@@ -8562,12 +8557,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="G10" s="35" t="inlineStr">
+      <c r="G10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H10" s="57" t="n">
+      <c r="H10" s="56" t="n">
         <v>-4581</v>
       </c>
       <c r="J10" s="30" t="n">
@@ -8578,12 +8573,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="L10" s="35" t="inlineStr">
+      <c r="L10" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M10" s="45" t="n">
+      <c r="M10" s="44" t="n">
         <v>2741</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -8594,12 +8589,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="P10" s="35" t="inlineStr">
+      <c r="P10" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q10" s="57" t="n">
+      <c r="Q10" s="56" t="n">
         <v>-1351</v>
       </c>
     </row>
@@ -8612,12 +8607,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D11" s="45" t="n">
+      <c r="D11" s="44" t="n">
         <v>1158</v>
       </c>
       <c r="E11" s="30" t="n">
@@ -8628,12 +8623,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G11" s="35" t="inlineStr">
+      <c r="G11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H11" s="57" t="n">
+      <c r="H11" s="56" t="n">
         <v>-4277</v>
       </c>
       <c r="J11" s="30" t="n">
@@ -8644,12 +8639,12 @@
           <t>삼성생명</t>
         </is>
       </c>
-      <c r="L11" s="35" t="inlineStr">
+      <c r="L11" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="M11" s="45" t="n">
+      <c r="M11" s="44" t="n">
         <v>2446</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -8660,12 +8655,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr">
+      <c r="P11" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q11" s="57" t="n">
+      <c r="Q11" s="56" t="n">
         <v>-1323</v>
       </c>
     </row>
@@ -8678,12 +8673,12 @@
           <t>HMM</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D12" s="44" t="n">
         <v>1103</v>
       </c>
       <c r="E12" s="30" t="n">
@@ -8694,12 +8689,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G12" s="35" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H12" s="57" t="n">
+      <c r="H12" s="56" t="n">
         <v>-3793</v>
       </c>
       <c r="J12" s="30" t="n">
@@ -8710,12 +8705,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="L12" s="35" t="inlineStr">
+      <c r="L12" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M12" s="45" t="n">
+      <c r="M12" s="44" t="n">
         <v>2337</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -8726,12 +8721,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q12" s="57" t="n">
+      <c r="Q12" s="56" t="n">
         <v>-1290</v>
       </c>
     </row>
@@ -8744,12 +8739,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D13" s="45" t="n">
+      <c r="D13" s="44" t="n">
         <v>938</v>
       </c>
       <c r="E13" s="30" t="n">
@@ -8760,12 +8755,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G13" s="35" t="inlineStr">
+      <c r="G13" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H13" s="57" t="n">
+      <c r="H13" s="56" t="n">
         <v>-3525</v>
       </c>
       <c r="J13" s="30" t="n">
@@ -8776,12 +8771,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="L13" s="35" t="inlineStr">
+      <c r="L13" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M13" s="45" t="n">
+      <c r="M13" s="44" t="n">
         <v>2184</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -8792,12 +8787,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="P13" s="35" t="inlineStr">
+      <c r="P13" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q13" s="57" t="n">
+      <c r="Q13" s="56" t="n">
         <v>-1288</v>
       </c>
     </row>
@@ -8810,12 +8805,12 @@
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D14" s="45" t="n">
+      <c r="D14" s="44" t="n">
         <v>873</v>
       </c>
       <c r="E14" s="30" t="n">
@@ -8826,12 +8821,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="G14" s="35" t="inlineStr">
+      <c r="G14" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H14" s="57" t="n">
+      <c r="H14" s="56" t="n">
         <v>-2628</v>
       </c>
       <c r="J14" s="30" t="n">
@@ -8842,12 +8837,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="L14" s="58" t="inlineStr">
+      <c r="L14" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M14" s="45" t="n">
+      <c r="M14" s="44" t="n">
         <v>2148</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -8858,12 +8853,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P14" s="35" t="inlineStr">
+      <c r="P14" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q14" s="57" t="n">
+      <c r="Q14" s="56" t="n">
         <v>-1142</v>
       </c>
     </row>
@@ -8876,12 +8871,12 @@
           <t>GS</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D15" s="45" t="n">
+      <c r="D15" s="44" t="n">
         <v>833</v>
       </c>
       <c r="E15" s="30" t="n">
@@ -8892,12 +8887,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="G15" s="35" t="inlineStr">
+      <c r="G15" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H15" s="57" t="n">
+      <c r="H15" s="56" t="n">
         <v>-2517</v>
       </c>
       <c r="J15" s="30" t="n">
@@ -8908,12 +8903,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L15" s="35" t="inlineStr">
+      <c r="L15" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M15" s="45" t="n">
+      <c r="M15" s="44" t="n">
         <v>1794</v>
       </c>
       <c r="N15" s="30" t="n">
@@ -8924,12 +8919,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P15" s="35" t="inlineStr">
+      <c r="P15" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q15" s="57" t="n">
+      <c r="Q15" s="56" t="n">
         <v>-1140</v>
       </c>
     </row>
@@ -8940,7 +8935,7 @@
           <t>F3 외인+기관</t>
         </is>
       </c>
-      <c r="E17" s="54" t="inlineStr">
+      <c r="E17" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -8950,111 +8945,111 @@
           <t>F4 개인</t>
         </is>
       </c>
-      <c r="N17" s="54" t="inlineStr">
+      <c r="N17" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="55" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E18" s="56" t="inlineStr">
+      <c r="E18" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J18" s="55" t="inlineStr">
+      <c r="J18" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N18" s="56" t="inlineStr">
+      <c r="N18" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D19" s="43" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E19" s="43" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F19" s="43" t="inlineStr">
+      <c r="F19" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G19" s="43" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H19" s="43" t="inlineStr">
+      <c r="H19" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J19" s="43" t="inlineStr">
+      <c r="J19" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K19" s="43" t="inlineStr">
+      <c r="K19" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L19" s="43" t="inlineStr">
+      <c r="L19" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M19" s="43" t="inlineStr">
+      <c r="M19" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N19" s="43" t="inlineStr">
+      <c r="N19" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O19" s="43" t="inlineStr">
+      <c r="O19" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P19" s="43" t="inlineStr">
+      <c r="P19" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q19" s="43" t="inlineStr">
+      <c r="Q19" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -9069,12 +9064,12 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D20" s="45" t="n">
+      <c r="D20" s="44" t="n">
         <v>4081</v>
       </c>
       <c r="E20" s="30" t="n">
@@ -9085,12 +9080,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G20" s="35" t="inlineStr">
+      <c r="G20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H20" s="57" t="n">
+      <c r="H20" s="56" t="n">
         <v>-97913</v>
       </c>
       <c r="J20" s="30" t="n">
@@ -9101,12 +9096,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L20" s="35" t="inlineStr">
+      <c r="L20" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M20" s="45" t="n">
+      <c r="M20" s="44" t="n">
         <v>29529</v>
       </c>
       <c r="N20" s="30" t="n">
@@ -9117,12 +9112,12 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="P20" s="35" t="inlineStr">
+      <c r="P20" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="Q20" s="57" t="n">
+      <c r="Q20" s="56" t="n">
         <v>-4828</v>
       </c>
     </row>
@@ -9135,12 +9130,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D21" s="45" t="n">
+      <c r="D21" s="44" t="n">
         <v>3174</v>
       </c>
       <c r="E21" s="30" t="n">
@@ -9151,12 +9146,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="G21" s="35" t="inlineStr">
+      <c r="G21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H21" s="57" t="n">
+      <c r="H21" s="56" t="n">
         <v>-42064</v>
       </c>
       <c r="J21" s="30" t="n">
@@ -9167,12 +9162,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="L21" s="35" t="inlineStr">
+      <c r="L21" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M21" s="45" t="n">
+      <c r="M21" s="44" t="n">
         <v>6002</v>
       </c>
       <c r="N21" s="30" t="n">
@@ -9183,12 +9178,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="P21" s="35" t="inlineStr">
+      <c r="P21" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="Q21" s="57" t="n">
+      <c r="Q21" s="56" t="n">
         <v>-3479</v>
       </c>
     </row>
@@ -9201,12 +9196,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D22" s="45" t="n">
+      <c r="D22" s="44" t="n">
         <v>2690</v>
       </c>
       <c r="E22" s="30" t="n">
@@ -9217,12 +9212,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="G22" s="35" t="inlineStr">
+      <c r="G22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H22" s="57" t="n">
+      <c r="H22" s="56" t="n">
         <v>-6596</v>
       </c>
       <c r="J22" s="30" t="n">
@@ -9233,12 +9228,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L22" s="35" t="inlineStr">
+      <c r="L22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M22" s="45" t="n">
+      <c r="M22" s="44" t="n">
         <v>4981</v>
       </c>
       <c r="N22" s="30" t="n">
@@ -9249,12 +9244,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="P22" s="35" t="inlineStr">
+      <c r="P22" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q22" s="57" t="n">
+      <c r="Q22" s="56" t="n">
         <v>-3149</v>
       </c>
     </row>
@@ -9267,12 +9262,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D23" s="45" t="n">
+      <c r="D23" s="44" t="n">
         <v>2315</v>
       </c>
       <c r="E23" s="30" t="n">
@@ -9283,12 +9278,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G23" s="35" t="inlineStr">
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H23" s="57" t="n">
+      <c r="H23" s="56" t="n">
         <v>-5290</v>
       </c>
       <c r="J23" s="30" t="n">
@@ -9299,12 +9294,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="L23" s="35" t="inlineStr">
+      <c r="L23" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M23" s="45" t="n">
+      <c r="M23" s="44" t="n">
         <v>4690</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -9315,12 +9310,12 @@
           <t>LG씨엔에스</t>
         </is>
       </c>
-      <c r="P23" s="35" t="inlineStr">
+      <c r="P23" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q23" s="57" t="n">
+      <c r="Q23" s="56" t="n">
         <v>-1939</v>
       </c>
     </row>
@@ -9333,12 +9328,12 @@
           <t>LG씨엔에스</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D24" s="45" t="n">
+      <c r="D24" s="44" t="n">
         <v>1964</v>
       </c>
       <c r="E24" s="30" t="n">
@@ -9349,12 +9344,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="G24" s="35" t="inlineStr">
+      <c r="G24" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H24" s="57" t="n">
+      <c r="H24" s="56" t="n">
         <v>-4708</v>
       </c>
       <c r="J24" s="30" t="n">
@@ -9365,12 +9360,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="L24" s="35" t="inlineStr">
+      <c r="L24" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M24" s="45" t="n">
+      <c r="M24" s="44" t="n">
         <v>4618</v>
       </c>
       <c r="N24" s="30" t="n">
@@ -9381,12 +9376,12 @@
           <t>HMM</t>
         </is>
       </c>
-      <c r="P24" s="35" t="inlineStr">
+      <c r="P24" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="Q24" s="57" t="n">
+      <c r="Q24" s="56" t="n">
         <v>-1861</v>
       </c>
     </row>
@@ -9399,12 +9394,12 @@
           <t>HMM</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D25" s="45" t="n">
+      <c r="D25" s="44" t="n">
         <v>1875</v>
       </c>
       <c r="E25" s="30" t="n">
@@ -9415,12 +9410,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G25" s="35" t="inlineStr">
+      <c r="G25" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H25" s="57" t="n">
+      <c r="H25" s="56" t="n">
         <v>-4667</v>
       </c>
       <c r="J25" s="30" t="n">
@@ -9431,12 +9426,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L25" s="35" t="inlineStr">
+      <c r="L25" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M25" s="45" t="n">
+      <c r="M25" s="44" t="n">
         <v>2980</v>
       </c>
       <c r="N25" s="30" t="n">
@@ -9447,12 +9442,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="P25" s="35" t="inlineStr">
+      <c r="P25" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q25" s="57" t="n">
+      <c r="Q25" s="56" t="n">
         <v>-1816</v>
       </c>
     </row>
@@ -9465,12 +9460,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D26" s="45" t="n">
+      <c r="D26" s="44" t="n">
         <v>1567</v>
       </c>
       <c r="E26" s="30" t="n">
@@ -9481,12 +9476,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="G26" s="35" t="inlineStr">
+      <c r="G26" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H26" s="57" t="n">
+      <c r="H26" s="56" t="n">
         <v>-2999</v>
       </c>
       <c r="J26" s="30" t="n">
@@ -9497,12 +9492,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="L26" s="35" t="inlineStr">
+      <c r="L26" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M26" s="45" t="n">
+      <c r="M26" s="44" t="n">
         <v>2537</v>
       </c>
       <c r="N26" s="30" t="n">
@@ -9513,12 +9508,12 @@
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="P26" s="35" t="inlineStr">
+      <c r="P26" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="Q26" s="57" t="n">
+      <c r="Q26" s="56" t="n">
         <v>-1552</v>
       </c>
     </row>
@@ -9531,12 +9526,12 @@
           <t>하이브</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="D27" s="45" t="n">
+      <c r="D27" s="44" t="n">
         <v>1130</v>
       </c>
       <c r="E27" s="30" t="n">
@@ -9547,12 +9542,12 @@
           <t>LG전자</t>
         </is>
       </c>
-      <c r="G27" s="35" t="inlineStr">
+      <c r="G27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H27" s="57" t="n">
+      <c r="H27" s="56" t="n">
         <v>-2581</v>
       </c>
       <c r="J27" s="30" t="n">
@@ -9563,12 +9558,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="L27" s="35" t="inlineStr">
+      <c r="L27" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M27" s="45" t="n">
+      <c r="M27" s="44" t="n">
         <v>1739</v>
       </c>
       <c r="N27" s="30" t="n">
@@ -9579,12 +9574,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="P27" s="35" t="inlineStr">
+      <c r="P27" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q27" s="57" t="n">
+      <c r="Q27" s="56" t="n">
         <v>-1175</v>
       </c>
     </row>
@@ -9597,12 +9592,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D28" s="45" t="n">
+      <c r="D28" s="44" t="n">
         <v>1052</v>
       </c>
       <c r="E28" s="30" t="n">
@@ -9613,12 +9608,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G28" s="35" t="inlineStr">
+      <c r="G28" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H28" s="57" t="n">
+      <c r="H28" s="56" t="n">
         <v>-1728</v>
       </c>
       <c r="J28" s="30" t="n">
@@ -9629,12 +9624,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="L28" s="58" t="inlineStr">
+      <c r="L28" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M28" s="45" t="n">
+      <c r="M28" s="44" t="n">
         <v>1732</v>
       </c>
       <c r="N28" s="30" t="n">
@@ -9645,12 +9640,12 @@
           <t>하이브</t>
         </is>
       </c>
-      <c r="P28" s="35" t="inlineStr">
+      <c r="P28" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="Q28" s="57" t="n">
+      <c r="Q28" s="56" t="n">
         <v>-1174</v>
       </c>
     </row>
@@ -9663,12 +9658,12 @@
           <t>삼성물산</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="D29" s="45" t="n">
+      <c r="D29" s="44" t="n">
         <v>914</v>
       </c>
       <c r="E29" s="30" t="n">
@@ -9679,12 +9674,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="G29" s="58" t="inlineStr">
+      <c r="G29" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H29" s="57" t="n">
+      <c r="H29" s="56" t="n">
         <v>-1712</v>
       </c>
       <c r="J29" s="30" t="n">
@@ -9695,12 +9690,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="L29" s="35" t="inlineStr">
+      <c r="L29" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M29" s="45" t="n">
+      <c r="M29" s="44" t="n">
         <v>1627</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -9711,12 +9706,12 @@
           <t>삼성물산</t>
         </is>
       </c>
-      <c r="P29" s="35" t="inlineStr">
+      <c r="P29" s="34" t="inlineStr">
         <is>
           <t>유통</t>
         </is>
       </c>
-      <c r="Q29" s="57" t="n">
+      <c r="Q29" s="56" t="n">
         <v>-885</v>
       </c>
     </row>
@@ -9727,7 +9722,7 @@
           <t>F5 금융투자</t>
         </is>
       </c>
-      <c r="E31" s="54" t="inlineStr">
+      <c r="E31" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -9737,111 +9732,111 @@
           <t>F6 투신(사모)</t>
         </is>
       </c>
-      <c r="N31" s="54" t="inlineStr">
+      <c r="N31" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="55" t="inlineStr">
+      <c r="A32" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E32" s="56" t="inlineStr">
+      <c r="E32" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J32" s="55" t="inlineStr">
+      <c r="J32" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N32" s="56" t="inlineStr">
+      <c r="N32" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B33" s="43" t="inlineStr">
+      <c r="B33" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C33" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
+      <c r="D33" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E33" s="43" t="inlineStr">
+      <c r="E33" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F33" s="43" t="inlineStr">
+      <c r="F33" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G33" s="43" t="inlineStr">
+      <c r="G33" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H33" s="43" t="inlineStr">
+      <c r="H33" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J33" s="43" t="inlineStr">
+      <c r="J33" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K33" s="43" t="inlineStr">
+      <c r="K33" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L33" s="43" t="inlineStr">
+      <c r="L33" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M33" s="43" t="inlineStr">
+      <c r="M33" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N33" s="43" t="inlineStr">
+      <c r="N33" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O33" s="43" t="inlineStr">
+      <c r="O33" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P33" s="43" t="inlineStr">
+      <c r="P33" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q33" s="43" t="inlineStr">
+      <c r="Q33" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -9856,12 +9851,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="C34" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D34" s="45" t="n">
+      <c r="D34" s="44" t="n">
         <v>3296</v>
       </c>
       <c r="E34" s="30" t="n">
@@ -9872,12 +9867,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="G34" s="35" t="inlineStr">
+      <c r="G34" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H34" s="57" t="n">
+      <c r="H34" s="56" t="n">
         <v>-1357</v>
       </c>
       <c r="J34" s="30" t="n">
@@ -9888,12 +9883,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="L34" s="35" t="inlineStr">
+      <c r="L34" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M34" s="45" t="n">
+      <c r="M34" s="44" t="n">
         <v>5943</v>
       </c>
       <c r="N34" s="30" t="n">
@@ -9904,12 +9899,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P34" s="35" t="inlineStr">
+      <c r="P34" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q34" s="57" t="n">
+      <c r="Q34" s="56" t="n">
         <v>-18725</v>
       </c>
     </row>
@@ -9922,12 +9917,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D35" s="45" t="n">
+      <c r="D35" s="44" t="n">
         <v>2704</v>
       </c>
       <c r="E35" s="30" t="n">
@@ -9938,12 +9933,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="G35" s="35" t="inlineStr">
+      <c r="G35" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H35" s="57" t="n">
+      <c r="H35" s="56" t="n">
         <v>-660</v>
       </c>
       <c r="J35" s="30" t="n">
@@ -9954,12 +9949,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L35" s="35" t="inlineStr">
+      <c r="L35" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M35" s="45" t="n">
+      <c r="M35" s="44" t="n">
         <v>3574</v>
       </c>
       <c r="N35" s="30" t="n">
@@ -9970,12 +9965,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P35" s="35" t="inlineStr">
+      <c r="P35" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q35" s="57" t="n">
+      <c r="Q35" s="56" t="n">
         <v>-3651</v>
       </c>
     </row>
@@ -9988,12 +9983,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C36" s="35" t="inlineStr">
+      <c r="C36" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D36" s="45" t="n">
+      <c r="D36" s="44" t="n">
         <v>1767</v>
       </c>
       <c r="E36" s="30" t="n">
@@ -10004,12 +9999,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="G36" s="35" t="inlineStr">
+      <c r="G36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H36" s="57" t="n">
+      <c r="H36" s="56" t="n">
         <v>-409</v>
       </c>
       <c r="J36" s="30" t="n">
@@ -10020,12 +10015,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="L36" s="35" t="inlineStr">
+      <c r="L36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M36" s="45" t="n">
+      <c r="M36" s="44" t="n">
         <v>1833</v>
       </c>
       <c r="N36" s="30" t="n">
@@ -10036,12 +10031,12 @@
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="P36" s="35" t="inlineStr">
+      <c r="P36" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q36" s="57" t="n">
+      <c r="Q36" s="56" t="n">
         <v>-1840</v>
       </c>
     </row>
@@ -10054,12 +10049,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C37" s="35" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D37" s="45" t="n">
+      <c r="D37" s="44" t="n">
         <v>1151</v>
       </c>
       <c r="E37" s="30" t="n">
@@ -10070,12 +10065,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="G37" s="35" t="inlineStr">
+      <c r="G37" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H37" s="57" t="n">
+      <c r="H37" s="56" t="n">
         <v>-392</v>
       </c>
       <c r="J37" s="30" t="n">
@@ -10086,12 +10081,12 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="L37" s="35" t="inlineStr">
+      <c r="L37" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M37" s="45" t="n">
+      <c r="M37" s="44" t="n">
         <v>1557</v>
       </c>
       <c r="N37" s="30" t="n">
@@ -10102,12 +10097,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="P37" s="35" t="inlineStr">
+      <c r="P37" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q37" s="57" t="n">
+      <c r="Q37" s="56" t="n">
         <v>-1705</v>
       </c>
     </row>
@@ -10120,12 +10115,12 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C38" s="35" t="inlineStr">
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D38" s="45" t="n">
+      <c r="D38" s="44" t="n">
         <v>1025</v>
       </c>
       <c r="E38" s="30" t="n">
@@ -10136,12 +10131,12 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="G38" s="35" t="inlineStr">
+      <c r="G38" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H38" s="57" t="n">
+      <c r="H38" s="56" t="n">
         <v>-337</v>
       </c>
       <c r="J38" s="30" t="n">
@@ -10152,12 +10147,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="L38" s="58" t="inlineStr">
+      <c r="L38" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M38" s="45" t="n">
+      <c r="M38" s="44" t="n">
         <v>1135</v>
       </c>
       <c r="N38" s="30" t="n">
@@ -10168,12 +10163,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P38" s="35" t="inlineStr">
+      <c r="P38" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q38" s="57" t="n">
+      <c r="Q38" s="56" t="n">
         <v>-1327</v>
       </c>
     </row>
@@ -10186,12 +10181,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C39" s="35" t="inlineStr">
+      <c r="C39" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D39" s="45" t="n">
+      <c r="D39" s="44" t="n">
         <v>833</v>
       </c>
       <c r="E39" s="30" t="n">
@@ -10202,12 +10197,12 @@
           <t>대한항공</t>
         </is>
       </c>
-      <c r="G39" s="35" t="inlineStr">
+      <c r="G39" s="34" t="inlineStr">
         <is>
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="H39" s="57" t="n">
+      <c r="H39" s="56" t="n">
         <v>-209</v>
       </c>
       <c r="J39" s="30" t="n">
@@ -10218,12 +10213,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="L39" s="35" t="inlineStr">
+      <c r="L39" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M39" s="45" t="n">
+      <c r="M39" s="44" t="n">
         <v>939</v>
       </c>
       <c r="N39" s="30" t="n">
@@ -10234,12 +10229,12 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="P39" s="35" t="inlineStr">
+      <c r="P39" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q39" s="57" t="n">
+      <c r="Q39" s="56" t="n">
         <v>-1321</v>
       </c>
     </row>
@@ -10252,12 +10247,12 @@
           <t>LG화학</t>
         </is>
       </c>
-      <c r="C40" s="35" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D40" s="45" t="n">
+      <c r="D40" s="44" t="n">
         <v>819</v>
       </c>
       <c r="E40" s="30" t="n">
@@ -10268,12 +10263,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="G40" s="35" t="inlineStr">
+      <c r="G40" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H40" s="57" t="n">
+      <c r="H40" s="56" t="n">
         <v>-205</v>
       </c>
       <c r="J40" s="30" t="n">
@@ -10284,12 +10279,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="L40" s="35" t="inlineStr">
+      <c r="L40" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M40" s="45" t="n">
+      <c r="M40" s="44" t="n">
         <v>928</v>
       </c>
       <c r="N40" s="30" t="n">
@@ -10300,12 +10295,12 @@
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="P40" s="35" t="inlineStr">
+      <c r="P40" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q40" s="57" t="n">
+      <c r="Q40" s="56" t="n">
         <v>-1189</v>
       </c>
     </row>
@@ -10318,12 +10313,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="C41" s="35" t="inlineStr">
+      <c r="C41" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D41" s="45" t="n">
+      <c r="D41" s="44" t="n">
         <v>765</v>
       </c>
       <c r="E41" s="30" t="n">
@@ -10334,12 +10329,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="G41" s="35" t="inlineStr">
+      <c r="G41" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H41" s="57" t="n">
+      <c r="H41" s="56" t="n">
         <v>-181</v>
       </c>
       <c r="J41" s="30" t="n">
@@ -10350,12 +10345,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L41" s="35" t="inlineStr">
+      <c r="L41" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M41" s="45" t="n">
+      <c r="M41" s="44" t="n">
         <v>885</v>
       </c>
       <c r="N41" s="30" t="n">
@@ -10366,12 +10361,12 @@
           <t>테스</t>
         </is>
       </c>
-      <c r="P41" s="35" t="inlineStr">
+      <c r="P41" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q41" s="57" t="n">
+      <c r="Q41" s="56" t="n">
         <v>-914</v>
       </c>
     </row>
@@ -10384,12 +10379,12 @@
           <t>HPSP</t>
         </is>
       </c>
-      <c r="C42" s="35" t="inlineStr">
+      <c r="C42" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D42" s="45" t="n">
+      <c r="D42" s="44" t="n">
         <v>719</v>
       </c>
       <c r="E42" s="30" t="n">
@@ -10400,12 +10395,12 @@
           <t>엘앤에프</t>
         </is>
       </c>
-      <c r="G42" s="35" t="inlineStr">
+      <c r="G42" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H42" s="57" t="n">
+      <c r="H42" s="56" t="n">
         <v>-150</v>
       </c>
       <c r="J42" s="30" t="n">
@@ -10416,12 +10411,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="L42" s="35" t="inlineStr">
+      <c r="L42" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="M42" s="45" t="n">
+      <c r="M42" s="44" t="n">
         <v>734</v>
       </c>
       <c r="N42" s="30" t="n">
@@ -10432,12 +10427,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="P42" s="35" t="inlineStr">
+      <c r="P42" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q42" s="57" t="n">
+      <c r="Q42" s="56" t="n">
         <v>-878</v>
       </c>
     </row>
@@ -10450,12 +10445,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="C43" s="58" t="inlineStr">
+      <c r="C43" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D43" s="45" t="n">
+      <c r="D43" s="44" t="n">
         <v>692</v>
       </c>
       <c r="E43" s="30" t="n">
@@ -10466,12 +10461,12 @@
           <t>엘앤씨바이오</t>
         </is>
       </c>
-      <c r="G43" s="35" t="inlineStr">
+      <c r="G43" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="H43" s="57" t="n">
+      <c r="H43" s="56" t="n">
         <v>-135</v>
       </c>
       <c r="J43" s="30" t="n">
@@ -10482,12 +10477,12 @@
           <t>대덕전자</t>
         </is>
       </c>
-      <c r="L43" s="35" t="inlineStr">
+      <c r="L43" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M43" s="45" t="n">
+      <c r="M43" s="44" t="n">
         <v>703</v>
       </c>
       <c r="N43" s="30" t="n">
@@ -10498,12 +10493,12 @@
           <t>DB하이텍</t>
         </is>
       </c>
-      <c r="P43" s="35" t="inlineStr">
+      <c r="P43" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q43" s="57" t="n">
+      <c r="Q43" s="56" t="n">
         <v>-862</v>
       </c>
     </row>
@@ -10514,7 +10509,7 @@
           <t>F7 연기금</t>
         </is>
       </c>
-      <c r="E45" s="54" t="inlineStr">
+      <c r="E45" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
@@ -10524,111 +10519,111 @@
           <t>F8 보험</t>
         </is>
       </c>
-      <c r="N45" s="54" t="inlineStr">
+      <c r="N45" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="55" t="inlineStr">
+      <c r="A46" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E46" s="56" t="inlineStr">
+      <c r="E46" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
-      <c r="J46" s="55" t="inlineStr">
+      <c r="J46" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="N46" s="56" t="inlineStr">
+      <c r="N46" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="43" t="inlineStr">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B47" s="43" t="inlineStr">
+      <c r="B47" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C47" s="43" t="inlineStr">
+      <c r="C47" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D47" s="43" t="inlineStr">
+      <c r="D47" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E47" s="43" t="inlineStr">
+      <c r="E47" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F47" s="43" t="inlineStr">
+      <c r="F47" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G47" s="43" t="inlineStr">
+      <c r="G47" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H47" s="43" t="inlineStr">
+      <c r="H47" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="J47" s="43" t="inlineStr">
+      <c r="J47" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="K47" s="43" t="inlineStr">
+      <c r="K47" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="L47" s="43" t="inlineStr">
+      <c r="L47" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="M47" s="43" t="inlineStr">
+      <c r="M47" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="N47" s="43" t="inlineStr">
+      <c r="N47" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O47" s="43" t="inlineStr">
+      <c r="O47" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P47" s="43" t="inlineStr">
+      <c r="P47" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q47" s="43" t="inlineStr">
+      <c r="Q47" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -10643,12 +10638,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C48" s="35" t="inlineStr">
+      <c r="C48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D48" s="45" t="n">
+      <c r="D48" s="44" t="n">
         <v>7808</v>
       </c>
       <c r="E48" s="30" t="n">
@@ -10659,12 +10654,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="G48" s="35" t="inlineStr">
+      <c r="G48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H48" s="57" t="n">
+      <c r="H48" s="56" t="n">
         <v>-3630</v>
       </c>
       <c r="J48" s="30" t="n">
@@ -10675,12 +10670,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="L48" s="35" t="inlineStr">
+      <c r="L48" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M48" s="45" t="n">
+      <c r="M48" s="44" t="n">
         <v>2440</v>
       </c>
       <c r="N48" s="30" t="n">
@@ -10691,12 +10686,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P48" s="58" t="inlineStr">
+      <c r="P48" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q48" s="57" t="n">
+      <c r="Q48" s="56" t="n">
         <v>-136</v>
       </c>
     </row>
@@ -10709,12 +10704,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C49" s="35" t="inlineStr">
+      <c r="C49" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D49" s="45" t="n">
+      <c r="D49" s="44" t="n">
         <v>3894</v>
       </c>
       <c r="E49" s="30" t="n">
@@ -10725,12 +10720,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G49" s="58" t="inlineStr">
+      <c r="G49" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H49" s="57" t="n">
+      <c r="H49" s="56" t="n">
         <v>-1405</v>
       </c>
       <c r="J49" s="30" t="n">
@@ -10741,12 +10736,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="L49" s="35" t="inlineStr">
+      <c r="L49" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M49" s="45" t="n">
+      <c r="M49" s="44" t="n">
         <v>1601</v>
       </c>
       <c r="N49" s="30" t="n">
@@ -10757,12 +10752,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="P49" s="35" t="inlineStr">
+      <c r="P49" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="Q49" s="57" t="n">
+      <c r="Q49" s="56" t="n">
         <v>-119</v>
       </c>
     </row>
@@ -10775,12 +10770,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C50" s="35" t="inlineStr">
+      <c r="C50" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D50" s="45" t="n">
+      <c r="D50" s="44" t="n">
         <v>2611</v>
       </c>
       <c r="E50" s="30" t="n">
@@ -10791,12 +10786,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="G50" s="35" t="inlineStr">
+      <c r="G50" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="H50" s="57" t="n">
+      <c r="H50" s="56" t="n">
         <v>-1203</v>
       </c>
       <c r="J50" s="30" t="n">
@@ -10807,12 +10802,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="L50" s="35" t="inlineStr">
+      <c r="L50" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M50" s="45" t="n">
+      <c r="M50" s="44" t="n">
         <v>489</v>
       </c>
       <c r="N50" s="30" t="n">
@@ -10823,12 +10818,12 @@
           <t>HD건설기계</t>
         </is>
       </c>
-      <c r="P50" s="35" t="inlineStr">
+      <c r="P50" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q50" s="57" t="n">
+      <c r="Q50" s="56" t="n">
         <v>-113</v>
       </c>
     </row>
@@ -10841,12 +10836,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="C51" s="35" t="inlineStr">
+      <c r="C51" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D51" s="45" t="n">
+      <c r="D51" s="44" t="n">
         <v>2522</v>
       </c>
       <c r="E51" s="30" t="n">
@@ -10857,12 +10852,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="G51" s="35" t="inlineStr">
+      <c r="G51" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H51" s="57" t="n">
+      <c r="H51" s="56" t="n">
         <v>-1148</v>
       </c>
       <c r="J51" s="30" t="n">
@@ -10873,12 +10868,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="L51" s="35" t="inlineStr">
+      <c r="L51" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M51" s="45" t="n">
+      <c r="M51" s="44" t="n">
         <v>411</v>
       </c>
       <c r="N51" s="30" t="n">
@@ -10889,12 +10884,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P51" s="35" t="inlineStr">
+      <c r="P51" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q51" s="57" t="n">
+      <c r="Q51" s="56" t="n">
         <v>-97</v>
       </c>
     </row>
@@ -10907,12 +10902,12 @@
           <t>삼성생명</t>
         </is>
       </c>
-      <c r="C52" s="35" t="inlineStr">
+      <c r="C52" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="D52" s="45" t="n">
+      <c r="D52" s="44" t="n">
         <v>1705</v>
       </c>
       <c r="E52" s="30" t="n">
@@ -10923,12 +10918,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="G52" s="35" t="inlineStr">
+      <c r="G52" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="H52" s="57" t="n">
+      <c r="H52" s="56" t="n">
         <v>-1059</v>
       </c>
       <c r="J52" s="30" t="n">
@@ -10939,12 +10934,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="L52" s="35" t="inlineStr">
+      <c r="L52" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M52" s="45" t="n">
+      <c r="M52" s="44" t="n">
         <v>400</v>
       </c>
       <c r="N52" s="30" t="n">
@@ -10955,12 +10950,12 @@
           <t>현대건설</t>
         </is>
       </c>
-      <c r="P52" s="35" t="inlineStr">
+      <c r="P52" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="Q52" s="57" t="n">
+      <c r="Q52" s="56" t="n">
         <v>-74</v>
       </c>
     </row>
@@ -10973,12 +10968,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="C53" s="35" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="D53" s="45" t="n">
+      <c r="D53" s="44" t="n">
         <v>1518</v>
       </c>
       <c r="E53" s="30" t="n">
@@ -10989,12 +10984,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G53" s="58" t="inlineStr">
+      <c r="G53" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H53" s="57" t="n">
+      <c r="H53" s="56" t="n">
         <v>-972</v>
       </c>
       <c r="J53" s="30" t="n">
@@ -11005,12 +11000,12 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="L53" s="35" t="inlineStr">
+      <c r="L53" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M53" s="45" t="n">
+      <c r="M53" s="44" t="n">
         <v>352</v>
       </c>
       <c r="N53" s="30" t="n">
@@ -11021,12 +11016,12 @@
           <t>NAVER</t>
         </is>
       </c>
-      <c r="P53" s="35" t="inlineStr">
+      <c r="P53" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="Q53" s="57" t="n">
+      <c r="Q53" s="56" t="n">
         <v>-70</v>
       </c>
     </row>
@@ -11039,12 +11034,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C54" s="35" t="inlineStr">
+      <c r="C54" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D54" s="45" t="n">
+      <c r="D54" s="44" t="n">
         <v>1406</v>
       </c>
       <c r="E54" s="30" t="n">
@@ -11055,12 +11050,12 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="G54" s="35" t="inlineStr">
+      <c r="G54" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H54" s="57" t="n">
+      <c r="H54" s="56" t="n">
         <v>-867</v>
       </c>
       <c r="J54" s="30" t="n">
@@ -11071,12 +11066,12 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="L54" s="35" t="inlineStr">
+      <c r="L54" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M54" s="45" t="n">
+      <c r="M54" s="44" t="n">
         <v>210</v>
       </c>
       <c r="N54" s="30" t="n">
@@ -11087,12 +11082,12 @@
           <t>DB손해보험</t>
         </is>
       </c>
-      <c r="P54" s="35" t="inlineStr">
+      <c r="P54" s="34" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="Q54" s="57" t="n">
+      <c r="Q54" s="56" t="n">
         <v>-56</v>
       </c>
     </row>
@@ -11105,12 +11100,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="C55" s="35" t="inlineStr">
+      <c r="C55" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D55" s="45" t="n">
+      <c r="D55" s="44" t="n">
         <v>1119</v>
       </c>
       <c r="E55" s="30" t="n">
@@ -11121,12 +11116,12 @@
           <t>두산</t>
         </is>
       </c>
-      <c r="G55" s="35" t="inlineStr">
+      <c r="G55" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H55" s="57" t="n">
+      <c r="H55" s="56" t="n">
         <v>-851</v>
       </c>
       <c r="J55" s="30" t="n">
@@ -11137,12 +11132,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="L55" s="35" t="inlineStr">
+      <c r="L55" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="M55" s="45" t="n">
+      <c r="M55" s="44" t="n">
         <v>188</v>
       </c>
       <c r="N55" s="30" t="n">
@@ -11153,12 +11148,12 @@
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="P55" s="35" t="inlineStr">
+      <c r="P55" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q55" s="57" t="n">
+      <c r="Q55" s="56" t="n">
         <v>-52</v>
       </c>
     </row>
@@ -11171,12 +11166,12 @@
           <t>LG씨엔에스</t>
         </is>
       </c>
-      <c r="C56" s="35" t="inlineStr">
+      <c r="C56" s="34" t="inlineStr">
         <is>
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="D56" s="45" t="n">
+      <c r="D56" s="44" t="n">
         <v>1021</v>
       </c>
       <c r="E56" s="30" t="n">
@@ -11187,12 +11182,12 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="G56" s="58" t="inlineStr">
+      <c r="G56" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H56" s="57" t="n">
+      <c r="H56" s="56" t="n">
         <v>-745</v>
       </c>
       <c r="J56" s="30" t="n">
@@ -11203,12 +11198,12 @@
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="L56" s="58" t="inlineStr">
+      <c r="L56" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M56" s="45" t="n">
+      <c r="M56" s="44" t="n">
         <v>174</v>
       </c>
       <c r="N56" s="30" t="n">
@@ -11219,12 +11214,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="P56" s="58" t="inlineStr">
+      <c r="P56" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q56" s="57" t="n">
+      <c r="Q56" s="56" t="n">
         <v>-46</v>
       </c>
     </row>
@@ -11237,12 +11232,12 @@
           <t>우리금융지주</t>
         </is>
       </c>
-      <c r="C57" s="35" t="inlineStr">
+      <c r="C57" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D57" s="45" t="n">
+      <c r="D57" s="44" t="n">
         <v>836</v>
       </c>
       <c r="E57" s="30" t="n">
@@ -11253,12 +11248,12 @@
           <t>기아</t>
         </is>
       </c>
-      <c r="G57" s="58" t="inlineStr">
+      <c r="G57" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H57" s="57" t="n">
+      <c r="H57" s="56" t="n">
         <v>-713</v>
       </c>
       <c r="J57" s="30" t="n">
@@ -11269,12 +11264,12 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="L57" s="35" t="inlineStr">
+      <c r="L57" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M57" s="45" t="n">
+      <c r="M57" s="44" t="n">
         <v>167</v>
       </c>
       <c r="N57" s="30" t="n">
@@ -11285,12 +11280,12 @@
           <t>심텍</t>
         </is>
       </c>
-      <c r="P57" s="35" t="inlineStr">
+      <c r="P57" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q57" s="57" t="n">
+      <c r="Q57" s="56" t="n">
         <v>-41</v>
       </c>
     </row>
@@ -11301,61 +11296,61 @@
           <t>F9 기타법인</t>
         </is>
       </c>
-      <c r="E59" s="54" t="inlineStr">
+      <c r="E59" s="53" t="inlineStr">
         <is>
           <t>월간 누적 · 억원</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="55" t="inlineStr">
+      <c r="A60" s="54" t="inlineStr">
         <is>
           <t>순매수 상위</t>
         </is>
       </c>
-      <c r="E60" s="56" t="inlineStr">
+      <c r="E60" s="55" t="inlineStr">
         <is>
           <t>순매도 상위</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="43" t="inlineStr">
+      <c r="A61" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B61" s="43" t="inlineStr">
+      <c r="B61" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C61" s="43" t="inlineStr">
+      <c r="C61" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D61" s="43" t="inlineStr">
+      <c r="D61" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="E61" s="43" t="inlineStr">
+      <c r="E61" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="F61" s="43" t="inlineStr">
+      <c r="F61" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G61" s="43" t="inlineStr">
+      <c r="G61" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="H61" s="43" t="inlineStr">
+      <c r="H61" s="42" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -11370,12 +11365,12 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C62" s="35" t="inlineStr">
+      <c r="C62" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D62" s="45" t="n">
+      <c r="D62" s="44" t="n">
         <v>97536</v>
       </c>
       <c r="E62" s="30" t="n">
@@ -11386,12 +11381,12 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="G62" s="35" t="inlineStr">
+      <c r="G62" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H62" s="57" t="n">
+      <c r="H62" s="56" t="n">
         <v>-499</v>
       </c>
     </row>
@@ -11404,12 +11399,12 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C63" s="35" t="inlineStr">
+      <c r="C63" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D63" s="45" t="n">
+      <c r="D63" s="44" t="n">
         <v>12535</v>
       </c>
       <c r="E63" s="30" t="n">
@@ -11420,12 +11415,12 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="G63" s="35" t="inlineStr">
+      <c r="G63" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H63" s="57" t="n">
+      <c r="H63" s="56" t="n">
         <v>-222</v>
       </c>
     </row>
@@ -11438,12 +11433,12 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="C64" s="35" t="inlineStr">
+      <c r="C64" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="D64" s="45" t="n">
+      <c r="D64" s="44" t="n">
         <v>789</v>
       </c>
       <c r="E64" s="30" t="n">
@@ -11454,12 +11449,12 @@
           <t>S-Oil</t>
         </is>
       </c>
-      <c r="G64" s="35" t="inlineStr">
+      <c r="G64" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="H64" s="57" t="n">
+      <c r="H64" s="56" t="n">
         <v>-120</v>
       </c>
     </row>
@@ -11472,12 +11467,12 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="C65" s="35" t="inlineStr">
+      <c r="C65" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D65" s="45" t="n">
+      <c r="D65" s="44" t="n">
         <v>747</v>
       </c>
       <c r="E65" s="30" t="n">
@@ -11488,12 +11483,12 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="G65" s="58" t="inlineStr">
+      <c r="G65" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H65" s="57" t="n">
+      <c r="H65" s="56" t="n">
         <v>-84</v>
       </c>
     </row>
@@ -11506,12 +11501,12 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="C66" s="35" t="inlineStr">
+      <c r="C66" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D66" s="45" t="n">
+      <c r="D66" s="44" t="n">
         <v>594</v>
       </c>
       <c r="E66" s="30" t="n">
@@ -11522,12 +11517,12 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="G66" s="35" t="inlineStr">
+      <c r="G66" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="H66" s="57" t="n">
+      <c r="H66" s="56" t="n">
         <v>-73</v>
       </c>
     </row>
@@ -11540,12 +11535,12 @@
           <t>KT&amp;G</t>
         </is>
       </c>
-      <c r="C67" s="35" t="inlineStr">
+      <c r="C67" s="34" t="inlineStr">
         <is>
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D67" s="45" t="n">
+      <c r="D67" s="44" t="n">
         <v>530</v>
       </c>
       <c r="E67" s="30" t="n">
@@ -11556,12 +11551,12 @@
           <t>KB금융</t>
         </is>
       </c>
-      <c r="G67" s="35" t="inlineStr">
+      <c r="G67" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="H67" s="57" t="n">
+      <c r="H67" s="56" t="n">
         <v>-71</v>
       </c>
     </row>
@@ -11574,12 +11569,12 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C68" s="35" t="inlineStr">
+      <c r="C68" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D68" s="45" t="n">
+      <c r="D68" s="44" t="n">
         <v>309</v>
       </c>
       <c r="E68" s="30" t="n">
@@ -11590,12 +11585,12 @@
           <t>LG이노텍</t>
         </is>
       </c>
-      <c r="G68" s="35" t="inlineStr">
+      <c r="G68" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="H68" s="57" t="n">
+      <c r="H68" s="56" t="n">
         <v>-65</v>
       </c>
     </row>
@@ -11608,12 +11603,12 @@
           <t>한화오션</t>
         </is>
       </c>
-      <c r="C69" s="58" t="inlineStr">
+      <c r="C69" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D69" s="45" t="n">
+      <c r="D69" s="44" t="n">
         <v>178</v>
       </c>
       <c r="E69" s="30" t="n">
@@ -11624,8 +11619,8 @@
           <t>인텔리빅스</t>
         </is>
       </c>
-      <c r="G69" s="35" t="inlineStr"/>
-      <c r="H69" s="57" t="n">
+      <c r="G69" s="34" t="inlineStr"/>
+      <c r="H69" s="56" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -11638,12 +11633,12 @@
           <t>현대로템</t>
         </is>
       </c>
-      <c r="C70" s="58" t="inlineStr">
+      <c r="C70" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D70" s="45" t="n">
+      <c r="D70" s="44" t="n">
         <v>145</v>
       </c>
       <c r="E70" s="30" t="n">
@@ -11654,12 +11649,12 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="G70" s="58" t="inlineStr">
+      <c r="G70" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="H70" s="57" t="n">
+      <c r="H70" s="56" t="n">
         <v>-51</v>
       </c>
     </row>
@@ -11672,12 +11667,12 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C71" s="35" t="inlineStr">
+      <c r="C71" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D71" s="45" t="n">
+      <c r="D71" s="44" t="n">
         <v>123</v>
       </c>
       <c r="E71" s="30" t="n">
@@ -11688,18 +11683,18 @@
           <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
-      <c r="G71" s="35" t="inlineStr">
+      <c r="G71" s="34" t="inlineStr">
         <is>
           <t>금속</t>
         </is>
       </c>
-      <c r="H71" s="57" t="n">
+      <c r="H71" s="56" t="n">
         <v>-49</v>
       </c>
     </row>
     <row r="72"/>
     <row r="73" ht="31" customHeight="1" s="15">
-      <c r="A73" s="59" t="inlineStr">
+      <c r="A73" s="58" t="inlineStr">
         <is>
           <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드, 기타법인=일반법인(자사주 매입 등) (확정 병합분) · 외인+기관=합산 카드와 동일</t>
         </is>
@@ -11817,87 +11812,87 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>금액(억)</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="G4" s="43" t="inlineStr">
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="H4" s="43" t="inlineStr">
+      <c r="H4" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
+      <c r="J4" s="42" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="K4" s="43" t="inlineStr">
+      <c r="K4" s="42" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="L4" s="43" t="inlineStr">
+      <c r="L4" s="42" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
       </c>
-      <c r="N4" s="43" t="inlineStr">
+      <c r="N4" s="42" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="O4" s="43" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="P4" s="43" t="inlineStr">
+      <c r="P4" s="42" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="Q4" s="43" t="inlineStr">
+      <c r="Q4" s="42" t="inlineStr">
         <is>
           <t>증감(억)</t>
         </is>
       </c>
-      <c r="R4" s="43" t="inlineStr">
+      <c r="R4" s="42" t="inlineStr">
         <is>
           <t>대차잔고(억)</t>
         </is>
       </c>
-      <c r="S4" s="43" t="inlineStr">
+      <c r="S4" s="42" t="inlineStr">
         <is>
           <t>시총대비(%)</t>
         </is>
@@ -11912,15 +11907,15 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D5" s="60" t="n">
+      <c r="D5" s="59" t="n">
         <v>40944</v>
       </c>
-      <c r="E5" s="61" t="n">
+      <c r="E5" s="60" t="n">
         <v>0.37</v>
       </c>
       <c r="G5" s="30" t="n">
@@ -11931,18 +11926,18 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J5" s="45" t="n">
+      <c r="J5" s="44" t="n">
         <v>5404.1</v>
       </c>
-      <c r="K5" s="62" t="n">
+      <c r="K5" s="61" t="n">
         <v>38372</v>
       </c>
-      <c r="L5" s="61" t="n">
+      <c r="L5" s="60" t="n">
         <v>4.61</v>
       </c>
       <c r="N5" s="30" t="n">
@@ -11953,18 +11948,18 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="P5" s="35" t="inlineStr">
+      <c r="P5" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q5" s="57" t="n">
+      <c r="Q5" s="56" t="n">
         <v>-55472.7</v>
       </c>
-      <c r="R5" s="62" t="n">
+      <c r="R5" s="61" t="n">
         <v>170244.4</v>
       </c>
-      <c r="S5" s="61" t="n">
+      <c r="S5" s="60" t="n">
         <v>1.53</v>
       </c>
     </row>
@@ -11977,15 +11972,15 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="60" t="n">
+      <c r="D6" s="59" t="n">
         <v>24610</v>
       </c>
-      <c r="E6" s="61" t="n">
+      <c r="E6" s="60" t="n">
         <v>0.18</v>
       </c>
       <c r="G6" s="30" t="n">
@@ -11996,18 +11991,18 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="I6" s="35" t="inlineStr">
+      <c r="I6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J6" s="45" t="n">
+      <c r="J6" s="44" t="n">
         <v>4743.7</v>
       </c>
-      <c r="K6" s="62" t="n">
+      <c r="K6" s="61" t="n">
         <v>18351.7</v>
       </c>
-      <c r="L6" s="61" t="n">
+      <c r="L6" s="60" t="n">
         <v>4.23</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -12018,18 +12013,18 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="P6" s="35" t="inlineStr">
+      <c r="P6" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q6" s="57" t="n">
+      <c r="Q6" s="56" t="n">
         <v>-19909.9</v>
       </c>
-      <c r="R6" s="62" t="n">
+      <c r="R6" s="61" t="n">
         <v>179807.7</v>
       </c>
-      <c r="S6" s="61" t="n">
+      <c r="S6" s="60" t="n">
         <v>1.33</v>
       </c>
     </row>
@@ -12042,15 +12037,15 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D7" s="60" t="n">
+      <c r="D7" s="59" t="n">
         <v>9780</v>
       </c>
-      <c r="E7" s="61" t="n">
+      <c r="E7" s="60" t="n">
         <v>1.17</v>
       </c>
       <c r="G7" s="30" t="n">
@@ -12061,14 +12056,14 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="I7" s="35" t="inlineStr"/>
-      <c r="J7" s="45" t="n">
+      <c r="I7" s="34" t="inlineStr"/>
+      <c r="J7" s="44" t="n">
         <v>2073.1</v>
       </c>
-      <c r="K7" s="62" t="n">
+      <c r="K7" s="61" t="n">
         <v>26608.1</v>
       </c>
-      <c r="L7" s="61" t="n">
+      <c r="L7" s="60" t="n">
         <v>1.8</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -12079,18 +12074,18 @@
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="P7" s="58" t="inlineStr">
+      <c r="P7" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q7" s="57" t="n">
+      <c r="Q7" s="56" t="n">
         <v>-12466.1</v>
       </c>
-      <c r="R7" s="62" t="n">
+      <c r="R7" s="61" t="n">
         <v>15469.6</v>
       </c>
-      <c r="S7" s="61" t="n">
+      <c r="S7" s="60" t="n">
         <v>5.42</v>
       </c>
     </row>
@@ -12103,15 +12098,15 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D8" s="60" t="n">
+      <c r="D8" s="59" t="n">
         <v>7970</v>
       </c>
-      <c r="E8" s="61" t="n">
+      <c r="E8" s="60" t="n">
         <v>4.25</v>
       </c>
       <c r="G8" s="30" t="n">
@@ -12122,18 +12117,18 @@
           <t>SK이노베이션</t>
         </is>
       </c>
-      <c r="I8" s="35" t="inlineStr">
+      <c r="I8" s="34" t="inlineStr">
         <is>
           <t>화학</t>
         </is>
       </c>
-      <c r="J8" s="45" t="n">
+      <c r="J8" s="44" t="n">
         <v>2018.3</v>
       </c>
-      <c r="K8" s="62" t="n">
+      <c r="K8" s="61" t="n">
         <v>5792.3</v>
       </c>
-      <c r="L8" s="61" t="n">
+      <c r="L8" s="60" t="n">
         <v>2.64</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -12144,18 +12139,18 @@
           <t>한미반도체</t>
         </is>
       </c>
-      <c r="P8" s="35" t="inlineStr">
+      <c r="P8" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q8" s="57" t="n">
+      <c r="Q8" s="56" t="n">
         <v>-9612.1</v>
       </c>
-      <c r="R8" s="62" t="n">
+      <c r="R8" s="61" t="n">
         <v>39971.3</v>
       </c>
-      <c r="S8" s="61" t="n">
+      <c r="S8" s="60" t="n">
         <v>21.3</v>
       </c>
     </row>
@@ -12168,15 +12163,15 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D9" s="60" t="n">
+      <c r="D9" s="59" t="n">
         <v>7511</v>
       </c>
-      <c r="E9" s="61" t="n">
+      <c r="E9" s="60" t="n">
         <v>0.6</v>
       </c>
       <c r="G9" s="30" t="n">
@@ -12187,18 +12182,18 @@
           <t>에스원</t>
         </is>
       </c>
-      <c r="I9" s="35" t="inlineStr">
+      <c r="I9" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="J9" s="45" t="n">
+      <c r="J9" s="44" t="n">
         <v>1928</v>
       </c>
-      <c r="K9" s="62" t="n">
+      <c r="K9" s="61" t="n">
         <v>3140.9</v>
       </c>
-      <c r="L9" s="61" t="n">
+      <c r="L9" s="60" t="n">
         <v>8.58</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -12209,18 +12204,18 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="P9" s="35" t="inlineStr">
+      <c r="P9" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q9" s="57" t="n">
+      <c r="Q9" s="56" t="n">
         <v>-6743.2</v>
       </c>
-      <c r="R9" s="62" t="n">
+      <c r="R9" s="61" t="n">
         <v>29739</v>
       </c>
-      <c r="S9" s="61" t="n">
+      <c r="S9" s="60" t="n">
         <v>3.08</v>
       </c>
     </row>
@@ -12233,15 +12228,15 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D10" s="60" t="n">
+      <c r="D10" s="59" t="n">
         <v>6717</v>
       </c>
-      <c r="E10" s="61" t="n">
+      <c r="E10" s="60" t="n">
         <v>1.85</v>
       </c>
       <c r="G10" s="30" t="n">
@@ -12252,18 +12247,18 @@
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="I10" s="35" t="inlineStr">
+      <c r="I10" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J10" s="45" t="n">
+      <c r="J10" s="44" t="n">
         <v>1549.6</v>
       </c>
-      <c r="K10" s="62" t="n">
+      <c r="K10" s="61" t="n">
         <v>4021.3</v>
       </c>
-      <c r="L10" s="61" t="n">
+      <c r="L10" s="60" t="n">
         <v>9.6</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -12274,18 +12269,18 @@
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="P10" s="35" t="inlineStr">
+      <c r="P10" s="34" t="inlineStr">
         <is>
           <t>기타금융</t>
         </is>
       </c>
-      <c r="Q10" s="57" t="n">
+      <c r="Q10" s="56" t="n">
         <v>-5675.5</v>
       </c>
-      <c r="R10" s="62" t="n">
+      <c r="R10" s="61" t="n">
         <v>25760.9</v>
       </c>
-      <c r="S10" s="61" t="n">
+      <c r="S10" s="60" t="n">
         <v>2.05</v>
       </c>
     </row>
@@ -12298,15 +12293,15 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="60" t="n">
+      <c r="D11" s="59" t="n">
         <v>6482</v>
       </c>
-      <c r="E11" s="61" t="n">
+      <c r="E11" s="60" t="n">
         <v>1.5</v>
       </c>
       <c r="G11" s="30" t="n">
@@ -12317,18 +12312,18 @@
           <t>하이브</t>
         </is>
       </c>
-      <c r="I11" s="35" t="inlineStr">
+      <c r="I11" s="34" t="inlineStr">
         <is>
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="J11" s="45" t="n">
+      <c r="J11" s="44" t="n">
         <v>1230.9</v>
       </c>
-      <c r="K11" s="62" t="n">
+      <c r="K11" s="61" t="n">
         <v>4773.8</v>
       </c>
-      <c r="L11" s="61" t="n">
+      <c r="L11" s="60" t="n">
         <v>7.01</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -12339,14 +12334,14 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr"/>
-      <c r="Q11" s="57" t="n">
+      <c r="P11" s="34" t="inlineStr"/>
+      <c r="Q11" s="56" t="n">
         <v>-5011.3</v>
       </c>
-      <c r="R11" s="62" t="n">
+      <c r="R11" s="61" t="n">
         <v>24458</v>
       </c>
-      <c r="S11" s="61" t="n">
+      <c r="S11" s="60" t="n">
         <v>4.11</v>
       </c>
     </row>
@@ -12359,15 +12354,15 @@
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D12" s="60" t="n">
+      <c r="D12" s="59" t="n">
         <v>6180</v>
       </c>
-      <c r="E12" s="61" t="n">
+      <c r="E12" s="60" t="n">
         <v>0.64</v>
       </c>
       <c r="G12" s="30" t="n">
@@ -12378,18 +12373,18 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
+      <c r="I12" s="34" t="inlineStr">
         <is>
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="J12" s="45" t="n">
+      <c r="J12" s="44" t="n">
         <v>1211</v>
       </c>
-      <c r="K12" s="62" t="n">
+      <c r="K12" s="61" t="n">
         <v>4245.9</v>
       </c>
-      <c r="L12" s="61" t="n">
+      <c r="L12" s="60" t="n">
         <v>3.45</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -12400,18 +12395,18 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="Q12" s="57" t="n">
+      <c r="Q12" s="56" t="n">
         <v>-4803</v>
       </c>
-      <c r="R12" s="62" t="n">
+      <c r="R12" s="61" t="n">
         <v>15616.7</v>
       </c>
-      <c r="S12" s="61" t="n">
+      <c r="S12" s="60" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -12424,15 +12419,15 @@
           <t>주성엔지니어링</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D13" s="60" t="n">
+      <c r="D13" s="59" t="n">
         <v>5752</v>
       </c>
-      <c r="E13" s="61" t="n">
+      <c r="E13" s="60" t="n">
         <v>6.99</v>
       </c>
       <c r="G13" s="30" t="n">
@@ -12443,18 +12438,18 @@
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="I13" s="35" t="inlineStr">
+      <c r="I13" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="J13" s="45" t="n">
+      <c r="J13" s="44" t="n">
         <v>1189</v>
       </c>
-      <c r="K13" s="62" t="n">
+      <c r="K13" s="61" t="n">
         <v>13904.2</v>
       </c>
-      <c r="L13" s="61" t="n">
+      <c r="L13" s="60" t="n">
         <v>3.16</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -12465,18 +12460,18 @@
           <t>한국항공우주</t>
         </is>
       </c>
-      <c r="P13" s="58" t="inlineStr">
+      <c r="P13" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q13" s="57" t="n">
+      <c r="Q13" s="56" t="n">
         <v>-4517.5</v>
       </c>
-      <c r="R13" s="62" t="n">
+      <c r="R13" s="61" t="n">
         <v>10090.8</v>
       </c>
-      <c r="S13" s="61" t="n">
+      <c r="S13" s="60" t="n">
         <v>10.31</v>
       </c>
     </row>
@@ -12489,11 +12484,11 @@
           <t>현대차</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr"/>
-      <c r="D14" s="60" t="n">
+      <c r="C14" s="34" t="inlineStr"/>
+      <c r="D14" s="59" t="n">
         <v>5360</v>
       </c>
-      <c r="E14" s="61" t="n">
+      <c r="E14" s="60" t="n">
         <v>0.9</v>
       </c>
       <c r="G14" s="30" t="n">
@@ -12504,18 +12499,18 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="I14" s="35" t="inlineStr">
+      <c r="I14" s="34" t="inlineStr">
         <is>
           <t>제약</t>
         </is>
       </c>
-      <c r="J14" s="45" t="n">
+      <c r="J14" s="44" t="n">
         <v>1102.9</v>
       </c>
-      <c r="K14" s="62" t="n">
+      <c r="K14" s="61" t="n">
         <v>10385.8</v>
       </c>
-      <c r="L14" s="61" t="n">
+      <c r="L14" s="60" t="n">
         <v>1.64</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -12526,24 +12521,24 @@
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="P14" s="58" t="inlineStr">
+      <c r="P14" s="57" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q14" s="57" t="n">
+      <c r="Q14" s="56" t="n">
         <v>-3966.1</v>
       </c>
-      <c r="R14" s="62" t="n">
+      <c r="R14" s="61" t="n">
         <v>9075.5</v>
       </c>
-      <c r="S14" s="61" t="n">
+      <c r="S14" s="60" t="n">
         <v>2.32</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16" ht="31" customHeight="1" s="15">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>랭킹 유니버스(순매수 상위 30 등재 종목) 한정 · 대차 증감=전월말 대비 최신 잔고 · 시총대비(%)=공매도 누적 금액÷시가총액, 대차잔고÷시가총액(KIS 마스터 시총(주 1회 갱신))</t>
         </is>
@@ -12636,77 +12631,77 @@
       <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>외인</t>
         </is>
       </c>
-      <c r="G4" s="43" t="inlineStr">
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>기관(합)</t>
         </is>
       </c>
-      <c r="H4" s="43" t="inlineStr">
+      <c r="H4" s="42" t="inlineStr">
         <is>
           <t>외인+기관</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="42" t="inlineStr">
         <is>
           <t>금융투자</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
+      <c r="J4" s="42" t="inlineStr">
         <is>
           <t>투신(사모)</t>
         </is>
       </c>
-      <c r="K4" s="43" t="inlineStr">
+      <c r="K4" s="42" t="inlineStr">
         <is>
           <t>연기금</t>
         </is>
       </c>
-      <c r="L4" s="43" t="inlineStr">
+      <c r="L4" s="42" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="M4" s="43" t="inlineStr">
+      <c r="M4" s="42" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="N4" s="43" t="inlineStr">
+      <c r="N4" s="42" t="inlineStr">
         <is>
           <t>기타법인</t>
         </is>
       </c>
-      <c r="O4" s="43" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>신호</t>
         </is>
@@ -12718,43 +12713,43 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="B5" s="63" t="n">
+      <c r="B5" s="62" t="n">
         <v>-11.42</v>
       </c>
-      <c r="C5" s="63" t="n">
+      <c r="C5" s="62" t="n">
         <v>-4.19</v>
       </c>
-      <c r="D5" s="64" t="n">
+      <c r="D5" s="63" t="n">
         <v>0.29</v>
       </c>
-      <c r="E5" s="64" t="n">
+      <c r="E5" s="63" t="n">
         <v>4.67</v>
       </c>
-      <c r="F5" s="65" t="n">
+      <c r="F5" s="64" t="n">
         <v>-2729</v>
       </c>
-      <c r="G5" s="66" t="n">
+      <c r="G5" s="65" t="n">
         <v>7121</v>
       </c>
-      <c r="H5" s="66" t="n">
+      <c r="H5" s="65" t="n">
         <v>4393</v>
       </c>
-      <c r="I5" s="65" t="n">
+      <c r="I5" s="64" t="n">
         <v>-463</v>
       </c>
-      <c r="J5" s="66" t="n">
+      <c r="J5" s="65" t="n">
         <v>2111</v>
       </c>
-      <c r="K5" s="66" t="n">
+      <c r="K5" s="65" t="n">
         <v>4884</v>
       </c>
-      <c r="L5" s="66" t="n">
+      <c r="L5" s="65" t="n">
         <v>602</v>
       </c>
-      <c r="M5" s="65" t="n">
+      <c r="M5" s="64" t="n">
         <v>-5629</v>
       </c>
-      <c r="N5" s="66" t="n">
+      <c r="N5" s="65" t="n">
         <v>1236</v>
       </c>
       <c r="O5" s="30" t="inlineStr"/>
@@ -12765,43 +12760,43 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="B6" s="64" t="n">
+      <c r="B6" s="63" t="n">
         <v>6.65</v>
       </c>
-      <c r="C6" s="63" t="n">
+      <c r="C6" s="62" t="n">
         <v>-6.53</v>
       </c>
-      <c r="D6" s="63" t="n">
+      <c r="D6" s="62" t="n">
         <v>-1.52</v>
       </c>
-      <c r="E6" s="64" t="n">
+      <c r="E6" s="63" t="n">
         <v>3.13</v>
       </c>
-      <c r="F6" s="65" t="n">
+      <c r="F6" s="64" t="n">
         <v>-1598</v>
       </c>
-      <c r="G6" s="66" t="n">
+      <c r="G6" s="65" t="n">
         <v>2757</v>
       </c>
-      <c r="H6" s="66" t="n">
+      <c r="H6" s="65" t="n">
         <v>1159</v>
       </c>
-      <c r="I6" s="66" t="n">
+      <c r="I6" s="65" t="n">
         <v>404</v>
       </c>
-      <c r="J6" s="66" t="n">
+      <c r="J6" s="65" t="n">
         <v>1058</v>
       </c>
-      <c r="K6" s="66" t="n">
+      <c r="K6" s="65" t="n">
         <v>1089</v>
       </c>
-      <c r="L6" s="66" t="n">
+      <c r="L6" s="65" t="n">
         <v>201</v>
       </c>
-      <c r="M6" s="65" t="n">
+      <c r="M6" s="64" t="n">
         <v>-2040</v>
       </c>
-      <c r="N6" s="66" t="n">
+      <c r="N6" s="65" t="n">
         <v>881</v>
       </c>
       <c r="O6" s="30" t="inlineStr"/>
@@ -12812,46 +12807,46 @@
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="B7" s="63" t="n">
+      <c r="B7" s="62" t="n">
         <v>-46.24</v>
       </c>
-      <c r="C7" s="63" t="n">
+      <c r="C7" s="62" t="n">
         <v>-34</v>
       </c>
-      <c r="D7" s="63" t="n">
+      <c r="D7" s="62" t="n">
         <v>-4.32</v>
       </c>
-      <c r="E7" s="63" t="n">
+      <c r="E7" s="62" t="n">
         <v>-1.17</v>
       </c>
-      <c r="F7" s="65" t="n">
+      <c r="F7" s="64" t="n">
         <v>-50</v>
       </c>
-      <c r="G7" s="66" t="n">
+      <c r="G7" s="65" t="n">
         <v>1551</v>
       </c>
-      <c r="H7" s="66" t="n">
+      <c r="H7" s="65" t="n">
         <v>1501</v>
       </c>
-      <c r="I7" s="66" t="n">
+      <c r="I7" s="65" t="n">
         <v>68</v>
       </c>
-      <c r="J7" s="66" t="n">
+      <c r="J7" s="65" t="n">
         <v>723</v>
       </c>
-      <c r="K7" s="66" t="n">
+      <c r="K7" s="65" t="n">
         <v>666</v>
       </c>
-      <c r="L7" s="66" t="n">
+      <c r="L7" s="65" t="n">
         <v>86</v>
       </c>
-      <c r="M7" s="65" t="n">
+      <c r="M7" s="64" t="n">
         <v>-1517</v>
       </c>
-      <c r="N7" s="66" t="n">
+      <c r="N7" s="65" t="n">
         <v>16</v>
       </c>
-      <c r="O7" s="67" t="inlineStr">
+      <c r="O7" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -12863,43 +12858,43 @@
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="B8" s="64" t="n">
+      <c r="B8" s="63" t="n">
         <v>24.9</v>
       </c>
-      <c r="C8" s="63" t="n">
+      <c r="C8" s="62" t="n">
         <v>-0.31</v>
       </c>
-      <c r="D8" s="64" t="n">
+      <c r="D8" s="63" t="n">
         <v>43.99</v>
       </c>
-      <c r="E8" s="63" t="n">
+      <c r="E8" s="62" t="n">
         <v>-1.74</v>
       </c>
-      <c r="F8" s="66" t="n">
+      <c r="F8" s="65" t="n">
         <v>237</v>
       </c>
-      <c r="G8" s="66" t="n">
+      <c r="G8" s="65" t="n">
         <v>368</v>
       </c>
-      <c r="H8" s="66" t="n">
+      <c r="H8" s="65" t="n">
         <v>606</v>
       </c>
-      <c r="I8" s="66" t="n">
+      <c r="I8" s="65" t="n">
         <v>153</v>
       </c>
-      <c r="J8" s="66" t="n">
+      <c r="J8" s="65" t="n">
         <v>214</v>
       </c>
-      <c r="K8" s="65" t="n">
+      <c r="K8" s="64" t="n">
         <v>-8</v>
       </c>
-      <c r="L8" s="66" t="n">
+      <c r="L8" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="M8" s="65" t="n">
+      <c r="M8" s="64" t="n">
         <v>-582</v>
       </c>
-      <c r="N8" s="65" t="n">
+      <c r="N8" s="64" t="n">
         <v>-24</v>
       </c>
       <c r="O8" s="30" t="inlineStr"/>
@@ -12910,43 +12905,43 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="B9" s="64" t="n">
+      <c r="B9" s="63" t="n">
         <v>7.98</v>
       </c>
-      <c r="C9" s="63" t="n">
+      <c r="C9" s="62" t="n">
         <v>-2.81</v>
       </c>
-      <c r="D9" s="64" t="n">
+      <c r="D9" s="63" t="n">
         <v>6.42</v>
       </c>
-      <c r="E9" s="63" t="n">
+      <c r="E9" s="62" t="n">
         <v>-1.89</v>
       </c>
-      <c r="F9" s="66" t="n">
+      <c r="F9" s="65" t="n">
         <v>1486</v>
       </c>
-      <c r="G9" s="66" t="n">
+      <c r="G9" s="65" t="n">
         <v>609</v>
       </c>
-      <c r="H9" s="66" t="n">
+      <c r="H9" s="65" t="n">
         <v>2095</v>
       </c>
-      <c r="I9" s="65" t="n">
+      <c r="I9" s="64" t="n">
         <v>-15</v>
       </c>
-      <c r="J9" s="65" t="n">
+      <c r="J9" s="64" t="n">
         <v>-48</v>
       </c>
-      <c r="K9" s="66" t="n">
+      <c r="K9" s="65" t="n">
         <v>634</v>
       </c>
-      <c r="L9" s="66" t="n">
+      <c r="L9" s="65" t="n">
         <v>45</v>
       </c>
-      <c r="M9" s="65" t="n">
+      <c r="M9" s="64" t="n">
         <v>-3372</v>
       </c>
-      <c r="N9" s="66" t="n">
+      <c r="N9" s="65" t="n">
         <v>1277</v>
       </c>
       <c r="O9" s="30" t="inlineStr"/>
@@ -12957,46 +12952,46 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="B10" s="64" t="n">
+      <c r="B10" s="63" t="n">
         <v>49.15</v>
       </c>
-      <c r="C10" s="64" t="n">
+      <c r="C10" s="63" t="n">
         <v>15.19</v>
       </c>
-      <c r="D10" s="64" t="n">
+      <c r="D10" s="63" t="n">
         <v>5.56</v>
       </c>
-      <c r="E10" s="63" t="n">
+      <c r="E10" s="62" t="n">
         <v>-2.19</v>
       </c>
-      <c r="F10" s="65" t="n">
+      <c r="F10" s="64" t="n">
         <v>-3203</v>
       </c>
-      <c r="G10" s="66" t="n">
+      <c r="G10" s="65" t="n">
         <v>4160</v>
       </c>
-      <c r="H10" s="66" t="n">
+      <c r="H10" s="65" t="n">
         <v>956</v>
       </c>
-      <c r="I10" s="66" t="n">
+      <c r="I10" s="65" t="n">
         <v>592</v>
       </c>
-      <c r="J10" s="66" t="n">
+      <c r="J10" s="65" t="n">
         <v>1668</v>
       </c>
-      <c r="K10" s="66" t="n">
+      <c r="K10" s="65" t="n">
         <v>1876</v>
       </c>
-      <c r="L10" s="66" t="n">
+      <c r="L10" s="65" t="n">
         <v>30</v>
       </c>
-      <c r="M10" s="65" t="n">
+      <c r="M10" s="64" t="n">
         <v>-993</v>
       </c>
-      <c r="N10" s="66" t="n">
+      <c r="N10" s="65" t="n">
         <v>37</v>
       </c>
-      <c r="O10" s="55" t="inlineStr">
+      <c r="O10" s="54" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -13008,43 +13003,43 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="B11" s="64" t="n">
+      <c r="B11" s="63" t="n">
         <v>2.27</v>
       </c>
-      <c r="C11" s="63" t="n">
+      <c r="C11" s="62" t="n">
         <v>-18.31</v>
       </c>
-      <c r="D11" s="64" t="n">
+      <c r="D11" s="63" t="n">
         <v>12.4</v>
       </c>
-      <c r="E11" s="63" t="n">
+      <c r="E11" s="62" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F11" s="66" t="n">
+      <c r="F11" s="65" t="n">
         <v>4714</v>
       </c>
-      <c r="G11" s="66" t="n">
+      <c r="G11" s="65" t="n">
         <v>1629</v>
       </c>
-      <c r="H11" s="66" t="n">
+      <c r="H11" s="65" t="n">
         <v>6344</v>
       </c>
-      <c r="I11" s="66" t="n">
+      <c r="I11" s="65" t="n">
         <v>1203</v>
       </c>
-      <c r="J11" s="66" t="n">
+      <c r="J11" s="65" t="n">
         <v>324</v>
       </c>
-      <c r="K11" s="66" t="n">
+      <c r="K11" s="65" t="n">
         <v>108</v>
       </c>
-      <c r="L11" s="66" t="n">
+      <c r="L11" s="65" t="n">
         <v>10</v>
       </c>
-      <c r="M11" s="65" t="n">
+      <c r="M11" s="64" t="n">
         <v>-7416</v>
       </c>
-      <c r="N11" s="66" t="n">
+      <c r="N11" s="65" t="n">
         <v>1073</v>
       </c>
       <c r="O11" s="30" t="inlineStr"/>
@@ -13055,46 +13050,46 @@
           <t>전기·가스</t>
         </is>
       </c>
-      <c r="B12" s="63" t="n">
+      <c r="B12" s="62" t="n">
         <v>-32.83</v>
       </c>
-      <c r="C12" s="63" t="n">
+      <c r="C12" s="62" t="n">
         <v>-30.36</v>
       </c>
-      <c r="D12" s="63" t="n">
+      <c r="D12" s="62" t="n">
         <v>-9.789999999999999</v>
       </c>
-      <c r="E12" s="63" t="n">
+      <c r="E12" s="62" t="n">
         <v>-4.23</v>
       </c>
-      <c r="F12" s="66" t="n">
+      <c r="F12" s="65" t="n">
         <v>27</v>
       </c>
-      <c r="G12" s="66" t="n">
+      <c r="G12" s="65" t="n">
         <v>721</v>
       </c>
-      <c r="H12" s="66" t="n">
+      <c r="H12" s="65" t="n">
         <v>748</v>
       </c>
-      <c r="I12" s="66" t="n">
+      <c r="I12" s="65" t="n">
         <v>432</v>
       </c>
-      <c r="J12" s="66" t="n">
+      <c r="J12" s="65" t="n">
         <v>274</v>
       </c>
-      <c r="K12" s="65" t="n">
+      <c r="K12" s="64" t="n">
         <v>-30</v>
       </c>
-      <c r="L12" s="66" t="n">
+      <c r="L12" s="65" t="n">
         <v>50</v>
       </c>
-      <c r="M12" s="65" t="n">
+      <c r="M12" s="64" t="n">
         <v>-752</v>
       </c>
-      <c r="N12" s="66" t="n">
+      <c r="N12" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="O12" s="67" t="inlineStr">
+      <c r="O12" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13106,46 +13101,46 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="B13" s="63" t="n">
+      <c r="B13" s="62" t="n">
         <v>-15.64</v>
       </c>
-      <c r="C13" s="63" t="n">
+      <c r="C13" s="62" t="n">
         <v>-20.75</v>
       </c>
-      <c r="D13" s="63" t="n">
+      <c r="D13" s="62" t="n">
         <v>-2.58</v>
       </c>
-      <c r="E13" s="63" t="n">
+      <c r="E13" s="62" t="n">
         <v>-5.63</v>
       </c>
-      <c r="F13" s="66" t="n">
+      <c r="F13" s="65" t="n">
         <v>55</v>
       </c>
-      <c r="G13" s="66" t="n">
+      <c r="G13" s="65" t="n">
         <v>30</v>
       </c>
-      <c r="H13" s="66" t="n">
+      <c r="H13" s="65" t="n">
         <v>85</v>
       </c>
-      <c r="I13" s="66" t="n">
+      <c r="I13" s="65" t="n">
         <v>294</v>
       </c>
-      <c r="J13" s="65" t="n">
+      <c r="J13" s="64" t="n">
         <v>-185</v>
       </c>
-      <c r="K13" s="65" t="n">
+      <c r="K13" s="64" t="n">
         <v>-46</v>
       </c>
-      <c r="L13" s="65" t="n">
+      <c r="L13" s="64" t="n">
         <v>-30</v>
       </c>
-      <c r="M13" s="65" t="n">
+      <c r="M13" s="64" t="n">
         <v>-77</v>
       </c>
-      <c r="N13" s="65" t="n">
+      <c r="N13" s="64" t="n">
         <v>-8</v>
       </c>
-      <c r="O13" s="67" t="inlineStr">
+      <c r="O13" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13157,46 +13152,46 @@
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="B14" s="63" t="n">
+      <c r="B14" s="62" t="n">
         <v>-11.24</v>
       </c>
-      <c r="C14" s="63" t="n">
+      <c r="C14" s="62" t="n">
         <v>-16.59</v>
       </c>
-      <c r="D14" s="63" t="n">
+      <c r="D14" s="62" t="n">
         <v>-9.18</v>
       </c>
-      <c r="E14" s="63" t="n">
+      <c r="E14" s="62" t="n">
         <v>-5.91</v>
       </c>
-      <c r="F14" s="66" t="n">
+      <c r="F14" s="65" t="n">
         <v>139</v>
       </c>
-      <c r="G14" s="66" t="n">
+      <c r="G14" s="65" t="n">
         <v>24</v>
       </c>
-      <c r="H14" s="66" t="n">
+      <c r="H14" s="65" t="n">
         <v>163</v>
       </c>
-      <c r="I14" s="66" t="n">
+      <c r="I14" s="65" t="n">
         <v>108</v>
       </c>
-      <c r="J14" s="65" t="n">
+      <c r="J14" s="64" t="n">
         <v>-43</v>
       </c>
-      <c r="K14" s="65" t="n">
+      <c r="K14" s="64" t="n">
         <v>-29</v>
       </c>
-      <c r="L14" s="65" t="n">
+      <c r="L14" s="64" t="n">
         <v>-8</v>
       </c>
-      <c r="M14" s="65" t="n">
+      <c r="M14" s="64" t="n">
         <v>-389</v>
       </c>
-      <c r="N14" s="66" t="n">
+      <c r="N14" s="65" t="n">
         <v>225</v>
       </c>
-      <c r="O14" s="67" t="inlineStr">
+      <c r="O14" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13208,46 +13203,46 @@
           <t>비금속</t>
         </is>
       </c>
-      <c r="B15" s="63" t="n">
+      <c r="B15" s="62" t="n">
         <v>-19.86</v>
       </c>
-      <c r="C15" s="63" t="n">
+      <c r="C15" s="62" t="n">
         <v>-25.28</v>
       </c>
-      <c r="D15" s="64" t="n">
+      <c r="D15" s="63" t="n">
         <v>0.05</v>
       </c>
-      <c r="E15" s="63" t="n">
+      <c r="E15" s="62" t="n">
         <v>-6.35</v>
       </c>
-      <c r="F15" s="66" t="n">
+      <c r="F15" s="65" t="n">
         <v>41</v>
       </c>
-      <c r="G15" s="66" t="n">
+      <c r="G15" s="65" t="n">
         <v>39</v>
       </c>
-      <c r="H15" s="66" t="n">
+      <c r="H15" s="65" t="n">
         <v>81</v>
       </c>
-      <c r="I15" s="66" t="n">
+      <c r="I15" s="65" t="n">
         <v>21</v>
       </c>
-      <c r="J15" s="65" t="n">
+      <c r="J15" s="64" t="n">
         <v>-9</v>
       </c>
-      <c r="K15" s="66" t="n">
+      <c r="K15" s="65" t="n">
         <v>29</v>
       </c>
-      <c r="L15" s="65" t="n">
+      <c r="L15" s="64" t="n">
         <v>-1</v>
       </c>
-      <c r="M15" s="65" t="n">
+      <c r="M15" s="64" t="n">
         <v>-82</v>
       </c>
-      <c r="N15" s="66" t="n">
+      <c r="N15" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="67" t="inlineStr">
+      <c r="O15" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13259,43 +13254,43 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="B16" s="64" t="n">
+      <c r="B16" s="63" t="n">
         <v>12.46</v>
       </c>
-      <c r="C16" s="63" t="n">
+      <c r="C16" s="62" t="n">
         <v>-13.59</v>
       </c>
-      <c r="D16" s="63" t="n">
+      <c r="D16" s="62" t="n">
         <v>-2.01</v>
       </c>
-      <c r="E16" s="63" t="n">
+      <c r="E16" s="62" t="n">
         <v>-8.289999999999999</v>
       </c>
-      <c r="F16" s="65" t="n">
+      <c r="F16" s="64" t="n">
         <v>-116</v>
       </c>
-      <c r="G16" s="66" t="n">
+      <c r="G16" s="65" t="n">
         <v>2452</v>
       </c>
-      <c r="H16" s="66" t="n">
+      <c r="H16" s="65" t="n">
         <v>2336</v>
       </c>
-      <c r="I16" s="66" t="n">
+      <c r="I16" s="65" t="n">
         <v>756</v>
       </c>
-      <c r="J16" s="66" t="n">
+      <c r="J16" s="65" t="n">
         <v>13</v>
       </c>
-      <c r="K16" s="66" t="n">
+      <c r="K16" s="65" t="n">
         <v>1478</v>
       </c>
-      <c r="L16" s="66" t="n">
+      <c r="L16" s="65" t="n">
         <v>237</v>
       </c>
-      <c r="M16" s="65" t="n">
+      <c r="M16" s="64" t="n">
         <v>-2377</v>
       </c>
-      <c r="N16" s="66" t="n">
+      <c r="N16" s="65" t="n">
         <v>41</v>
       </c>
       <c r="O16" s="30" t="inlineStr"/>
@@ -13306,43 +13301,43 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="B17" s="63" t="n">
+      <c r="B17" s="62" t="n">
         <v>-22.6</v>
       </c>
-      <c r="C17" s="63" t="n">
+      <c r="C17" s="62" t="n">
         <v>-18.89</v>
       </c>
-      <c r="D17" s="63" t="n">
+      <c r="D17" s="62" t="n">
         <v>-9.09</v>
       </c>
-      <c r="E17" s="63" t="n">
+      <c r="E17" s="62" t="n">
         <v>-9.390000000000001</v>
       </c>
-      <c r="F17" s="66" t="n">
+      <c r="F17" s="65" t="n">
         <v>80</v>
       </c>
-      <c r="G17" s="66" t="n">
+      <c r="G17" s="65" t="n">
         <v>1935</v>
       </c>
-      <c r="H17" s="66" t="n">
+      <c r="H17" s="65" t="n">
         <v>2016</v>
       </c>
-      <c r="I17" s="66" t="n">
+      <c r="I17" s="65" t="n">
         <v>1063</v>
       </c>
-      <c r="J17" s="66" t="n">
+      <c r="J17" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="66" t="n">
+      <c r="K17" s="65" t="n">
         <v>622</v>
       </c>
-      <c r="L17" s="66" t="n">
+      <c r="L17" s="65" t="n">
         <v>245</v>
       </c>
-      <c r="M17" s="65" t="n">
+      <c r="M17" s="64" t="n">
         <v>-1931</v>
       </c>
-      <c r="N17" s="65" t="n">
+      <c r="N17" s="64" t="n">
         <v>-85</v>
       </c>
       <c r="O17" s="30" t="inlineStr"/>
@@ -13353,46 +13348,46 @@
           <t>통신</t>
         </is>
       </c>
-      <c r="B18" s="64" t="n">
+      <c r="B18" s="63" t="n">
         <v>10.72</v>
       </c>
-      <c r="C18" s="63" t="n">
+      <c r="C18" s="62" t="n">
         <v>-20.22</v>
       </c>
-      <c r="D18" s="63" t="n">
+      <c r="D18" s="62" t="n">
         <v>-7.33</v>
       </c>
-      <c r="E18" s="63" t="n">
+      <c r="E18" s="62" t="n">
         <v>-10.15</v>
       </c>
-      <c r="F18" s="65" t="n">
+      <c r="F18" s="64" t="n">
         <v>-84</v>
       </c>
-      <c r="G18" s="66" t="n">
+      <c r="G18" s="65" t="n">
         <v>615</v>
       </c>
-      <c r="H18" s="66" t="n">
+      <c r="H18" s="65" t="n">
         <v>530</v>
       </c>
-      <c r="I18" s="66" t="n">
+      <c r="I18" s="65" t="n">
         <v>187</v>
       </c>
-      <c r="J18" s="66" t="n">
+      <c r="J18" s="65" t="n">
         <v>182</v>
       </c>
-      <c r="K18" s="65" t="n">
+      <c r="K18" s="64" t="n">
         <v>-6</v>
       </c>
-      <c r="L18" s="66" t="n">
+      <c r="L18" s="65" t="n">
         <v>272</v>
       </c>
-      <c r="M18" s="65" t="n">
+      <c r="M18" s="64" t="n">
         <v>-512</v>
       </c>
-      <c r="N18" s="65" t="n">
+      <c r="N18" s="64" t="n">
         <v>-19</v>
       </c>
-      <c r="O18" s="67" t="inlineStr">
+      <c r="O18" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13404,46 +13399,46 @@
           <t>종이·목재</t>
         </is>
       </c>
-      <c r="B19" s="63" t="n">
+      <c r="B19" s="62" t="n">
         <v>-32.6</v>
       </c>
-      <c r="C19" s="63" t="n">
+      <c r="C19" s="62" t="n">
         <v>-35.25</v>
       </c>
-      <c r="D19" s="63" t="n">
+      <c r="D19" s="62" t="n">
         <v>-8.789999999999999</v>
       </c>
-      <c r="E19" s="63" t="n">
+      <c r="E19" s="62" t="n">
         <v>-12.42</v>
       </c>
-      <c r="F19" s="66" t="n">
+      <c r="F19" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="66" t="n">
+      <c r="G19" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="H19" s="66" t="n">
+      <c r="H19" s="65" t="n">
         <v>11</v>
       </c>
-      <c r="I19" s="66" t="n">
+      <c r="I19" s="65" t="n">
         <v>14</v>
       </c>
-      <c r="J19" s="65" t="n">
+      <c r="J19" s="64" t="n">
         <v>-2</v>
       </c>
-      <c r="K19" s="65" t="n">
+      <c r="K19" s="64" t="n">
         <v>-5</v>
       </c>
-      <c r="L19" s="68" t="n">
+      <c r="L19" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="66" t="n">
+      <c r="M19" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="65" t="n">
+      <c r="N19" s="64" t="n">
         <v>-19</v>
       </c>
-      <c r="O19" s="67" t="inlineStr">
+      <c r="O19" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13455,46 +13450,46 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="B20" s="64" t="n">
+      <c r="B20" s="63" t="n">
         <v>23.58</v>
       </c>
-      <c r="C20" s="63" t="n">
+      <c r="C20" s="62" t="n">
         <v>-12.6</v>
       </c>
-      <c r="D20" s="63" t="n">
+      <c r="D20" s="62" t="n">
         <v>-2.38</v>
       </c>
-      <c r="E20" s="63" t="n">
+      <c r="E20" s="62" t="n">
         <v>-12.58</v>
       </c>
-      <c r="F20" s="65" t="n">
+      <c r="F20" s="64" t="n">
         <v>-11131</v>
       </c>
-      <c r="G20" s="66" t="n">
+      <c r="G20" s="65" t="n">
         <v>24597</v>
       </c>
-      <c r="H20" s="66" t="n">
+      <c r="H20" s="65" t="n">
         <v>13466</v>
       </c>
-      <c r="I20" s="66" t="n">
+      <c r="I20" s="65" t="n">
         <v>14367</v>
       </c>
-      <c r="J20" s="66" t="n">
+      <c r="J20" s="65" t="n">
         <v>8277</v>
       </c>
-      <c r="K20" s="65" t="n">
+      <c r="K20" s="64" t="n">
         <v>-380</v>
       </c>
-      <c r="L20" s="66" t="n">
+      <c r="L20" s="65" t="n">
         <v>558</v>
       </c>
-      <c r="M20" s="65" t="n">
+      <c r="M20" s="64" t="n">
         <v>-7400</v>
       </c>
-      <c r="N20" s="65" t="n">
+      <c r="N20" s="64" t="n">
         <v>-6065</v>
       </c>
-      <c r="O20" s="67" t="inlineStr">
+      <c r="O20" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13506,43 +13501,43 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="B21" s="63" t="n">
+      <c r="B21" s="62" t="n">
         <v>-1.89</v>
       </c>
-      <c r="C21" s="63" t="n">
+      <c r="C21" s="62" t="n">
         <v>-46.26</v>
       </c>
-      <c r="D21" s="63" t="n">
+      <c r="D21" s="62" t="n">
         <v>-11.2</v>
       </c>
-      <c r="E21" s="63" t="n">
+      <c r="E21" s="62" t="n">
         <v>-12.69</v>
       </c>
-      <c r="F21" s="65" t="n">
+      <c r="F21" s="64" t="n">
         <v>-781</v>
       </c>
-      <c r="G21" s="66" t="n">
+      <c r="G21" s="65" t="n">
         <v>1082</v>
       </c>
-      <c r="H21" s="66" t="n">
+      <c r="H21" s="65" t="n">
         <v>302</v>
       </c>
-      <c r="I21" s="66" t="n">
+      <c r="I21" s="65" t="n">
         <v>207</v>
       </c>
-      <c r="J21" s="66" t="n">
+      <c r="J21" s="65" t="n">
         <v>485</v>
       </c>
-      <c r="K21" s="65" t="n">
+      <c r="K21" s="64" t="n">
         <v>-7</v>
       </c>
-      <c r="L21" s="66" t="n">
+      <c r="L21" s="65" t="n">
         <v>113</v>
       </c>
-      <c r="M21" s="65" t="n">
+      <c r="M21" s="64" t="n">
         <v>-446</v>
       </c>
-      <c r="N21" s="66" t="n">
+      <c r="N21" s="65" t="n">
         <v>144</v>
       </c>
       <c r="O21" s="30" t="inlineStr"/>
@@ -13553,46 +13548,46 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="B22" s="63" t="n">
+      <c r="B22" s="62" t="n">
         <v>-0.9</v>
       </c>
-      <c r="C22" s="63" t="n">
+      <c r="C22" s="62" t="n">
         <v>-28.5</v>
       </c>
-      <c r="D22" s="63" t="n">
+      <c r="D22" s="62" t="n">
         <v>-2.65</v>
       </c>
-      <c r="E22" s="63" t="n">
+      <c r="E22" s="62" t="n">
         <v>-15.97</v>
       </c>
-      <c r="F22" s="66" t="n">
+      <c r="F22" s="65" t="n">
         <v>1251</v>
       </c>
-      <c r="G22" s="66" t="n">
+      <c r="G22" s="65" t="n">
         <v>906</v>
       </c>
-      <c r="H22" s="66" t="n">
+      <c r="H22" s="65" t="n">
         <v>2156</v>
       </c>
-      <c r="I22" s="66" t="n">
+      <c r="I22" s="65" t="n">
         <v>1864</v>
       </c>
-      <c r="J22" s="65" t="n">
+      <c r="J22" s="64" t="n">
         <v>-793</v>
       </c>
-      <c r="K22" s="65" t="n">
+      <c r="K22" s="64" t="n">
         <v>-302</v>
       </c>
-      <c r="L22" s="66" t="n">
+      <c r="L22" s="65" t="n">
         <v>162</v>
       </c>
-      <c r="M22" s="65" t="n">
+      <c r="M22" s="64" t="n">
         <v>-1633</v>
       </c>
-      <c r="N22" s="65" t="n">
+      <c r="N22" s="64" t="n">
         <v>-524</v>
       </c>
-      <c r="O22" s="67" t="inlineStr">
+      <c r="O22" s="66" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -13604,43 +13599,43 @@
           <t>제조</t>
         </is>
       </c>
-      <c r="B23" s="64" t="n">
+      <c r="B23" s="63" t="n">
         <v>42.23</v>
       </c>
-      <c r="C23" s="63" t="n">
+      <c r="C23" s="62" t="n">
         <v>-12.31</v>
       </c>
-      <c r="D23" s="64" t="n">
+      <c r="D23" s="63" t="n">
         <v>3.96</v>
       </c>
-      <c r="E23" s="63" t="n">
+      <c r="E23" s="62" t="n">
         <v>-17.66</v>
       </c>
-      <c r="F23" s="65" t="n">
+      <c r="F23" s="64" t="n">
         <v>-184035</v>
       </c>
-      <c r="G23" s="66" t="n">
+      <c r="G23" s="65" t="n">
         <v>16384</v>
       </c>
-      <c r="H23" s="65" t="n">
+      <c r="H23" s="64" t="n">
         <v>-167652</v>
       </c>
-      <c r="I23" s="66" t="n">
+      <c r="I23" s="65" t="n">
         <v>24041</v>
       </c>
-      <c r="J23" s="65" t="n">
+      <c r="J23" s="64" t="n">
         <v>-21338</v>
       </c>
-      <c r="K23" s="66" t="n">
+      <c r="K23" s="65" t="n">
         <v>6825</v>
       </c>
-      <c r="L23" s="66" t="n">
+      <c r="L23" s="65" t="n">
         <v>7421</v>
       </c>
-      <c r="M23" s="66" t="n">
+      <c r="M23" s="65" t="n">
         <v>58576</v>
       </c>
-      <c r="N23" s="66" t="n">
+      <c r="N23" s="65" t="n">
         <v>109075</v>
       </c>
       <c r="O23" s="30" t="inlineStr"/>
@@ -13651,43 +13646,43 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="B24" s="64" t="n">
+      <c r="B24" s="63" t="n">
         <v>76.94</v>
       </c>
-      <c r="C24" s="63" t="n">
+      <c r="C24" s="62" t="n">
         <v>-1.37</v>
       </c>
-      <c r="D24" s="64" t="n">
+      <c r="D24" s="63" t="n">
         <v>9.19</v>
       </c>
-      <c r="E24" s="63" t="n">
+      <c r="E24" s="62" t="n">
         <v>-18.08</v>
       </c>
-      <c r="F24" s="65" t="n">
+      <c r="F24" s="64" t="n">
         <v>-171834</v>
       </c>
-      <c r="G24" s="66" t="n">
+      <c r="G24" s="65" t="n">
         <v>3611</v>
       </c>
-      <c r="H24" s="65" t="n">
+      <c r="H24" s="64" t="n">
         <v>-168223</v>
       </c>
-      <c r="I24" s="66" t="n">
+      <c r="I24" s="65" t="n">
         <v>8546</v>
       </c>
-      <c r="J24" s="65" t="n">
+      <c r="J24" s="64" t="n">
         <v>-20000</v>
       </c>
-      <c r="K24" s="66" t="n">
+      <c r="K24" s="65" t="n">
         <v>8823</v>
       </c>
-      <c r="L24" s="66" t="n">
+      <c r="L24" s="65" t="n">
         <v>6676</v>
       </c>
-      <c r="M24" s="66" t="n">
+      <c r="M24" s="65" t="n">
         <v>56240</v>
       </c>
-      <c r="N24" s="66" t="n">
+      <c r="N24" s="65" t="n">
         <v>111983</v>
       </c>
       <c r="O24" s="30" t="inlineStr"/>
@@ -13698,46 +13693,46 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="B25" s="63" t="n">
+      <c r="B25" s="62" t="n">
         <v>-19.75</v>
       </c>
-      <c r="C25" s="63" t="n">
+      <c r="C25" s="62" t="n">
         <v>-45.29</v>
       </c>
-      <c r="D25" s="63" t="n">
+      <c r="D25" s="62" t="n">
         <v>-10.78</v>
       </c>
-      <c r="E25" s="63" t="n">
+      <c r="E25" s="62" t="n">
         <v>-19.57</v>
       </c>
-      <c r="F25" s="65" t="n">
+      <c r="F25" s="64" t="n">
         <v>-1113</v>
       </c>
-      <c r="G25" s="65" t="n">
+      <c r="G25" s="64" t="n">
         <v>-148</v>
       </c>
-      <c r="H25" s="65" t="n">
+      <c r="H25" s="64" t="n">
         <v>-1261</v>
       </c>
-      <c r="I25" s="66" t="n">
+      <c r="I25" s="65" t="n">
         <v>1572</v>
       </c>
-      <c r="J25" s="65" t="n">
+      <c r="J25" s="64" t="n">
         <v>-612</v>
       </c>
-      <c r="K25" s="65" t="n">
+      <c r="K25" s="64" t="n">
         <v>-1102</v>
       </c>
-      <c r="L25" s="65" t="n">
+      <c r="L25" s="64" t="n">
         <v>-9</v>
       </c>
-      <c r="M25" s="66" t="n">
+      <c r="M25" s="65" t="n">
         <v>1283</v>
       </c>
-      <c r="N25" s="65" t="n">
+      <c r="N25" s="64" t="n">
         <v>-22</v>
       </c>
-      <c r="O25" s="56" t="inlineStr">
+      <c r="O25" s="55" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -13749,43 +13744,43 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="B26" s="63" t="n">
+      <c r="B26" s="62" t="n">
         <v>-28.77</v>
       </c>
-      <c r="C26" s="63" t="n">
+      <c r="C26" s="62" t="n">
         <v>-48.71</v>
       </c>
-      <c r="D26" s="63" t="n">
+      <c r="D26" s="62" t="n">
         <v>-24.66</v>
       </c>
-      <c r="E26" s="63" t="n">
+      <c r="E26" s="62" t="n">
         <v>-23.23</v>
       </c>
-      <c r="F26" s="65" t="n">
+      <c r="F26" s="64" t="n">
         <v>-3019</v>
       </c>
-      <c r="G26" s="66" t="n">
+      <c r="G26" s="65" t="n">
         <v>3769</v>
       </c>
-      <c r="H26" s="66" t="n">
+      <c r="H26" s="65" t="n">
         <v>751</v>
       </c>
-      <c r="I26" s="66" t="n">
+      <c r="I26" s="65" t="n">
         <v>8641</v>
       </c>
-      <c r="J26" s="66" t="n">
+      <c r="J26" s="65" t="n">
         <v>263</v>
       </c>
-      <c r="K26" s="65" t="n">
+      <c r="K26" s="64" t="n">
         <v>-5083</v>
       </c>
-      <c r="L26" s="66" t="n">
+      <c r="L26" s="65" t="n">
         <v>17</v>
       </c>
-      <c r="M26" s="66" t="n">
+      <c r="M26" s="65" t="n">
         <v>3906</v>
       </c>
-      <c r="N26" s="65" t="n">
+      <c r="N26" s="64" t="n">
         <v>-4656</v>
       </c>
       <c r="O26" s="30" t="inlineStr"/>
@@ -13796,43 +13791,43 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="B27" s="64" t="n">
+      <c r="B27" s="63" t="n">
         <v>24.1</v>
       </c>
-      <c r="C27" s="63" t="n">
+      <c r="C27" s="62" t="n">
         <v>-48.67</v>
       </c>
-      <c r="D27" s="64" t="n">
+      <c r="D27" s="63" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="E27" s="63" t="n">
+      <c r="E27" s="62" t="n">
         <v>-25.75</v>
       </c>
-      <c r="F27" s="66" t="n">
+      <c r="F27" s="65" t="n">
         <v>2637</v>
       </c>
-      <c r="G27" s="65" t="n">
+      <c r="G27" s="64" t="n">
         <v>-3351</v>
       </c>
-      <c r="H27" s="65" t="n">
+      <c r="H27" s="64" t="n">
         <v>-714</v>
       </c>
-      <c r="I27" s="65" t="n">
+      <c r="I27" s="64" t="n">
         <v>-100</v>
       </c>
-      <c r="J27" s="65" t="n">
+      <c r="J27" s="64" t="n">
         <v>-1227</v>
       </c>
-      <c r="K27" s="65" t="n">
+      <c r="K27" s="64" t="n">
         <v>-1813</v>
       </c>
-      <c r="L27" s="65" t="n">
+      <c r="L27" s="64" t="n">
         <v>-202</v>
       </c>
-      <c r="M27" s="66" t="n">
+      <c r="M27" s="65" t="n">
         <v>718</v>
       </c>
-      <c r="N27" s="65" t="n">
+      <c r="N27" s="64" t="n">
         <v>-4</v>
       </c>
       <c r="O27" s="30" t="inlineStr"/>
@@ -13843,46 +13838,46 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="B28" s="63" t="n">
+      <c r="B28" s="62" t="n">
         <v>-19.23</v>
       </c>
-      <c r="C28" s="63" t="n">
+      <c r="C28" s="62" t="n">
         <v>-53.3</v>
       </c>
-      <c r="D28" s="63" t="n">
+      <c r="D28" s="62" t="n">
         <v>-6.82</v>
       </c>
-      <c r="E28" s="63" t="n">
+      <c r="E28" s="62" t="n">
         <v>-28.6</v>
       </c>
-      <c r="F28" s="65" t="n">
+      <c r="F28" s="64" t="n">
         <v>-5412</v>
       </c>
-      <c r="G28" s="65" t="n">
+      <c r="G28" s="64" t="n">
         <v>-2070</v>
       </c>
-      <c r="H28" s="65" t="n">
+      <c r="H28" s="64" t="n">
         <v>-7483</v>
       </c>
-      <c r="I28" s="66" t="n">
+      <c r="I28" s="65" t="n">
         <v>3181</v>
       </c>
-      <c r="J28" s="65" t="n">
+      <c r="J28" s="64" t="n">
         <v>-3523</v>
       </c>
-      <c r="K28" s="65" t="n">
+      <c r="K28" s="64" t="n">
         <v>-1471</v>
       </c>
-      <c r="L28" s="65" t="n">
+      <c r="L28" s="64" t="n">
         <v>-225</v>
       </c>
-      <c r="M28" s="66" t="n">
+      <c r="M28" s="65" t="n">
         <v>7495</v>
       </c>
-      <c r="N28" s="65" t="n">
+      <c r="N28" s="64" t="n">
         <v>-13</v>
       </c>
-      <c r="O28" s="56" t="inlineStr">
+      <c r="O28" s="55" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -13920,7 +13915,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{82B6610F-1135-4AAA-AB2E-0E883BAA3416}</x14:id>
+          <x14:id>{ABC6E77E-B231-44DD-B207-3E2ADC8C5F22}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13934,7 +13929,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{80BE1740-3F05-47C6-B5DF-75D8BCF696DA}</x14:id>
+          <x14:id>{0B3288D6-689C-48EC-8C5C-12EAE82A24AD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13948,7 +13943,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4D8FCCD7-90CE-4282-97ED-DB8ACD7B5E87}</x14:id>
+          <x14:id>{75C43FAC-C8E7-4CD4-84CE-8A08E174AFC0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13962,7 +13957,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11133010-1639-4F9B-A8BA-354C7C82E85F}</x14:id>
+          <x14:id>{2EA427F6-1CF2-461F-8D81-9EDDF088DE6F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13972,7 +13967,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{82B6610F-1135-4AAA-AB2E-0E883BAA3416}">
+          <x14:cfRule type="dataBar" id="{ABC6E77E-B231-44DD-B207-3E2ADC8C5F22}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13985,7 +13980,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{80BE1740-3F05-47C6-B5DF-75D8BCF696DA}">
+          <x14:cfRule type="dataBar" id="{0B3288D6-689C-48EC-8C5C-12EAE82A24AD}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -13998,7 +13993,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4D8FCCD7-90CE-4282-97ED-DB8ACD7B5E87}">
+          <x14:cfRule type="dataBar" id="{75C43FAC-C8E7-4CD4-84CE-8A08E174AFC0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -14011,7 +14006,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{11133010-1639-4F9B-A8BA-354C7C82E85F}">
+          <x14:cfRule type="dataBar" id="{2EA427F6-1CF2-461F-8D81-9EDDF088DE6F}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
